--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9CD3D54-DD64-4421-85D1-09A52FAD685D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA024D2-6AB5-4573-839F-6CE930EEB797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="5856" yWindow="1428" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -78,13 +78,16 @@
     <t>Descrição</t>
   </si>
   <si>
-    <t>Aterramento - Haste de aterramento - cobreada - 5/8\" x 2,40m</t>
-  </si>
-  <si>
-    <t>Aterramento - Conector tipo \"U\" - 5/8\"</t>
-  </si>
-  <si>
     <t>Aterramento - Caixa de inspeção - Polipropileno - Ø300x400mm</t>
+  </si>
+  <si>
+    <t>Aterramento - Haste de aterramento - cobreada - 5/8" x 2,40m</t>
+  </si>
+  <si>
+    <t>Aterramento - Conector tipo "U" - 5/8"</t>
+  </si>
+  <si>
+    <t>Aterramento - Caixa de inspeção - Polipropileno - Ø300x300mm</t>
   </si>
 </sst>
 </file>
@@ -469,22 +472,22 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA024D2-6AB5-4573-839F-6CE930EEB797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C859A4-20B3-47A3-8625-4913746C17F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5856" yWindow="1428" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -88,16 +88,40 @@
   </si>
   <si>
     <t>Aterramento - Caixa de inspeção - Polipropileno - Ø300x300mm</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.HEPR - ench.PVC - cob.PVC - 0,6/1kV - ref. Prysmian Eprotenax - 1.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.HEPR - ench.PVC - cob.PVC - 0,6/1kV - ref. Prysmian Eprotenax - 1.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.HEPR - ench.PVC - cob.PVC - 0,6/1kV - ref. Prysmian Eprotenax - 1.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.HEPR - ench.PVC - cob.PVC - 0,6/1kV - ref. Prysmian Eprotenax - 1.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 1,5 MM², ANTI-CHAMA 0,6/1,0 KV, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -123,8 +147,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,10 +486,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="96.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -488,6 +515,26 @@
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -497,16 +544,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="94.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="121.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -515,12 +563,12 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
@@ -529,12 +577,12 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
@@ -543,12 +591,12 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
@@ -557,12 +605,12 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
@@ -571,11 +619,68 @@
       <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>91925</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>91925</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>91925</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>91925</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C859A4-20B3-47A3-8625-4913746C17F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0899D6BA-8585-4093-8054-0377C0E96D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t>CAIXA DE INSPEÇÃO PARA ATERRAMENTO, CIRCULAR, EM POLIETILENO, DIÂMETRO INTERNO = 0,3 M. AF_12/2020</t>
-  </si>
-  <si>
-    <t>Descrição</t>
   </si>
   <si>
     <t>Aterramento - Caixa de inspeção - Polipropileno - Ø300x400mm</t>
@@ -486,55 +483,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>20</v>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -631,10 +656,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -645,10 +670,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -659,10 +684,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -673,10 +698,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0899D6BA-8585-4093-8054-0377C0E96D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208DB6AC-85B5-4FF4-BE53-72986B31B722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="58">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -103,6 +103,114 @@
   </si>
   <si>
     <t>M</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 10 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 10 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 10 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 10 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 10 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 10 MM², ANTI-CHAMA 0,6/1,0 KV, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 16 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 16 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 16 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 16 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 16 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 16 MM², ANTI-CHAMA 0,6/1,0 KV, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 2.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 2.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 2.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 2.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 2.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 2.5 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 2,5 MM², ANTI-CHAMA 0,6/1,0 KV, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 25 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 25 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 25 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 25 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 25 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 4 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 4 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 4 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 4 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 4 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 4 MM², ANTI-CHAMA 0,6/1,0 KV, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 6 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 6 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 6 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 6 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 6 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 6 MM², ANTI-CHAMA 0,6/1,0 KV, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
   </si>
 </sst>
 </file>
@@ -483,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" bestFit="1" customWidth="1"/>
@@ -562,6 +670,246 @@
         <v>21</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -569,7 +917,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -704,6 +1052,426 @@
         <v>21</v>
       </c>
     </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>91933</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>91933</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>91933</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>91933</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>91933</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>91935</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>91935</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>91935</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>91935</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>91935</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>91927</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>91927</v>
+      </c>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>91927</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>91927</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>91927</v>
+      </c>
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>91927</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>92984</v>
+      </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>92984</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>92984</v>
+      </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>92984</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>91929</v>
+      </c>
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>91929</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>91929</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>91929</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>91929</v>
+      </c>
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>91931</v>
+      </c>
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>91931</v>
+      </c>
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>91931</v>
+      </c>
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>91931</v>
+      </c>
+      <c r="B38" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>91931</v>
+      </c>
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208DB6AC-85B5-4FF4-BE53-72986B31B722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CDA675-1B83-41C7-A8FB-6D29B3259181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="61">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -211,6 +211,15 @@
   </si>
   <si>
     <t>CABO DE COBRE FLEXÍVEL ISOLADO, 6 MM², ANTI-CHAMA 0,6/1,0 KV, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabo - EPR - 2.5mm</t>
+  </si>
+  <si>
+    <t>- SINAPI - METROS - ELETRODUTO FLEXÍVEL CORRUGADO, PVC, DN 25 MM - 3/4" - , PARA CIRCUITOS TERMINAIS, INSTALADO EM FORRO</t>
+  </si>
+  <si>
+    <t>ELETRODUTO FLEXÍVEL CORRUGADO, PVC, DN 25 MM (3/4"), PARA CIRCUITOS TERMINAIS, INSTALADO EM FORRO - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
   </si>
 </sst>
 </file>
@@ -252,10 +261,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -591,15 +606,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="96.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -607,7 +622,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -615,7 +630,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -623,7 +638,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -631,7 +646,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -639,7 +654,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -647,7 +662,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -655,7 +670,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -663,7 +678,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -671,7 +686,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -679,7 +694,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -687,7 +702,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -695,7 +710,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -703,7 +718,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -711,7 +726,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -719,7 +734,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -727,7 +742,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -735,7 +750,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -743,7 +758,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -751,7 +766,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -759,7 +774,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -767,7 +782,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -775,7 +790,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -783,7 +798,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -791,7 +806,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -799,114 +814,130 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B28" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B29" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="B30" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B31" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B32" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="B33" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B34" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="B35" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="B36" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="B37" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="B38" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="B39" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B40" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -917,558 +948,586 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="121.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="121.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>91925</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>91925</v>
       </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>91925</v>
       </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>91925</v>
       </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>91933</v>
       </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>91933</v>
       </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>91933</v>
       </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>91933</v>
       </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>91933</v>
       </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>91935</v>
       </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>91935</v>
       </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>91935</v>
       </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>91935</v>
       </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <v>91935</v>
       </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <v>91927</v>
       </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <v>91927</v>
       </c>
-      <c r="B21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>91927</v>
       </c>
-      <c r="B22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <v>91927</v>
       </c>
-      <c r="B23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>91927</v>
       </c>
-      <c r="B24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>91927</v>
       </c>
-      <c r="B25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
         <v>92984</v>
       </c>
-      <c r="B26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="D27" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
         <v>92984</v>
       </c>
-      <c r="B27" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+      <c r="D28" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
         <v>92984</v>
       </c>
-      <c r="B28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+      <c r="D29" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
         <v>92984</v>
       </c>
-      <c r="B29" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+      <c r="D30" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
         <v>91929</v>
       </c>
-      <c r="B30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+      <c r="D31" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
         <v>91929</v>
       </c>
-      <c r="B31" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="D32" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
         <v>91929</v>
       </c>
-      <c r="B32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+      <c r="D33" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
         <v>91929</v>
       </c>
-      <c r="B33" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="D34" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
         <v>91929</v>
       </c>
-      <c r="B34" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+      <c r="D35" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
         <v>91931</v>
       </c>
-      <c r="B35" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+      <c r="D36" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
         <v>91931</v>
       </c>
-      <c r="B36" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+      <c r="D37" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
         <v>91931</v>
       </c>
-      <c r="B37" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+      <c r="D38" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
         <v>91931</v>
       </c>
-      <c r="B38" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+      <c r="D39" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
         <v>91931</v>
       </c>
-      <c r="B39" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D40" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>91834</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>21</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CDA675-1B83-41C7-A8FB-6D29B3259181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73940D82-FB28-4490-93AE-E7E12E332B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="64">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -220,6 +220,15 @@
   </si>
   <si>
     <t>ELETRODUTO FLEXÍVEL CORRUGADO, PVC, DN 25 MM (3/4"), PARA CIRCUITOS TERMINAIS, INSTALADO EM FORRO - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto leve - 3/4" - Forro</t>
+  </si>
+  <si>
+    <t>- SINAPI - METROS - ELETRODUTO FLEXÍVEL CORRUGADO, PVC, DN 25 MM - 3/4" - , PARA CIRCUITOS TERMINAIS, INSTALADO EM PAREDE</t>
+  </si>
+  <si>
+    <t>ELETRODUTO FLEXÍVEL CORRUGADO, PVC, DN 25 MM (3/4"), PARA CIRCUITOS TERMINAIS, INSTALADO EM PAREDE - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
   </si>
 </sst>
 </file>
@@ -606,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -941,6 +950,22 @@
         <v>21</v>
       </c>
     </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -948,7 +973,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -1531,6 +1556,34 @@
         <v>21</v>
       </c>
     </row>
+    <row r="42" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>91834</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>91854</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73940D82-FB28-4490-93AE-E7E12E332B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D96233B-4058-4D51-A0BE-2AE800A3777D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="71">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -229,6 +229,27 @@
   </si>
   <si>
     <t>ELETRODUTO FLEXÍVEL CORRUGADO, PVC, DN 25 MM (3/4"), PARA CIRCUITOS TERMINAIS, INSTALADO EM PAREDE - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - metálico - UTP-CAT.6 - 4</t>
+  </si>
+  <si>
+    <t>CABO ELETRÔNICO CATEGORIA 6, INSTALADO EM EDIFICAÇÃO INSTITUCIONAL - FORNECIMENTO E INSTALAÇÃO. AF_08/2025</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto leve - 3/4" - Parede</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - óptico - CFOI-MM-COR - 1</t>
+  </si>
+  <si>
+    <t>Comp 1182</t>
+  </si>
+  <si>
+    <t>PRÓPRIO</t>
+  </si>
+  <si>
+    <t>CABO FIBRA OPTICA CFOA-MM62.5-DDR-S-12F 62.5 ANTI ROEDOR 12F (COMPOSIÇÃO DE REFERÊNCIA: 059561 SBC 05/2025)</t>
   </si>
 </sst>
 </file>
@@ -615,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -966,6 +987,30 @@
         <v>21</v>
       </c>
     </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -973,11 +1018,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="3" customWidth="1"/>
     <col min="3" max="3" width="121.21875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="2"/>
   </cols>
@@ -1584,6 +1629,48 @@
         <v>21</v>
       </c>
     </row>
+    <row r="44" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>91854</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>98297</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D96233B-4058-4D51-A0BE-2AE800A3777D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29DF2AE-2D6F-455D-AEFE-0EF451A584F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="98">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -250,6 +250,87 @@
   </si>
   <si>
     <t>CABO FIBRA OPTICA CFOA-MM62.5-DDR-S-12F 62.5 ANTI ROEDOR 12F (COMPOSIÇÃO DE REFERÊNCIA: 059561 SBC 05/2025)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Eletrocalha perfurada tipo U - 50x50mm chapa 18</t>
+  </si>
+  <si>
+    <t>ELETROCALHA LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA 50MM E ALTURA 50MM, INCLUSIVE SUPORTE DE FIXAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: 063036 SBC 05/2024)</t>
+  </si>
+  <si>
+    <t>Comp 103</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - METROS - CABO ISOLADO PP 3 X 1,5 MM2</t>
+  </si>
+  <si>
+    <t>CABO ISOLADO PP 3 X 1,5 MM2 (COMPOSIÇÃO REFERÊNCIA COD 070561 AGETOP CIVIL 05/2023)</t>
+  </si>
+  <si>
+    <t>Comp 33</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Eletrocalha perfurada tipo U - 100x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>ELETROCALHA LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA 100 E ALTURA 100MM E , INCLUSIVE FIXAÇÃO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: 061108 SBC 05/2024)</t>
+  </si>
+  <si>
+    <t>Comp 137</t>
+  </si>
+  <si>
+    <t>Comp 322</t>
+  </si>
+  <si>
+    <t>ELETROCALHA LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA 200 E ALTURA 100MM E , INCLUSIVE FIXAÇÃO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: 062321 SBC 05/2024)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Eletrocalha perfurada tipo U - 200x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Eletrocalha perfurada tipo U - 300x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 237</t>
+  </si>
+  <si>
+    <t>ELETROCALHA LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA 300MM E ALTURA 100MM, INCLUSIVE FIXAÇÃO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: 061107 SBC 05/2024)</t>
+  </si>
+  <si>
+    <t>Perfilados perfurados - Galvanizados à fogo - 38x38mm</t>
+  </si>
+  <si>
+    <t>Comp 41</t>
+  </si>
+  <si>
+    <t>PERFILADO PERFURADO 38x38 (REFERENCIA COD 078028 SBC 11/2022)</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto pesado - 1.1/2" - Piso</t>
+  </si>
+  <si>
+    <t>ELETRODUTO FLEXÍVEL CORRUGADO, PEAD, DN 50 (1 1/2"), PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>- SINAPI - METROS - ELETRODUTO FLEXÍVEL CORRUGADO, PVC, DN 32 MM - 1" - , PARA CIRCUITOS TERMINAIS, INSTALADO EM FORRO</t>
+  </si>
+  <si>
+    <t>ELETRODUTO FLEXÍVEL CORRUGADO, PVC, DN 32 MM (1"), PARA CIRCUITOS TERMINAIS, INSTALADO EM FORRO - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - METROS - ELETRODUTO FLEXÍVEL CORRUGADO, 3/4", INSTALADO NO PISO</t>
+  </si>
+  <si>
+    <t>ELETRODUTO FLEXÍVEL CORRUGADO, 3/4", INSTALADO NO PISO (COMPOSIÇÃO DE REFERÊNCIA: FDE 16.20.113 - 04/2022)</t>
+  </si>
+  <si>
+    <t>Comp 848</t>
+  </si>
+  <si>
+    <t>- SINAPI - METROS - ELETRODUTO FLEXÍVEL CORRUGADO, PVC, DN 32 MM - 1" - , PARA CIRCUITOS TERMINAIS, INSTALADO EM PAREDE</t>
+  </si>
+  <si>
+    <t>ELETRODUTO FLEXÍVEL CORRUGADO, PVC, DN 32 MM (1"), PARA CIRCUITOS TERMINAIS, INSTALADO EM PAREDE - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
   </si>
 </sst>
 </file>
@@ -636,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -1011,6 +1092,86 @@
         <v>21</v>
       </c>
     </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -1018,7 +1179,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1647,9 +1808,6 @@
       <c r="A45" s="2">
         <v>98297</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="C45" s="3" t="s">
         <v>65</v>
       </c>
@@ -1668,6 +1826,146 @@
         <v>70</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>97667</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>91836</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>91856</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>21</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29DF2AE-2D6F-455D-AEFE-0EF451A584F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640A69ED-1FCB-45F1-B1A3-4D9459987C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="112">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -331,6 +331,48 @@
   </si>
   <si>
     <t>ELETRODUTO FLEXÍVEL CORRUGADO, PVC, DN 32 MM (1"), PARA CIRCUITOS TERMINAIS, INSTALADO EM PAREDE - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Eletroduto metálico rígido leve - Eletroduto galvanizado, vara 3,0m - 3/4"</t>
+  </si>
+  <si>
+    <t>ELETRODUTO RIGIDO, EM ACO ZINCADO OU GALVANIZADO, TIPO PESADO, DN=3/4", APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022 (COMPOSIÇÃO REFERÊNCIA: SINAPI 104406 - 08/2025)</t>
+  </si>
+  <si>
+    <t>Comp 1616</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto pesado - 4" - Piso</t>
+  </si>
+  <si>
+    <t>ELETRODUTO FLEXÍVEL CORRUGADO, PEAD, DN 100 (4"), PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>Perfilados perfurados - Gancho curto para perfilado - 44x32mm</t>
+  </si>
+  <si>
+    <t>GANCHO CURTO PARA PERFILADO 44X32MM (COMPOSIÇÃO DE REFERÊNCIA: 9526 ORSE)</t>
+  </si>
+  <si>
+    <t>Comp 812</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - SAIDA LATERAL SIMPLES</t>
+  </si>
+  <si>
+    <t>SAIDA LATERAL SIMPLES (REFERÊNCIA: SBC 062572 01/2025)</t>
+  </si>
+  <si>
+    <t>Comp 895</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - SAIDA LATERAL DUPLA</t>
+  </si>
+  <si>
+    <t>Comp 896</t>
+  </si>
+  <si>
+    <t>SAIDA LATERAL DUPLA (REFERÊNCIA: SBC 062572 01/2025)</t>
   </si>
 </sst>
 </file>
@@ -717,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -1172,6 +1214,46 @@
         <v>21</v>
       </c>
     </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -1179,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1808,6 +1890,9 @@
       <c r="A45" s="2">
         <v>98297</v>
       </c>
+      <c r="B45" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="C45" s="3" t="s">
         <v>65</v>
       </c>
@@ -1967,6 +2052,76 @@
       </c>
       <c r="D56" s="2" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>97670</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640A69ED-1FCB-45F1-B1A3-4D9459987C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53DD8C6-CC1A-4019-AA9E-31CD24842456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="140">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -373,6 +373,90 @@
   </si>
   <si>
     <t>SAIDA LATERAL DUPLA (REFERÊNCIA: SBC 062572 01/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor unipolar termomagnético - 220 V/127 V - DIN - Curva C - 20 A - 5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR MONOPOLAR TIPO DIN, CORRENTE NOMINAL DE 20A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor unipolar termomagnético - 220 V/127 V - DIN - Curva B - 16 A - 5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR MONOPOLAR TIPO DIN, CORRENTE NOMINAL DE 16A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 220 V/127 V - DIN - Curva C - 25 A - 3 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR BIPOLAR TIPO DIN, CORRENTE NOMINAL DE 25A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 220 V/127 V - DIN - Curva B - 16 A - 5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR BIPOLAR TIPO DIN, CORRENTE NOMINAL DE 16A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Unipolar Termomagnético - norma DIN - Curva C - 16 A - 3 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 32 A - 5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 32A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Acessórios para eletrocalha - Base fixa para perfilado 38x38mm</t>
+  </si>
+  <si>
+    <t>Comp 792</t>
+  </si>
+  <si>
+    <t>BASE FIXA PARA PERFILADO 38X38MM (COMPOSIÇÃO DE REFERÊNCIA: 059531 SBC 05/2023)</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Terminal - 38x38mm</t>
+  </si>
+  <si>
+    <t>Comp 397</t>
+  </si>
+  <si>
+    <t>TERMINAL ACABAMENTO PERFILADO 38x38mm (REFERENCIA SBC: 062562  04/2022)</t>
+  </si>
+  <si>
+    <t>PLUGUE FÊMEA LUMINARIA LED (REFERENCIA:  AGETOP CIVIL COD 072578 06/2023)</t>
+  </si>
+  <si>
+    <t>Comp 530</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PLUGUE FÊMEA LUMINARIA LED</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PLUGUE MACHO LUMINARIA LED</t>
+  </si>
+  <si>
+    <t>Comp 531</t>
+  </si>
+  <si>
+    <t>PLUGUE MACHO LUMINARIA LED (REFERENCIA:  AGETOP CIVIL COD 072578 06/2023)</t>
+  </si>
+  <si>
+    <t>INTERRUPTOR PARALELO (2 MÓDULOS), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 2x4" - Interruptor paralelo - 2 teclas</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Tala plana perfurada - 38mm</t>
+  </si>
+  <si>
+    <t>Comp 465</t>
+  </si>
+  <si>
+    <t>TALA PLANA PERFURADA - 38MM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
   </si>
 </sst>
 </file>
@@ -759,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -1254,6 +1338,102 @@
         <v>7</v>
       </c>
     </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -1261,7 +1441,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -2124,6 +2304,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>93655</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>93654</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>93663</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>93661</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>93654</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>93671</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>91961</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53DD8C6-CC1A-4019-AA9E-31CD24842456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED07F2D-F782-4E20-B30E-56B31EA4F3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="142">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -457,6 +457,12 @@
   </si>
   <si>
     <t>TALA PLANA PERFURADA - 38MM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 2x4" - Interruptor simples - 1 tecla</t>
+  </si>
+  <si>
+    <t>INTERRUPTOR SIMPLES (1 MÓDULO), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
   </si>
 </sst>
 </file>
@@ -843,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -1434,6 +1440,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -1441,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -2472,6 +2486,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>91953</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED07F2D-F782-4E20-B30E-56B31EA4F3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47302E3-DAAE-4318-BE66-E6023BFA26F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="195">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -463,6 +463,165 @@
   </si>
   <si>
     <t>INTERRUPTOR SIMPLES (1 MÓDULO), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Suporte vertical - 70x81mm</t>
+  </si>
+  <si>
+    <t>Comp 742</t>
+  </si>
+  <si>
+    <t>SUPORTE VERTICAL - 70X81MM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Suporte vertical - 120x175mm</t>
+  </si>
+  <si>
+    <t>Comp 822</t>
+  </si>
+  <si>
+    <t>SUPORTE VERTICAL 120X175MM - (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Suporte vertical - 120x204mm</t>
+  </si>
+  <si>
+    <t>Comp 797</t>
+  </si>
+  <si>
+    <t>SUPORTE VERTICAL 120X204MM - (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Suporte vertical - 120x146mm</t>
+  </si>
+  <si>
+    <t>Comp 1397</t>
+  </si>
+  <si>
+    <t>SUPORTE VERTICAL 120X146MM - (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Curva horizontal 90° - 38x38mm</t>
+  </si>
+  <si>
+    <t>Comp 330</t>
+  </si>
+  <si>
+    <t>CURVA HORIZONTAL 90° PARA PERFILADOS PERFURADOS 38x38mm (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Dispositivo de proteção contra surto - 175 V - 25 KA</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO DE PROTEÇÃO CONTRA SURTO DPS 25KA - 175V (COMPOSIÇÃO DE REFERÊNCIA: ORSE 13150 - 05/2023)</t>
+  </si>
+  <si>
+    <t>Comp 785</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Dispositivo de proteção contra surto - 175 V - 80 KA</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO DE PROTEÇÃO CONTRA SURTO DPS 80KA - 175V (COMPOSIÇÃO DE REFERÊNCIA: ORSE 9041 - 05/2023)</t>
+  </si>
+  <si>
+    <t>Comp 1536</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Dispositivo de proteção contra surto - 175 V - 8 KA</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO DE PROTEÇÃO CONTRA SURTO DPS 8KA - 175V (COMPOSIÇÃO DE REFERÊNCIA: ORSE 13150 - 05/2023)</t>
+  </si>
+  <si>
+    <t>Comp 1629</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor unipolar termomagnético - 220 V/127 V - DIN - Curva B - 20 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 2x4" - Interruptor simples &amp; paralelo - 2 teclas</t>
+  </si>
+  <si>
+    <t>INTERRUPTOR SIMPLES (1 MÓDULO) COM INTERRUPTOR PARALELO (1 MÓDULO), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 2 - 2P+T 10A - Média</t>
+  </si>
+  <si>
+    <t>TOMADA MÉDIA DE EMBUTIR (2 MÓDULOS), 2P+T 10 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 2P+T 10A - Média</t>
+  </si>
+  <si>
+    <t>TOMADA MÉDIA DE EMBUTIR (1 MÓDULO), 2P+T 10 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva horizontal 90° - 300x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 453</t>
+  </si>
+  <si>
+    <t>CURVA HORIZONTAL 90º PARA ELETROCALHA, LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA DE 300MM E ALTURA DE 100MM - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97278 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - T horizontal 90° - 300x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>TE HORIZONTAL PARA ELETROCALHA 300X100MM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97315 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Comp 463</t>
+  </si>
+  <si>
+    <t>Comp 461</t>
+  </si>
+  <si>
+    <t>TERMINAL 300 X 100 PARA ELETROCALHA (COMPOSIÇÃO REFERÊNCIA: 12611 ORSE 05/23)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Terminal - 300x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Terminal - 200x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 460</t>
+  </si>
+  <si>
+    <t>TERMINAL 200 X 100 PARA ELETROCALHA (COMPOSIÇÃO REFERÊNCIA: 12611 ORSE 05/23)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Terminal - 100x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 458</t>
+  </si>
+  <si>
+    <t>TERMINAL 100 X 100 PARA ELETROCALHA (COMPOSIÇÃO REFERÊNCIA: 12611 ORSE 05/23)</t>
+  </si>
+  <si>
+    <t>.S.O.S CAIXAS - 80x80 - piso - CAIXA DE PASSAGEM EM ALVENARIA, DIM.: 80x80cm, COM TAMPA DE FERRO FUNDIDO T-33. FORNECIMENTO E INSTALAÇÃO.</t>
+  </si>
+  <si>
+    <t>CAIXA ENTERRADA ELÉTRICA RETANGULAR, EM ALVENARIA COM TIJOLOS CERÂMICOS MACIÇOS, FUNDO COM BRITA, DIMENSÕES INTERNAS: 0,8X0,8X0,6 M. AF_12/2020</t>
+  </si>
+  <si>
+    <t>.S.O.S CAIXA DE PASSAGEM - EMBUTIR NO PISO - Alvenaria - 60x60x60 cm</t>
+  </si>
+  <si>
+    <t>CAIXA ENTERRADA ELÉTRICA RETANGULAR, EM ALVENARIA COM TIJOLOS CERÂMICOS MACIÇOS, FUNDO COM BRITA, DIMENSÕES INTERNAS: 0,6X0,6X0,6 M. AF_12/2020</t>
+  </si>
+  <si>
+    <t>Intelbras - Equipamentos de Rede e Rack - Rack de Piso - 16U unc 19” x 570mm RPD 1657</t>
+  </si>
+  <si>
+    <t>Comp 226</t>
+  </si>
+  <si>
+    <t>RACK ABERTO PADRÃO 19" 16U  (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
   </si>
 </sst>
 </file>
@@ -849,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -1354,7 +1513,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
@@ -1362,7 +1521,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>7</v>
@@ -1370,7 +1529,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>7</v>
@@ -1378,7 +1537,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>7</v>
@@ -1386,7 +1545,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>7</v>
@@ -1394,7 +1553,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>7</v>
@@ -1402,7 +1561,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>7</v>
@@ -1410,7 +1569,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>7</v>
@@ -1418,7 +1577,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>7</v>
@@ -1426,7 +1585,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>7</v>
@@ -1434,7 +1593,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>7</v>
@@ -1442,9 +1601,169 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1455,7 +1774,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -2334,13 +2653,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>93654</v>
+        <v>93655</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>7</v>
@@ -2348,13 +2667,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>93663</v>
+        <v>93654</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>7</v>
@@ -2362,13 +2681,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>93661</v>
+        <v>93663</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>7</v>
@@ -2376,13 +2695,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>93654</v>
+        <v>93661</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>7</v>
@@ -2390,27 +2709,27 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
+        <v>93654</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
         <v>93671</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C67" s="3" t="s">
+      <c r="B68" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>7</v>
@@ -2418,13 +2737,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>7</v>
@@ -2432,13 +2751,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>7</v>
@@ -2446,57 +2765,337 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
+      <c r="D72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
         <v>91961</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C72" s="3" t="s">
+      <c r="B73" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+      <c r="D73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B74" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
+      <c r="D74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
         <v>91953</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" s="3" t="s">
+      <c r="B75" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>91957</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>92004</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>91996</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>97889</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>97888</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A97847-D785-4D34-8431-DDE541EF4990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A0422F-C701-42A9-B702-CBB8BF6D601E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="265">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -697,6 +697,141 @@
   </si>
   <si>
     <t>REPETIDOR DE SINAL (COMPOSIÇÃO DE REFERÊNCIA: CPOS/CDHU: 61.15.140 09/2024)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Ótico - Extensão ótica MM - 2 fibras - Conetor ST</t>
+  </si>
+  <si>
+    <t>Comp 1183</t>
+  </si>
+  <si>
+    <t>EXTENSÃO ÓPTICA LC/SC MM 2FO (COMPOSIÇÃO DE REFERÊNCIA: 13596 ORSE 05/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Switch - 10/100 - BaseTX - 48 portas</t>
+  </si>
+  <si>
+    <t>Comp 1613</t>
+  </si>
+  <si>
+    <t>SWITCH 48 PORTAS (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>Comp 371</t>
+  </si>
+  <si>
+    <t>TE HORIZONTAL PARA ELETROCALHA 50X50 (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - T horizontal 90° - 50x50mm chapa 18</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Terminal - 50x50mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 1608</t>
+  </si>
+  <si>
+    <t>TERMINAL 50 X 50 PARA ELETROCALHA (COMPOSIÇÃO REFERÊNCIA: 12611 ORSE 05/23)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Acessórios para eletrocalha - Saída dupla para eletroduto</t>
+  </si>
+  <si>
+    <t>Comp 451</t>
+  </si>
+  <si>
+    <t>SAIDA HORIZONTAL DUPLA PARA ELETRODUTO (COMPOSIÇÃO DE REFERÊNCIA: 063756 SBC 05/2024)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Ótico - Conetor - ST</t>
+  </si>
+  <si>
+    <t>Comp 1181</t>
+  </si>
+  <si>
+    <t>CONECTOR ÓPTICO ST (COMPOSIÇÃO DE REFERÊNCIA: 059566 SBC 05/2025)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva horizontal 90° - 50x50mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 516</t>
+  </si>
+  <si>
+    <t>CURVA HORIZONTAL 90º PARA ELETROCALHA, LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA DE 50MM E ALTURA DE 50MM - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97278 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva vertical externa 90° - 50x50mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 885</t>
+  </si>
+  <si>
+    <t>CURVA VERTICAL EXTERNA 90º PARA ELETROCALHA PERFURADA OU LISA,50X50MM. (REFERÊNCIA: EMOP 15.018.0630-0)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva vertical interna 90° - 50x50mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 884</t>
+  </si>
+  <si>
+    <t>CURVA VERTICAL INTERNA 90º PARA ELETROCALHA PERFURADA OU LISA,50X50MM. (REFERÊNCIA: EMOP 15.018.0688-0)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Patch panel - 48 posições</t>
+  </si>
+  <si>
+    <t>Comp 919</t>
+  </si>
+  <si>
+    <t>PATCH PANEL 48 PORTAS CAT 6 T568 T568a/b FURUKAWA (REFERÊNCIA: SBC 059439 01/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Patch panel - 24 posições</t>
+  </si>
+  <si>
+    <t>Comp 1990</t>
+  </si>
+  <si>
+    <t>PATCH PANEL 24 PORTAS CAT 6 T568 T568a/b FURUKAWA (REFERÊNCIA: SBC 059439 01/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - T horizontal 90° - 38x38mm</t>
+  </si>
+  <si>
+    <t>Comp 796</t>
+  </si>
+  <si>
+    <t>TE HORIZONTAL PARA ELETROCALHA 38x38 (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Tala plana perfurada - 50mm</t>
+  </si>
+  <si>
+    <t>Comp 455</t>
+  </si>
+  <si>
+    <t>TALA PLANA PERFURADA PARA ELETROCALHA 50MM METALICA (COMPOSIÇÃO DE REFERÊNCIA: 9524 ORSE 03/2024)</t>
+  </si>
+  <si>
+    <t>.S.O.S CFTV e Segurança - CFTV - IP/POE - Câmera de Segurança tipo Bullet 90° IP66</t>
+  </si>
+  <si>
+    <t>Comp 1159</t>
+  </si>
+  <si>
+    <t>CÂMERA DE MONITORAMENTO COM ATÉ 25 METROS DE ALCANCE TIPO BULLET - FORNECIMENTO E INSTALAÇÃO. AF_09/2024 (BASEADO EM SINAPI 97603 03/2025)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Acessórios para eletrocalha - Saída horizontal para eletroduto</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO X, PARA ELETRODUTO DE AÇO GALVANIZADO DN 32 MM (1 1/4&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022</t>
+  </si>
+  <si>
+    <t>.S.O.S CAIXAS - Conduletes - CAIXA DE DERIVAÇÃO EM ALUMÍNIO SILÍCIO INJETADO, CONDULETE DE Ø1". FORNECIMENTO E INSTALAÇÃO.</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -1914,6 +2049,134 @@
         <v>7</v>
       </c>
     </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -1921,7 +2184,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -3372,6 +3635,230 @@
         <v>7</v>
       </c>
     </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>95803</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A0422F-C701-42A9-B702-CBB8BF6D601E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F575C74C-F953-4BAB-8447-A2622DB055FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="275">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -832,6 +832,36 @@
   </si>
   <si>
     <t>.S.O.S CAIXAS - Conduletes - CAIXA DE DERIVAÇÃO EM ALUMÍNIO SILÍCIO INJETADO, CONDULETE DE Ø1". FORNECIMENTO E INSTALAÇÃO.</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Conector - RJ45 - CM8v - Cat 6, para Patch Panel - Keystone</t>
+  </si>
+  <si>
+    <t>Comp 349</t>
+  </si>
+  <si>
+    <t>CONECTOR RJ-45 CAT. 6 (COMPOSIÇÃO DE REFERÊNCIA: AGETOP CIVIL 071026 - 04/2022)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Conector - RJ45 - CM8v</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Conector - RJ45 - Blindado - Cat 6</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Plugue - RJ45 - CM8v - Cat 6</t>
+  </si>
+  <si>
+    <t>Comp 1267</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CONECTOR  MACHO, PARA RJ45  CAT 6 - REF. SBC (061359)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Conector - 110 IDC - 4 pares</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Plugue - 110 IDC - 4 pares</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B125"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -2177,6 +2207,54 @@
         <v>7</v>
       </c>
     </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2184,7 +2262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -3859,6 +3937,90 @@
         <v>7</v>
       </c>
     </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F575C74C-F953-4BAB-8447-A2622DB055FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1333BD21-C7BE-4974-9386-3C0D7AA2AB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="316">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -862,6 +862,129 @@
   </si>
   <si>
     <t>Acessórios Cabeamento - Metálico - Plugue - 110 IDC - 4 pares</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, - DIN - Ref. Moratori - Cap. 50 disj. unip. - In barr. 225 A</t>
+  </si>
+  <si>
+    <t>Comp 985</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, COM BARRAMENTO TRIFÁSICO, PARA 50 DISJUNTORES DIN 225A (REFERÊNCIA: SINAPI 101878)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, - DIN - Ref. Moratori - Cap. 40 disj. unip. - In barr. 150 A</t>
+  </si>
+  <si>
+    <t>Comp 1310</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, COM BARRAMENTO TRIFÁSICO, PARA 40 DISJUNTORES DIN 150A - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101882 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Comp 901</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, COM BARRAMENTO TRIFÁSICO, PARA 18 DISJUNTORES DIN 150A - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101882 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, compacto - DIN - Ref. Moratori - Cap. 18 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, compacto - DIN - Ref. Moratori - Cap. 24 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>Comp 981</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, COM BARRAMENTO TRIFÁSICO, PARA 24 DISJUNTORES DIN 100A (REFERÊNCIA: SINAPI 101878)</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Refletores - 200W IP66</t>
+  </si>
+  <si>
+    <t>Comp 1408</t>
+  </si>
+  <si>
+    <t>REFLETOR LED, 200W (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101659 - 11/2022)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva horizontal 90° - 100x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 323</t>
+  </si>
+  <si>
+    <t>CURVA HORIZONTAL 90º PARA ELETROCALHA, LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA DE 100MM E ALTURA DE 100MM - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97278 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Interruptor tetrapolar DR - 3 fases/neutro - In 30mA - DIN - 125 A</t>
+  </si>
+  <si>
+    <t>Comp 296</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TETRAPOLAR DR 125A TIPO AC 30MA - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: ORSE 9969 - 05/2023)</t>
+  </si>
+  <si>
+    <t>Caixa de passagem - embutir - Alvenaria - 300x300x300mm</t>
+  </si>
+  <si>
+    <t>CAIXA ENTERRADA ELÉTRICA RETANGULAR, EM ALVENARIA COM TIJOLOS CERÂMICOS MACIÇOS, FUNDO COM BRITA, DIMENSÕES INTERNAS: 0,3X0,3X0,3 M. AF_12/2020</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 2x4" - Interruptor paralelo - 1 tecla</t>
+  </si>
+  <si>
+    <t>INTERRUPTOR PARALELO (1 MÓDULO), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 2x4" - Interruptor simples - 3 teclas</t>
+  </si>
+  <si>
+    <t>INTERRUPTOR SIMPLES (3 MÓDULOS), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 2x4" - Interruptor simples - 2 teclas</t>
+  </si>
+  <si>
+    <t>INTERRUPTOR SIMPLES (2 MÓDULOS), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Caixa PVC octogonal - 4"x 4"</t>
+  </si>
+  <si>
+    <t>CAIXA OCTOGONAL 4" X 4", PVC, INSTALADA EM LAJE - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Tala plana perfurada - 100mm</t>
+  </si>
+  <si>
+    <t>Comp 456</t>
+  </si>
+  <si>
+    <t>TALA PLANA PERFURADA PARA ELETROCALHA 100MM METALICA (COMPOSIÇÃO DE REFERÊNCIA: 9519 ORSE 03/2024)</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Refletores - Luminária Industrial LED High Bay UFO 200W Branco Frio</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 2x4" - Placa c/ furo</t>
+  </si>
+  <si>
+    <t>Comp 880</t>
+  </si>
+  <si>
+    <t>CONJUNTO ESPELHO COM FURO SAIDA DE FIO 4X2 BRANCO ALTA, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO (REFERÊNCIA: SINAPI 91933 12/2024)</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 2x4" - Placa cega</t>
+  </si>
+  <si>
+    <t>Comp 1604</t>
+  </si>
+  <si>
+    <t>CAIXA DE PASSAGEM PVC 4X2" - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: ORSE 777 - 06/2022)</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B125"/>
+  <dimension ref="A1:B141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -2255,6 +2378,134 @@
         <v>7</v>
       </c>
     </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2262,11 +2513,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="121.21875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="2"/>
   </cols>
@@ -4021,6 +4272,230 @@
         <v>7</v>
       </c>
     </row>
+    <row r="126" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <v>97886</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="2">
+        <v>91955</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <v>91967</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="2">
+        <v>91959</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="2">
+        <v>91936</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1333BD21-C7BE-4974-9386-3C0D7AA2AB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D643266F-BB0A-4029-915A-D692A600C454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="326">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -985,6 +985,36 @@
   </si>
   <si>
     <t>CAIXA DE PASSAGEM PVC 4X2" - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: ORSE 777 - 06/2022)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 220 V/127 V - DIN - Curva C - 20 A - 5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR BIPOLAR TIPO DIN, CORRENTE NOMINAL DE 20A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 100 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Comp 128</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 100A - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101895 - 04/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 125 A - 40 kA</t>
+  </si>
+  <si>
+    <t>Comp 705</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 125A - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 (COMPOSIÇÃO REFERÊNCIA: SINAPI 93673)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Comando - Relé fotoelétrico - fotocélula</t>
+  </si>
+  <si>
+    <t>RELÉ FOTOELÉTRICO PARA COMANDO DE ILUMINAÇÃO EXTERNA 1000 W - FORNECIMENTO E INSTALAÇÃO. AF_02/2025</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B145"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -2162,7 +2192,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>207</v>
       </c>
@@ -2322,7 +2352,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>264</v>
       </c>
@@ -2503,6 +2533,38 @@
         <v>313</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2513,7 +2575,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -4286,7 +4348,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>279</v>
       </c>
@@ -4493,6 +4555,62 @@
         <v>315</v>
       </c>
       <c r="D141" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" s="2">
+        <v>93662</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="2">
+        <v>101632</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D145" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D643266F-BB0A-4029-915A-D692A600C454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE026E1-F517-4AF3-A79E-7EFEEA4A2202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="339">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1015,6 +1015,45 @@
   </si>
   <si>
     <t>RELÉ FOTOELÉTRICO PARA COMANDO DE ILUMINAÇÃO EXTERNA 1000 W - FORNECIMENTO E INSTALAÇÃO. AF_02/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 220 V/127 V - DIN - Curva B - 20 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva C - 32 A - 25 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR BIPOLAR TIPO DIN, CORRENTE NOMINAL DE 32A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Luminária Pública - Lâmpada 120W</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA DE LED PARA ILUMINAÇÃO PÚBLICA, DE 98 W ATÉ 137 W - FORNECIMENTO E INSTALAÇÃO. AF_02/2025_PS</t>
+  </si>
+  <si>
+    <t>Poste - Cônico em Aço Galvanizado - 7 metros</t>
+  </si>
+  <si>
+    <t>POSTE DE AÇO CÔNICO CONTÍNUO RETO, ENGASTAMENTO SIMPLES COM 1 M DE SOLO, H=7M - FORNECIMENTO E INSTALAÇÃO. AF_04/2025</t>
+  </si>
+  <si>
+    <t>Comp 1991</t>
+  </si>
+  <si>
+    <t>POSTE DE AÇO CONICO CONTÍNUO CURVO DUPLO, FLANGEADO, H=7M, INCLUSIVE LUMINÁRIAS, SEM LÂMPADAS - FORNECIMENTO E INSTALACAO. AF_11/2019  (COMPOSIÇÃO REFERÊNCIA: SINAPI 100621 08/2025)</t>
+  </si>
+  <si>
+    <t>Poste - Cônico duplo em Aço Galvanizado - 7 metros</t>
+  </si>
+  <si>
+    <t>Comp 1609</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, SEM BARRAMENTO, PARA 16 DISJUNTORES DIN - FORNECIMENTO E INSTALAÇÃO. AF_10/2020  (COMPOSIÇÃO REFERÊNCIA: SINAPI 101883)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Sem barr., - DIN - Cap. 16 disj. unip.</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B145"/>
+  <dimension ref="A1:B151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -2568,6 +2607,54 @@
         <v>7</v>
       </c>
     </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2575,7 +2662,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -4614,6 +4701,90 @@
         <v>7</v>
       </c>
     </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="2">
+        <v>93662</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="2">
+        <v>93664</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="2">
+        <v>101657</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="2">
+        <v>105953</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE026E1-F517-4AF3-A79E-7EFEEA4A2202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B08D84-9518-4CCD-A028-D25813535C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="352">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1054,6 +1054,45 @@
   </si>
   <si>
     <t>Quadro distrib. chapa pintada - sobrepor - Sem barr., - DIN - Cap. 16 disj. unip.</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 2 - 2P+T 10A - Alta</t>
+  </si>
+  <si>
+    <t>TOMADA ALTA DE EMBUTIR (1 MÓDULO), 2P+T 10 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 2x4" - Tomada hexagonal - NBR 14136 - 2P+T 20A - Alta</t>
+  </si>
+  <si>
+    <t>TOMADA ALTA DE EMBUTIR (1 MÓDULO), 2P+T 20 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 2 - 2P+T 10A - Baixa</t>
+  </si>
+  <si>
+    <t>TOMADA BAIXA DE EMBUTIR (2 MÓDULOS), 2P+T 10 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 2P+T 10A - Baixa</t>
+  </si>
+  <si>
+    <t>TOMADA BAIXA DE EMBUTIR (1 MÓDULO), 2P+T 10 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>TOMADA MÉDIA DE EMBUTIR (1 MÓDULO), 2P+T 20 A, SEM SUPORTE E SEM PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 2P+T 20A - Média</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 2P+T 20A - Baixa</t>
+  </si>
+  <si>
+    <t>TOMADA BAIXA DE EMBUTIR (1 MÓDULO), 2P+T 20 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 2x4" - Tomada hexagonal - NBR 14136 - 2P+T 20A - Baixa</t>
   </si>
 </sst>
 </file>
@@ -1440,7 +1479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B151"/>
+  <dimension ref="A1:B158"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -2655,6 +2694,62 @@
         <v>7</v>
       </c>
     </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2662,7 +2757,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -4785,6 +4880,104 @@
         <v>7</v>
       </c>
     </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="2">
+        <v>91992</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="2">
+        <v>91993</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" s="2">
+        <v>92008</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" s="2">
+        <v>92000</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" s="2">
+        <v>91995</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" s="2">
+        <v>92001</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="2">
+        <v>92001</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B08D84-9518-4CCD-A028-D25813535C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C9960D-3B92-4293-BE9C-420AB6D9557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="360">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1093,6 +1093,30 @@
   </si>
   <si>
     <t>Dispositivo Elétrico - embutido - Placa 2x4" - Tomada hexagonal - NBR 14136 - 2P+T 20A - Baixa</t>
+  </si>
+  <si>
+    <t>Condutores de proteção - SPDA - Cabo de cobre Nú - 7 fios - 50mm²</t>
+  </si>
+  <si>
+    <t>CORDOALHA DE COBRE NU 50 MM², ENTERRADA - FORNECIMENTO E INSTALAÇÃO. AF_08/2023</t>
+  </si>
+  <si>
+    <t>Condutores de proteção - SPDA - Cabo de alumínio Nú - 7 fios - 70 mm²</t>
+  </si>
+  <si>
+    <t>Comp 1638</t>
+  </si>
+  <si>
+    <t>CABO DE ALUMÍNIO NÚ, 70 MM² PARA SPDA - FORNECIMENTO E INSTALAÇÃO. AF_08/2023 (COMPOSIÇÃI REFERÊNCIA: SINAPI 96980 - 08/2025)</t>
+  </si>
+  <si>
+    <t>Comp 1018</t>
+  </si>
+  <si>
+    <t>RE-BAR REDONDA AÇO GALVANIZADO - 70MM² (COMPOSIÇÃO REFERENCIA CÓDIGO 72315 SINAPI 01/2020 )</t>
+  </si>
+  <si>
+    <t>Condutores de proteção - SPDA - Re-bar redonda aço galvanizado - 70mm²</t>
   </si>
 </sst>
 </file>
@@ -1479,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B158"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -2750,6 +2774,30 @@
         <v>7</v>
       </c>
     </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2757,7 +2805,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -4978,6 +5026,48 @@
         <v>7</v>
       </c>
     </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="2">
+        <v>96977</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C9960D-3B92-4293-BE9C-420AB6D9557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09270462-B3C5-4AFE-8C89-F9E106AEE32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="366">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1117,6 +1117,24 @@
   </si>
   <si>
     <t>Condutores de proteção - SPDA - Re-bar redonda aço galvanizado - 70mm²</t>
+  </si>
+  <si>
+    <t>TERMINAL AEREO EM ACO GALVANIZADO 600 MM - (COMPOSIÇÃO REFERENCIA  CÓDIGO 72315  SINAPI  01/2020 )</t>
+  </si>
+  <si>
+    <t>Comp 1401</t>
+  </si>
+  <si>
+    <t>Captores - Terminal Aéreo - 600 mm - Fixação horizontal</t>
+  </si>
+  <si>
+    <t>Acessórios uso geral - Outros - Fixador Omega Latão Cabo 70mm²</t>
+  </si>
+  <si>
+    <t>Comp 78</t>
+  </si>
+  <si>
+    <t>FIXADOR TIPO ÔMEGA EM COBRE, L=15MM, C/FUROS D=5,5MM E TRAVA P/CABO DE 35MM², REF:TEL-833 OU SIMILAR (P/SPDA) -(COMPOSIÇÃO REFERENCIA CÓDIGO 10091 ORSE 05/2023 )</t>
   </si>
 </sst>
 </file>
@@ -1503,7 +1521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B161"/>
+  <dimension ref="A1:B163"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -2798,6 +2816,22 @@
         <v>21</v>
       </c>
     </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2805,7 +2839,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D163"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5036,7 +5070,7 @@
       <c r="C159" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="D159" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5050,7 +5084,7 @@
       <c r="C160" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="D160" s="2" t="s">
+      <c r="D160" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5064,8 +5098,36 @@
       <c r="C161" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="D161" s="2" t="s">
-        <v>21</v>
+      <c r="D161" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09270462-B3C5-4AFE-8C89-F9E106AEE32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74907152-45EA-46DC-B222-21EFE87CE636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="379">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1135,6 +1135,45 @@
   </si>
   <si>
     <t>FIXADOR TIPO ÔMEGA EM COBRE, L=15MM, C/FUROS D=5,5MM E TRAVA P/CABO DE 35MM², REF:TEL-833 OU SIMILAR (P/SPDA) -(COMPOSIÇÃO REFERENCIA CÓDIGO 10091 ORSE 05/2023 )</t>
+  </si>
+  <si>
+    <t>SPDA - Conector estrutural - Conector Split Bolt</t>
+  </si>
+  <si>
+    <t>CONECTOR SPLIT-BOLT, PARA SPDA, PARA CABOS DE 16 A 70 MM2 - FORNECIMENTO E INSTALAÇÃO. AF_08/2023</t>
+  </si>
+  <si>
+    <t>.S.O.S CAIXA DE PASSAGEM - EMBUTIR NO PISO - Alvenaria - 80x80x30 cm</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 95 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 95 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 95 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 95 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 95 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 50 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 50 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>Eletroduto metálico rígido médio - Eletroduto galvanizado - 1"</t>
+  </si>
+  <si>
+    <t>Comp 1158</t>
+  </si>
+  <si>
+    <t>ELETRODUTO RIGIDO, EM ACO ZINCADO OU GALVANIZADO, TIPO PESADO, DN=1", APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022 (BASEADO EM SINAPI 104407 03/2025)</t>
   </si>
 </sst>
 </file>
@@ -1521,7 +1560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B163"/>
+  <dimension ref="A1:B171"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -2832,6 +2871,70 @@
         <v>7</v>
       </c>
     </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2839,7 +2942,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5130,6 +5233,118 @@
         <v>7</v>
       </c>
     </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" s="2">
+        <v>96982</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A165" s="2">
+        <v>97889</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A166" s="2">
+        <v>92992</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A167" s="2">
+        <v>92992</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A168" s="2">
+        <v>92992</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A169" s="2">
+        <v>92992</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A170" s="2">
+        <v>92988</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A171" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74907152-45EA-46DC-B222-21EFE87CE636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A0EB51-E156-4EA6-841B-51E4EBFB668B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="392">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1174,6 +1174,45 @@
   </si>
   <si>
     <t>ELETRODUTO RIGIDO, EM ACO ZINCADO OU GALVANIZADO, TIPO PESADO, DN=1", APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022 (BASEADO EM SINAPI 104407 03/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 150 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 127</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 150A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Comp 950</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 200A, 18kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 200 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 220 V/127 V - DIN - Curva B - 32 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, - DIN - Ref. Moratori - Cap. 32 disj. unip. - In barr. 150 A</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, COM BARRAMENTO TRIFÁSICO, PARA 32 DISJUNTORES DIN 150A (REFERÊNCIA 101878 12/2024)</t>
+  </si>
+  <si>
+    <t>Comp 982</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - T horizontal 90° - 100x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 325</t>
+  </si>
+  <si>
+    <t>TE HORIZONTAL PARA ELETROCALHA 100X100MM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97315 - 02/2023)</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B171"/>
+  <dimension ref="A1:B176"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -2935,6 +2974,46 @@
         <v>21</v>
       </c>
     </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2942,7 +3021,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:D176"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5345,6 +5424,76 @@
         <v>21</v>
       </c>
     </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" s="2">
+        <v>93664</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A175" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A0EB51-E156-4EA6-841B-51E4EBFB668B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A72DE3D-770C-4F20-8AF8-752F13A4C6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="399">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1213,6 +1213,27 @@
   </si>
   <si>
     <t>TE HORIZONTAL PARA ELETROCALHA 100X100MM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97315 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo LL - 1" sem tampa</t>
+  </si>
+  <si>
+    <t>Comp 1632</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo LR - 1" sem tampa</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo T - 1" sem tampa</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO LL, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022 (COMPOSIÇÃO REFERÊNCIA: SINAPI 95788 - 08/2025)</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO LR, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO T, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
   </si>
 </sst>
 </file>
@@ -1599,7 +1620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B176"/>
+  <dimension ref="A1:B179"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -3014,6 +3035,30 @@
         <v>7</v>
       </c>
     </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3021,7 +3066,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D176"/>
+  <dimension ref="A1:D179"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5494,6 +5539,48 @@
         <v>7</v>
       </c>
     </row>
+    <row r="177" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A178" s="2">
+        <v>95789</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A179" s="2">
+        <v>95796</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A72DE3D-770C-4F20-8AF8-752F13A4C6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32A7E9A-6845-4B23-AB6C-BAB4B128016D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="420">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1234,6 +1234,69 @@
   </si>
   <si>
     <t>CONDULETE DE ALUMÍNIO, TIPO T, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Comp 1993</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE 2X1,5MM2 - ISOLAMENTO PARA 0,6KV - CLASSE 5 - FLEXÍVEL - ISOLAÇÃO EM EPR 90 C - PARA DETECÇÃO DE INCÊNDIO (COMPOSIÇÃO REFERÊNCIA: SIURB 9003118 07/2025)</t>
+  </si>
+  <si>
+    <t>Cabeamento de Incêndio - Cabo Alarme De Incêndio 2x1,50mm² Blindado - 2</t>
+  </si>
+  <si>
+    <t>Cabeamento de Incêndio - Cabo Alarme De Incêndio 2x2,50mm² Blindado - 2</t>
+  </si>
+  <si>
+    <t>Comp 1994</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE 2X2,5MM2 - ISOLAMENTO PARA 0,6KV - CLASSE 5 - FLEXÍVEL - ISOLAÇÃO EM EPR 90 C - PARA DETECÇÃO DE INCÊNDIO (COMPOSIÇÃO REFERÊNCIA: SIURB 9003118 07/2025)</t>
+  </si>
+  <si>
+    <t>Cabeamento de Incêndio - Cabo Alarme De Incêndio 4x1,50mm² Blindado - 2</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC rosca - Eletroduto, vara 3,0m - 1"</t>
+  </si>
+  <si>
+    <t>Comp 1995</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE 4X1,5MM2 - ISOLAMENTO PARA 0,6KV - CLASSE 5 - FLEXÍVEL - ISOLAÇÃO EM EPR 90 C - PARA DETECÇÃO DE INCÊNDIO (COMPOSIÇÃO REFERÊNCIA: SIURB 9003118 07/2025)</t>
+  </si>
+  <si>
+    <t>ELETRODUTO RÍGIDO ROSCÁVEL, PVC, DN 32 MM (1"), PARA CIRCUITOS TERMINAIS, INSTALADO EM LAJE - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Eletroduto metálico rígido médio - Eletroduto galvanizado - 1.1/2"</t>
+  </si>
+  <si>
+    <t>Comp 1400</t>
+  </si>
+  <si>
+    <t>ELETRODUTO RIGIDO, EM ACO ZINCADO OU GALVANIZADO, TIPO PESADO, DN=1.1/2", APARENTE - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI (104406) 03/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo C - 1" sem tampa</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO C, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo LB - 1" sem tampa</t>
+  </si>
+  <si>
+    <t>Comp 1628</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO LB, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022 (COMPOSIÇÃO REFERÊNCIA: SINAPI 95793 - 08/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo E - 1" sem tampa</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO E, ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
   </si>
 </sst>
 </file>
@@ -1620,7 +1683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B179"/>
+  <dimension ref="A1:B187"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -3059,6 +3122,70 @@
         <v>7</v>
       </c>
     </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3066,7 +3193,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D179"/>
+  <dimension ref="A1:D187"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5581,6 +5708,118 @@
         <v>7</v>
       </c>
     </row>
+    <row r="180" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A180" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A181" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A182" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="2">
+        <v>91868</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A184" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A185" s="2">
+        <v>95781</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A186" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A187" s="2">
+        <v>95782</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32A7E9A-6845-4B23-AB6C-BAB4B128016D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C29F39-5395-441E-BBE7-A6BF2416677A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="429">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1281,22 +1281,49 @@
     <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo C - 1" sem tampa</t>
   </si>
   <si>
-    <t>CONDULETE DE ALUMÍNIO, TIPO C, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
-  </si>
-  <si>
     <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo LB - 1" sem tampa</t>
   </si>
   <si>
     <t>Comp 1628</t>
   </si>
   <si>
-    <t>CONDULETE DE ALUMÍNIO, TIPO LB, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022 (COMPOSIÇÃO REFERÊNCIA: SINAPI 95793 - 08/2025)</t>
-  </si>
-  <si>
     <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo E - 1" sem tampa</t>
   </si>
   <si>
-    <t>CONDULETE DE ALUMÍNIO, TIPO E, ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo T - 3/4" sem tampa</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo X - 3/4" sem tampa</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo E - 3/4" sem tampa</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO C, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO LB, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022 (COMPOSIÇÃO REFERÊNCIA: SINAPI 95793 - 08/2025)</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO E, ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO T, PARA ELETRODUTO DE AÇO GALVANIZADO DN 20 MM (3/4"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO X, PARA ELETRODUTO DE AÇO GALVANIZADO DN 20 MM (3/4"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO E, PARA ELETRODUTO DE AÇO GALVANIZADO DN 20 MM (3/4"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - sobrepor - Tampa metálica p/ condulete - Interruptor 1 tecla paralela</t>
+  </si>
+  <si>
+    <t>Comp 1996</t>
+  </si>
+  <si>
+    <t>CONJUNTO PARA CONDULETE COM UM (1) INTERRUPTOR PARALELO,  TENSÃO 250V, (10A 250V) E PLACA DE UM (1) POSTO, INCLUSIVE FORNECIMENTO, INSTALAÇÃO, SUPORTE, MÓDULO E PLACA, SEM CONDULETE (COMPOSIÇÃP REFERÊNCIA: SETOP ED-17981 10/2025)</t>
   </si>
 </sst>
 </file>
@@ -1683,7 +1710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B187"/>
+  <dimension ref="A1:B191"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -3172,7 +3199,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>7</v>
@@ -3180,9 +3207,41 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="B189" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3193,7 +3252,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D187"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5786,7 +5845,7 @@
         <v>5</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>7</v>
@@ -5794,19 +5853,19 @@
     </row>
     <row r="186" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
         <v>95782</v>
       </c>
@@ -5814,9 +5873,65 @@
         <v>5</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D187" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A188" s="2">
+        <v>95795</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A189" s="2">
+        <v>95801</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A190" s="2">
+        <v>95779</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A191" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D191" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C29F39-5395-441E-BBE7-A6BF2416677A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9389B22D-6381-4CA7-8DA4-0AE569B0CA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="435">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1324,6 +1324,24 @@
   </si>
   <si>
     <t>CONJUNTO PARA CONDULETE COM UM (1) INTERRUPTOR PARALELO,  TENSÃO 250V, (10A 250V) E PLACA DE UM (1) POSTO, INCLUSIVE FORNECIMENTO, INSTALAÇÃO, SUPORTE, MÓDULO E PLACA, SEM CONDULETE (COMPOSIÇÃP REFERÊNCIA: SETOP ED-17981 10/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo LB - 3/4" sem tampa</t>
+  </si>
+  <si>
+    <t>Comp 1627</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO LB, PARA ELETRODUTO DE AÇO GALVANIZADO DN 20 MM (3/4"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022 (COMPOSIÇÃO REFERÊNCIA: SINAPI 95792 - 08/2025)</t>
+  </si>
+  <si>
+    <t>Comp 1997</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA LED REDONDA DE EMBUTIR PARA PAREDE OU PISO, ÁREA INTERNA OU EXTERNA, BIVOLT - POTÊNCIA 12 W (COMPOSIÇÃO REFERÊNCIA: CPOS/CDHU 41.11.712 01/2026)</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Spot de embutir no chão - 12W</t>
   </si>
 </sst>
 </file>
@@ -1710,7 +1728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B191"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -3245,6 +3263,22 @@
         <v>7</v>
       </c>
     </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3252,7 +3286,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D191"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5935,6 +5969,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="192" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A192" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A193" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9389B22D-6381-4CA7-8DA4-0AE569B0CA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1AB345-E1B0-448B-A0EA-065900DD93F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="471">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1342,6 +1342,114 @@
   </si>
   <si>
     <t>Lâmpadas Led - Spot de embutir no chão - 12W</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 120 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 120 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 120 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 120 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 120 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 70 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 70 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 70 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 70 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 70 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 70 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 70 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2022</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 70 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2023</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 70 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2024</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 70 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2025</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - SINAPI - 35 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 35 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>Eletroduto metálico rígido leve - Eletroduto galvanizado, vara 3,0m - 1"</t>
+  </si>
+  <si>
+    <t>Eletroduto metálico rígido médio - Eletroduto galvanizado - 2"</t>
+  </si>
+  <si>
+    <t>Comp 1626</t>
+  </si>
+  <si>
+    <t>ELETRODUTO RIGIDO, EM ACO ZINCADO OU GALVANIZADO, TIPO PESADO, DN=2", APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022 (COMPOSIÇÃO REFERÊNCIA: SINAPI 104409 - 08/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 32 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 1082</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 32A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 630 A - 50 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 630A, 35kA - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 03/2024)</t>
+  </si>
+  <si>
+    <t>Comp 1667</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético caixa moldada - 380/415 V - 32 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 1611</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA, BIPOLAR 32A, 25kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - T horizontal 90° - 200x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 326</t>
+  </si>
+  <si>
+    <t>TE HORIZONTAL PARA ELETROCALHA 200X100MM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97315 - 02/2023)</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -1500x600x600mm</t>
+  </si>
+  <si>
+    <t>PAINEL MODULAR -1500x600x600mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>Comp 1519</t>
   </si>
 </sst>
 </file>
@@ -1728,7 +1836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B210"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -3279,6 +3387,142 @@
         <v>7</v>
       </c>
     </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3286,7 +3530,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D210"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5997,6 +6241,244 @@
         <v>7</v>
       </c>
     </row>
+    <row r="194" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A194" s="2">
+        <v>92994</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A195" s="2">
+        <v>92994</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A196" s="2">
+        <v>92994</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A197" s="2">
+        <v>92994</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A198" s="2">
+        <v>92990</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A199" s="2">
+        <v>92991</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A200" s="2">
+        <v>92992</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A201" s="2">
+        <v>92993</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A202" s="2">
+        <v>92994</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A203" s="2">
+        <v>92986</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A204" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A206" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A207" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A208" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A209" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A210" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1AB345-E1B0-448B-A0EA-065900DD93F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7BA68C-7154-407D-8C1E-475F6C45397F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="480">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1450,6 +1450,33 @@
   </si>
   <si>
     <t>Comp 1519</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -1200x800x350mm</t>
+  </si>
+  <si>
+    <t>Comp 821</t>
+  </si>
+  <si>
+    <t>PAINEL MODULAR -1200x800x350mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>Comp 1523</t>
+  </si>
+  <si>
+    <t>PAINEL MODULAR -500x400x200mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>- Quadro distrib. - PAINÉIS - 500x400x200</t>
+  </si>
+  <si>
+    <t>Comp 1365</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE TRIFASICO 150A (REFERÊNCIA: SIURB 9006079 07/2024)</t>
+  </si>
+  <si>
+    <t>Acessórios uso geral - Outros - Kit barramento trifásico 150A</t>
   </si>
 </sst>
 </file>
@@ -1836,7 +1863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B210"/>
+  <dimension ref="A1:B213"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -3523,6 +3550,30 @@
         <v>7</v>
       </c>
     </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3530,7 +3581,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D210"/>
+  <dimension ref="A1:D213"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -6479,6 +6530,48 @@
         <v>7</v>
       </c>
     </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A211" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A212" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A213" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7BA68C-7154-407D-8C1E-475F6C45397F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3773245F-E3A7-42CB-A6BF-C9CAA08B68B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="492">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1477,6 +1477,42 @@
   </si>
   <si>
     <t>Acessórios uso geral - Outros - Kit barramento trifásico 150A</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Barra de led - 31W</t>
+  </si>
+  <si>
+    <t>Comp 1998</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA DE EMBUTIR EM FORRO DE GESSO OU MODULADO COM PERFIL “T”, COM BARRA DE LED 31W (COMPOSIÇÃO REFERÊNCIA: SBC 060105 02/2026)</t>
+  </si>
+  <si>
+    <t>Comp 1999</t>
+  </si>
+  <si>
+    <t>Comp 2000</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Barra de led - 39W</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA DE EMBUTIR EM FORRO DE GESSO OU MODULADO COM PERFIL “T”, COM BARRA DE LED 39W (COMPOSIÇÃO REFERÊNCIA: SBC 060105 02/2026)</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA DE EMBUTIR EM FORRO DE GESSO OU MODULADO COM PERFIL “T”, COM BARRA DE LED 17W (COMPOSIÇÃO REFERÊNCIA: SBC 060105 02/2026)</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Barra de led - 17W</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Tubular Led - 18W</t>
+  </si>
+  <si>
+    <t>LÂMPADA TUBULAR LED T8 18W, COM CALHA ACOPLADA (COMPOSIÇÃO REFERÊNCIA: SBC 060105 02/2026)</t>
+  </si>
+  <si>
+    <t>Comp 2001</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B213"/>
+  <dimension ref="A1:B217"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -3574,6 +3610,38 @@
         <v>7</v>
       </c>
     </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3581,7 +3649,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D213"/>
+  <dimension ref="A1:D217"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -6138,7 +6206,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>91868</v>
       </c>
@@ -6572,8 +6640,65 @@
         <v>7</v>
       </c>
     </row>
+    <row r="214" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A214" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A215" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A216" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A217" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3773245F-E3A7-42CB-A6BF-C9CAA08B68B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623F9525-C28C-40CC-93C7-30BBCD2C50A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="500">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1513,6 +1513,30 @@
   </si>
   <si>
     <t>Comp 2001</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo LR - 3/4" sem tampa</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO LR, PARA ELETRODUTO DE AÇO GALVANIZADO DN 20 MM (3/4''), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Comp 2002</t>
+  </si>
+  <si>
+    <t>CONJUNTO PARA CONDULETE COM UM (1) INTERRUPTOR SIMPLES,  TENSÃO 250V, (10A 250V) E PLACA DE UM (1) POSTO, INCLUSIVE FORNECIMENTO, INSTALAÇÃO, SUPORTE, MÓDULO E PLACA, SEM CONDULETE (COMPOSIÇÃP REFERÊNCIA: SETOP ED-17981 10/2025)</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - E27 A55 4000K - 24W</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - sobrepor - Tampa metálica p/ condulete - Interruptor 1 tecla simples</t>
+  </si>
+  <si>
+    <t>Comp 866</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA ARANDELA SOBREPOR EXTERNA, COM 1 LÂMPADA LED DE 24 W, SEM REATOR - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA SINAPI COD. 97607 09/2024))</t>
   </si>
 </sst>
 </file>
@@ -1899,7 +1923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B217"/>
+  <dimension ref="A1:B220"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -3642,6 +3666,30 @@
         <v>7</v>
       </c>
     </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3649,7 +3697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D217"/>
+  <dimension ref="A1:D220"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -6696,6 +6744,48 @@
         <v>7</v>
       </c>
     </row>
+    <row r="218" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A218" s="2">
+        <v>95787</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A219" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A220" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623F9525-C28C-40CC-93C7-30BBCD2C50A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B78B86-9E0A-49C5-93C0-F72885780E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="507">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1537,6 +1537,27 @@
   </si>
   <si>
     <t>LUMINÁRIA ARANDELA SOBREPOR EXTERNA, COM 1 LÂMPADA LED DE 24 W, SEM REATOR - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA SINAPI COD. 97607 09/2024))</t>
+  </si>
+  <si>
+    <t>Captores - Mastro simples - 3m x ø1.1/2"</t>
+  </si>
+  <si>
+    <t>MASTRO 1 ½", COM 3 METROS, PARA SPDA - FORNECIMENTO E INSTALAÇÃO. AF_08/2023</t>
+  </si>
+  <si>
+    <t>BASE METÁLICA PARA MASTRO 1 ½" PARA SPDA - FORNECIMENTO E INSTALAÇÃO. AF_08/2023</t>
+  </si>
+  <si>
+    <t>Captores - Captor Franklin - H=250mm - 01 descida</t>
+  </si>
+  <si>
+    <t>SPDA - SINALEIRA - SINALIZADOR SIMPLES - 1 LÂMPADA</t>
+  </si>
+  <si>
+    <t>INSTALAÇÃO DE GAMBIARRA PARA SINALIZAÇÃO, INCLUINDO LÂMPADA, E SINALIZADOR. AF_03/2024</t>
+  </si>
+  <si>
+    <t>CAPTOR TIPO FRANKLIN PARA SPDA - FORNECIMENTO E INSTALAÇÃO. AF_08/2023</t>
   </si>
 </sst>
 </file>
@@ -1923,7 +1944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B224"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -3690,6 +3711,38 @@
         <v>7</v>
       </c>
     </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3697,7 +3750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D220"/>
+  <dimension ref="A1:D224"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -6786,6 +6839,62 @@
         <v>7</v>
       </c>
     </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A221" s="2">
+        <v>96988</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A222" s="2">
+        <v>96987</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A223" s="2">
+        <v>96989</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A224" s="2">
+        <v>97052</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B78B86-9E0A-49C5-93C0-F72885780E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28902B37-5B02-458E-B689-C57BC5635A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="513">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1558,6 +1558,24 @@
   </si>
   <si>
     <t>CAPTOR TIPO FRANKLIN PARA SPDA - FORNECIMENTO E INSTALAÇÃO. AF_08/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 110 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 2003</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 110A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Caixa de passagem - sobrepor - Aço pintada - ref Lukbox - 100x100x80 mm</t>
+  </si>
+  <si>
+    <t>Comp 1615</t>
+  </si>
+  <si>
+    <t>CAIXA DE PASSAGEM METÁLICA 10x10x8 CM (COMPOSIÇÃIO REFERÊNCIA: SINAPI 068209 01/2025)</t>
   </si>
 </sst>
 </file>
@@ -1944,7 +1962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B224"/>
+  <dimension ref="A1:B226"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -3743,6 +3761,22 @@
         <v>7</v>
       </c>
     </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3750,7 +3784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:D226"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -6895,6 +6929,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28902B37-5B02-458E-B689-C57BC5635A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A691793-16DD-439F-ADE6-686C6A0BB71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -6567,7 +6567,7 @@
     </row>
     <row r="199" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
-        <v>92991</v>
+        <v>92990</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>5</v>
@@ -6581,7 +6581,7 @@
     </row>
     <row r="200" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
-        <v>92992</v>
+        <v>92990</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>5</v>
@@ -6595,7 +6595,7 @@
     </row>
     <row r="201" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
-        <v>92993</v>
+        <v>92990</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>5</v>
@@ -6609,7 +6609,7 @@
     </row>
     <row r="202" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
-        <v>92994</v>
+        <v>92990</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>5</v>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A691793-16DD-439F-ADE6-686C6A0BB71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABE975F-7A25-4B80-9324-0D0A52B2D592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
     <sheet name="Descricao" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Descricao!$A$1:$D$226</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="514">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -69,9 +72,6 @@
     <t>CONECTOR SPLIT-BOLT, PARA SPDA, PARA CABOS ATÉ 50 MM2 - FORNECIMENTO E INSTALAÇÃO. AF_08/2023</t>
   </si>
   <si>
-    <t>981111</t>
-  </si>
-  <si>
     <t>CAIXA DE INSPEÇÃO PARA ATERRAMENTO, CIRCULAR, EM POLIETILENO, DIÂMETRO INTERNO = 0,3 M. AF_12/2020</t>
   </si>
   <si>
@@ -1140,9 +1140,6 @@
     <t>SPDA - Conector estrutural - Conector Split Bolt</t>
   </si>
   <si>
-    <t>CONECTOR SPLIT-BOLT, PARA SPDA, PARA CABOS DE 16 A 70 MM2 - FORNECIMENTO E INSTALAÇÃO. AF_08/2023</t>
-  </si>
-  <si>
     <t>.S.O.S CAIXA DE PASSAGEM - EMBUTIR NO PISO - Alvenaria - 80x80x30 cm</t>
   </si>
   <si>
@@ -1554,9 +1551,6 @@
     <t>SPDA - SINALEIRA - SINALIZADOR SIMPLES - 1 LÂMPADA</t>
   </si>
   <si>
-    <t>INSTALAÇÃO DE GAMBIARRA PARA SINALIZAÇÃO, INCLUINDO LÂMPADA, E SINALIZADOR. AF_03/2024</t>
-  </si>
-  <si>
     <t>CAPTOR TIPO FRANKLIN PARA SPDA - FORNECIMENTO E INSTALAÇÃO. AF_08/2023</t>
   </si>
   <si>
@@ -1576,6 +1570,18 @@
   </si>
   <si>
     <t>CAIXA DE PASSAGEM METÁLICA 10x10x8 CM (COMPOSIÇÃIO REFERÊNCIA: SINAPI 068209 01/2025)</t>
+  </si>
+  <si>
+    <t>Comp 2005</t>
+  </si>
+  <si>
+    <t>INSTALAÇÃO DE GAMBIARRA PARA SINALIZAÇÃO, INCLUINDO LÂMPADA, E SINALIZADOR. AF_03/2024 (COMPOSIÇÃO REFERÊNCIA: SINAPI 97052 01/2026)</t>
+  </si>
+  <si>
+    <t>Comp 2006</t>
+  </si>
+  <si>
+    <t>CONECTOR SPLIT-BOLT, PARA SPDA, PARA CABOS DE 16 A 70 MM2 - FORNECIMENTO E INSTALAÇÃO. AF_08/2023 (COMPOSIÇÃO REFERÊNCIA: SINAPI 96982 01/2026)</t>
   </si>
 </sst>
 </file>
@@ -1979,7 +1985,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1987,7 +1993,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -1995,7 +2001,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2003,7 +2009,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -2011,431 +2017,431 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
@@ -2443,7 +2449,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
@@ -2451,7 +2457,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>7</v>
@@ -2459,7 +2465,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>7</v>
@@ -2467,7 +2473,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
@@ -2475,7 +2481,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>7</v>
@@ -2483,7 +2489,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>7</v>
@@ -2491,7 +2497,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>7</v>
@@ -2499,7 +2505,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>7</v>
@@ -2507,7 +2513,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>7</v>
@@ -2515,7 +2521,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>7</v>
@@ -2523,7 +2529,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>7</v>
@@ -2531,7 +2537,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>7</v>
@@ -2539,7 +2545,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>7</v>
@@ -2547,7 +2553,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>7</v>
@@ -2555,7 +2561,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>7</v>
@@ -2563,7 +2569,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>7</v>
@@ -2571,7 +2577,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>7</v>
@@ -2579,7 +2585,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>7</v>
@@ -2587,7 +2593,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>7</v>
@@ -2595,7 +2601,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>7</v>
@@ -2603,7 +2609,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>7</v>
@@ -2611,7 +2617,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>7</v>
@@ -2619,7 +2625,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>7</v>
@@ -2627,7 +2633,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>7</v>
@@ -2635,7 +2641,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>7</v>
@@ -2643,7 +2649,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>7</v>
@@ -2651,7 +2657,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>7</v>
@@ -2659,7 +2665,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>7</v>
@@ -2667,7 +2673,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>7</v>
@@ -2675,7 +2681,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>7</v>
@@ -2683,7 +2689,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>7</v>
@@ -2691,7 +2697,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>7</v>
@@ -2699,7 +2705,7 @@
     </row>
     <row r="92" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>7</v>
@@ -2707,7 +2713,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>7</v>
@@ -2715,7 +2721,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>7</v>
@@ -2723,7 +2729,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>7</v>
@@ -2731,7 +2737,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>7</v>
@@ -2739,7 +2745,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>7</v>
@@ -2747,7 +2753,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>7</v>
@@ -2755,7 +2761,7 @@
     </row>
     <row r="99" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>7</v>
@@ -2763,7 +2769,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>7</v>
@@ -2771,7 +2777,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>7</v>
@@ -2779,7 +2785,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>7</v>
@@ -2787,7 +2793,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>7</v>
@@ -2795,7 +2801,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>7</v>
@@ -2803,7 +2809,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>7</v>
@@ -2811,7 +2817,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>7</v>
@@ -2819,7 +2825,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>7</v>
@@ -2827,7 +2833,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>7</v>
@@ -2835,7 +2841,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>7</v>
@@ -2843,7 +2849,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>7</v>
@@ -2851,7 +2857,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>7</v>
@@ -2859,7 +2865,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>7</v>
@@ -2867,7 +2873,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>7</v>
@@ -2875,7 +2881,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>7</v>
@@ -2883,7 +2889,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>7</v>
@@ -2891,7 +2897,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>7</v>
@@ -2899,7 +2905,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>7</v>
@@ -2907,7 +2913,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>7</v>
@@ -2915,7 +2921,7 @@
     </row>
     <row r="119" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>7</v>
@@ -2923,7 +2929,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>7</v>
@@ -2931,7 +2937,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>7</v>
@@ -2939,7 +2945,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>7</v>
@@ -2947,7 +2953,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>7</v>
@@ -2955,7 +2961,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>7</v>
@@ -2963,7 +2969,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>7</v>
@@ -2971,7 +2977,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>7</v>
@@ -2979,7 +2985,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>7</v>
@@ -2987,7 +2993,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>7</v>
@@ -2995,7 +3001,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>7</v>
@@ -3003,7 +3009,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>7</v>
@@ -3011,7 +3017,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>7</v>
@@ -3019,7 +3025,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>7</v>
@@ -3027,7 +3033,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>7</v>
@@ -3035,7 +3041,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>7</v>
@@ -3043,7 +3049,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>7</v>
@@ -3051,7 +3057,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>7</v>
@@ -3059,7 +3065,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>7</v>
@@ -3067,7 +3073,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>7</v>
@@ -3075,7 +3081,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>7</v>
@@ -3083,7 +3089,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>7</v>
@@ -3091,7 +3097,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>7</v>
@@ -3099,7 +3105,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>7</v>
@@ -3107,7 +3113,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>7</v>
@@ -3115,7 +3121,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>7</v>
@@ -3123,7 +3129,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>7</v>
@@ -3131,7 +3137,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>7</v>
@@ -3139,7 +3145,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>7</v>
@@ -3147,7 +3153,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>7</v>
@@ -3155,7 +3161,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>7</v>
@@ -3163,7 +3169,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>7</v>
@@ -3171,7 +3177,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>7</v>
@@ -3179,7 +3185,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>7</v>
@@ -3187,7 +3193,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>7</v>
@@ -3195,7 +3201,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>7</v>
@@ -3203,7 +3209,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>7</v>
@@ -3211,7 +3217,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>7</v>
@@ -3219,7 +3225,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>7</v>
@@ -3227,7 +3233,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>7</v>
@@ -3235,31 +3241,31 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>7</v>
@@ -3267,7 +3273,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>7</v>
@@ -3275,7 +3281,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>7</v>
@@ -3283,7 +3289,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>7</v>
@@ -3291,55 +3297,55 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>7</v>
@@ -3347,7 +3353,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>7</v>
@@ -3355,7 +3361,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>7</v>
@@ -3363,7 +3369,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>7</v>
@@ -3371,7 +3377,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>7</v>
@@ -3379,7 +3385,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>7</v>
@@ -3387,7 +3393,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>7</v>
@@ -3395,7 +3401,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>7</v>
@@ -3403,47 +3409,47 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>7</v>
@@ -3451,7 +3457,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>7</v>
@@ -3459,7 +3465,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>7</v>
@@ -3467,7 +3473,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>7</v>
@@ -3475,7 +3481,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>7</v>
@@ -3483,7 +3489,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>7</v>
@@ -3491,7 +3497,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>7</v>
@@ -3499,7 +3505,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>7</v>
@@ -3507,7 +3513,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>7</v>
@@ -3515,103 +3521,103 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>7</v>
@@ -3619,7 +3625,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>7</v>
@@ -3627,7 +3633,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>7</v>
@@ -3635,7 +3641,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>7</v>
@@ -3643,7 +3649,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>7</v>
@@ -3651,7 +3657,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>7</v>
@@ -3659,7 +3665,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>7</v>
@@ -3667,7 +3673,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>7</v>
@@ -3675,7 +3681,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>7</v>
@@ -3683,7 +3689,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>7</v>
@@ -3691,7 +3697,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>7</v>
@@ -3699,7 +3705,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>7</v>
@@ -3707,7 +3713,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>7</v>
@@ -3715,7 +3721,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>7</v>
@@ -3723,7 +3729,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>7</v>
@@ -3731,7 +3737,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>7</v>
@@ -3739,7 +3745,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>7</v>
@@ -3747,7 +3753,7 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>7</v>
@@ -3755,7 +3761,7 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>7</v>
@@ -3763,7 +3769,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>7</v>
@@ -3771,7 +3777,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>7</v>
@@ -3836,28 +3842,28 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="2">
+        <v>98111</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="2">
+        <v>98111</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>7</v>
@@ -3871,10 +3877,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -3885,10 +3891,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -3899,10 +3905,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -3913,10 +3919,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -3927,10 +3933,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -3941,10 +3947,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -3955,10 +3961,10 @@
         <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -3969,10 +3975,10 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -3983,10 +3989,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -3997,10 +4003,10 @@
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -4011,10 +4017,10 @@
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -4025,10 +4031,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -4039,10 +4045,10 @@
         <v>5</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -4053,10 +4059,10 @@
         <v>5</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -4067,10 +4073,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -4081,10 +4087,10 @@
         <v>5</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -4095,10 +4101,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -4109,10 +4115,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -4123,10 +4129,10 @@
         <v>5</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -4137,10 +4143,10 @@
         <v>5</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -4151,10 +4157,10 @@
         <v>5</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4165,10 +4171,10 @@
         <v>5</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4179,10 +4185,10 @@
         <v>5</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4193,10 +4199,10 @@
         <v>5</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4207,10 +4213,10 @@
         <v>5</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -4221,10 +4227,10 @@
         <v>5</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -4235,10 +4241,10 @@
         <v>5</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -4249,10 +4255,10 @@
         <v>5</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -4263,10 +4269,10 @@
         <v>5</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -4277,10 +4283,10 @@
         <v>5</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -4291,10 +4297,10 @@
         <v>5</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -4305,10 +4311,10 @@
         <v>5</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -4319,10 +4325,10 @@
         <v>5</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -4333,10 +4339,10 @@
         <v>5</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -4347,10 +4353,10 @@
         <v>5</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4361,10 +4367,10 @@
         <v>5</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4375,10 +4381,10 @@
         <v>5</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4389,10 +4395,10 @@
         <v>5</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4403,10 +4409,10 @@
         <v>5</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -4417,108 +4423,108 @@
         <v>5</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="D50" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="D51" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4529,10 +4535,10 @@
         <v>5</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4543,24 +4549,24 @@
         <v>5</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4571,24 +4577,24 @@
         <v>5</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -4599,21 +4605,21 @@
         <v>5</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>7</v>
@@ -4621,13 +4627,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>7</v>
@@ -4635,13 +4641,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>7</v>
@@ -4655,7 +4661,7 @@
         <v>5</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>7</v>
@@ -4669,7 +4675,7 @@
         <v>5</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>7</v>
@@ -4683,7 +4689,7 @@
         <v>5</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>7</v>
@@ -4697,7 +4703,7 @@
         <v>5</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>7</v>
@@ -4711,7 +4717,7 @@
         <v>5</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>7</v>
@@ -4725,7 +4731,7 @@
         <v>5</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>7</v>
@@ -4739,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>7</v>
@@ -4747,13 +4753,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>7</v>
@@ -4761,13 +4767,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>7</v>
@@ -4775,13 +4781,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>7</v>
@@ -4789,13 +4795,13 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>7</v>
@@ -4809,7 +4815,7 @@
         <v>5</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>7</v>
@@ -4817,13 +4823,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>7</v>
@@ -4837,7 +4843,7 @@
         <v>5</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>7</v>
@@ -4845,13 +4851,13 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>7</v>
@@ -4859,13 +4865,13 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>7</v>
@@ -4873,13 +4879,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>7</v>
@@ -4887,13 +4893,13 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>7</v>
@@ -4901,13 +4907,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>7</v>
@@ -4915,13 +4921,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>7</v>
@@ -4929,13 +4935,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>7</v>
@@ -4943,13 +4949,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>7</v>
@@ -4963,7 +4969,7 @@
         <v>5</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>7</v>
@@ -4977,7 +4983,7 @@
         <v>5</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>7</v>
@@ -4991,7 +4997,7 @@
         <v>5</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>7</v>
@@ -4999,13 +5005,13 @@
     </row>
     <row r="87" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>7</v>
@@ -5013,13 +5019,13 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>7</v>
@@ -5027,13 +5033,13 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>7</v>
@@ -5041,13 +5047,13 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>7</v>
@@ -5055,13 +5061,13 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>7</v>
@@ -5075,7 +5081,7 @@
         <v>5</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>7</v>
@@ -5089,7 +5095,7 @@
         <v>5</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>7</v>
@@ -5097,13 +5103,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>7</v>
@@ -5111,13 +5117,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>7</v>
@@ -5125,13 +5131,13 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>7</v>
@@ -5139,13 +5145,13 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>7</v>
@@ -5153,13 +5159,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>7</v>
@@ -5167,13 +5173,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>209</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>7</v>
@@ -5181,13 +5187,13 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>7</v>
@@ -5195,13 +5201,13 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>7</v>
@@ -5209,13 +5215,13 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>7</v>
@@ -5223,13 +5229,13 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>219</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>7</v>
@@ -5237,13 +5243,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>7</v>
@@ -5251,13 +5257,13 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>7</v>
@@ -5265,13 +5271,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>7</v>
@@ -5279,13 +5285,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>7</v>
@@ -5293,13 +5299,13 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>7</v>
@@ -5307,13 +5313,13 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>7</v>
@@ -5321,13 +5327,13 @@
     </row>
     <row r="110" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>7</v>
@@ -5335,13 +5341,13 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>7</v>
@@ -5349,13 +5355,13 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>7</v>
@@ -5363,13 +5369,13 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>7</v>
@@ -5377,13 +5383,13 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>7</v>
@@ -5391,13 +5397,13 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>7</v>
@@ -5405,13 +5411,13 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>7</v>
@@ -5419,13 +5425,13 @@
     </row>
     <row r="117" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>7</v>
@@ -5433,13 +5439,13 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>7</v>
@@ -5453,7 +5459,7 @@
         <v>5</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>7</v>
@@ -5461,13 +5467,13 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>7</v>
@@ -5475,13 +5481,13 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>7</v>
@@ -5489,13 +5495,13 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>7</v>
@@ -5503,13 +5509,13 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>7</v>
@@ -5517,13 +5523,13 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>7</v>
@@ -5531,13 +5537,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>7</v>
@@ -5545,13 +5551,13 @@
     </row>
     <row r="126" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>277</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>7</v>
@@ -5559,13 +5565,13 @@
     </row>
     <row r="127" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>7</v>
@@ -5573,13 +5579,13 @@
     </row>
     <row r="128" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>7</v>
@@ -5587,13 +5593,13 @@
     </row>
     <row r="129" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>286</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>7</v>
@@ -5601,13 +5607,13 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>7</v>
@@ -5615,13 +5621,13 @@
     </row>
     <row r="131" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>292</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>7</v>
@@ -5629,13 +5635,13 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C132" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>7</v>
@@ -5649,7 +5655,7 @@
         <v>5</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>7</v>
@@ -5663,7 +5669,7 @@
         <v>5</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>7</v>
@@ -5677,7 +5683,7 @@
         <v>5</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>7</v>
@@ -5691,7 +5697,7 @@
         <v>5</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>7</v>
@@ -5705,7 +5711,7 @@
         <v>5</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>7</v>
@@ -5713,13 +5719,13 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>307</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>7</v>
@@ -5727,13 +5733,13 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>7</v>
@@ -5741,13 +5747,13 @@
     </row>
     <row r="140" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>312</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>7</v>
@@ -5755,13 +5761,13 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>314</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>315</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>7</v>
@@ -5775,7 +5781,7 @@
         <v>5</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>7</v>
@@ -5783,13 +5789,13 @@
     </row>
     <row r="143" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C143" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>320</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>7</v>
@@ -5797,13 +5803,13 @@
     </row>
     <row r="144" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C144" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>323</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>7</v>
@@ -5817,7 +5823,7 @@
         <v>5</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>7</v>
@@ -5831,7 +5837,7 @@
         <v>5</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>7</v>
@@ -5845,7 +5851,7 @@
         <v>5</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>7</v>
@@ -5859,7 +5865,7 @@
         <v>5</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>7</v>
@@ -5873,7 +5879,7 @@
         <v>5</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>7</v>
@@ -5881,13 +5887,13 @@
     </row>
     <row r="150" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C150" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>334</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>7</v>
@@ -5895,13 +5901,13 @@
     </row>
     <row r="151" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C151" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>337</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>7</v>
@@ -5915,7 +5921,7 @@
         <v>5</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>7</v>
@@ -5929,7 +5935,7 @@
         <v>5</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>7</v>
@@ -5943,7 +5949,7 @@
         <v>5</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>7</v>
@@ -5957,7 +5963,7 @@
         <v>5</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>7</v>
@@ -5971,7 +5977,7 @@
         <v>5</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>7</v>
@@ -5985,7 +5991,7 @@
         <v>5</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>7</v>
@@ -5999,7 +6005,7 @@
         <v>5</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>7</v>
@@ -6013,49 +6019,49 @@
         <v>5</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C160" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B160" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>356</v>
-      </c>
       <c r="D160" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C161" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B161" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>358</v>
-      </c>
       <c r="D161" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>7</v>
@@ -6063,27 +6069,27 @@
     </row>
     <row r="163" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C163" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B163" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>365</v>
-      </c>
       <c r="D163" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="2">
-        <v>96982</v>
+    <row r="164" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
+        <v>512</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>367</v>
+        <v>513</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>7</v>
@@ -6097,7 +6103,7 @@
         <v>5</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>7</v>
@@ -6111,10 +6117,10 @@
         <v>5</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6125,10 +6131,10 @@
         <v>5</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6139,10 +6145,10 @@
         <v>5</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6153,10 +6159,10 @@
         <v>5</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6167,35 +6173,35 @@
         <v>5</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>7</v>
@@ -6203,13 +6209,13 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>7</v>
@@ -6223,7 +6229,7 @@
         <v>5</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>7</v>
@@ -6231,13 +6237,13 @@
     </row>
     <row r="175" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>7</v>
@@ -6245,13 +6251,13 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>7</v>
@@ -6259,13 +6265,13 @@
     </row>
     <row r="177" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>7</v>
@@ -6279,7 +6285,7 @@
         <v>5</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>7</v>
@@ -6293,7 +6299,7 @@
         <v>5</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>7</v>
@@ -6301,44 +6307,44 @@
     </row>
     <row r="180" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6349,24 +6355,24 @@
         <v>5</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6377,7 +6383,7 @@
         <v>5</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>7</v>
@@ -6385,13 +6391,13 @@
     </row>
     <row r="186" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>7</v>
@@ -6405,7 +6411,7 @@
         <v>5</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>7</v>
@@ -6419,7 +6425,7 @@
         <v>5</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>7</v>
@@ -6433,7 +6439,7 @@
         <v>5</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>7</v>
@@ -6447,7 +6453,7 @@
         <v>5</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>7</v>
@@ -6455,13 +6461,13 @@
     </row>
     <row r="191" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>7</v>
@@ -6469,13 +6475,13 @@
     </row>
     <row r="192" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>7</v>
@@ -6483,13 +6489,13 @@
     </row>
     <row r="193" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>7</v>
@@ -6503,10 +6509,10 @@
         <v>5</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6517,10 +6523,10 @@
         <v>5</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6531,10 +6537,10 @@
         <v>5</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6545,10 +6551,10 @@
         <v>5</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6559,10 +6565,10 @@
         <v>5</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6573,10 +6579,10 @@
         <v>5</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6587,10 +6593,10 @@
         <v>5</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6601,10 +6607,10 @@
         <v>5</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6615,10 +6621,10 @@
         <v>5</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -6629,49 +6635,49 @@
         <v>5</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>7</v>
@@ -6679,13 +6685,13 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>7</v>
@@ -6693,13 +6699,13 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>7</v>
@@ -6707,13 +6713,13 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>7</v>
@@ -6721,13 +6727,13 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>7</v>
@@ -6735,13 +6741,13 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>7</v>
@@ -6749,13 +6755,13 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>7</v>
@@ -6763,13 +6769,13 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>7</v>
@@ -6777,13 +6783,13 @@
     </row>
     <row r="214" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>7</v>
@@ -6791,13 +6797,13 @@
     </row>
     <row r="215" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>7</v>
@@ -6805,13 +6811,13 @@
     </row>
     <row r="216" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>7</v>
@@ -6819,13 +6825,13 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>7</v>
@@ -6839,7 +6845,7 @@
         <v>5</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>7</v>
@@ -6847,13 +6853,13 @@
     </row>
     <row r="219" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>7</v>
@@ -6861,13 +6867,13 @@
     </row>
     <row r="220" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>7</v>
@@ -6881,7 +6887,7 @@
         <v>5</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>7</v>
@@ -6895,7 +6901,7 @@
         <v>5</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>7</v>
@@ -6909,21 +6915,21 @@
         <v>5</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A224" s="2">
-        <v>97052</v>
+      <c r="A224" s="2" t="s">
+        <v>510</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>7</v>
@@ -6931,13 +6937,13 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>7</v>
@@ -6945,19 +6951,20 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABE975F-7A25-4B80-9324-0D0A52B2D592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6722D4D5-EE99-4347-A0EF-1511838306DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="563">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1582,6 +1582,153 @@
   </si>
   <si>
     <t>CONECTOR SPLIT-BOLT, PARA SPDA, PARA CABOS DE 16 A 70 MM2 - FORNECIMENTO E INSTALAÇÃO. AF_08/2023 (COMPOSIÇÃO REFERÊNCIA: SINAPI 96982 01/2026)</t>
+  </si>
+  <si>
+    <t>.S.O.S CAIXA DE PASSAGEM - EMBUTIR NO PISO - Alvenaria - 30x30x30 cm</t>
+  </si>
+  <si>
+    <t>CAIXA ENTERRADA ELÉTRICA RETANGULAR, EM ALVENARIA COM TIJOLOS CERÂMICOS MACIÇOS, FUNDO COM BRITA, DIMENSÕES INTERNAS: 0,4X0,4X0,4 M. AF_12/2020</t>
+  </si>
+  <si>
+    <t>.S.O.S CAIXA DE PASSAGEM - EMBUTIR NO PISO - Alvenaria - 40x40x40 cm</t>
+  </si>
+  <si>
+    <t>.S.O.S CFTV e Segurança - NVR-PoE - 16 câmeras</t>
+  </si>
+  <si>
+    <t>Comp 652</t>
+  </si>
+  <si>
+    <t>NVR INTELBRAS 16 CANAIS FULL HD 1080P 2MP (COMPOSIÇÃO DE REFERÊNCIA: 068414 SBC 07/2024)</t>
+  </si>
+  <si>
+    <t>.S.O.S EQUIPAMENTOS DE TELECOMUNICAÇÕES - CABEAMENTO WIFI - Repetidor</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Bloco conexão - 110 IDC - 100 pares</t>
+  </si>
+  <si>
+    <t>Comp 532</t>
+  </si>
+  <si>
+    <t>BLOCO CONEXÃO - 110 IDC - 100 PARES (COMPOSIÇÃO DE REFERÊNCIA: SBC 059427 - 05/2023)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Conector - RJ45 - Blindado</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Plugue - RJ45 - CM8v</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Switch - 10/100 - BaseTX - 24 portas</t>
+  </si>
+  <si>
+    <t>Comp 1612</t>
+  </si>
+  <si>
+    <t>SWITCH 24 - PORTAS (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Rack - Bandeja de ventilação 1U - Kit 2 ventiladores - 400W</t>
+  </si>
+  <si>
+    <t>Comp 906</t>
+  </si>
+  <si>
+    <t>BANDEJA DE VENTILAÇÃO 1U COM 4 VENTILADORES - 400W. (REFERÊNCIA: SETOP ED-48376 10/2024)</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 1.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 1.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 1.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 1.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 1.5 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 1,5 MM², ANTI-CHAMA 450/750 V, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 2.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 2.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 2.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 2.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 2.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 2.5 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 2,5 MM², ANTI-CHAMA 450/750 V, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 4 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 4 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 4 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 4 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 4 MM², ANTI-CHAMA 450/750 V, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 16 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 16 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 16 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 16 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 16 MM², ANTI-CHAMA 450/750 V, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabo - Plugue - Plugue fêmea</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - metálico - UTP-5e - 24AWG - 4</t>
+  </si>
+  <si>
+    <t>CABO ELETRÔNICO CATEGORIA 5E, INSTALADO EM EDIFICAÇÃO INSTITUCIONAL - FORNECIMENTO E INSTALAÇÃO. AF_08/2025</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 16 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 25 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 25 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 25 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 25 mm² - Vermelho</t>
   </si>
 </sst>
 </file>
@@ -1968,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B226"/>
+  <dimension ref="A1:B261"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -3783,6 +3930,286 @@
         <v>7</v>
       </c>
     </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3790,7 +4217,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D226"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -6963,6 +7390,496 @@
         <v>7</v>
       </c>
     </row>
+    <row r="227" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A227" s="2">
+        <v>97886</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A228" s="2">
+        <v>97887</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A231" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A232" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A233" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A234" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A235" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A236" s="2">
+        <v>91924</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A237" s="2">
+        <v>91924</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A238" s="2">
+        <v>91924</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A239" s="2">
+        <v>91924</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A240" s="2">
+        <v>91924</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A241" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A242" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A243" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A244" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A245" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A246" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A247" s="2">
+        <v>91928</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A248" s="2">
+        <v>91928</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A249" s="2">
+        <v>91928</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A250" s="2">
+        <v>91928</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A251" s="2">
+        <v>91934</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A252" s="2">
+        <v>91934</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A253" s="2">
+        <v>91934</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A254" s="2">
+        <v>91934</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A255" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A256" s="2">
+        <v>98295</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A257" s="2">
+        <v>91935</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A258" s="2">
+        <v>92984</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A259" s="2">
+        <v>92984</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A260" s="2">
+        <v>92984</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A261" s="2">
+        <v>92984</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6722D4D5-EE99-4347-A0EF-1511838306DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF5DA64-1357-4529-95CF-3004EFE2086B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="620">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1729,6 +1729,177 @@
   </si>
   <si>
     <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 25 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - METROS - ELETRODUTO FLEXÍVEL CORRUGADO, 1", INSTALADO NO PISO</t>
+  </si>
+  <si>
+    <t>Comp 847</t>
+  </si>
+  <si>
+    <t>ELETRODUTO FLEXÍVEL CORRUGADO, 1", INSTALADO NO PISO (COMPOSIÇÃO DE REFERÊNCIA: FDE 16.20.113 - 04/2022)</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - TOMADA DE PISO 4X4 LATÃO, COM CAIXA E 2 MÓDULOS</t>
+  </si>
+  <si>
+    <t>Comp 922</t>
+  </si>
+  <si>
+    <t>TOMADA RJ45, 2 MÓDULOS,  INSTALADA NO PISO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA:ORSE  13604 - 11/2024)</t>
+  </si>
+  <si>
+    <t>Comp 528</t>
+  </si>
+  <si>
+    <t>PAINEL MODULAR -300X400mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>- Quadro distrib. - PAINÉIS - 300X400X200</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - INTERRUPTOR PARALELO - 1 MÓDULO - , 10A/250V, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - INTERRUPTOR PARALELO - 2 MÓDULOS - , 10A/250V, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - INTERRUPTOR PARALELO - 3 MÓDULOS - , 10A/250V, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>INTERRUPTOR PARALELO (3 MÓDULOS), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - INTERRUPTOR SIMPLES - 1 MÓDULO - , 10A/250V, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - INTERRUPTOR SIMPLES - 1 MÓDULO - COM INTERRUPTOR PARALELO - 1 MÓDULO - , 10A/250V, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - INTERRUPTOR SIMPLES - 2 MÓDULOS - , 10A/250V, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - INTERRUPTOR SIMPLES - 3 MÓDULOS - , 10A/250V, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - INTERRUPTOR SIMPLES - 4 MÓDULOS - , 10A/250V, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>INTERRUPTOR SIMPLES (4 MÓDULOS), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - TOMADA ALTA DE EMBUTIR - 1 MÓDULO - , 2P+T 10 A, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - TOMADA BAIXA DE EMBUTIR - 1 MÓDULO - , 2P+T 10 A, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - TOMADA BAIXA DE EMBUTIR - 2 MÓDULOS - , 2P+T 10 A, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>- SINAPI - UNIDADES - TOMADA MÉDIA DE EMBUTIR - 1 MÓDULO - , 2P+T 10 A, INCLUINDO SUPORTE E PLACA</t>
+  </si>
+  <si>
+    <t>.S.O.S EQUIPAMENTOS DE TELECOMUNICAÇÕES - Rack PADRÃO - RACK PADRÃO 19”, 42U X 600 MM - LARGURA - X 1100 MM - PROFUNDIDADE - , COM PORTA PERFURADA, IP20, COM CAPACIDADE MÍNIMA PARA 1.000 KG DE CARGA DINÂMICA.</t>
+  </si>
+  <si>
+    <t>Comp 537</t>
+  </si>
+  <si>
+    <t>RACK ABERTO PADRÃO 19" 42U  (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>.S.O.S QUADROS ELÉTRICOS - QUADROS - Painel modular 1900x800x600mm</t>
+  </si>
+  <si>
+    <t>Comp 138</t>
+  </si>
+  <si>
+    <t>PAINEL MODULAR -1900x800x600mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Switch - 10/100 - BaseTX + - 10/100/1000 - Base T - 8 + 2 - portas</t>
+  </si>
+  <si>
+    <t>Comp 338</t>
+  </si>
+  <si>
+    <t>SWITCH 8 + 2 - PORTAS (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Rack - Bandeja de ventilação 1U - Kit 4 ventiladores - 400W</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Caixa alumínio 4"x2" - Contulete múltiplo X - 3/4"</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo LL - 3/4" sem tampa</t>
+  </si>
+  <si>
+    <t>Comp 1631</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO LL, PARA ELETRODUTO DE AÇO GALVANIZADO DN 20 MM (3/4"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022 (COMPOSIÇÃO REFERÊNCIA: SINAPI 95786 08/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Caixa PVC octogonal - 4x4"</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Curva horizontal 45° - 38x38mm</t>
+  </si>
+  <si>
+    <t>Comp 521</t>
+  </si>
+  <si>
+    <t>CURVA HORIZONTAL 45° PARA PERFILADOS PERFURADOS 38x38mm (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Cotovelo reto - 38x38mm</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Acessórios para Perfilados - Saída lateral simples</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Acessórios para Perfilados - Saída dupla para eletroduto</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Curva vertical interna 90° - 38x38mm</t>
+  </si>
+  <si>
+    <t>Comp 697</t>
+  </si>
+  <si>
+    <t>CURVA VERTICAL INTERNA 90° PARA PERFILADOS PERFURADOS 38x38mm (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Acessórios uso geral - Outros - Barramento para 1600A</t>
+  </si>
+  <si>
+    <t>Comp 860</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE PARA 1600A - (COMPOSIÇÃO DE REFERÊNCIA: 9006083 SIURB 07/2024)</t>
+  </si>
+  <si>
+    <t>Acessórios uso geral - Outros - Barramento para 630A</t>
+  </si>
+  <si>
+    <t>Comp 899</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE PARA 630A. (REFERÊNCIA: SIURB 9006079 07/2024)</t>
+  </si>
+  <si>
+    <t>Acessórios uso geral - Outros - FIXADOR OMEGA LATÃO CABO 35MM2 FURO 5MM TEL733</t>
+  </si>
+  <si>
+    <t>Acessórios uso geral - Outros - Kit barramento trifásico 300A</t>
+  </si>
+  <si>
+    <t>Comp 1427</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE TRIFASICO 300A (REFERÊNCIA: SIURB 9006079 07/2024)</t>
   </si>
 </sst>
 </file>
@@ -2115,7 +2286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B261"/>
+  <dimension ref="A1:B292"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -4210,6 +4381,254 @@
         <v>20</v>
       </c>
     </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4217,7 +4636,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D261"/>
+  <dimension ref="A1:D292"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -7880,6 +8299,440 @@
         <v>20</v>
       </c>
     </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A262" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A263" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A264" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A265" s="2">
+        <v>91955</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A266" s="2">
+        <v>91961</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A267" s="2">
+        <v>91969</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A268" s="2">
+        <v>91953</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A269" s="2">
+        <v>91957</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A270" s="2">
+        <v>91959</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A271" s="2">
+        <v>91967</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A272" s="2">
+        <v>91975</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A273" s="2">
+        <v>91992</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A274" s="2">
+        <v>92000</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A275" s="2">
+        <v>92008</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A276" s="2">
+        <v>91996</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A277" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A278" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A279" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A280" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A281" s="2">
+        <v>95801</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A282" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A283" s="2">
+        <v>91936</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A284" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A285" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A286" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B286" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A287" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A288" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C288" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A289" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C289" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A290" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C290" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A291" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A292" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF5DA64-1357-4529-95CF-3004EFE2086B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DADB26D-51DC-4F57-8D8A-035A62D19F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="689">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1900,6 +1900,213 @@
   </si>
   <si>
     <t>BARRAMENTO DE COBRE TRIFASICO 300A (REFERÊNCIA: SIURB 9006079 07/2024)</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 10mm</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 150mm</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 16mm</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 185mm</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 25mm</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 35mm</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 6mm</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 70mm</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 95mm</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 150 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 185 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 1.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 1.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 1.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 1.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 10 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 10 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 10 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 10 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 10 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 150 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 150 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 150 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 150 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 16 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 16 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 16 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 16 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 185 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 185 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 185 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 185 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 2.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 2.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 2.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 2.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 2.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 2.5 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 25 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 35 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 35 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 35 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 35 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 35 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 4 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 4 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 4 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 4 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 4 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 50 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 50 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 50 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 6 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 6 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 6 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 6 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 6 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 70 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 70 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 70 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 70 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 95 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 6 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 6 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 6 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 6 MM², ANTI-CHAMA 450/750 V, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Caixa de passagem - embutir - PVC - 15x15cm</t>
+  </si>
+  <si>
+    <t>Comp 1020</t>
+  </si>
+  <si>
+    <t>CAIXA DE PASSAGEM 15X15X10CM, FORNECIMENTO E INSTALACAO. (COMPOSIÇÃO REFERÊNCIA SINAPI COD: 100556 02/2025)</t>
   </si>
 </sst>
 </file>
@@ -2286,7 +2493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B292"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -4629,6 +4836,518 @@
         <v>7</v>
       </c>
     </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A350" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A351" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A352" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A353" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A354" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4636,7 +5355,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D292"/>
+  <dimension ref="A1:D356"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -8733,6 +9452,902 @@
         <v>7</v>
       </c>
     </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A293" s="2">
+        <v>91933</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A294" s="2">
+        <v>92996</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A295" s="2">
+        <v>91935</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A296" s="2">
+        <v>92998</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A297" s="2">
+        <v>92984</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A298" s="2">
+        <v>92986</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C298" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A299" s="2">
+        <v>91931</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A300" s="2">
+        <v>92990</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A301" s="2">
+        <v>92992</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A302" s="2">
+        <v>91925</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C302" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A303" s="2">
+        <v>91925</v>
+      </c>
+      <c r="B303" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C303" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A304" s="2">
+        <v>91925</v>
+      </c>
+      <c r="B304" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C304" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A305" s="2">
+        <v>91925</v>
+      </c>
+      <c r="B305" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C305" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A306" s="2">
+        <v>91933</v>
+      </c>
+      <c r="B306" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A307" s="2">
+        <v>91933</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A308" s="2">
+        <v>91933</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C308" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A309" s="2">
+        <v>91933</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A310" s="2">
+        <v>91933</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A311" s="2">
+        <v>92996</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A312" s="2">
+        <v>92996</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C312" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A313" s="2">
+        <v>92996</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A314" s="2">
+        <v>92996</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A315" s="2">
+        <v>91935</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C315" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A316" s="2">
+        <v>91935</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C316" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A317" s="2">
+        <v>91935</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A318" s="2">
+        <v>91935</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C318" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A319" s="2">
+        <v>92998</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C319" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A320" s="2">
+        <v>92998</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C320" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A321" s="2">
+        <v>92998</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C321" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A322" s="2">
+        <v>92998</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C322" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A323" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C323" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A324" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C324" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A325" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C325" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A326" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A327" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C327" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A328" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B328" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C328" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A329" s="2">
+        <v>92984</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C329" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A330" s="2">
+        <v>92986</v>
+      </c>
+      <c r="B330" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C330" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A331" s="2">
+        <v>92986</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C331" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A332" s="2">
+        <v>92986</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A333" s="2">
+        <v>92986</v>
+      </c>
+      <c r="B333" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C333" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A334" s="2">
+        <v>92986</v>
+      </c>
+      <c r="B334" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C334" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A335" s="2">
+        <v>91929</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C335" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A336" s="2">
+        <v>91929</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C336" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A337" s="2">
+        <v>91929</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C337" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A338" s="2">
+        <v>91929</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A339" s="2">
+        <v>91929</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A340" s="2">
+        <v>92988</v>
+      </c>
+      <c r="B340" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C340" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A341" s="2">
+        <v>92988</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A342" s="2">
+        <v>92988</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C342" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A343" s="2">
+        <v>91931</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C343" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A344" s="2">
+        <v>91931</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C344" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A345" s="2">
+        <v>91931</v>
+      </c>
+      <c r="B345" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A346" s="2">
+        <v>91931</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C346" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A347" s="2">
+        <v>91931</v>
+      </c>
+      <c r="B347" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C347" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A348" s="2">
+        <v>92990</v>
+      </c>
+      <c r="B348" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A349" s="2">
+        <v>92990</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A350" s="2">
+        <v>92990</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A351" s="2">
+        <v>92990</v>
+      </c>
+      <c r="B351" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A352" s="2">
+        <v>92992</v>
+      </c>
+      <c r="B352" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A353" s="2">
+        <v>91930</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A354" s="2">
+        <v>91930</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A355" s="2">
+        <v>91930</v>
+      </c>
+      <c r="B355" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A356" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DADB26D-51DC-4F57-8D8A-035A62D19F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F386CF7D-FACC-4C90-A453-3CC943A5FDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="707">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2107,6 +2107,60 @@
   </si>
   <si>
     <t>CAIXA DE PASSAGEM 15X15X10CM, FORNECIMENTO E INSTALACAO. (COMPOSIÇÃO REFERÊNCIA SINAPI COD: 100556 02/2025)</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto leve - 3/4" - Piso</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Eletrocalha perfurada tipo U - 400x100mm chapa 16</t>
+  </si>
+  <si>
+    <t>Comp 136</t>
+  </si>
+  <si>
+    <t>ELETROCALHA LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA 400 E ALTURA 100MM E , INCLUSIVE FIXAÇÃO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: 062702 SBC 05/2024)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Eletrocalha perfurada tipo U - 150x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 1345</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ELETROCALHA LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA 150 E ALTURA 100MM E , INCLUSIVE FIXAÇÃO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: 060106 SBC 05/2024))</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Suporte vertical - 120x160mm</t>
+  </si>
+  <si>
+    <t>Comp 795</t>
+  </si>
+  <si>
+    <t>SUPORTE VERTICAL 120X160MM -  (COMPOSIÇÃO  DE  REFERÊNCIA:  SINAPI  97274  -  09/2022)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 220 V/127 V - DIN - Curva C - 32 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 380 V/220 V - DIN - Curva C - 20 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 20A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 16 A - 4,5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 16A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 800 A - 50 kA</t>
+  </si>
+  <si>
+    <t>Comp 834</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 800A, 50kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
   </si>
 </sst>
 </file>
@@ -2493,7 +2547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B364"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -4644,7 +4698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
         <v>577</v>
       </c>
@@ -4708,7 +4762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
         <v>586</v>
       </c>
@@ -5345,6 +5399,70 @@
         <v>686</v>
       </c>
       <c r="B356" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A359" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="B364" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -5355,7 +5473,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D356"/>
+  <dimension ref="A1:D364"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -8486,7 +8604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>510</v>
       </c>
@@ -8962,7 +9080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A258" s="2">
         <v>92984</v>
       </c>
@@ -9466,7 +9584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A294" s="2">
         <v>92996</v>
       </c>
@@ -9494,7 +9612,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A296" s="2">
         <v>92998</v>
       </c>
@@ -9508,7 +9626,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A297" s="2">
         <v>92984</v>
       </c>
@@ -9522,7 +9640,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A298" s="2">
         <v>92986</v>
       </c>
@@ -9550,7 +9668,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A300" s="2">
         <v>92990</v>
       </c>
@@ -9564,7 +9682,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A301" s="2">
         <v>92992</v>
       </c>
@@ -9704,7 +9822,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A311" s="2">
         <v>92996</v>
       </c>
@@ -9718,7 +9836,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A312" s="2">
         <v>92996</v>
       </c>
@@ -9732,7 +9850,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A313" s="2">
         <v>92996</v>
       </c>
@@ -9746,7 +9864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A314" s="2">
         <v>92996</v>
       </c>
@@ -9816,7 +9934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A319" s="2">
         <v>92998</v>
       </c>
@@ -9830,7 +9948,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A320" s="2">
         <v>92998</v>
       </c>
@@ -9844,7 +9962,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A321" s="2">
         <v>92998</v>
       </c>
@@ -9858,7 +9976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A322" s="2">
         <v>92998</v>
       </c>
@@ -9970,7 +10088,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A330" s="2">
         <v>92986</v>
       </c>
@@ -10222,7 +10340,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A348" s="2">
         <v>92990</v>
       </c>
@@ -10345,6 +10463,118 @@
         <v>688</v>
       </c>
       <c r="D356" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A357" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A358" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A359" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B359" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A360" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B360" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A361" s="2">
+        <v>93664</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A362" s="2">
+        <v>93669</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C362" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A363" s="2">
+        <v>93668</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A364" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="D364" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F386CF7D-FACC-4C90-A453-3CC943A5FDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7BDA6B-4576-401C-AAF9-74A5FBA30CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="746">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2161,6 +2161,123 @@
   </si>
   <si>
     <t>DISJUNTOR CAIXA MOLDADA 800A, 50kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Fita Led 24V - ALL LIGHT 24V PRO 8W/m</t>
+  </si>
+  <si>
+    <t>Comp 1309</t>
+  </si>
+  <si>
+    <t>FITA DE LED SLIM 8W, 180 LEDS, 12V IP20, TONALIDADE DA LUZ NEUTRA/QUENTE (REFERÊNCIA: AGESUL1201001009 06/2024)</t>
+  </si>
+  <si>
+    <t>Eletrocalha Aramada - Eletrocalha Aramada Ac Ge - 100x105mm</t>
+  </si>
+  <si>
+    <t>Comp 1326</t>
+  </si>
+  <si>
+    <t>ELETROCALHA ARAMADA AI304 100x105MM (REFERÊNCIA: SBC 063566 01/2025)</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Sobrepor - Ledvance Livin 32W</t>
+  </si>
+  <si>
+    <t>Comp 37</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA LED SOBREPOR LEDVANCE LIVIN 32W (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 103782 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Sobrepor - Ledvance Livin 18W</t>
+  </si>
+  <si>
+    <t>Comp 1630</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA LED SOBREPOR LEDVANCE LIVIN 18W (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 103782 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto pesado - 1.1/2" - Forro</t>
+  </si>
+  <si>
+    <t>Comp 1346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELETRODUTO FLEXÍVEL CORRUGADO, PEAD, DN 50 (1 1/2"), FORRO - FORNECIMENTO E INSTALAÇÃO. AF_12/2021 (COMPOSIÇÃO REFERÊNCIA: Copia da SINAPI 97667) </t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Sobrepor - Ledvance Livin 24W</t>
+  </si>
+  <si>
+    <t>Comp 1585</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA TIPO PLAFON QUADRADA, DE SOBREPOR, COM LED DE 24 W - FORNECIMENTO E INSTALAÇÃO. ( COMPOSIÇÃO REFERÊNCIA SINAPI CÓD. 103785 05/2025)</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Par 30 - 11W</t>
+  </si>
+  <si>
+    <t>Comp 1473</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA TIPO SPOT PAR 30, DE EMBUTIR, COM LED DE 11W - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: SINAPI 103782 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Fonte automática - ULTRAFINA 24V DE 48W - STELLA</t>
+  </si>
+  <si>
+    <t>Comp 1047</t>
+  </si>
+  <si>
+    <t>FONTE DE ALIMENTACAO P/ FITA LED, ULTRAFINA 24V DE 48W - STELLA (REFERÊNCIA: SBC 060563 04/2025 )</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Terminal - 400x100mm chapa 16</t>
+  </si>
+  <si>
+    <t>Comp 462</t>
+  </si>
+  <si>
+    <t>TERMINAL 400 X 100 PARA ELETROCALHA (COMPOSIÇÃO REFERÊNCIA: 12611 ORSE 05/23)</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Hermética - 2x18W</t>
+  </si>
+  <si>
+    <t>Comp 1323</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA HERMÉTICA TUBULAR LED 2x18W IP66 LUZ BRANCA (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 103782 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Sobrepor - Ledvance Panel 40W - 6500K</t>
+  </si>
+  <si>
+    <t>Comp 1540</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA LED SOBREPOR LEDVANCE LIVIN 40W (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 103782 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Suporte vertical - 120x233mm</t>
+  </si>
+  <si>
+    <t>Comp 1063</t>
+  </si>
+  <si>
+    <t>SUPORTE VERTICAL - 120X233MM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto pesado - 2" - Piso</t>
+  </si>
+  <si>
+    <t>ELETRODUTO FLEXÍVEL CORRUGADO, PEAD, DN 63 (2"), PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>CONECTOR  MACHO, PARA RJ45  CAT 6 - REF. SBC (061359)</t>
   </si>
 </sst>
 </file>
@@ -2547,7 +2664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B364"/>
+  <dimension ref="A1:B377"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -5466,6 +5583,110 @@
         <v>7</v>
       </c>
     </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A365" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A366" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A375" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -5473,7 +5694,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D364"/>
+  <dimension ref="A1:D377"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -8738,7 +8959,7 @@
         <v>68</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>271</v>
+        <v>745</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>7</v>
@@ -10576,6 +10797,188 @@
       </c>
       <c r="D364" s="2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A365" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C365" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A366" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B366" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C366" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A367" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B367" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A368" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B368" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C368" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A369" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B369" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C369" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A370" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B370" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C370" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A371" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B371" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C371" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A372" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B372" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C372" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A373" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B373" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C373" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A374" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B374" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A375" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="B375" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C375" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A376" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B376" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C376" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A377" s="2">
+        <v>97668</v>
+      </c>
+      <c r="B377" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C377" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7BDA6B-4576-401C-AAF9-74A5FBA30CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9A4A48-D39F-4662-A602-EB5B39987F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="755">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2278,6 +2278,33 @@
   </si>
   <si>
     <t>CONECTOR  MACHO, PARA RJ45  CAT 6 - REF. SBC (061359)</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto leve - 1" - Forro</t>
+  </si>
+  <si>
+    <t>ELETRODUTO FLEXÍVEL CORRUGADO, PEAD, DN 32 MM (1"), PARA CIRCUITOS TERMINAIS, INSTALADO EM FORRO - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - óptico - Cabo ótico - interna - 1</t>
+  </si>
+  <si>
+    <t>Eletrocalha lisa tipo C pré-galv. quente - Eletrocalha lisa tipo C - 100x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto leve - 1" - Piso</t>
+  </si>
+  <si>
+    <t>Cabos Telefônicos - CCI - 50 - CCI - 50 - 2</t>
+  </si>
+  <si>
+    <t>CABO TELEFÔNICO CCI-50 2 PARES, SEM BLINDAGEM, INSTALADO EM DISTRIBUIÇÃO DE EDIFICAÇÃO INSTITUCIONAL - FORNECIMENTO E INSTALAÇÃO. AF_08/2025</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto pesado - 1.1/2"</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto pesado - 4" - Forro</t>
   </si>
 </sst>
 </file>
@@ -2664,7 +2691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B386"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -5687,6 +5714,78 @@
         <v>20</v>
       </c>
     </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B380" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A381" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A382" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A383" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A384" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A385" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A386" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -5694,7 +5793,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D377"/>
+  <dimension ref="A1:D386"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -10981,6 +11080,132 @@
         <v>20</v>
       </c>
     </row>
+    <row r="378" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A378" s="2">
+        <v>91838</v>
+      </c>
+      <c r="B378" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C378" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A379" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B379" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C379" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A380" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B380" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C380" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D380" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A381" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B381" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C381" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A382" s="2">
+        <v>98288</v>
+      </c>
+      <c r="B382" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C382" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="D382" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A383" s="2">
+        <v>91836</v>
+      </c>
+      <c r="B383" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C383" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A384" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B384" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C384" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A385" s="2">
+        <v>97667</v>
+      </c>
+      <c r="B385" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C385" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A386" s="2">
+        <v>97670</v>
+      </c>
+      <c r="B386" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C386" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9A4A48-D39F-4662-A602-EB5B39987F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C18993-A8DB-4744-A2DA-012657077BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2205" uniqueCount="792">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2305,6 +2305,117 @@
   </si>
   <si>
     <t>Eletroduto PVC flexível - Eletroduto pesado - 4" - Forro</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto pesado - 2"</t>
+  </si>
+  <si>
+    <t>Eletroduto metálico rígido leve - Eletroduto galvanizado, vara 3,0m - 1.1/2"</t>
+  </si>
+  <si>
+    <t>Dispositivo Telefônico - embutir - Tomada - Tomada RJ11</t>
+  </si>
+  <si>
+    <t>TOMADA PARA TELEFONE RJ11 - FORNECIMENTO E INSTALAÇÃO. AF_08/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva B - 16 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Unipolar Termomagnético - norma DIN - Curva C - 20 A - 3 kA</t>
+  </si>
+  <si>
+    <t>Caixa de passagem - embutir - Aço pintada - ref Lukbox - 100x100x80 mm</t>
+  </si>
+  <si>
+    <t>Dispositivo de Comando - Contator com bobina 127V - Unipolar - NA+NF</t>
+  </si>
+  <si>
+    <t>Comp 1056</t>
+  </si>
+  <si>
+    <t>CONTATOR DE POTÊNCIA DE RELE AUXILIAR MONOPOLAR 110V/127V (COMPOSIÇÃO DE REFERÊNCIA: 063746 SINAPI 03/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva C - 20 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 32 A - 3 kA</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Luminária Pública - Lâmpada 150W</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA DE LED PARA ILUMINAÇÃO PÚBLICA, DE 138 W ATÉ 180 W - FORNECIMENTO E INSTALAÇÃO. AF_02/2025_PS</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - T horizontal 90° - 400x100mm chapa 16</t>
+  </si>
+  <si>
+    <t>Comp 464</t>
+  </si>
+  <si>
+    <t>TE HORIZONTAL PARA ELETROCALHA 400X100MM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97315 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Acessórios para telefonia - Bloco terminal BLI - BLI-10</t>
+  </si>
+  <si>
+    <t>Comp 538</t>
+  </si>
+  <si>
+    <t>BLOCO TERMINAL TELEFONICO BLI-10 C/CANALETA DE MONTAGEM (COMPOSIÇÃO DE REFERÊNCIA: SBC 059220 - 05/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Unipolar Termomagnético - norma DIN - Curva C - 25 A - 3 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR MONOPOLAR TIPO DIN, CORRENTE NOMINAL DE 25A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva C - 32 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, - DIN - Ref. Moratori - Cap. 70 disj. unip. - In barr. 225 A</t>
+  </si>
+  <si>
+    <t>Comp 1058</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, COM BARRAMENTO TRIFÁSICO, PARA 70 DISJUNTORES DIN 225A - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REF.  101879 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>Rack - Aberto padrão - 19" - 16U</t>
+  </si>
+  <si>
+    <t>.S.O.S TELEFONIA - PABX - Para Quadro de distribuição e com 8 ramais analógicos - modelo de acordo com cliente</t>
+  </si>
+  <si>
+    <t>Comp 1419</t>
+  </si>
+  <si>
+    <t>CENTRAL PABX INTELBRAS IMPACTA 220 - (COMPOSIÇÃO REFERÊNCIA: SBC 067395 -  08/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 125A - 10 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 90A - 10 kA</t>
+  </si>
+  <si>
+    <t>Comp 526</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 90A - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 93673 - 04/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 1600 A - 50 kA</t>
+  </si>
+  <si>
+    <t>Comp 386</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 1600A, 60kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
   </si>
 </sst>
 </file>
@@ -2691,7 +2802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B386"/>
+  <dimension ref="A1:B406"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -5786,6 +5897,166 @@
         <v>20</v>
       </c>
     </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A387" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A388" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A389" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A390" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="B390" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A391" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="B391" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A392" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="B392" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A393" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A394" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A395" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A396" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A397" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A398" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A399" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A400" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A401" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A402" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A403" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A404" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A405" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A406" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -5793,7 +6064,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D386"/>
+  <dimension ref="A1:D406"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -11206,6 +11477,286 @@
         <v>20</v>
       </c>
     </row>
+    <row r="387" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A387" s="2">
+        <v>97668</v>
+      </c>
+      <c r="B387" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A388" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B388" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C388" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A389" s="2">
+        <v>98308</v>
+      </c>
+      <c r="B389" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C389" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="D389" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A390" s="2">
+        <v>93661</v>
+      </c>
+      <c r="B390" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C390" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D390" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A391" s="2">
+        <v>93655</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D391" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A392" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D392" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A393" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B393" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C393" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="D393" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A394" s="2">
+        <v>93662</v>
+      </c>
+      <c r="B394" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C394" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D394" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A395" s="2">
+        <v>93671</v>
+      </c>
+      <c r="B395" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C395" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D395" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A396" s="2">
+        <v>101658</v>
+      </c>
+      <c r="B396" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C396" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="D396" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A397" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B397" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="D397" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A398" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B398" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C398" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="D398" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A399" s="2">
+        <v>93656</v>
+      </c>
+      <c r="B399" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A400" s="2">
+        <v>93664</v>
+      </c>
+      <c r="B400" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C400" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D400" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A401" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B401" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C401" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="D401" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A402" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B402" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C402" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D402" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A403" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B403" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C403" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="D403" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A404" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B404" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C404" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D404" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A405" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B405" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C405" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="D405" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A406" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B406" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C406" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="D406" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C18993-A8DB-4744-A2DA-012657077BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703B9762-620E-4070-B305-CA1E7B73CAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2205" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="804">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2416,6 +2416,42 @@
   </si>
   <si>
     <t>DISJUNTOR CAIXA MOLDADA 1600A, 60kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Transformador - Transformador - Transformador de corrente 1600/5A</t>
+  </si>
+  <si>
+    <t>Comp 438</t>
+  </si>
+  <si>
+    <t>TRANSFORMADOR DE CORRENTE 1600/5A (COMPOSIÇÃO DE REFERÊNCIA: C2520 - SEINFRA 028)</t>
+  </si>
+  <si>
+    <t>Transformador - Transformador - Transformador de corrente 800/5A</t>
+  </si>
+  <si>
+    <t>Comp 439</t>
+  </si>
+  <si>
+    <t>TRANSFORMADOR DE CORRENTE 800/5A (COMPOSIÇÃO DE REFERÊNCIA: C2519 - SEINFRA 028)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. plástico - sobrepor - Barr. bif., - DIN - Ref. Hager - Cap. 12 disj. unip. - In Pente 63A</t>
+  </si>
+  <si>
+    <t>Comp 991</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM PVC, DE SOBREPOR, COM BARRAMENTO TRIFÁSICO, PARA 12 DISJUNTORES DIN 63A (REFERÊNCIA 101878 12/2024)</t>
+  </si>
+  <si>
+    <t>Acessórios uso geral - Outros - Barramento para 800A</t>
+  </si>
+  <si>
+    <t>Comp 789</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE PARA 800A. (REFERÊNCIA: SIURB 9006079 07/2024)</t>
   </si>
 </sst>
 </file>
@@ -2802,7 +2838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B406"/>
+  <dimension ref="A1:B410"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -6057,6 +6093,38 @@
         <v>7</v>
       </c>
     </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A407" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A408" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A409" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A410" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6064,7 +6132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D406"/>
+  <dimension ref="A1:D410"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -11757,6 +11825,62 @@
         <v>7</v>
       </c>
     </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A407" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B407" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C407" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="D407" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A408" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B408" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C408" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="D408" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A409" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B409" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C409" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="D409" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A410" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C410" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="D410" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703B9762-620E-4070-B305-CA1E7B73CAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67429BE-BE2F-4C15-8C1F-E60E12388063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2353" uniqueCount="846">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2452,6 +2452,132 @@
   </si>
   <si>
     <t>BARRAMENTO DE COBRE PARA 800A. (REFERÊNCIA: SIURB 9006079 07/2024)</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 240 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 240 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 240 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 240 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 240 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 120 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 120 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 120 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 120 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 120 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 70 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 50 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Canaleta de Concreto - Pré moldada - 300x300mm</t>
+  </si>
+  <si>
+    <t>CANALETA MEIA CANA PRÉ-MOLDADA DE CONCRETO (D = 30 CM) - FORNECIMENTO E INSTALAÇÃO. AF_05/2025</t>
+  </si>
+  <si>
+    <t>CANALETA MEIA CANA PRÉ-MOLDADA DE CONCRETO (D = 40 CM) - FORNECIMENTO E INSTALAÇÃO. AF_05/2025</t>
+  </si>
+  <si>
+    <t>Canaleta de Concreto - Pré moldada - 400x400mm</t>
+  </si>
+  <si>
+    <t>Eletroduto metálico rígido pesado - Eletroduto galvanizado - 4"</t>
+  </si>
+  <si>
+    <t>Comp 859</t>
+  </si>
+  <si>
+    <t>ELETRODUTO EM AÇO GALVANIZADO A FOGO DIÂMETRO 4" - (COMPOSIÇÃO DE REFERÊNCIA: 071258 AGETOP CIVIL 08/2024)</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto pesado - 4"</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 50 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 1084</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 50A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 500 A - 65 kA</t>
+  </si>
+  <si>
+    <t>Comp 1395</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 500A, 35kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 63 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 863</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 63A, 5kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: ORSE 9687 - 09/2024)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 100 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 1535</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 100A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 125 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 1080</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 125A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 20 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 2023</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 20A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 80 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 1661</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 80A, 5kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: ORSE 9687 - 09/2024)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 800 A - 65 kA</t>
   </si>
 </sst>
 </file>
@@ -2838,7 +2964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B433"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -6125,6 +6251,190 @@
         <v>7</v>
       </c>
     </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A411" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A412" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A413" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A414" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A415" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A416" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A417" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A418" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A419" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A420" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A421" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A422" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A423" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A424" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A425" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A426" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A427" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A428" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="B428" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A429" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A430" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A431" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A432" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A433" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6132,11 +6442,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D410"/>
+  <dimension ref="A1:D433"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="121.21875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="2"/>
   </cols>
@@ -6145,7 +6455,7 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -6159,7 +6469,7 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -6173,7 +6483,7 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -6187,7 +6497,7 @@
       <c r="A4" s="2">
         <v>98111</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -6201,7 +6511,7 @@
       <c r="A5" s="2">
         <v>98111</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -6215,7 +6525,7 @@
       <c r="A6" s="2">
         <v>91925</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -6229,7 +6539,7 @@
       <c r="A7" s="2">
         <v>91925</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -6243,7 +6553,7 @@
       <c r="A8" s="2">
         <v>91925</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -6257,7 +6567,7 @@
       <c r="A9" s="2">
         <v>91925</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -6271,7 +6581,7 @@
       <c r="A10" s="2">
         <v>91933</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -6285,7 +6595,7 @@
       <c r="A11" s="2">
         <v>91933</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -6299,7 +6609,7 @@
       <c r="A12" s="2">
         <v>91933</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -6313,7 +6623,7 @@
       <c r="A13" s="2">
         <v>91933</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -6327,7 +6637,7 @@
       <c r="A14" s="2">
         <v>91933</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -6341,7 +6651,7 @@
       <c r="A15" s="2">
         <v>91935</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -6355,7 +6665,7 @@
       <c r="A16" s="2">
         <v>91935</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -6369,7 +6679,7 @@
       <c r="A17" s="2">
         <v>91935</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -6383,7 +6693,7 @@
       <c r="A18" s="2">
         <v>91935</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -6397,7 +6707,7 @@
       <c r="A19" s="2">
         <v>91935</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -6411,7 +6721,7 @@
       <c r="A20" s="2">
         <v>91927</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -6425,7 +6735,7 @@
       <c r="A21" s="2">
         <v>91927</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -6439,7 +6749,7 @@
       <c r="A22" s="2">
         <v>91927</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -6453,7 +6763,7 @@
       <c r="A23" s="2">
         <v>91927</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -6467,7 +6777,7 @@
       <c r="A24" s="2">
         <v>91927</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -6481,7 +6791,7 @@
       <c r="A25" s="2">
         <v>91927</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -6495,7 +6805,7 @@
       <c r="A26" s="2">
         <v>91927</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -6509,7 +6819,7 @@
       <c r="A27" s="2">
         <v>92984</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -6523,7 +6833,7 @@
       <c r="A28" s="2">
         <v>92984</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -6537,7 +6847,7 @@
       <c r="A29" s="2">
         <v>92984</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -6551,7 +6861,7 @@
       <c r="A30" s="2">
         <v>92984</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -6565,7 +6875,7 @@
       <c r="A31" s="2">
         <v>91929</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -6579,7 +6889,7 @@
       <c r="A32" s="2">
         <v>91929</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="3" t="s">
@@ -6593,7 +6903,7 @@
       <c r="A33" s="2">
         <v>91929</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="3" t="s">
@@ -6607,7 +6917,7 @@
       <c r="A34" s="2">
         <v>91929</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C34" s="3" t="s">
@@ -6621,7 +6931,7 @@
       <c r="A35" s="2">
         <v>91929</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C35" s="3" t="s">
@@ -6635,7 +6945,7 @@
       <c r="A36" s="2">
         <v>91931</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -6649,7 +6959,7 @@
       <c r="A37" s="2">
         <v>91931</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="3" t="s">
@@ -6663,7 +6973,7 @@
       <c r="A38" s="2">
         <v>91931</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -6677,7 +6987,7 @@
       <c r="A39" s="2">
         <v>91931</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -6691,7 +7001,7 @@
       <c r="A40" s="2">
         <v>91931</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -6705,7 +7015,7 @@
       <c r="A41" s="2">
         <v>91834</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -6719,7 +7029,7 @@
       <c r="A42" s="2">
         <v>91834</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="3" t="s">
@@ -6733,7 +7043,7 @@
       <c r="A43" s="2">
         <v>91854</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -6747,7 +7057,7 @@
       <c r="A44" s="2">
         <v>91854</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -6761,7 +7071,7 @@
       <c r="A45" s="2">
         <v>98297</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -6775,7 +7085,7 @@
       <c r="A46" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -6789,7 +7099,7 @@
       <c r="A47" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C47" s="3" t="s">
@@ -6803,7 +7113,7 @@
       <c r="A48" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C48" s="3" t="s">
@@ -6817,7 +7127,7 @@
       <c r="A49" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -6831,7 +7141,7 @@
       <c r="A50" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C50" s="3" t="s">
@@ -6845,7 +7155,7 @@
       <c r="A51" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C51" s="3" t="s">
@@ -6859,7 +7169,7 @@
       <c r="A52" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C52" s="3" t="s">
@@ -6873,7 +7183,7 @@
       <c r="A53" s="2">
         <v>97667</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C53" s="3" t="s">
@@ -6887,7 +7197,7 @@
       <c r="A54" s="2">
         <v>91836</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C54" s="3" t="s">
@@ -6901,7 +7211,7 @@
       <c r="A55" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C55" s="3" t="s">
@@ -6915,7 +7225,7 @@
       <c r="A56" s="2">
         <v>91856</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C56" s="3" t="s">
@@ -6929,7 +7239,7 @@
       <c r="A57" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C57" s="3" t="s">
@@ -6943,7 +7253,7 @@
       <c r="A58" s="2">
         <v>97670</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C58" s="3" t="s">
@@ -6957,7 +7267,7 @@
       <c r="A59" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C59" s="3" t="s">
@@ -6971,7 +7281,7 @@
       <c r="A60" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C60" s="3" t="s">
@@ -6985,7 +7295,7 @@
       <c r="A61" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C61" s="3" t="s">
@@ -6999,7 +7309,7 @@
       <c r="A62" s="2">
         <v>93655</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C62" s="3" t="s">
@@ -7013,7 +7323,7 @@
       <c r="A63" s="2">
         <v>93655</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C63" s="3" t="s">
@@ -7027,7 +7337,7 @@
       <c r="A64" s="2">
         <v>93654</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -7041,7 +7351,7 @@
       <c r="A65" s="2">
         <v>93663</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C65" s="3" t="s">
@@ -7055,7 +7365,7 @@
       <c r="A66" s="2">
         <v>93661</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C66" s="3" t="s">
@@ -7069,7 +7379,7 @@
       <c r="A67" s="2">
         <v>93654</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C67" s="3" t="s">
@@ -7083,7 +7393,7 @@
       <c r="A68" s="2">
         <v>93671</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C68" s="3" t="s">
@@ -7097,7 +7407,7 @@
       <c r="A69" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C69" s="3" t="s">
@@ -7111,7 +7421,7 @@
       <c r="A70" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C70" s="3" t="s">
@@ -7125,7 +7435,7 @@
       <c r="A71" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C71" s="3" t="s">
@@ -7139,7 +7449,7 @@
       <c r="A72" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C72" s="3" t="s">
@@ -7153,7 +7463,7 @@
       <c r="A73" s="2">
         <v>91961</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C73" s="3" t="s">
@@ -7167,7 +7477,7 @@
       <c r="A74" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C74" s="3" t="s">
@@ -7181,7 +7491,7 @@
       <c r="A75" s="2">
         <v>91953</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C75" s="3" t="s">
@@ -7195,7 +7505,7 @@
       <c r="A76" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C76" s="3" t="s">
@@ -7209,7 +7519,7 @@
       <c r="A77" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C77" s="3" t="s">
@@ -7223,7 +7533,7 @@
       <c r="A78" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C78" s="3" t="s">
@@ -7237,7 +7547,7 @@
       <c r="A79" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C79" s="3" t="s">
@@ -7251,7 +7561,7 @@
       <c r="A80" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C80" s="3" t="s">
@@ -7265,7 +7575,7 @@
       <c r="A81" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C81" s="3" t="s">
@@ -7279,7 +7589,7 @@
       <c r="A82" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C82" s="3" t="s">
@@ -7293,7 +7603,7 @@
       <c r="A83" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C83" s="3" t="s">
@@ -7307,7 +7617,7 @@
       <c r="A84" s="2">
         <v>91957</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C84" s="3" t="s">
@@ -7321,7 +7631,7 @@
       <c r="A85" s="2">
         <v>92004</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C85" s="3" t="s">
@@ -7335,7 +7645,7 @@
       <c r="A86" s="2">
         <v>91996</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C86" s="3" t="s">
@@ -7349,7 +7659,7 @@
       <c r="A87" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C87" s="3" t="s">
@@ -7363,7 +7673,7 @@
       <c r="A88" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C88" s="3" t="s">
@@ -7377,7 +7687,7 @@
       <c r="A89" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C89" s="3" t="s">
@@ -7391,7 +7701,7 @@
       <c r="A90" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C90" s="3" t="s">
@@ -7405,7 +7715,7 @@
       <c r="A91" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C91" s="3" t="s">
@@ -7419,7 +7729,7 @@
       <c r="A92" s="2">
         <v>97889</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C92" s="3" t="s">
@@ -7433,7 +7743,7 @@
       <c r="A93" s="2">
         <v>97888</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C93" s="3" t="s">
@@ -7447,7 +7757,7 @@
       <c r="A94" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C94" s="3" t="s">
@@ -7461,7 +7771,7 @@
       <c r="A95" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C95" s="3" t="s">
@@ -7475,7 +7785,7 @@
       <c r="A96" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C96" s="3" t="s">
@@ -7489,7 +7799,7 @@
       <c r="A97" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C97" s="3" t="s">
@@ -7503,7 +7813,7 @@
       <c r="A98" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C98" s="3" t="s">
@@ -7517,7 +7827,7 @@
       <c r="A99" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C99" s="3" t="s">
@@ -7531,7 +7841,7 @@
       <c r="A100" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C100" s="3" t="s">
@@ -7545,7 +7855,7 @@
       <c r="A101" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C101" s="3" t="s">
@@ -7559,7 +7869,7 @@
       <c r="A102" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C102" s="3" t="s">
@@ -7573,7 +7883,7 @@
       <c r="A103" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C103" s="3" t="s">
@@ -7587,7 +7897,7 @@
       <c r="A104" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C104" s="3" t="s">
@@ -7601,7 +7911,7 @@
       <c r="A105" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C105" s="3" t="s">
@@ -7615,7 +7925,7 @@
       <c r="A106" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C106" s="3" t="s">
@@ -7629,7 +7939,7 @@
       <c r="A107" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C107" s="3" t="s">
@@ -7643,7 +7953,7 @@
       <c r="A108" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C108" s="3" t="s">
@@ -7657,7 +7967,7 @@
       <c r="A109" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C109" s="3" t="s">
@@ -7671,7 +7981,7 @@
       <c r="A110" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C110" s="3" t="s">
@@ -7685,7 +7995,7 @@
       <c r="A111" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C111" s="3" t="s">
@@ -7699,7 +8009,7 @@
       <c r="A112" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C112" s="3" t="s">
@@ -7713,7 +8023,7 @@
       <c r="A113" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C113" s="3" t="s">
@@ -7727,7 +8037,7 @@
       <c r="A114" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C114" s="3" t="s">
@@ -7741,7 +8051,7 @@
       <c r="A115" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C115" s="3" t="s">
@@ -7755,7 +8065,7 @@
       <c r="A116" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C116" s="3" t="s">
@@ -7769,7 +8079,7 @@
       <c r="A117" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C117" s="3" t="s">
@@ -7783,7 +8093,7 @@
       <c r="A118" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C118" s="3" t="s">
@@ -7797,7 +8107,7 @@
       <c r="A119" s="2">
         <v>95803</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C119" s="3" t="s">
@@ -7811,7 +8121,7 @@
       <c r="A120" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C120" s="3" t="s">
@@ -7825,7 +8135,7 @@
       <c r="A121" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C121" s="3" t="s">
@@ -7839,7 +8149,7 @@
       <c r="A122" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C122" s="3" t="s">
@@ -7853,7 +8163,7 @@
       <c r="A123" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C123" s="3" t="s">
@@ -7867,7 +8177,7 @@
       <c r="A124" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C124" s="3" t="s">
@@ -7881,7 +8191,7 @@
       <c r="A125" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C125" s="3" t="s">
@@ -7895,7 +8205,7 @@
       <c r="A126" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C126" s="3" t="s">
@@ -7909,7 +8219,7 @@
       <c r="A127" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C127" s="3" t="s">
@@ -7923,7 +8233,7 @@
       <c r="A128" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C128" s="3" t="s">
@@ -7937,7 +8247,7 @@
       <c r="A129" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C129" s="3" t="s">
@@ -7951,7 +8261,7 @@
       <c r="A130" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C130" s="3" t="s">
@@ -7965,7 +8275,7 @@
       <c r="A131" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C131" s="3" t="s">
@@ -7979,7 +8289,7 @@
       <c r="A132" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C132" s="3" t="s">
@@ -7993,7 +8303,7 @@
       <c r="A133" s="2">
         <v>97886</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C133" s="3" t="s">
@@ -8007,7 +8317,7 @@
       <c r="A134" s="2">
         <v>91955</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C134" s="3" t="s">
@@ -8021,7 +8331,7 @@
       <c r="A135" s="2">
         <v>91967</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C135" s="3" t="s">
@@ -8035,7 +8345,7 @@
       <c r="A136" s="2">
         <v>91959</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C136" s="3" t="s">
@@ -8049,7 +8359,7 @@
       <c r="A137" s="2">
         <v>91936</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C137" s="3" t="s">
@@ -8063,7 +8373,7 @@
       <c r="A138" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C138" s="3" t="s">
@@ -8077,7 +8387,7 @@
       <c r="A139" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C139" s="3" t="s">
@@ -8091,7 +8401,7 @@
       <c r="A140" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C140" s="3" t="s">
@@ -8105,7 +8415,7 @@
       <c r="A141" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C141" s="3" t="s">
@@ -8119,7 +8429,7 @@
       <c r="A142" s="2">
         <v>93662</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C142" s="3" t="s">
@@ -8133,7 +8443,7 @@
       <c r="A143" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C143" s="3" t="s">
@@ -8147,7 +8457,7 @@
       <c r="A144" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C144" s="3" t="s">
@@ -8161,7 +8471,7 @@
       <c r="A145" s="2">
         <v>101632</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C145" s="3" t="s">
@@ -8175,7 +8485,7 @@
       <c r="A146" s="2">
         <v>93662</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C146" s="3" t="s">
@@ -8189,7 +8499,7 @@
       <c r="A147" s="2">
         <v>93664</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C147" s="3" t="s">
@@ -8203,7 +8513,7 @@
       <c r="A148" s="2">
         <v>101657</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C148" s="3" t="s">
@@ -8217,7 +8527,7 @@
       <c r="A149" s="2">
         <v>105953</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C149" s="3" t="s">
@@ -8231,7 +8541,7 @@
       <c r="A150" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C150" s="3" t="s">
@@ -8245,7 +8555,7 @@
       <c r="A151" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B151" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C151" s="3" t="s">
@@ -8259,7 +8569,7 @@
       <c r="A152" s="2">
         <v>91992</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B152" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C152" s="3" t="s">
@@ -8273,7 +8583,7 @@
       <c r="A153" s="2">
         <v>91993</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C153" s="3" t="s">
@@ -8287,7 +8597,7 @@
       <c r="A154" s="2">
         <v>92008</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C154" s="3" t="s">
@@ -8301,7 +8611,7 @@
       <c r="A155" s="2">
         <v>92000</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B155" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C155" s="3" t="s">
@@ -8315,7 +8625,7 @@
       <c r="A156" s="2">
         <v>91995</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C156" s="3" t="s">
@@ -8329,7 +8639,7 @@
       <c r="A157" s="2">
         <v>92001</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C157" s="3" t="s">
@@ -8343,7 +8653,7 @@
       <c r="A158" s="2">
         <v>92001</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C158" s="3" t="s">
@@ -8357,7 +8667,7 @@
       <c r="A159" s="2">
         <v>96977</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C159" s="3" t="s">
@@ -8371,7 +8681,7 @@
       <c r="A160" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C160" s="3" t="s">
@@ -8385,7 +8695,7 @@
       <c r="A161" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C161" s="3" t="s">
@@ -8399,7 +8709,7 @@
       <c r="A162" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="B162" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C162" s="3" t="s">
@@ -8413,7 +8723,7 @@
       <c r="A163" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C163" s="3" t="s">
@@ -8427,7 +8737,7 @@
       <c r="A164" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B164" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C164" s="3" t="s">
@@ -8441,7 +8751,7 @@
       <c r="A165" s="2">
         <v>97889</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C165" s="3" t="s">
@@ -8455,7 +8765,7 @@
       <c r="A166" s="2">
         <v>92992</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B166" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C166" s="3" t="s">
@@ -8469,7 +8779,7 @@
       <c r="A167" s="2">
         <v>92992</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C167" s="3" t="s">
@@ -8483,7 +8793,7 @@
       <c r="A168" s="2">
         <v>92992</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C168" s="3" t="s">
@@ -8497,7 +8807,7 @@
       <c r="A169" s="2">
         <v>92992</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C169" s="3" t="s">
@@ -8511,7 +8821,7 @@
       <c r="A170" s="2">
         <v>92988</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C170" s="3" t="s">
@@ -8525,7 +8835,7 @@
       <c r="A171" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B171" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C171" s="3" t="s">
@@ -8539,7 +8849,7 @@
       <c r="A172" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="B172" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C172" s="3" t="s">
@@ -8553,7 +8863,7 @@
       <c r="A173" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C173" s="3" t="s">
@@ -8567,7 +8877,7 @@
       <c r="A174" s="2">
         <v>93664</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="B174" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C174" s="3" t="s">
@@ -8581,7 +8891,7 @@
       <c r="A175" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C175" s="3" t="s">
@@ -8595,7 +8905,7 @@
       <c r="A176" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C176" s="3" t="s">
@@ -8609,7 +8919,7 @@
       <c r="A177" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B177" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C177" s="3" t="s">
@@ -8623,7 +8933,7 @@
       <c r="A178" s="2">
         <v>95789</v>
       </c>
-      <c r="B178" s="3" t="s">
+      <c r="B178" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C178" s="3" t="s">
@@ -8637,7 +8947,7 @@
       <c r="A179" s="2">
         <v>95796</v>
       </c>
-      <c r="B179" s="3" t="s">
+      <c r="B179" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C179" s="3" t="s">
@@ -8651,7 +8961,7 @@
       <c r="A180" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B180" s="3" t="s">
+      <c r="B180" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C180" s="3" t="s">
@@ -8665,7 +8975,7 @@
       <c r="A181" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="B181" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C181" s="3" t="s">
@@ -8679,7 +8989,7 @@
       <c r="A182" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B182" s="3" t="s">
+      <c r="B182" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C182" s="3" t="s">
@@ -8693,7 +9003,7 @@
       <c r="A183" s="2">
         <v>91868</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C183" s="3" t="s">
@@ -8707,7 +9017,7 @@
       <c r="A184" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B184" s="3" t="s">
+      <c r="B184" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C184" s="3" t="s">
@@ -8721,7 +9031,7 @@
       <c r="A185" s="2">
         <v>95781</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C185" s="3" t="s">
@@ -8735,7 +9045,7 @@
       <c r="A186" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C186" s="3" t="s">
@@ -8749,7 +9059,7 @@
       <c r="A187" s="2">
         <v>95782</v>
       </c>
-      <c r="B187" s="3" t="s">
+      <c r="B187" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C187" s="3" t="s">
@@ -8763,7 +9073,7 @@
       <c r="A188" s="2">
         <v>95795</v>
       </c>
-      <c r="B188" s="3" t="s">
+      <c r="B188" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C188" s="3" t="s">
@@ -8777,7 +9087,7 @@
       <c r="A189" s="2">
         <v>95801</v>
       </c>
-      <c r="B189" s="3" t="s">
+      <c r="B189" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C189" s="3" t="s">
@@ -8791,7 +9101,7 @@
       <c r="A190" s="2">
         <v>95779</v>
       </c>
-      <c r="B190" s="3" t="s">
+      <c r="B190" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C190" s="3" t="s">
@@ -8805,7 +9115,7 @@
       <c r="A191" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B191" s="3" t="s">
+      <c r="B191" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C191" s="3" t="s">
@@ -8819,7 +9129,7 @@
       <c r="A192" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B192" s="3" t="s">
+      <c r="B192" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C192" s="3" t="s">
@@ -8833,7 +9143,7 @@
       <c r="A193" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B193" s="3" t="s">
+      <c r="B193" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C193" s="3" t="s">
@@ -8847,7 +9157,7 @@
       <c r="A194" s="2">
         <v>92994</v>
       </c>
-      <c r="B194" s="3" t="s">
+      <c r="B194" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C194" s="3" t="s">
@@ -8861,7 +9171,7 @@
       <c r="A195" s="2">
         <v>92994</v>
       </c>
-      <c r="B195" s="3" t="s">
+      <c r="B195" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C195" s="3" t="s">
@@ -8875,7 +9185,7 @@
       <c r="A196" s="2">
         <v>92994</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B196" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C196" s="3" t="s">
@@ -8889,7 +9199,7 @@
       <c r="A197" s="2">
         <v>92994</v>
       </c>
-      <c r="B197" s="3" t="s">
+      <c r="B197" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C197" s="3" t="s">
@@ -8903,7 +9213,7 @@
       <c r="A198" s="2">
         <v>92990</v>
       </c>
-      <c r="B198" s="3" t="s">
+      <c r="B198" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C198" s="3" t="s">
@@ -8917,7 +9227,7 @@
       <c r="A199" s="2">
         <v>92990</v>
       </c>
-      <c r="B199" s="3" t="s">
+      <c r="B199" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C199" s="3" t="s">
@@ -8931,7 +9241,7 @@
       <c r="A200" s="2">
         <v>92990</v>
       </c>
-      <c r="B200" s="3" t="s">
+      <c r="B200" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C200" s="3" t="s">
@@ -8945,7 +9255,7 @@
       <c r="A201" s="2">
         <v>92990</v>
       </c>
-      <c r="B201" s="3" t="s">
+      <c r="B201" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C201" s="3" t="s">
@@ -8959,7 +9269,7 @@
       <c r="A202" s="2">
         <v>92990</v>
       </c>
-      <c r="B202" s="3" t="s">
+      <c r="B202" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C202" s="3" t="s">
@@ -8973,7 +9283,7 @@
       <c r="A203" s="2">
         <v>92986</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="B203" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C203" s="3" t="s">
@@ -8987,7 +9297,7 @@
       <c r="A204" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B204" s="3" t="s">
+      <c r="B204" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C204" s="3" t="s">
@@ -9001,7 +9311,7 @@
       <c r="A205" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B205" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C205" s="3" t="s">
@@ -9015,7 +9325,7 @@
       <c r="A206" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B206" s="3" t="s">
+      <c r="B206" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C206" s="3" t="s">
@@ -9029,7 +9339,7 @@
       <c r="A207" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B207" s="3" t="s">
+      <c r="B207" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C207" s="3" t="s">
@@ -9043,7 +9353,7 @@
       <c r="A208" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B208" s="3" t="s">
+      <c r="B208" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C208" s="3" t="s">
@@ -9057,7 +9367,7 @@
       <c r="A209" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="B209" s="3" t="s">
+      <c r="B209" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C209" s="3" t="s">
@@ -9071,7 +9381,7 @@
       <c r="A210" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="B210" s="3" t="s">
+      <c r="B210" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C210" s="3" t="s">
@@ -9085,7 +9395,7 @@
       <c r="A211" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="B211" s="3" t="s">
+      <c r="B211" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C211" s="3" t="s">
@@ -9099,7 +9409,7 @@
       <c r="A212" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="B212" s="3" t="s">
+      <c r="B212" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C212" s="3" t="s">
@@ -9113,7 +9423,7 @@
       <c r="A213" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B213" s="3" t="s">
+      <c r="B213" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C213" s="3" t="s">
@@ -9127,7 +9437,7 @@
       <c r="A214" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="B214" s="3" t="s">
+      <c r="B214" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C214" s="3" t="s">
@@ -9141,7 +9451,7 @@
       <c r="A215" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="B215" s="3" t="s">
+      <c r="B215" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C215" s="3" t="s">
@@ -9155,7 +9465,7 @@
       <c r="A216" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B216" s="3" t="s">
+      <c r="B216" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C216" s="3" t="s">
@@ -9169,7 +9479,7 @@
       <c r="A217" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B217" s="3" t="s">
+      <c r="B217" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C217" s="3" t="s">
@@ -9183,7 +9493,7 @@
       <c r="A218" s="2">
         <v>95787</v>
       </c>
-      <c r="B218" s="3" t="s">
+      <c r="B218" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C218" s="3" t="s">
@@ -9197,7 +9507,7 @@
       <c r="A219" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="B219" s="3" t="s">
+      <c r="B219" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C219" s="3" t="s">
@@ -9211,7 +9521,7 @@
       <c r="A220" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B220" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C220" s="3" t="s">
@@ -9225,7 +9535,7 @@
       <c r="A221" s="2">
         <v>96988</v>
       </c>
-      <c r="B221" s="3" t="s">
+      <c r="B221" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C221" s="3" t="s">
@@ -9239,7 +9549,7 @@
       <c r="A222" s="2">
         <v>96987</v>
       </c>
-      <c r="B222" s="3" t="s">
+      <c r="B222" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C222" s="3" t="s">
@@ -9253,7 +9563,7 @@
       <c r="A223" s="2">
         <v>96989</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="B223" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C223" s="3" t="s">
@@ -9267,7 +9577,7 @@
       <c r="A224" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B224" s="3" t="s">
+      <c r="B224" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C224" s="3" t="s">
@@ -9281,7 +9591,7 @@
       <c r="A225" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="B225" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C225" s="3" t="s">
@@ -9295,7 +9605,7 @@
       <c r="A226" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B226" s="3" t="s">
+      <c r="B226" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C226" s="3" t="s">
@@ -9309,7 +9619,7 @@
       <c r="A227" s="2">
         <v>97886</v>
       </c>
-      <c r="B227" s="3" t="s">
+      <c r="B227" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C227" s="3" t="s">
@@ -9323,7 +9633,7 @@
       <c r="A228" s="2">
         <v>97887</v>
       </c>
-      <c r="B228" s="3" t="s">
+      <c r="B228" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C228" s="3" t="s">
@@ -9337,7 +9647,7 @@
       <c r="A229" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B229" s="3" t="s">
+      <c r="B229" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C229" s="3" t="s">
@@ -9351,7 +9661,7 @@
       <c r="A230" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B230" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C230" s="3" t="s">
@@ -9365,7 +9675,7 @@
       <c r="A231" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C231" s="3" t="s">
@@ -9379,7 +9689,7 @@
       <c r="A232" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B232" s="3" t="s">
+      <c r="B232" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C232" s="3" t="s">
@@ -9393,7 +9703,7 @@
       <c r="A233" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B233" s="3" t="s">
+      <c r="B233" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C233" s="3" t="s">
@@ -9407,7 +9717,7 @@
       <c r="A234" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="B234" s="3" t="s">
+      <c r="B234" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C234" s="3" t="s">
@@ -9421,7 +9731,7 @@
       <c r="A235" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B235" s="3" t="s">
+      <c r="B235" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C235" s="3" t="s">
@@ -9435,7 +9745,7 @@
       <c r="A236" s="2">
         <v>91924</v>
       </c>
-      <c r="B236" s="3" t="s">
+      <c r="B236" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C236" s="3" t="s">
@@ -9449,7 +9759,7 @@
       <c r="A237" s="2">
         <v>91924</v>
       </c>
-      <c r="B237" s="3" t="s">
+      <c r="B237" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C237" s="3" t="s">
@@ -9463,7 +9773,7 @@
       <c r="A238" s="2">
         <v>91924</v>
       </c>
-      <c r="B238" s="3" t="s">
+      <c r="B238" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C238" s="3" t="s">
@@ -9477,7 +9787,7 @@
       <c r="A239" s="2">
         <v>91924</v>
       </c>
-      <c r="B239" s="3" t="s">
+      <c r="B239" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C239" s="3" t="s">
@@ -9491,7 +9801,7 @@
       <c r="A240" s="2">
         <v>91924</v>
       </c>
-      <c r="B240" s="3" t="s">
+      <c r="B240" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C240" s="3" t="s">
@@ -9505,7 +9815,7 @@
       <c r="A241" s="2">
         <v>91926</v>
       </c>
-      <c r="B241" s="3" t="s">
+      <c r="B241" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C241" s="3" t="s">
@@ -9519,7 +9829,7 @@
       <c r="A242" s="2">
         <v>91926</v>
       </c>
-      <c r="B242" s="3" t="s">
+      <c r="B242" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C242" s="3" t="s">
@@ -9533,7 +9843,7 @@
       <c r="A243" s="2">
         <v>91926</v>
       </c>
-      <c r="B243" s="3" t="s">
+      <c r="B243" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C243" s="3" t="s">
@@ -9547,7 +9857,7 @@
       <c r="A244" s="2">
         <v>91926</v>
       </c>
-      <c r="B244" s="3" t="s">
+      <c r="B244" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C244" s="3" t="s">
@@ -9561,7 +9871,7 @@
       <c r="A245" s="2">
         <v>91926</v>
       </c>
-      <c r="B245" s="3" t="s">
+      <c r="B245" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C245" s="3" t="s">
@@ -9575,7 +9885,7 @@
       <c r="A246" s="2">
         <v>91926</v>
       </c>
-      <c r="B246" s="3" t="s">
+      <c r="B246" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C246" s="3" t="s">
@@ -9589,7 +9899,7 @@
       <c r="A247" s="2">
         <v>91928</v>
       </c>
-      <c r="B247" s="3" t="s">
+      <c r="B247" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C247" s="3" t="s">
@@ -9603,7 +9913,7 @@
       <c r="A248" s="2">
         <v>91928</v>
       </c>
-      <c r="B248" s="3" t="s">
+      <c r="B248" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C248" s="3" t="s">
@@ -9617,7 +9927,7 @@
       <c r="A249" s="2">
         <v>91928</v>
       </c>
-      <c r="B249" s="3" t="s">
+      <c r="B249" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C249" s="3" t="s">
@@ -9631,7 +9941,7 @@
       <c r="A250" s="2">
         <v>91928</v>
       </c>
-      <c r="B250" s="3" t="s">
+      <c r="B250" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C250" s="3" t="s">
@@ -9645,7 +9955,7 @@
       <c r="A251" s="2">
         <v>91934</v>
       </c>
-      <c r="B251" s="3" t="s">
+      <c r="B251" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C251" s="3" t="s">
@@ -9659,7 +9969,7 @@
       <c r="A252" s="2">
         <v>91934</v>
       </c>
-      <c r="B252" s="3" t="s">
+      <c r="B252" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C252" s="3" t="s">
@@ -9673,7 +9983,7 @@
       <c r="A253" s="2">
         <v>91934</v>
       </c>
-      <c r="B253" s="3" t="s">
+      <c r="B253" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C253" s="3" t="s">
@@ -9687,7 +9997,7 @@
       <c r="A254" s="2">
         <v>91934</v>
       </c>
-      <c r="B254" s="3" t="s">
+      <c r="B254" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C254" s="3" t="s">
@@ -9701,7 +10011,7 @@
       <c r="A255" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B255" s="3" t="s">
+      <c r="B255" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C255" s="3" t="s">
@@ -9715,7 +10025,7 @@
       <c r="A256" s="2">
         <v>98295</v>
       </c>
-      <c r="B256" s="3" t="s">
+      <c r="B256" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C256" s="3" t="s">
@@ -9729,7 +10039,7 @@
       <c r="A257" s="2">
         <v>91935</v>
       </c>
-      <c r="B257" s="3" t="s">
+      <c r="B257" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C257" s="3" t="s">
@@ -9743,7 +10053,7 @@
       <c r="A258" s="2">
         <v>92984</v>
       </c>
-      <c r="B258" s="3" t="s">
+      <c r="B258" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C258" s="3" t="s">
@@ -9757,7 +10067,7 @@
       <c r="A259" s="2">
         <v>92984</v>
       </c>
-      <c r="B259" s="3" t="s">
+      <c r="B259" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C259" s="3" t="s">
@@ -9771,7 +10081,7 @@
       <c r="A260" s="2">
         <v>92984</v>
       </c>
-      <c r="B260" s="3" t="s">
+      <c r="B260" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C260" s="3" t="s">
@@ -9785,7 +10095,7 @@
       <c r="A261" s="2">
         <v>92984</v>
       </c>
-      <c r="B261" s="3" t="s">
+      <c r="B261" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C261" s="3" t="s">
@@ -9799,7 +10109,7 @@
       <c r="A262" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="B262" s="3" t="s">
+      <c r="B262" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C262" s="3" t="s">
@@ -9813,7 +10123,7 @@
       <c r="A263" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="B263" s="3" t="s">
+      <c r="B263" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C263" s="3" t="s">
@@ -9827,7 +10137,7 @@
       <c r="A264" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B264" s="3" t="s">
+      <c r="B264" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C264" s="3" t="s">
@@ -9841,7 +10151,7 @@
       <c r="A265" s="2">
         <v>91955</v>
       </c>
-      <c r="B265" s="3" t="s">
+      <c r="B265" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C265" s="3" t="s">
@@ -9855,7 +10165,7 @@
       <c r="A266" s="2">
         <v>91961</v>
       </c>
-      <c r="B266" s="3" t="s">
+      <c r="B266" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C266" s="3" t="s">
@@ -9869,7 +10179,7 @@
       <c r="A267" s="2">
         <v>91969</v>
       </c>
-      <c r="B267" s="3" t="s">
+      <c r="B267" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C267" s="3" t="s">
@@ -9883,7 +10193,7 @@
       <c r="A268" s="2">
         <v>91953</v>
       </c>
-      <c r="B268" s="3" t="s">
+      <c r="B268" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C268" s="3" t="s">
@@ -9897,7 +10207,7 @@
       <c r="A269" s="2">
         <v>91957</v>
       </c>
-      <c r="B269" s="3" t="s">
+      <c r="B269" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C269" s="3" t="s">
@@ -9911,7 +10221,7 @@
       <c r="A270" s="2">
         <v>91959</v>
       </c>
-      <c r="B270" s="3" t="s">
+      <c r="B270" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C270" s="3" t="s">
@@ -9925,7 +10235,7 @@
       <c r="A271" s="2">
         <v>91967</v>
       </c>
-      <c r="B271" s="3" t="s">
+      <c r="B271" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C271" s="3" t="s">
@@ -9939,7 +10249,7 @@
       <c r="A272" s="2">
         <v>91975</v>
       </c>
-      <c r="B272" s="3" t="s">
+      <c r="B272" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C272" s="3" t="s">
@@ -9953,7 +10263,7 @@
       <c r="A273" s="2">
         <v>91992</v>
       </c>
-      <c r="B273" s="3" t="s">
+      <c r="B273" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C273" s="3" t="s">
@@ -9967,7 +10277,7 @@
       <c r="A274" s="2">
         <v>92000</v>
       </c>
-      <c r="B274" s="3" t="s">
+      <c r="B274" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C274" s="3" t="s">
@@ -9981,7 +10291,7 @@
       <c r="A275" s="2">
         <v>92008</v>
       </c>
-      <c r="B275" s="3" t="s">
+      <c r="B275" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C275" s="3" t="s">
@@ -9995,7 +10305,7 @@
       <c r="A276" s="2">
         <v>91996</v>
       </c>
-      <c r="B276" s="3" t="s">
+      <c r="B276" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C276" s="3" t="s">
@@ -10009,7 +10319,7 @@
       <c r="A277" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B277" s="3" t="s">
+      <c r="B277" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C277" s="3" t="s">
@@ -10023,7 +10333,7 @@
       <c r="A278" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="B278" s="3" t="s">
+      <c r="B278" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C278" s="3" t="s">
@@ -10037,7 +10347,7 @@
       <c r="A279" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B279" s="3" t="s">
+      <c r="B279" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C279" s="3" t="s">
@@ -10051,7 +10361,7 @@
       <c r="A280" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B280" s="3" t="s">
+      <c r="B280" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C280" s="3" t="s">
@@ -10065,7 +10375,7 @@
       <c r="A281" s="2">
         <v>95801</v>
       </c>
-      <c r="B281" s="3" t="s">
+      <c r="B281" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C281" s="3" t="s">
@@ -10079,7 +10389,7 @@
       <c r="A282" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B282" s="3" t="s">
+      <c r="B282" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C282" s="3" t="s">
@@ -10093,7 +10403,7 @@
       <c r="A283" s="2">
         <v>91936</v>
       </c>
-      <c r="B283" s="3" t="s">
+      <c r="B283" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C283" s="3" t="s">
@@ -10107,7 +10417,7 @@
       <c r="A284" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B284" s="3" t="s">
+      <c r="B284" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C284" s="3" t="s">
@@ -10121,7 +10431,7 @@
       <c r="A285" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B285" s="3" t="s">
+      <c r="B285" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C285" s="3" t="s">
@@ -10135,7 +10445,7 @@
       <c r="A286" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B286" s="3" t="s">
+      <c r="B286" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C286" s="3" t="s">
@@ -10149,7 +10459,7 @@
       <c r="A287" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B287" s="3" t="s">
+      <c r="B287" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C287" s="3" t="s">
@@ -10163,7 +10473,7 @@
       <c r="A288" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B288" s="3" t="s">
+      <c r="B288" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C288" s="3" t="s">
@@ -10177,7 +10487,7 @@
       <c r="A289" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="B289" s="3" t="s">
+      <c r="B289" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C289" s="3" t="s">
@@ -10191,7 +10501,7 @@
       <c r="A290" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B290" s="3" t="s">
+      <c r="B290" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C290" s="3" t="s">
@@ -10205,7 +10515,7 @@
       <c r="A291" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B291" s="3" t="s">
+      <c r="B291" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C291" s="3" t="s">
@@ -10219,7 +10529,7 @@
       <c r="A292" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B292" s="3" t="s">
+      <c r="B292" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C292" s="3" t="s">
@@ -10233,7 +10543,7 @@
       <c r="A293" s="2">
         <v>91933</v>
       </c>
-      <c r="B293" s="3" t="s">
+      <c r="B293" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C293" s="3" t="s">
@@ -10247,7 +10557,7 @@
       <c r="A294" s="2">
         <v>92996</v>
       </c>
-      <c r="B294" s="3" t="s">
+      <c r="B294" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C294" s="3" t="s">
@@ -10261,7 +10571,7 @@
       <c r="A295" s="2">
         <v>91935</v>
       </c>
-      <c r="B295" s="3" t="s">
+      <c r="B295" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C295" s="3" t="s">
@@ -10275,7 +10585,7 @@
       <c r="A296" s="2">
         <v>92998</v>
       </c>
-      <c r="B296" s="3" t="s">
+      <c r="B296" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C296" s="3" t="s">
@@ -10289,7 +10599,7 @@
       <c r="A297" s="2">
         <v>92984</v>
       </c>
-      <c r="B297" s="3" t="s">
+      <c r="B297" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C297" s="3" t="s">
@@ -10303,7 +10613,7 @@
       <c r="A298" s="2">
         <v>92986</v>
       </c>
-      <c r="B298" s="3" t="s">
+      <c r="B298" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C298" s="3" t="s">
@@ -10317,7 +10627,7 @@
       <c r="A299" s="2">
         <v>91931</v>
       </c>
-      <c r="B299" s="3" t="s">
+      <c r="B299" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C299" s="3" t="s">
@@ -10331,7 +10641,7 @@
       <c r="A300" s="2">
         <v>92990</v>
       </c>
-      <c r="B300" s="3" t="s">
+      <c r="B300" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C300" s="3" t="s">
@@ -10345,7 +10655,7 @@
       <c r="A301" s="2">
         <v>92992</v>
       </c>
-      <c r="B301" s="3" t="s">
+      <c r="B301" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C301" s="3" t="s">
@@ -10359,7 +10669,7 @@
       <c r="A302" s="2">
         <v>91925</v>
       </c>
-      <c r="B302" s="3" t="s">
+      <c r="B302" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C302" s="3" t="s">
@@ -10373,7 +10683,7 @@
       <c r="A303" s="2">
         <v>91925</v>
       </c>
-      <c r="B303" s="3" t="s">
+      <c r="B303" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C303" s="3" t="s">
@@ -10387,7 +10697,7 @@
       <c r="A304" s="2">
         <v>91925</v>
       </c>
-      <c r="B304" s="3" t="s">
+      <c r="B304" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C304" s="3" t="s">
@@ -10401,7 +10711,7 @@
       <c r="A305" s="2">
         <v>91925</v>
       </c>
-      <c r="B305" s="3" t="s">
+      <c r="B305" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C305" s="3" t="s">
@@ -10415,7 +10725,7 @@
       <c r="A306" s="2">
         <v>91933</v>
       </c>
-      <c r="B306" s="3" t="s">
+      <c r="B306" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C306" s="3" t="s">
@@ -10429,7 +10739,7 @@
       <c r="A307" s="2">
         <v>91933</v>
       </c>
-      <c r="B307" s="3" t="s">
+      <c r="B307" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C307" s="3" t="s">
@@ -10443,7 +10753,7 @@
       <c r="A308" s="2">
         <v>91933</v>
       </c>
-      <c r="B308" s="3" t="s">
+      <c r="B308" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C308" s="3" t="s">
@@ -10457,7 +10767,7 @@
       <c r="A309" s="2">
         <v>91933</v>
       </c>
-      <c r="B309" s="3" t="s">
+      <c r="B309" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C309" s="3" t="s">
@@ -10471,7 +10781,7 @@
       <c r="A310" s="2">
         <v>91933</v>
       </c>
-      <c r="B310" s="3" t="s">
+      <c r="B310" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C310" s="3" t="s">
@@ -10485,7 +10795,7 @@
       <c r="A311" s="2">
         <v>92996</v>
       </c>
-      <c r="B311" s="3" t="s">
+      <c r="B311" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C311" s="3" t="s">
@@ -10499,7 +10809,7 @@
       <c r="A312" s="2">
         <v>92996</v>
       </c>
-      <c r="B312" s="3" t="s">
+      <c r="B312" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C312" s="3" t="s">
@@ -10513,7 +10823,7 @@
       <c r="A313" s="2">
         <v>92996</v>
       </c>
-      <c r="B313" s="3" t="s">
+      <c r="B313" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C313" s="3" t="s">
@@ -10527,7 +10837,7 @@
       <c r="A314" s="2">
         <v>92996</v>
       </c>
-      <c r="B314" s="3" t="s">
+      <c r="B314" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C314" s="3" t="s">
@@ -10541,7 +10851,7 @@
       <c r="A315" s="2">
         <v>91935</v>
       </c>
-      <c r="B315" s="3" t="s">
+      <c r="B315" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C315" s="3" t="s">
@@ -10555,7 +10865,7 @@
       <c r="A316" s="2">
         <v>91935</v>
       </c>
-      <c r="B316" s="3" t="s">
+      <c r="B316" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C316" s="3" t="s">
@@ -10569,7 +10879,7 @@
       <c r="A317" s="2">
         <v>91935</v>
       </c>
-      <c r="B317" s="3" t="s">
+      <c r="B317" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C317" s="3" t="s">
@@ -10583,7 +10893,7 @@
       <c r="A318" s="2">
         <v>91935</v>
       </c>
-      <c r="B318" s="3" t="s">
+      <c r="B318" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C318" s="3" t="s">
@@ -10597,7 +10907,7 @@
       <c r="A319" s="2">
         <v>92998</v>
       </c>
-      <c r="B319" s="3" t="s">
+      <c r="B319" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C319" s="3" t="s">
@@ -10611,7 +10921,7 @@
       <c r="A320" s="2">
         <v>92998</v>
       </c>
-      <c r="B320" s="3" t="s">
+      <c r="B320" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C320" s="3" t="s">
@@ -10625,7 +10935,7 @@
       <c r="A321" s="2">
         <v>92998</v>
       </c>
-      <c r="B321" s="3" t="s">
+      <c r="B321" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C321" s="3" t="s">
@@ -10639,7 +10949,7 @@
       <c r="A322" s="2">
         <v>92998</v>
       </c>
-      <c r="B322" s="3" t="s">
+      <c r="B322" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C322" s="3" t="s">
@@ -10653,7 +10963,7 @@
       <c r="A323" s="2">
         <v>91927</v>
       </c>
-      <c r="B323" s="3" t="s">
+      <c r="B323" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C323" s="3" t="s">
@@ -10667,7 +10977,7 @@
       <c r="A324" s="2">
         <v>91927</v>
       </c>
-      <c r="B324" s="3" t="s">
+      <c r="B324" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C324" s="3" t="s">
@@ -10681,7 +10991,7 @@
       <c r="A325" s="2">
         <v>91927</v>
       </c>
-      <c r="B325" s="3" t="s">
+      <c r="B325" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C325" s="3" t="s">
@@ -10695,7 +11005,7 @@
       <c r="A326" s="2">
         <v>91927</v>
       </c>
-      <c r="B326" s="3" t="s">
+      <c r="B326" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C326" s="3" t="s">
@@ -10709,7 +11019,7 @@
       <c r="A327" s="2">
         <v>91927</v>
       </c>
-      <c r="B327" s="3" t="s">
+      <c r="B327" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C327" s="3" t="s">
@@ -10723,7 +11033,7 @@
       <c r="A328" s="2">
         <v>91927</v>
       </c>
-      <c r="B328" s="3" t="s">
+      <c r="B328" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C328" s="3" t="s">
@@ -10737,7 +11047,7 @@
       <c r="A329" s="2">
         <v>92984</v>
       </c>
-      <c r="B329" s="3" t="s">
+      <c r="B329" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C329" s="3" t="s">
@@ -10751,7 +11061,7 @@
       <c r="A330" s="2">
         <v>92986</v>
       </c>
-      <c r="B330" s="3" t="s">
+      <c r="B330" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C330" s="3" t="s">
@@ -10765,7 +11075,7 @@
       <c r="A331" s="2">
         <v>92986</v>
       </c>
-      <c r="B331" s="3" t="s">
+      <c r="B331" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C331" s="3" t="s">
@@ -10779,7 +11089,7 @@
       <c r="A332" s="2">
         <v>92986</v>
       </c>
-      <c r="B332" s="3" t="s">
+      <c r="B332" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C332" s="3" t="s">
@@ -10793,7 +11103,7 @@
       <c r="A333" s="2">
         <v>92986</v>
       </c>
-      <c r="B333" s="3" t="s">
+      <c r="B333" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C333" s="3" t="s">
@@ -10807,7 +11117,7 @@
       <c r="A334" s="2">
         <v>92986</v>
       </c>
-      <c r="B334" s="3" t="s">
+      <c r="B334" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C334" s="3" t="s">
@@ -10821,7 +11131,7 @@
       <c r="A335" s="2">
         <v>91929</v>
       </c>
-      <c r="B335" s="3" t="s">
+      <c r="B335" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C335" s="3" t="s">
@@ -10835,7 +11145,7 @@
       <c r="A336" s="2">
         <v>91929</v>
       </c>
-      <c r="B336" s="3" t="s">
+      <c r="B336" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C336" s="3" t="s">
@@ -10849,7 +11159,7 @@
       <c r="A337" s="2">
         <v>91929</v>
       </c>
-      <c r="B337" s="3" t="s">
+      <c r="B337" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C337" s="3" t="s">
@@ -10863,7 +11173,7 @@
       <c r="A338" s="2">
         <v>91929</v>
       </c>
-      <c r="B338" s="3" t="s">
+      <c r="B338" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C338" s="3" t="s">
@@ -10877,7 +11187,7 @@
       <c r="A339" s="2">
         <v>91929</v>
       </c>
-      <c r="B339" s="3" t="s">
+      <c r="B339" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C339" s="3" t="s">
@@ -10891,7 +11201,7 @@
       <c r="A340" s="2">
         <v>92988</v>
       </c>
-      <c r="B340" s="3" t="s">
+      <c r="B340" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C340" s="3" t="s">
@@ -10905,7 +11215,7 @@
       <c r="A341" s="2">
         <v>92988</v>
       </c>
-      <c r="B341" s="3" t="s">
+      <c r="B341" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C341" s="3" t="s">
@@ -10919,7 +11229,7 @@
       <c r="A342" s="2">
         <v>92988</v>
       </c>
-      <c r="B342" s="3" t="s">
+      <c r="B342" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C342" s="3" t="s">
@@ -10933,7 +11243,7 @@
       <c r="A343" s="2">
         <v>91931</v>
       </c>
-      <c r="B343" s="3" t="s">
+      <c r="B343" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C343" s="3" t="s">
@@ -10947,7 +11257,7 @@
       <c r="A344" s="2">
         <v>91931</v>
       </c>
-      <c r="B344" s="3" t="s">
+      <c r="B344" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C344" s="3" t="s">
@@ -10961,7 +11271,7 @@
       <c r="A345" s="2">
         <v>91931</v>
       </c>
-      <c r="B345" s="3" t="s">
+      <c r="B345" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C345" s="3" t="s">
@@ -10975,7 +11285,7 @@
       <c r="A346" s="2">
         <v>91931</v>
       </c>
-      <c r="B346" s="3" t="s">
+      <c r="B346" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C346" s="3" t="s">
@@ -10989,7 +11299,7 @@
       <c r="A347" s="2">
         <v>91931</v>
       </c>
-      <c r="B347" s="3" t="s">
+      <c r="B347" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C347" s="3" t="s">
@@ -11003,7 +11313,7 @@
       <c r="A348" s="2">
         <v>92990</v>
       </c>
-      <c r="B348" s="3" t="s">
+      <c r="B348" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C348" s="3" t="s">
@@ -11017,7 +11327,7 @@
       <c r="A349" s="2">
         <v>92990</v>
       </c>
-      <c r="B349" s="3" t="s">
+      <c r="B349" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C349" s="3" t="s">
@@ -11031,7 +11341,7 @@
       <c r="A350" s="2">
         <v>92990</v>
       </c>
-      <c r="B350" s="3" t="s">
+      <c r="B350" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C350" s="3" t="s">
@@ -11045,7 +11355,7 @@
       <c r="A351" s="2">
         <v>92990</v>
       </c>
-      <c r="B351" s="3" t="s">
+      <c r="B351" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C351" s="3" t="s">
@@ -11059,7 +11369,7 @@
       <c r="A352" s="2">
         <v>92992</v>
       </c>
-      <c r="B352" s="3" t="s">
+      <c r="B352" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C352" s="3" t="s">
@@ -11073,7 +11383,7 @@
       <c r="A353" s="2">
         <v>91930</v>
       </c>
-      <c r="B353" s="3" t="s">
+      <c r="B353" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C353" s="3" t="s">
@@ -11087,7 +11397,7 @@
       <c r="A354" s="2">
         <v>91930</v>
       </c>
-      <c r="B354" s="3" t="s">
+      <c r="B354" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C354" s="3" t="s">
@@ -11101,7 +11411,7 @@
       <c r="A355" s="2">
         <v>91930</v>
       </c>
-      <c r="B355" s="3" t="s">
+      <c r="B355" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C355" s="3" t="s">
@@ -11115,7 +11425,7 @@
       <c r="A356" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="B356" s="3" t="s">
+      <c r="B356" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C356" s="3" t="s">
@@ -11129,7 +11439,7 @@
       <c r="A357" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B357" s="3" t="s">
+      <c r="B357" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C357" s="3" t="s">
@@ -11143,7 +11453,7 @@
       <c r="A358" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="B358" s="3" t="s">
+      <c r="B358" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C358" s="3" t="s">
@@ -11157,7 +11467,7 @@
       <c r="A359" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="B359" s="3" t="s">
+      <c r="B359" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C359" s="3" t="s">
@@ -11171,7 +11481,7 @@
       <c r="A360" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="B360" s="3" t="s">
+      <c r="B360" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C360" s="3" t="s">
@@ -11185,7 +11495,7 @@
       <c r="A361" s="2">
         <v>93664</v>
       </c>
-      <c r="B361" s="3" t="s">
+      <c r="B361" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C361" s="3" t="s">
@@ -11199,7 +11509,7 @@
       <c r="A362" s="2">
         <v>93669</v>
       </c>
-      <c r="B362" s="3" t="s">
+      <c r="B362" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C362" s="3" t="s">
@@ -11213,7 +11523,7 @@
       <c r="A363" s="2">
         <v>93668</v>
       </c>
-      <c r="B363" s="3" t="s">
+      <c r="B363" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C363" s="3" t="s">
@@ -11227,7 +11537,7 @@
       <c r="A364" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="B364" s="3" t="s">
+      <c r="B364" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C364" s="3" t="s">
@@ -11241,7 +11551,7 @@
       <c r="A365" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="B365" s="3" t="s">
+      <c r="B365" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C365" s="3" t="s">
@@ -11255,7 +11565,7 @@
       <c r="A366" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="B366" s="3" t="s">
+      <c r="B366" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C366" s="3" t="s">
@@ -11269,7 +11579,7 @@
       <c r="A367" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="B367" s="3" t="s">
+      <c r="B367" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C367" s="3" t="s">
@@ -11283,7 +11593,7 @@
       <c r="A368" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="B368" s="3" t="s">
+      <c r="B368" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C368" s="3" t="s">
@@ -11297,7 +11607,7 @@
       <c r="A369" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="B369" s="3" t="s">
+      <c r="B369" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C369" s="3" t="s">
@@ -11311,7 +11621,7 @@
       <c r="A370" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="B370" s="3" t="s">
+      <c r="B370" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C370" s="3" t="s">
@@ -11325,7 +11635,7 @@
       <c r="A371" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="B371" s="3" t="s">
+      <c r="B371" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C371" s="3" t="s">
@@ -11339,7 +11649,7 @@
       <c r="A372" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="B372" s="3" t="s">
+      <c r="B372" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C372" s="3" t="s">
@@ -11353,7 +11663,7 @@
       <c r="A373" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="B373" s="3" t="s">
+      <c r="B373" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C373" s="3" t="s">
@@ -11367,7 +11677,7 @@
       <c r="A374" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="B374" s="3" t="s">
+      <c r="B374" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C374" s="3" t="s">
@@ -11381,7 +11691,7 @@
       <c r="A375" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="B375" s="3" t="s">
+      <c r="B375" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C375" s="3" t="s">
@@ -11395,7 +11705,7 @@
       <c r="A376" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="B376" s="3" t="s">
+      <c r="B376" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C376" s="3" t="s">
@@ -11409,7 +11719,7 @@
       <c r="A377" s="2">
         <v>97668</v>
       </c>
-      <c r="B377" s="3" t="s">
+      <c r="B377" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C377" s="3" t="s">
@@ -11423,7 +11733,7 @@
       <c r="A378" s="2">
         <v>91838</v>
       </c>
-      <c r="B378" s="3" t="s">
+      <c r="B378" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C378" s="3" t="s">
@@ -11437,7 +11747,7 @@
       <c r="A379" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B379" s="3" t="s">
+      <c r="B379" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C379" s="3" t="s">
@@ -11451,7 +11761,7 @@
       <c r="A380" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B380" s="3" t="s">
+      <c r="B380" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C380" s="3" t="s">
@@ -11465,7 +11775,7 @@
       <c r="A381" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="B381" s="3" t="s">
+      <c r="B381" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C381" s="3" t="s">
@@ -11479,7 +11789,7 @@
       <c r="A382" s="2">
         <v>98288</v>
       </c>
-      <c r="B382" s="3" t="s">
+      <c r="B382" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C382" s="3" t="s">
@@ -11493,7 +11803,7 @@
       <c r="A383" s="2">
         <v>91836</v>
       </c>
-      <c r="B383" s="3" t="s">
+      <c r="B383" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C383" s="3" t="s">
@@ -11507,7 +11817,7 @@
       <c r="A384" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B384" s="3" t="s">
+      <c r="B384" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C384" s="3" t="s">
@@ -11521,7 +11831,7 @@
       <c r="A385" s="2">
         <v>97667</v>
       </c>
-      <c r="B385" s="3" t="s">
+      <c r="B385" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C385" s="3" t="s">
@@ -11535,7 +11845,7 @@
       <c r="A386" s="2">
         <v>97670</v>
       </c>
-      <c r="B386" s="3" t="s">
+      <c r="B386" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C386" s="3" t="s">
@@ -11549,7 +11859,7 @@
       <c r="A387" s="2">
         <v>97668</v>
       </c>
-      <c r="B387" s="3" t="s">
+      <c r="B387" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C387" s="3" t="s">
@@ -11563,7 +11873,7 @@
       <c r="A388" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B388" s="3" t="s">
+      <c r="B388" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C388" s="3" t="s">
@@ -11577,7 +11887,7 @@
       <c r="A389" s="2">
         <v>98308</v>
       </c>
-      <c r="B389" s="3" t="s">
+      <c r="B389" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C389" s="3" t="s">
@@ -11591,7 +11901,7 @@
       <c r="A390" s="2">
         <v>93661</v>
       </c>
-      <c r="B390" s="3" t="s">
+      <c r="B390" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C390" s="3" t="s">
@@ -11605,7 +11915,7 @@
       <c r="A391" s="2">
         <v>93655</v>
       </c>
-      <c r="B391" s="3" t="s">
+      <c r="B391" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C391" s="3" t="s">
@@ -11619,7 +11929,7 @@
       <c r="A392" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B392" s="3" t="s">
+      <c r="B392" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C392" s="3" t="s">
@@ -11633,7 +11943,7 @@
       <c r="A393" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="B393" s="3" t="s">
+      <c r="B393" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C393" s="3" t="s">
@@ -11647,7 +11957,7 @@
       <c r="A394" s="2">
         <v>93662</v>
       </c>
-      <c r="B394" s="3" t="s">
+      <c r="B394" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C394" s="3" t="s">
@@ -11661,7 +11971,7 @@
       <c r="A395" s="2">
         <v>93671</v>
       </c>
-      <c r="B395" s="3" t="s">
+      <c r="B395" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C395" s="3" t="s">
@@ -11675,7 +11985,7 @@
       <c r="A396" s="2">
         <v>101658</v>
       </c>
-      <c r="B396" s="3" t="s">
+      <c r="B396" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C396" s="3" t="s">
@@ -11689,7 +11999,7 @@
       <c r="A397" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="B397" s="3" t="s">
+      <c r="B397" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C397" s="3" t="s">
@@ -11703,7 +12013,7 @@
       <c r="A398" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="B398" s="3" t="s">
+      <c r="B398" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C398" s="3" t="s">
@@ -11717,7 +12027,7 @@
       <c r="A399" s="2">
         <v>93656</v>
       </c>
-      <c r="B399" s="3" t="s">
+      <c r="B399" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C399" s="3" t="s">
@@ -11731,7 +12041,7 @@
       <c r="A400" s="2">
         <v>93664</v>
       </c>
-      <c r="B400" s="3" t="s">
+      <c r="B400" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C400" s="3" t="s">
@@ -11745,7 +12055,7 @@
       <c r="A401" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="B401" s="3" t="s">
+      <c r="B401" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C401" s="3" t="s">
@@ -11759,7 +12069,7 @@
       <c r="A402" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B402" s="3" t="s">
+      <c r="B402" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C402" s="3" t="s">
@@ -11773,7 +12083,7 @@
       <c r="A403" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="B403" s="3" t="s">
+      <c r="B403" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C403" s="3" t="s">
@@ -11787,7 +12097,7 @@
       <c r="A404" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B404" s="3" t="s">
+      <c r="B404" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C404" s="3" t="s">
@@ -11801,7 +12111,7 @@
       <c r="A405" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="B405" s="3" t="s">
+      <c r="B405" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C405" s="3" t="s">
@@ -11815,7 +12125,7 @@
       <c r="A406" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="B406" s="3" t="s">
+      <c r="B406" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C406" s="3" t="s">
@@ -11829,7 +12139,7 @@
       <c r="A407" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B407" s="3" t="s">
+      <c r="B407" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C407" s="3" t="s">
@@ -11843,7 +12153,7 @@
       <c r="A408" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="B408" s="3" t="s">
+      <c r="B408" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C408" s="3" t="s">
@@ -11857,7 +12167,7 @@
       <c r="A409" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="B409" s="3" t="s">
+      <c r="B409" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C409" s="3" t="s">
@@ -11871,13 +12181,335 @@
       <c r="A410" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="B410" s="3" t="s">
+      <c r="B410" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C410" s="3" t="s">
         <v>803</v>
       </c>
       <c r="D410" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A411" s="2">
+        <v>93000</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C411" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="D411" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A412" s="2">
+        <v>93000</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C412" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="D412" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A413" s="2">
+        <v>93000</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C413" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="D413" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A414" s="2">
+        <v>93000</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C414" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="D414" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A415" s="2">
+        <v>92994</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C415" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D415" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A416" s="2">
+        <v>92994</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C416" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A417" s="2">
+        <v>92994</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D417" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A418" s="2">
+        <v>92994</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C418" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D418" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A419" s="2">
+        <v>92994</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C419" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D419" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A420" s="2">
+        <v>92990</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D420" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A421" s="2">
+        <v>92988</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C421" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D421" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A422" s="2">
+        <v>102990</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C422" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="D422" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A423" s="2">
+        <v>102991</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C423" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="D423" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A424" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C424" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="D424" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A425" s="1">
+        <v>97670</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C425" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A426" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C426" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="D426" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A427" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C427" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="D427" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A428" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C428" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="D428" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A429" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C429" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="D429" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A430" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C430" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="D430" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A431" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C431" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="D431" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A432" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C432" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="D432" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A433" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C433" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="D433" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67429BE-BE2F-4C15-8C1F-E60E12388063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA7EE60-54C3-4B7F-B3A6-D65C83186A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2353" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2359" uniqueCount="849">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2578,6 +2578,15 @@
   </si>
   <si>
     <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 800 A - 65 kA</t>
+  </si>
+  <si>
+    <t>Caixa de passagem - sobrepor - Aço pintada - ref Lukbox - 400x400x150 mm</t>
+  </si>
+  <si>
+    <t>Comp 869</t>
+  </si>
+  <si>
+    <t>CAIXA DE PASSAGEM METÁLICA DE EMBUTIR, 40X40X15 CM - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: AGETOP CIVIL 070645 - 11/2017)</t>
   </si>
 </sst>
 </file>
@@ -2964,7 +2973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B433"/>
+  <dimension ref="A1:B434"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -6435,6 +6444,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A434" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6442,7 +6459,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D433"/>
+  <dimension ref="A1:D434"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -12513,6 +12530,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="434" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A434" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C434" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="D434" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA7EE60-54C3-4B7F-B3A6-D65C83186A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D8EDD0-8513-4DDB-88D1-909684BAE087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2359" uniqueCount="849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2393" uniqueCount="864">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2587,6 +2587,51 @@
   </si>
   <si>
     <t>CAIXA DE PASSAGEM METÁLICA DE EMBUTIR, 40X40X15 CM - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: AGETOP CIVIL 070645 - 11/2017)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 32 A - 4,5 kA</t>
+  </si>
+  <si>
+    <t>Acessórios uso geral - Outros - Multimedidor de grandezas elétricas para painel</t>
+  </si>
+  <si>
+    <t>Comp 862</t>
+  </si>
+  <si>
+    <t>MEDIDOR DE GRANDEZAS ELÉTRICAS PARA PAINÉS MODULARES (COMPOSIÇÃO DE REFERÊNCIA: ORSE 12855 - 03/2025)</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -800x600x350mm</t>
+  </si>
+  <si>
+    <t>Comp 525</t>
+  </si>
+  <si>
+    <t>PAINEL MODULAR -800x600x350mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Unipolar Termomagnético - norma DIN - Curva C - 10 A - 3 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR MONOPOLAR TIPO DIN, CORRENTE NOMINAL DE 10A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva horizontal 90° - 200x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 324</t>
+  </si>
+  <si>
+    <t>CURVA HORIZONTAL 90º PARA ELETROCALHA, LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA DE 200MM E ALTURA DE 100MM - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97278 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, - DIN - Ref. Moratori - Cap. 24 disj. unip. - In barr. 150 A</t>
+  </si>
+  <si>
+    <t>Comp 241</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE EMBUTIR, COM BARRAMENTO TRIFÁSICO, PARA 24 DISJUNTORES DIN 150A - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REF.  101879 SINAPI 09/23)</t>
   </si>
 </sst>
 </file>
@@ -2973,7 +3018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B434"/>
+  <dimension ref="A1:B440"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -6452,6 +6497,54 @@
         <v>7</v>
       </c>
     </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A435" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A436" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A437" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A438" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A439" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A440" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6459,7 +6552,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D434"/>
+  <dimension ref="A1:D440"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -12544,6 +12637,90 @@
         <v>7</v>
       </c>
     </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A435" s="2">
+        <v>93671</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C435" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D435" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A436" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C436" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="D436" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A437" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C437" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="D437" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A438" s="2">
+        <v>93653</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C438" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="D438" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A439" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C439" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="D439" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A440" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C440" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="D440" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D8EDD0-8513-4DDB-88D1-909684BAE087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE17302-99BD-4A27-82E5-6237406B1AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2393" uniqueCount="864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="868">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2632,6 +2632,18 @@
   </si>
   <si>
     <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE EMBUTIR, COM BARRAMENTO TRIFÁSICO, PARA 24 DISJUNTORES DIN 150A - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REF.  101879 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Interruptor bipolar DR - fase/neutro - In 30mA - DIN - 40 A</t>
+  </si>
+  <si>
+    <t>DISJUNTOR BIPOLAR TIPO DIN, CORRENTE NOMINAL DE 40A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Comp 1086</t>
+  </si>
+  <si>
+    <t>DISJUNTOR BIPOLAR DR 100A TIPO AC 30MA - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: ORSE 7996 - 05/2023)</t>
   </si>
 </sst>
 </file>
@@ -3018,7 +3030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B440"/>
+  <dimension ref="A1:B442"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -6545,6 +6557,22 @@
         <v>7</v>
       </c>
     </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A441" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A442" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6552,7 +6580,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D440"/>
+  <dimension ref="A1:D442"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -12721,6 +12749,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A441" s="2">
+        <v>93675</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C441" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="D441" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A442" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C442" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="D442" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE17302-99BD-4A27-82E5-6237406B1AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FEF36A-D4E4-4EFE-A076-F26BF623EAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FEF36A-D4E4-4EFE-A076-F26BF623EAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD72434C-20E7-417F-A3C9-581F7339A9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="884">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2644,6 +2644,54 @@
   </si>
   <si>
     <t>DISJUNTOR BIPOLAR DR 100A TIPO AC 30MA - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: ORSE 7996 - 05/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Interruptor bipolar DR - fase/neutro - In 30mA - DIN - 100 A</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 160 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 806</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 160A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - sobrepor - Tomada de sobrepor - Tomada blindada 3P+T - 200A</t>
+  </si>
+  <si>
+    <t>Comp 2026</t>
+  </si>
+  <si>
+    <t>TOMADA INDUSTRIAL TRIFÁSICA, 3P+T, DE 200A (COMPOSIÇÃO REFERÊNCIA: SEDOP 170955 10/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - sobrepor - Tomada de sobrepor - Tomada blindada 3P+T - 125A</t>
+  </si>
+  <si>
+    <t>Comp 2025</t>
+  </si>
+  <si>
+    <t>TOMADA INDUSTRIAL TRIFÁSICA, 3P+T, DE 125A (COMPOSIÇÃO REFERÊNCIA: SEDOP 170955 10/2025)</t>
+  </si>
+  <si>
+    <t>Comp 2024</t>
+  </si>
+  <si>
+    <t>TOMADA INDUSTRIAL TRIFÁSICA, 3P+T, DE 63A (COMPOSIÇÃO REFERÊNCIA: SEDOP 170955 10/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - sobrepor - Tomada de sobrepor - Tomada blindada 3P+T - 63A</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - sobrepor - Tampa metálica p/ condulete - Tomada hexagonal - NBR 14136 - 2P+T 10A</t>
+  </si>
+  <si>
+    <t>Comp 2027</t>
+  </si>
+  <si>
+    <t>CONJUNTO PARA CONDULETE COM UMA (1) TOMADA,  TENSÃO 250V, (10A 250V) E PLACA DE UM (1) POSTO, INCLUSIVE FORNECIMENTO, INSTALAÇÃO, SUPORTE, MÓDULO E PLACA, SEM CONDULETE (COMPOSIÇÃP REFERÊNCIA: SETOP ED-17981 10/2025)</t>
   </si>
 </sst>
 </file>
@@ -3030,7 +3078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B442"/>
+  <dimension ref="A1:B447"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -6567,9 +6615,49 @@
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" s="3" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="B442" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A443" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A444" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="B444" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A445" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A446" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="B446" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A447" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="B447" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -6580,7 +6668,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D442"/>
+  <dimension ref="A1:D447"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -12777,6 +12865,76 @@
         <v>7</v>
       </c>
     </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A443" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C443" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="D443" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A444" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C444" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="D444" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A445" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C445" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="D445" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A446" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C446" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="D446" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A447" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C447" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="D447" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD72434C-20E7-417F-A3C9-581F7339A9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC676818-A977-40FA-9E0C-50A1769A0977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="889">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2692,6 +2692,21 @@
   </si>
   <si>
     <t>CONJUNTO PARA CONDULETE COM UMA (1) TOMADA,  TENSÃO 250V, (10A 250V) E PLACA DE UM (1) POSTO, INCLUSIVE FORNECIMENTO, INSTALAÇÃO, SUPORTE, MÓDULO E PLACA, SEM CONDULETE (COMPOSIÇÃP REFERÊNCIA: SETOP ED-17981 10/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios para telefonia - Canaleta de montagem - 1 módulo BLI-10</t>
+  </si>
+  <si>
+    <t>Quadro p/ telefonia - Caixa distribuição geral p/ telefonia - Nº 4 - A=60, L=60, P=12 - cm</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUICÃO PARA TELEFONE N.4, 60X60X12CM EM CHAPA METÁLICA, DE EMBUTIR, SEM ACESSÓRIOS, PADRÃO TELEBRAS - FORNECIMENTO E INSTALAÇÃO. AF_08/2025</t>
+  </si>
+  <si>
+    <t>Eletrocalha lisa tipo C pré-galv. quente - Suporte vertical - 120x146mm</t>
+  </si>
+  <si>
+    <t>Eletrocalha lisa tipo C pré-galv. quente - Tala plana perfurada - 100mm</t>
   </si>
 </sst>
 </file>
@@ -3078,7 +3093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B447"/>
+  <dimension ref="A1:B451"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -6661,6 +6676,38 @@
         <v>7</v>
       </c>
     </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A448" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="B448" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A449" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="B449" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A450" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="B450" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A451" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="B451" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6668,7 +6715,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D447"/>
+  <dimension ref="A1:D451"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -12935,6 +12982,62 @@
         <v>7</v>
       </c>
     </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A448" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C448" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="D448" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A449" s="2">
+        <v>100562</v>
+      </c>
+      <c r="B449" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C449" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="D449" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A450" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C450" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D450" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A451" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C451" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D451" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC676818-A977-40FA-9E0C-50A1769A0977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23CDC85-D2C2-4403-904B-4B8BC553A3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="899">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2707,6 +2707,36 @@
   </si>
   <si>
     <t>Eletrocalha lisa tipo C pré-galv. quente - Tala plana perfurada - 100mm</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva vertical interna 90° - 200x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 2031</t>
+  </si>
+  <si>
+    <t>CURVA VERTICAL INTERNA, 90º, PARA ELETROCALHA PERFURADA OU LISA, 200X100MM. FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: EMOP 15.018.0724-0 01/2026)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva vertical externa 90° - 200x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 2028</t>
+  </si>
+  <si>
+    <t>CURVA VERTICAL EXTERNA, 90º, PARA ELETROCALHA PERFURADA OU LISA, 200X100MM. FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: EMOP 15.018.0644-0 01/2026)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva vertical externa 90° - 100x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 2029</t>
+  </si>
+  <si>
+    <t>CURVA VERTICAL EXTERNA, 90º, PARA ELETROCALHA PERFURADA OU LISA, 100X100MM. FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: EMOP 15.018.0682-A 01/2026)</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 50mm</t>
   </si>
 </sst>
 </file>
@@ -3093,7 +3123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B451"/>
+  <dimension ref="A1:B455"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -6708,6 +6738,38 @@
         <v>7</v>
       </c>
     </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A452" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="B452" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A453" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="B453" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A454" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="B454" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A455" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="B455" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6715,7 +6777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D451"/>
+  <dimension ref="A1:D455"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -13038,6 +13100,62 @@
         <v>7</v>
       </c>
     </row>
+    <row r="452" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A452" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C452" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="D452" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A453" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C453" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="D453" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A454" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C454" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="D454" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A455" s="2">
+        <v>92988</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C455" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D455" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23CDC85-D2C2-4403-904B-4B8BC553A3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D32FD7-C216-44CA-B309-ADA3B46EB8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -1743,12 +1743,6 @@
     <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - TOMADA DE PISO 4X4 LATÃO, COM CAIXA E 2 MÓDULOS</t>
   </si>
   <si>
-    <t>Comp 922</t>
-  </si>
-  <si>
-    <t>TOMADA RJ45, 2 MÓDULOS,  INSTALADA NO PISO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA:ORSE  13604 - 11/2024)</t>
-  </si>
-  <si>
     <t>Comp 528</t>
   </si>
   <si>
@@ -2737,6 +2731,12 @@
   </si>
   <si>
     <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 50mm</t>
+  </si>
+  <si>
+    <t>Comp 903</t>
+  </si>
+  <si>
+    <t>TOMADA DE PISO 4X4 LATÃO, COM CAIXA E 2 MÓDULOS. (REFERÊNCIA: SBC 61526 01/2025)</t>
   </si>
 </sst>
 </file>
@@ -5236,7 +5236,7 @@
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>7</v>
@@ -5252,7 +5252,7 @@
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>7</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>7</v>
@@ -5268,7 +5268,7 @@
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>7</v>
@@ -5276,7 +5276,7 @@
     </row>
     <row r="269" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>7</v>
@@ -5284,7 +5284,7 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>7</v>
@@ -5292,7 +5292,7 @@
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>7</v>
@@ -5300,7 +5300,7 @@
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>7</v>
@@ -5308,7 +5308,7 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>7</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>7</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>7</v>
@@ -5332,7 +5332,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>7</v>
@@ -5340,7 +5340,7 @@
     </row>
     <row r="277" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>7</v>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>7</v>
@@ -5356,7 +5356,7 @@
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>7</v>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>7</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>7</v>
@@ -5388,7 +5388,7 @@
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>7</v>
@@ -5396,7 +5396,7 @@
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>7</v>
@@ -5404,7 +5404,7 @@
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>7</v>
@@ -5412,7 +5412,7 @@
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>7</v>
@@ -5420,7 +5420,7 @@
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>7</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>7</v>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>7</v>
@@ -5444,7 +5444,7 @@
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" s="3" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>7</v>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>7</v>
@@ -5460,7 +5460,7 @@
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>7</v>
@@ -5468,7 +5468,7 @@
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>20</v>
@@ -5476,7 +5476,7 @@
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>20</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>20</v>
@@ -5492,7 +5492,7 @@
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>20</v>
@@ -5500,7 +5500,7 @@
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>20</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>20</v>
@@ -5516,7 +5516,7 @@
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>20</v>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>20</v>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>20</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>20</v>
@@ -5548,7 +5548,7 @@
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>20</v>
@@ -5556,7 +5556,7 @@
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>20</v>
@@ -5564,7 +5564,7 @@
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>20</v>
@@ -5572,7 +5572,7 @@
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" s="3" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>20</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>20</v>
@@ -5588,7 +5588,7 @@
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>20</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B309" s="1" t="s">
         <v>20</v>
@@ -5604,7 +5604,7 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B310" s="1" t="s">
         <v>20</v>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>20</v>
@@ -5620,7 +5620,7 @@
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" s="3" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>20</v>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B313" s="1" t="s">
         <v>20</v>
@@ -5636,7 +5636,7 @@
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>20</v>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>20</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B316" s="1" t="s">
         <v>20</v>
@@ -5660,7 +5660,7 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B317" s="1" t="s">
         <v>20</v>
@@ -5668,7 +5668,7 @@
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B318" s="1" t="s">
         <v>20</v>
@@ -5676,7 +5676,7 @@
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>20</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>20</v>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>20</v>
@@ -5700,7 +5700,7 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>20</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>20</v>
@@ -5716,7 +5716,7 @@
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" s="3" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>20</v>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>20</v>
@@ -5732,7 +5732,7 @@
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>20</v>
@@ -5740,7 +5740,7 @@
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>20</v>
@@ -5748,7 +5748,7 @@
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>20</v>
@@ -5756,7 +5756,7 @@
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>20</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>20</v>
@@ -5772,7 +5772,7 @@
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>20</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>20</v>
@@ -5788,7 +5788,7 @@
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B333" s="1" t="s">
         <v>20</v>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" s="3" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>20</v>
@@ -5804,7 +5804,7 @@
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>20</v>
@@ -5812,7 +5812,7 @@
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>20</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>20</v>
@@ -5828,7 +5828,7 @@
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>20</v>
@@ -5836,7 +5836,7 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>20</v>
@@ -5844,7 +5844,7 @@
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>20</v>
@@ -5852,7 +5852,7 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B341" s="1" t="s">
         <v>20</v>
@@ -5860,7 +5860,7 @@
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>20</v>
@@ -5868,7 +5868,7 @@
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>20</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" s="3" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>20</v>
@@ -5884,7 +5884,7 @@
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>20</v>
@@ -5892,7 +5892,7 @@
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>20</v>
@@ -5900,7 +5900,7 @@
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B347" s="1" t="s">
         <v>20</v>
@@ -5908,7 +5908,7 @@
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>20</v>
@@ -5916,7 +5916,7 @@
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B349" s="1" t="s">
         <v>20</v>
@@ -5924,7 +5924,7 @@
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>20</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>20</v>
@@ -5940,7 +5940,7 @@
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>20</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>20</v>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>20</v>
@@ -5964,7 +5964,7 @@
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>20</v>
@@ -5972,7 +5972,7 @@
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>7</v>
@@ -5980,7 +5980,7 @@
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>20</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" s="3" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>20</v>
@@ -5996,7 +5996,7 @@
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>20</v>
@@ -6004,7 +6004,7 @@
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>7</v>
@@ -6012,7 +6012,7 @@
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>7</v>
@@ -6020,7 +6020,7 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>7</v>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>7</v>
@@ -6036,7 +6036,7 @@
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>7</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>20</v>
@@ -6052,7 +6052,7 @@
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>20</v>
@@ -6060,7 +6060,7 @@
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>7</v>
@@ -6068,7 +6068,7 @@
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>7</v>
@@ -6076,7 +6076,7 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>20</v>
@@ -6084,7 +6084,7 @@
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" s="3" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>7</v>
@@ -6092,7 +6092,7 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>7</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>7</v>
@@ -6108,7 +6108,7 @@
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>7</v>
@@ -6116,7 +6116,7 @@
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>7</v>
@@ -6124,7 +6124,7 @@
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>7</v>
@@ -6132,7 +6132,7 @@
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>7</v>
@@ -6140,7 +6140,7 @@
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>20</v>
@@ -6148,7 +6148,7 @@
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B378" s="1" t="s">
         <v>20</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>20</v>
@@ -6164,7 +6164,7 @@
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>20</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>20</v>
@@ -6180,7 +6180,7 @@
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>20</v>
@@ -6188,7 +6188,7 @@
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>20</v>
@@ -6196,7 +6196,7 @@
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>20</v>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>20</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>20</v>
@@ -6220,7 +6220,7 @@
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>20</v>
@@ -6228,7 +6228,7 @@
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>20</v>
@@ -6236,7 +6236,7 @@
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>7</v>
@@ -6244,7 +6244,7 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>7</v>
@@ -6252,7 +6252,7 @@
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>7</v>
@@ -6260,7 +6260,7 @@
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>7</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>7</v>
@@ -6276,7 +6276,7 @@
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>7</v>
@@ -6284,7 +6284,7 @@
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>7</v>
@@ -6292,7 +6292,7 @@
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" s="3" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>7</v>
@@ -6300,7 +6300,7 @@
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>7</v>
@@ -6308,7 +6308,7 @@
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>7</v>
@@ -6316,7 +6316,7 @@
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B399" s="1" t="s">
         <v>7</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>7</v>
@@ -6340,7 +6340,7 @@
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>7</v>
@@ -6348,7 +6348,7 @@
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>7</v>
@@ -6356,7 +6356,7 @@
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" s="3" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>7</v>
@@ -6364,7 +6364,7 @@
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>7</v>
@@ -6372,7 +6372,7 @@
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>7</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>7</v>
@@ -6388,7 +6388,7 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" s="3" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B408" s="1" t="s">
         <v>7</v>
@@ -6396,7 +6396,7 @@
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B409" s="1" t="s">
         <v>7</v>
@@ -6404,7 +6404,7 @@
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B410" s="1" t="s">
         <v>7</v>
@@ -6412,7 +6412,7 @@
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>20</v>
@@ -6420,7 +6420,7 @@
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>20</v>
@@ -6428,7 +6428,7 @@
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>20</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" s="3" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B414" s="1" t="s">
         <v>20</v>
@@ -6444,7 +6444,7 @@
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>20</v>
@@ -6452,7 +6452,7 @@
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>20</v>
@@ -6460,7 +6460,7 @@
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>20</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" s="3" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>20</v>
@@ -6476,7 +6476,7 @@
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>20</v>
@@ -6484,7 +6484,7 @@
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" s="3" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>20</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>20</v>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" s="3" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>20</v>
@@ -6508,7 +6508,7 @@
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>20</v>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>20</v>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>20</v>
@@ -6532,7 +6532,7 @@
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" s="3" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>7</v>
@@ -6540,7 +6540,7 @@
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>7</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>7</v>
@@ -6556,7 +6556,7 @@
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>7</v>
@@ -6564,7 +6564,7 @@
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430" s="3" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>7</v>
@@ -6572,7 +6572,7 @@
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>7</v>
@@ -6580,7 +6580,7 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" s="3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>7</v>
@@ -6588,7 +6588,7 @@
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>7</v>
@@ -6596,7 +6596,7 @@
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" s="3" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>7</v>
@@ -6612,7 +6612,7 @@
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" s="3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>7</v>
@@ -6620,7 +6620,7 @@
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>7</v>
@@ -6628,7 +6628,7 @@
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>7</v>
@@ -6636,7 +6636,7 @@
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>7</v>
@@ -6644,7 +6644,7 @@
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>7</v>
@@ -6652,7 +6652,7 @@
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>7</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>7</v>
@@ -6668,7 +6668,7 @@
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>7</v>
@@ -6676,7 +6676,7 @@
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444" s="3" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>7</v>
@@ -6684,7 +6684,7 @@
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>7</v>
@@ -6692,7 +6692,7 @@
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" s="3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>7</v>
@@ -6700,7 +6700,7 @@
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>7</v>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>7</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>7</v>
@@ -6724,7 +6724,7 @@
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>7</v>
@@ -6732,7 +6732,7 @@
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>7</v>
@@ -6748,7 +6748,7 @@
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>7</v>
@@ -6756,7 +6756,7 @@
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>7</v>
@@ -6764,7 +6764,7 @@
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>20</v>
@@ -10042,7 +10042,7 @@
         <v>68</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>7</v>
@@ -10456,13 +10456,13 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
-        <v>567</v>
+        <v>897</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>568</v>
+        <v>898</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>7</v>
@@ -10470,13 +10470,13 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>7</v>
@@ -10518,7 +10518,7 @@
         <v>5</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>7</v>
@@ -10588,7 +10588,7 @@
         <v>5</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>7</v>
@@ -10652,13 +10652,13 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>7</v>
@@ -10666,13 +10666,13 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>7</v>
@@ -10680,13 +10680,13 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>7</v>
@@ -10722,13 +10722,13 @@
     </row>
     <row r="282" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>7</v>
@@ -10750,13 +10750,13 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>7</v>
@@ -10806,13 +10806,13 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>7</v>
@@ -10820,13 +10820,13 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>7</v>
@@ -10834,13 +10834,13 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>7</v>
@@ -10862,13 +10862,13 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>7</v>
@@ -10896,7 +10896,7 @@
         <v>5</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>20</v>
@@ -10924,7 +10924,7 @@
         <v>5</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>20</v>
@@ -11134,7 +11134,7 @@
         <v>5</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>20</v>
@@ -11148,7 +11148,7 @@
         <v>5</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>20</v>
@@ -11162,7 +11162,7 @@
         <v>5</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>20</v>
@@ -11176,7 +11176,7 @@
         <v>5</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>20</v>
@@ -11246,7 +11246,7 @@
         <v>5</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>20</v>
@@ -11260,7 +11260,7 @@
         <v>5</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>20</v>
@@ -11274,7 +11274,7 @@
         <v>5</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>20</v>
@@ -11288,7 +11288,7 @@
         <v>5</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>20</v>
@@ -11722,7 +11722,7 @@
         <v>5</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>20</v>
@@ -11736,7 +11736,7 @@
         <v>5</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>20</v>
@@ -11750,7 +11750,7 @@
         <v>5</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D355" s="1" t="s">
         <v>20</v>
@@ -11758,13 +11758,13 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>7</v>
@@ -11786,13 +11786,13 @@
     </row>
     <row r="358" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>20</v>
@@ -11800,13 +11800,13 @@
     </row>
     <row r="359" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>20</v>
@@ -11814,13 +11814,13 @@
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>7</v>
@@ -11848,7 +11848,7 @@
         <v>5</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>7</v>
@@ -11862,7 +11862,7 @@
         <v>5</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>7</v>
@@ -11870,13 +11870,13 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>7</v>
@@ -11884,13 +11884,13 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>20</v>
@@ -11898,13 +11898,13 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>20</v>
@@ -11912,13 +11912,13 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>7</v>
@@ -11926,13 +11926,13 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D368" s="2" t="s">
         <v>7</v>
@@ -11940,13 +11940,13 @@
     </row>
     <row r="369" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>7</v>
@@ -11954,13 +11954,13 @@
     </row>
     <row r="370" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>7</v>
@@ -11968,13 +11968,13 @@
     </row>
     <row r="371" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>7</v>
@@ -11982,13 +11982,13 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D372" s="2" t="s">
         <v>7</v>
@@ -11996,13 +11996,13 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>7</v>
@@ -12010,13 +12010,13 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>7</v>
@@ -12024,13 +12024,13 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D375" s="2" t="s">
         <v>7</v>
@@ -12038,13 +12038,13 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D376" s="2" t="s">
         <v>7</v>
@@ -12058,7 +12058,7 @@
         <v>5</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D377" s="2" t="s">
         <v>20</v>
@@ -12072,7 +12072,7 @@
         <v>5</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>20</v>
@@ -12128,7 +12128,7 @@
         <v>5</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>20</v>
@@ -12198,7 +12198,7 @@
         <v>5</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D387" s="2" t="s">
         <v>20</v>
@@ -12226,7 +12226,7 @@
         <v>5</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D389" s="2" t="s">
         <v>7</v>
@@ -12276,13 +12276,13 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D393" s="2" t="s">
         <v>7</v>
@@ -12324,7 +12324,7 @@
         <v>5</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D396" s="2" t="s">
         <v>7</v>
@@ -12332,13 +12332,13 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D397" s="2" t="s">
         <v>7</v>
@@ -12346,13 +12346,13 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>7</v>
@@ -12366,7 +12366,7 @@
         <v>5</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D399" s="2" t="s">
         <v>7</v>
@@ -12388,13 +12388,13 @@
     </row>
     <row r="401" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D401" s="2" t="s">
         <v>7</v>
@@ -12416,13 +12416,13 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D403" s="2" t="s">
         <v>7</v>
@@ -12444,13 +12444,13 @@
     </row>
     <row r="405" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D405" s="2" t="s">
         <v>7</v>
@@ -12458,13 +12458,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>7</v>
@@ -12472,13 +12472,13 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>7</v>
@@ -12486,13 +12486,13 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D408" s="2" t="s">
         <v>7</v>
@@ -12500,13 +12500,13 @@
     </row>
     <row r="409" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D409" s="2" t="s">
         <v>7</v>
@@ -12514,13 +12514,13 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D410" s="2" t="s">
         <v>7</v>
@@ -12534,7 +12534,7 @@
         <v>5</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D411" s="2" t="s">
         <v>20</v>
@@ -12548,7 +12548,7 @@
         <v>5</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D412" s="2" t="s">
         <v>20</v>
@@ -12562,7 +12562,7 @@
         <v>5</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>20</v>
@@ -12576,7 +12576,7 @@
         <v>5</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D414" s="2" t="s">
         <v>20</v>
@@ -12688,7 +12688,7 @@
         <v>5</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D422" s="2" t="s">
         <v>20</v>
@@ -12702,7 +12702,7 @@
         <v>5</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D423" s="2" t="s">
         <v>20</v>
@@ -12710,13 +12710,13 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D424" s="2" t="s">
         <v>20</v>
@@ -12738,13 +12738,13 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D426" s="2" t="s">
         <v>7</v>
@@ -12752,13 +12752,13 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D427" s="2" t="s">
         <v>7</v>
@@ -12766,13 +12766,13 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D428" s="2" t="s">
         <v>7</v>
@@ -12780,13 +12780,13 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C429" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D429" s="2" t="s">
         <v>7</v>
@@ -12794,13 +12794,13 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D430" s="2" t="s">
         <v>7</v>
@@ -12808,13 +12808,13 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="D431" s="2" t="s">
         <v>7</v>
@@ -12822,13 +12822,13 @@
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D432" s="2" t="s">
         <v>7</v>
@@ -12836,13 +12836,13 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D433" s="2" t="s">
         <v>7</v>
@@ -12850,13 +12850,13 @@
     </row>
     <row r="434" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>7</v>
@@ -12878,13 +12878,13 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D436" s="2" t="s">
         <v>7</v>
@@ -12892,13 +12892,13 @@
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D437" s="2" t="s">
         <v>7</v>
@@ -12912,7 +12912,7 @@
         <v>5</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>7</v>
@@ -12920,13 +12920,13 @@
     </row>
     <row r="439" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D439" s="2" t="s">
         <v>7</v>
@@ -12934,13 +12934,13 @@
     </row>
     <row r="440" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D440" s="2" t="s">
         <v>7</v>
@@ -12954,7 +12954,7 @@
         <v>5</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D441" s="2" t="s">
         <v>7</v>
@@ -12962,13 +12962,13 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D442" s="2" t="s">
         <v>7</v>
@@ -12976,13 +12976,13 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>7</v>
@@ -12990,13 +12990,13 @@
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D444" s="2" t="s">
         <v>7</v>
@@ -13004,13 +13004,13 @@
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>7</v>
@@ -13018,13 +13018,13 @@
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D446" s="2" t="s">
         <v>7</v>
@@ -13032,13 +13032,13 @@
     </row>
     <row r="447" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D447" s="2" t="s">
         <v>7</v>
@@ -13046,13 +13046,13 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D448" s="2" t="s">
         <v>7</v>
@@ -13066,7 +13066,7 @@
         <v>5</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D449" s="2" t="s">
         <v>7</v>
@@ -13102,13 +13102,13 @@
     </row>
     <row r="452" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="D452" s="2" t="s">
         <v>7</v>
@@ -13116,13 +13116,13 @@
     </row>
     <row r="453" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D453" s="2" t="s">
         <v>7</v>
@@ -13130,13 +13130,13 @@
     </row>
     <row r="454" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C454" s="3" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D454" s="2" t="s">
         <v>7</v>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D32FD7-C216-44CA-B309-ADA3B46EB8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E801BAE8-1683-4AC0-A5B8-903A1483CD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="901">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -828,9 +828,6 @@
     <t>Eletrocalha furada tipo U pré-galv. quen - Acessórios para eletrocalha - Saída horizontal para eletroduto</t>
   </si>
   <si>
-    <t>CONDULETE DE ALUMÍNIO, TIPO X, PARA ELETRODUTO DE AÇO GALVANIZADO DN 32 MM (1 1/4&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022</t>
-  </si>
-  <si>
     <t>.S.O.S CAIXAS - Conduletes - CAIXA DE DERIVAÇÃO EM ALUMÍNIO SILÍCIO INJETADO, CONDULETE DE Ø1". FORNECIMENTO E INSTALAÇÃO.</t>
   </si>
   <si>
@@ -2737,6 +2734,15 @@
   </si>
   <si>
     <t>TOMADA DE PISO 4X4 LATÃO, COM CAIXA E 2 MÓDULOS. (REFERÊNCIA: SBC 61526 01/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete alum. encaixe tipo X - 1" sem tampa</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO X, PARA ELETRODUTO DE AÇO GALVANIZADO DN 32 MM (1 1/4"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO X, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
   </si>
 </sst>
 </file>
@@ -3123,7 +3129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B455"/>
+  <dimension ref="A1:B456"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -4076,7 +4082,7 @@
     </row>
     <row r="119" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>7</v>
@@ -4084,7 +4090,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>7</v>
@@ -4092,7 +4098,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>7</v>
@@ -4100,7 +4106,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>7</v>
@@ -4108,7 +4114,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>7</v>
@@ -4116,7 +4122,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>7</v>
@@ -4124,7 +4130,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>7</v>
@@ -4132,7 +4138,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>7</v>
@@ -4140,7 +4146,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>7</v>
@@ -4148,7 +4154,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>7</v>
@@ -4156,7 +4162,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>7</v>
@@ -4164,7 +4170,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>7</v>
@@ -4172,7 +4178,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>7</v>
@@ -4180,7 +4186,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>7</v>
@@ -4188,7 +4194,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>7</v>
@@ -4196,7 +4202,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>7</v>
@@ -4204,7 +4210,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>7</v>
@@ -4212,7 +4218,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>7</v>
@@ -4220,7 +4226,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>7</v>
@@ -4228,7 +4234,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>7</v>
@@ -4236,7 +4242,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>7</v>
@@ -4244,7 +4250,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>7</v>
@@ -4252,7 +4258,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>7</v>
@@ -4260,7 +4266,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>7</v>
@@ -4268,7 +4274,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>7</v>
@@ -4276,7 +4282,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>7</v>
@@ -4284,7 +4290,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>7</v>
@@ -4292,7 +4298,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>7</v>
@@ -4300,7 +4306,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>7</v>
@@ -4308,7 +4314,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>7</v>
@@ -4316,7 +4322,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>7</v>
@@ -4324,7 +4330,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>7</v>
@@ -4332,7 +4338,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>7</v>
@@ -4340,7 +4346,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>7</v>
@@ -4348,7 +4354,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>7</v>
@@ -4356,7 +4362,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>7</v>
@@ -4364,7 +4370,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>7</v>
@@ -4372,7 +4378,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>7</v>
@@ -4380,7 +4386,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>7</v>
@@ -4388,7 +4394,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>7</v>
@@ -4396,7 +4402,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>20</v>
@@ -4404,7 +4410,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>20</v>
@@ -4412,7 +4418,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>20</v>
@@ -4420,7 +4426,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>7</v>
@@ -4428,7 +4434,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>7</v>
@@ -4436,7 +4442,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>7</v>
@@ -4444,7 +4450,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>7</v>
@@ -4452,7 +4458,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>20</v>
@@ -4460,7 +4466,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>20</v>
@@ -4468,7 +4474,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>20</v>
@@ -4476,7 +4482,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>20</v>
@@ -4484,7 +4490,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>20</v>
@@ -4492,7 +4498,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>20</v>
@@ -4500,7 +4506,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>7</v>
@@ -4508,7 +4514,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>7</v>
@@ -4516,7 +4522,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>7</v>
@@ -4524,7 +4530,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>7</v>
@@ -4532,7 +4538,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>7</v>
@@ -4540,7 +4546,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>7</v>
@@ -4548,7 +4554,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>7</v>
@@ -4556,7 +4562,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>7</v>
@@ -4564,7 +4570,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>20</v>
@@ -4572,7 +4578,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>20</v>
@@ -4580,7 +4586,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>20</v>
@@ -4588,7 +4594,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>20</v>
@@ -4596,7 +4602,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>20</v>
@@ -4604,7 +4610,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>7</v>
@@ -4612,7 +4618,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>7</v>
@@ -4620,7 +4626,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>7</v>
@@ -4628,7 +4634,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>7</v>
@@ -4636,7 +4642,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>7</v>
@@ -4644,7 +4650,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>7</v>
@@ -4652,7 +4658,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>7</v>
@@ -4660,7 +4666,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>7</v>
@@ -4668,7 +4674,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>7</v>
@@ -4676,7 +4682,7 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>20</v>
@@ -4684,7 +4690,7 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>20</v>
@@ -4692,7 +4698,7 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>20</v>
@@ -4700,7 +4706,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>20</v>
@@ -4708,7 +4714,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>20</v>
@@ -4716,7 +4722,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>20</v>
@@ -4724,7 +4730,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>20</v>
@@ -4732,7 +4738,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>20</v>
@@ -4740,7 +4746,7 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>20</v>
@@ -4748,7 +4754,7 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>20</v>
@@ -4756,7 +4762,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>20</v>
@@ -4764,7 +4770,7 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>20</v>
@@ -4772,7 +4778,7 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>7</v>
@@ -4780,7 +4786,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>7</v>
@@ -4788,7 +4794,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>7</v>
@@ -4796,7 +4802,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>7</v>
@@ -4804,7 +4810,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>7</v>
@@ -4812,7 +4818,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>7</v>
@@ -4820,7 +4826,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>7</v>
@@ -4828,7 +4834,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>7</v>
@@ -4836,7 +4842,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>7</v>
@@ -4844,7 +4850,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>7</v>
@@ -4852,7 +4858,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>7</v>
@@ -4860,7 +4866,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>7</v>
@@ -4868,7 +4874,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>7</v>
@@ -4876,7 +4882,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>7</v>
@@ -4884,7 +4890,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>7</v>
@@ -4892,7 +4898,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>7</v>
@@ -4900,7 +4906,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>7</v>
@@ -4908,7 +4914,7 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>7</v>
@@ -4916,7 +4922,7 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>7</v>
@@ -4924,7 +4930,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>7</v>
@@ -4932,7 +4938,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>7</v>
@@ -4940,7 +4946,7 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>7</v>
@@ -4948,7 +4954,7 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>7</v>
@@ -4956,7 +4962,7 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>7</v>
@@ -4964,7 +4970,7 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>7</v>
@@ -4972,7 +4978,7 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>7</v>
@@ -4980,7 +4986,7 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>7</v>
@@ -4988,7 +4994,7 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>7</v>
@@ -4996,7 +5002,7 @@
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>7</v>
@@ -5004,7 +5010,7 @@
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>7</v>
@@ -5012,7 +5018,7 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>20</v>
@@ -5020,7 +5026,7 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>20</v>
@@ -5028,7 +5034,7 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>20</v>
@@ -5036,7 +5042,7 @@
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>20</v>
@@ -5044,7 +5050,7 @@
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>20</v>
@@ -5052,7 +5058,7 @@
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>20</v>
@@ -5060,7 +5066,7 @@
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>20</v>
@@ -5068,7 +5074,7 @@
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>20</v>
@@ -5076,7 +5082,7 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>20</v>
@@ -5084,7 +5090,7 @@
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>20</v>
@@ -5092,7 +5098,7 @@
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>20</v>
@@ -5100,7 +5106,7 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>20</v>
@@ -5108,7 +5114,7 @@
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>20</v>
@@ -5116,7 +5122,7 @@
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>20</v>
@@ -5124,7 +5130,7 @@
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>20</v>
@@ -5132,7 +5138,7 @@
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>20</v>
@@ -5140,7 +5146,7 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>20</v>
@@ -5148,7 +5154,7 @@
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>20</v>
@@ -5156,7 +5162,7 @@
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>20</v>
@@ -5164,7 +5170,7 @@
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>7</v>
@@ -5172,7 +5178,7 @@
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>20</v>
@@ -5180,7 +5186,7 @@
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>20</v>
@@ -5188,7 +5194,7 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>20</v>
@@ -5196,7 +5202,7 @@
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>20</v>
@@ -5204,7 +5210,7 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>20</v>
@@ -5212,7 +5218,7 @@
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>20</v>
@@ -5220,7 +5226,7 @@
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>20</v>
@@ -5228,7 +5234,7 @@
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>7</v>
@@ -5236,7 +5242,7 @@
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>7</v>
@@ -5244,7 +5250,7 @@
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>7</v>
@@ -5252,7 +5258,7 @@
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>7</v>
@@ -5260,7 +5266,7 @@
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>7</v>
@@ -5268,7 +5274,7 @@
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>7</v>
@@ -5276,7 +5282,7 @@
     </row>
     <row r="269" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>7</v>
@@ -5284,7 +5290,7 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>7</v>
@@ -5292,7 +5298,7 @@
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>7</v>
@@ -5300,7 +5306,7 @@
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>7</v>
@@ -5308,7 +5314,7 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>7</v>
@@ -5316,7 +5322,7 @@
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>7</v>
@@ -5324,7 +5330,7 @@
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>7</v>
@@ -5332,7 +5338,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>7</v>
@@ -5340,7 +5346,7 @@
     </row>
     <row r="277" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>7</v>
@@ -5348,7 +5354,7 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>7</v>
@@ -5356,7 +5362,7 @@
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>7</v>
@@ -5364,7 +5370,7 @@
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>7</v>
@@ -5372,7 +5378,7 @@
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>7</v>
@@ -5380,7 +5386,7 @@
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>7</v>
@@ -5388,7 +5394,7 @@
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>7</v>
@@ -5396,7 +5402,7 @@
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>7</v>
@@ -5404,7 +5410,7 @@
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>7</v>
@@ -5412,7 +5418,7 @@
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>7</v>
@@ -5420,7 +5426,7 @@
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>7</v>
@@ -5428,7 +5434,7 @@
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>7</v>
@@ -5436,7 +5442,7 @@
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>7</v>
@@ -5444,7 +5450,7 @@
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>7</v>
@@ -5452,7 +5458,7 @@
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>7</v>
@@ -5460,7 +5466,7 @@
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>7</v>
@@ -5468,7 +5474,7 @@
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>20</v>
@@ -5476,7 +5482,7 @@
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>20</v>
@@ -5484,7 +5490,7 @@
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>20</v>
@@ -5492,7 +5498,7 @@
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>20</v>
@@ -5500,7 +5506,7 @@
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>20</v>
@@ -5508,7 +5514,7 @@
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>20</v>
@@ -5516,7 +5522,7 @@
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>20</v>
@@ -5524,7 +5530,7 @@
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>20</v>
@@ -5532,7 +5538,7 @@
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>20</v>
@@ -5540,7 +5546,7 @@
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>20</v>
@@ -5548,7 +5554,7 @@
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>20</v>
@@ -5556,7 +5562,7 @@
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>20</v>
@@ -5564,7 +5570,7 @@
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>20</v>
@@ -5572,7 +5578,7 @@
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>20</v>
@@ -5580,7 +5586,7 @@
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>20</v>
@@ -5588,7 +5594,7 @@
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>20</v>
@@ -5596,7 +5602,7 @@
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B309" s="1" t="s">
         <v>20</v>
@@ -5604,7 +5610,7 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B310" s="1" t="s">
         <v>20</v>
@@ -5612,7 +5618,7 @@
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>20</v>
@@ -5620,7 +5626,7 @@
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>20</v>
@@ -5628,7 +5634,7 @@
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B313" s="1" t="s">
         <v>20</v>
@@ -5636,7 +5642,7 @@
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>20</v>
@@ -5644,7 +5650,7 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>20</v>
@@ -5652,7 +5658,7 @@
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B316" s="1" t="s">
         <v>20</v>
@@ -5660,7 +5666,7 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B317" s="1" t="s">
         <v>20</v>
@@ -5668,7 +5674,7 @@
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B318" s="1" t="s">
         <v>20</v>
@@ -5676,7 +5682,7 @@
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>20</v>
@@ -5684,7 +5690,7 @@
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>20</v>
@@ -5692,7 +5698,7 @@
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>20</v>
@@ -5700,7 +5706,7 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>20</v>
@@ -5708,7 +5714,7 @@
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>20</v>
@@ -5716,7 +5722,7 @@
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>20</v>
@@ -5724,7 +5730,7 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>20</v>
@@ -5732,7 +5738,7 @@
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>20</v>
@@ -5740,7 +5746,7 @@
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>20</v>
@@ -5748,7 +5754,7 @@
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>20</v>
@@ -5756,7 +5762,7 @@
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>20</v>
@@ -5764,7 +5770,7 @@
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>20</v>
@@ -5772,7 +5778,7 @@
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>20</v>
@@ -5780,7 +5786,7 @@
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>20</v>
@@ -5788,7 +5794,7 @@
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B333" s="1" t="s">
         <v>20</v>
@@ -5796,7 +5802,7 @@
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>20</v>
@@ -5804,7 +5810,7 @@
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>20</v>
@@ -5812,7 +5818,7 @@
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>20</v>
@@ -5820,7 +5826,7 @@
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>20</v>
@@ -5828,7 +5834,7 @@
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>20</v>
@@ -5836,7 +5842,7 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>20</v>
@@ -5844,7 +5850,7 @@
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>20</v>
@@ -5852,7 +5858,7 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B341" s="1" t="s">
         <v>20</v>
@@ -5860,7 +5866,7 @@
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>20</v>
@@ -5868,7 +5874,7 @@
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>20</v>
@@ -5876,7 +5882,7 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>20</v>
@@ -5884,7 +5890,7 @@
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>20</v>
@@ -5892,7 +5898,7 @@
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>20</v>
@@ -5900,7 +5906,7 @@
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B347" s="1" t="s">
         <v>20</v>
@@ -5908,7 +5914,7 @@
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>20</v>
@@ -5916,7 +5922,7 @@
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B349" s="1" t="s">
         <v>20</v>
@@ -5924,7 +5930,7 @@
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>20</v>
@@ -5932,7 +5938,7 @@
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>20</v>
@@ -5940,7 +5946,7 @@
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>20</v>
@@ -5948,7 +5954,7 @@
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>20</v>
@@ -5956,7 +5962,7 @@
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>20</v>
@@ -5964,7 +5970,7 @@
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>20</v>
@@ -5972,7 +5978,7 @@
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>7</v>
@@ -5980,7 +5986,7 @@
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>20</v>
@@ -5988,7 +5994,7 @@
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>20</v>
@@ -5996,7 +6002,7 @@
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>20</v>
@@ -6004,7 +6010,7 @@
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>7</v>
@@ -6012,7 +6018,7 @@
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>7</v>
@@ -6020,7 +6026,7 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>7</v>
@@ -6028,7 +6034,7 @@
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>7</v>
@@ -6036,7 +6042,7 @@
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>7</v>
@@ -6044,7 +6050,7 @@
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>20</v>
@@ -6052,7 +6058,7 @@
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>20</v>
@@ -6060,7 +6066,7 @@
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>7</v>
@@ -6068,7 +6074,7 @@
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>7</v>
@@ -6076,7 +6082,7 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>20</v>
@@ -6084,7 +6090,7 @@
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>7</v>
@@ -6092,7 +6098,7 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>7</v>
@@ -6100,7 +6106,7 @@
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>7</v>
@@ -6108,7 +6114,7 @@
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>7</v>
@@ -6116,7 +6122,7 @@
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>7</v>
@@ -6124,7 +6130,7 @@
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>7</v>
@@ -6132,7 +6138,7 @@
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>7</v>
@@ -6140,7 +6146,7 @@
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>20</v>
@@ -6148,7 +6154,7 @@
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B378" s="1" t="s">
         <v>20</v>
@@ -6156,7 +6162,7 @@
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>20</v>
@@ -6164,7 +6170,7 @@
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" s="3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>20</v>
@@ -6172,7 +6178,7 @@
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>20</v>
@@ -6180,7 +6186,7 @@
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>20</v>
@@ -6188,7 +6194,7 @@
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>20</v>
@@ -6196,7 +6202,7 @@
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384" s="3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>20</v>
@@ -6204,7 +6210,7 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>20</v>
@@ -6212,7 +6218,7 @@
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>20</v>
@@ -6220,7 +6226,7 @@
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>20</v>
@@ -6228,7 +6234,7 @@
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>20</v>
@@ -6236,7 +6242,7 @@
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>7</v>
@@ -6244,7 +6250,7 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>7</v>
@@ -6252,7 +6258,7 @@
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>7</v>
@@ -6260,7 +6266,7 @@
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>7</v>
@@ -6268,7 +6274,7 @@
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>7</v>
@@ -6276,7 +6282,7 @@
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>7</v>
@@ -6284,7 +6290,7 @@
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>7</v>
@@ -6292,7 +6298,7 @@
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>7</v>
@@ -6300,7 +6306,7 @@
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>7</v>
@@ -6308,7 +6314,7 @@
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>7</v>
@@ -6316,7 +6322,7 @@
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B399" s="1" t="s">
         <v>7</v>
@@ -6324,7 +6330,7 @@
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>7</v>
@@ -6332,7 +6338,7 @@
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>7</v>
@@ -6340,7 +6346,7 @@
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>7</v>
@@ -6348,7 +6354,7 @@
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>7</v>
@@ -6356,7 +6362,7 @@
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>7</v>
@@ -6364,7 +6370,7 @@
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>7</v>
@@ -6372,7 +6378,7 @@
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>7</v>
@@ -6380,7 +6386,7 @@
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>7</v>
@@ -6388,7 +6394,7 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B408" s="1" t="s">
         <v>7</v>
@@ -6396,7 +6402,7 @@
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B409" s="1" t="s">
         <v>7</v>
@@ -6404,7 +6410,7 @@
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B410" s="1" t="s">
         <v>7</v>
@@ -6412,7 +6418,7 @@
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>20</v>
@@ -6420,7 +6426,7 @@
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>20</v>
@@ -6428,7 +6434,7 @@
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>20</v>
@@ -6436,7 +6442,7 @@
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B414" s="1" t="s">
         <v>20</v>
@@ -6444,7 +6450,7 @@
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>20</v>
@@ -6452,7 +6458,7 @@
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>20</v>
@@ -6460,7 +6466,7 @@
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>20</v>
@@ -6468,7 +6474,7 @@
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>20</v>
@@ -6476,7 +6482,7 @@
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>20</v>
@@ -6484,7 +6490,7 @@
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>20</v>
@@ -6492,7 +6498,7 @@
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>20</v>
@@ -6500,7 +6506,7 @@
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>20</v>
@@ -6508,7 +6514,7 @@
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>20</v>
@@ -6516,7 +6522,7 @@
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>20</v>
@@ -6524,7 +6530,7 @@
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>20</v>
@@ -6532,7 +6538,7 @@
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" s="3" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>7</v>
@@ -6540,7 +6546,7 @@
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>7</v>
@@ -6548,7 +6554,7 @@
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" s="3" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>7</v>
@@ -6556,7 +6562,7 @@
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>7</v>
@@ -6564,7 +6570,7 @@
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430" s="3" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>7</v>
@@ -6572,7 +6578,7 @@
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>7</v>
@@ -6580,7 +6586,7 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>7</v>
@@ -6588,7 +6594,7 @@
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>7</v>
@@ -6596,7 +6602,7 @@
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>7</v>
@@ -6604,7 +6610,7 @@
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>7</v>
@@ -6612,7 +6618,7 @@
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>7</v>
@@ -6620,7 +6626,7 @@
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>7</v>
@@ -6628,7 +6634,7 @@
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438" s="3" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>7</v>
@@ -6636,7 +6642,7 @@
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>7</v>
@@ -6644,7 +6650,7 @@
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>7</v>
@@ -6652,7 +6658,7 @@
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>7</v>
@@ -6660,7 +6666,7 @@
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>7</v>
@@ -6668,7 +6674,7 @@
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>7</v>
@@ -6676,7 +6682,7 @@
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>7</v>
@@ -6684,7 +6690,7 @@
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>7</v>
@@ -6692,7 +6698,7 @@
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>7</v>
@@ -6700,7 +6706,7 @@
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>7</v>
@@ -6708,7 +6714,7 @@
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>7</v>
@@ -6716,7 +6722,7 @@
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>7</v>
@@ -6724,7 +6730,7 @@
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>7</v>
@@ -6732,7 +6738,7 @@
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>7</v>
@@ -6740,7 +6746,7 @@
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>7</v>
@@ -6748,7 +6754,7 @@
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>7</v>
@@ -6756,7 +6762,7 @@
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>7</v>
@@ -6764,10 +6770,18 @@
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A456" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="B456" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6777,7 +6791,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D455"/>
+  <dimension ref="A1:D456"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -8446,7 +8460,7 @@
         <v>5</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>262</v>
+        <v>899</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>7</v>
@@ -8454,13 +8468,13 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>7</v>
@@ -8468,13 +8482,13 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>7</v>
@@ -8482,13 +8496,13 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>7</v>
@@ -8496,13 +8510,13 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>7</v>
@@ -8510,13 +8524,13 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>7</v>
@@ -8524,13 +8538,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>7</v>
@@ -8538,13 +8552,13 @@
     </row>
     <row r="126" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>7</v>
@@ -8552,13 +8566,13 @@
     </row>
     <row r="127" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>7</v>
@@ -8566,13 +8580,13 @@
     </row>
     <row r="128" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>281</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>7</v>
@@ -8580,13 +8594,13 @@
     </row>
     <row r="129" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>7</v>
@@ -8594,13 +8608,13 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>7</v>
@@ -8608,13 +8622,13 @@
     </row>
     <row r="131" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>7</v>
@@ -8622,13 +8636,13 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C132" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>7</v>
@@ -8642,7 +8656,7 @@
         <v>5</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>7</v>
@@ -8656,7 +8670,7 @@
         <v>5</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>7</v>
@@ -8670,7 +8684,7 @@
         <v>5</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>7</v>
@@ -8684,7 +8698,7 @@
         <v>5</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>7</v>
@@ -8698,7 +8712,7 @@
         <v>5</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>7</v>
@@ -8706,13 +8720,13 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>7</v>
@@ -8720,13 +8734,13 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>7</v>
@@ -8734,13 +8748,13 @@
     </row>
     <row r="140" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>311</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>7</v>
@@ -8748,13 +8762,13 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>7</v>
@@ -8768,7 +8782,7 @@
         <v>5</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>7</v>
@@ -8776,13 +8790,13 @@
     </row>
     <row r="143" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C143" s="3" t="s">
         <v>318</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>319</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>7</v>
@@ -8790,13 +8804,13 @@
     </row>
     <row r="144" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C144" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>7</v>
@@ -8810,7 +8824,7 @@
         <v>5</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>7</v>
@@ -8824,7 +8838,7 @@
         <v>5</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>7</v>
@@ -8838,7 +8852,7 @@
         <v>5</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>7</v>
@@ -8852,7 +8866,7 @@
         <v>5</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>7</v>
@@ -8866,7 +8880,7 @@
         <v>5</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>7</v>
@@ -8874,13 +8888,13 @@
     </row>
     <row r="150" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C150" s="3" t="s">
         <v>332</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>333</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>7</v>
@@ -8888,13 +8902,13 @@
     </row>
     <row r="151" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C151" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>336</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>7</v>
@@ -8908,7 +8922,7 @@
         <v>5</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>7</v>
@@ -8922,7 +8936,7 @@
         <v>5</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>7</v>
@@ -8936,7 +8950,7 @@
         <v>5</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>7</v>
@@ -8950,7 +8964,7 @@
         <v>5</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>7</v>
@@ -8964,7 +8978,7 @@
         <v>5</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>7</v>
@@ -8978,7 +8992,7 @@
         <v>5</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>7</v>
@@ -8992,7 +9006,7 @@
         <v>5</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>7</v>
@@ -9006,7 +9020,7 @@
         <v>5</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>20</v>
@@ -9014,13 +9028,13 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C160" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>20</v>
@@ -9028,13 +9042,13 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C161" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>20</v>
@@ -9042,13 +9056,13 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>7</v>
@@ -9056,13 +9070,13 @@
     </row>
     <row r="163" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C163" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>364</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>7</v>
@@ -9070,13 +9084,13 @@
     </row>
     <row r="164" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C164" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>513</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>7</v>
@@ -9104,7 +9118,7 @@
         <v>5</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>20</v>
@@ -9118,7 +9132,7 @@
         <v>5</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>20</v>
@@ -9132,7 +9146,7 @@
         <v>5</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>20</v>
@@ -9146,7 +9160,7 @@
         <v>5</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>20</v>
@@ -9160,7 +9174,7 @@
         <v>5</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>20</v>
@@ -9168,13 +9182,13 @@
     </row>
     <row r="171" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C171" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>376</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>20</v>
@@ -9182,13 +9196,13 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C172" s="3" t="s">
         <v>378</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C172" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>7</v>
@@ -9196,13 +9210,13 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C173" s="3" t="s">
         <v>380</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>381</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>7</v>
@@ -9216,7 +9230,7 @@
         <v>5</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>7</v>
@@ -9224,13 +9238,13 @@
     </row>
     <row r="175" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>7</v>
@@ -9238,13 +9252,13 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C176" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>389</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>7</v>
@@ -9252,13 +9266,13 @@
     </row>
     <row r="177" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>7</v>
@@ -9272,7 +9286,7 @@
         <v>5</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>7</v>
@@ -9286,7 +9300,7 @@
         <v>5</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>7</v>
@@ -9294,13 +9308,13 @@
     </row>
     <row r="180" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C180" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C180" s="3" t="s">
-        <v>398</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>20</v>
@@ -9308,13 +9322,13 @@
     </row>
     <row r="181" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C181" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C181" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>20</v>
@@ -9322,13 +9336,13 @@
     </row>
     <row r="182" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C182" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C182" s="3" t="s">
-        <v>406</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>20</v>
@@ -9342,7 +9356,7 @@
         <v>5</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>20</v>
@@ -9350,13 +9364,13 @@
     </row>
     <row r="184" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C184" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C184" s="3" t="s">
-        <v>410</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>20</v>
@@ -9370,7 +9384,7 @@
         <v>5</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>7</v>
@@ -9378,13 +9392,13 @@
     </row>
     <row r="186" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>7</v>
@@ -9398,7 +9412,7 @@
         <v>5</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>7</v>
@@ -9412,7 +9426,7 @@
         <v>5</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>7</v>
@@ -9426,7 +9440,7 @@
         <v>5</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>7</v>
@@ -9440,7 +9454,7 @@
         <v>5</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>7</v>
@@ -9448,13 +9462,13 @@
     </row>
     <row r="191" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C191" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C191" s="3" t="s">
-        <v>426</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>7</v>
@@ -9462,13 +9476,13 @@
     </row>
     <row r="192" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C192" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C192" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>7</v>
@@ -9476,13 +9490,13 @@
     </row>
     <row r="193" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C193" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C193" s="3" t="s">
-        <v>431</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>7</v>
@@ -9496,7 +9510,7 @@
         <v>5</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>20</v>
@@ -9510,7 +9524,7 @@
         <v>5</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>20</v>
@@ -9524,7 +9538,7 @@
         <v>5</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>20</v>
@@ -9538,7 +9552,7 @@
         <v>5</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>20</v>
@@ -9552,7 +9566,7 @@
         <v>5</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>20</v>
@@ -9566,7 +9580,7 @@
         <v>5</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>20</v>
@@ -9580,7 +9594,7 @@
         <v>5</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>20</v>
@@ -9594,7 +9608,7 @@
         <v>5</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>20</v>
@@ -9608,7 +9622,7 @@
         <v>5</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>20</v>
@@ -9622,7 +9636,7 @@
         <v>5</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>20</v>
@@ -9630,13 +9644,13 @@
     </row>
     <row r="204" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C204" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C204" s="3" t="s">
-        <v>376</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>20</v>
@@ -9644,13 +9658,13 @@
     </row>
     <row r="205" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C205" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C205" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>20</v>
@@ -9658,13 +9672,13 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C206" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C206" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>7</v>
@@ -9672,13 +9686,13 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>7</v>
@@ -9686,13 +9700,13 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C208" s="3" t="s">
         <v>461</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C208" s="3" t="s">
-        <v>462</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>7</v>
@@ -9700,13 +9714,13 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C209" s="3" t="s">
         <v>464</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C209" s="3" t="s">
-        <v>465</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>7</v>
@@ -9714,13 +9728,13 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>7</v>
@@ -9728,13 +9742,13 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C211" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C211" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>7</v>
@@ -9742,13 +9756,13 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C212" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C212" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>7</v>
@@ -9756,13 +9770,13 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C213" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>476</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>7</v>
@@ -9770,13 +9784,13 @@
     </row>
     <row r="214" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C214" s="3" t="s">
         <v>479</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>480</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>7</v>
@@ -9784,13 +9798,13 @@
     </row>
     <row r="215" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>7</v>
@@ -9798,13 +9812,13 @@
     </row>
     <row r="216" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>7</v>
@@ -9812,13 +9826,13 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>7</v>
@@ -9832,7 +9846,7 @@
         <v>5</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>7</v>
@@ -9840,13 +9854,13 @@
     </row>
     <row r="219" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C219" s="3" t="s">
         <v>492</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C219" s="3" t="s">
-        <v>493</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>7</v>
@@ -9854,13 +9868,13 @@
     </row>
     <row r="220" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C220" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C220" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>7</v>
@@ -9874,7 +9888,7 @@
         <v>5</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>7</v>
@@ -9888,7 +9902,7 @@
         <v>5</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>7</v>
@@ -9902,7 +9916,7 @@
         <v>5</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>7</v>
@@ -9910,13 +9924,13 @@
     </row>
     <row r="224" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C224" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>511</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>7</v>
@@ -9924,13 +9938,13 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C225" s="3" t="s">
         <v>505</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C225" s="3" t="s">
-        <v>506</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>7</v>
@@ -9938,13 +9952,13 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C226" s="3" t="s">
         <v>508</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>509</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>7</v>
@@ -9958,7 +9972,7 @@
         <v>5</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>7</v>
@@ -9972,7 +9986,7 @@
         <v>5</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>7</v>
@@ -9980,13 +9994,13 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C229" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>7</v>
@@ -10008,13 +10022,13 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C231" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C231" s="3" t="s">
-        <v>523</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>7</v>
@@ -10022,13 +10036,13 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C232" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C232" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>7</v>
@@ -10036,13 +10050,13 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>7</v>
@@ -10050,13 +10064,13 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C234" s="3" t="s">
         <v>527</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C234" s="3" t="s">
-        <v>528</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>7</v>
@@ -10064,13 +10078,13 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C235" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C235" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>7</v>
@@ -10084,7 +10098,7 @@
         <v>5</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>20</v>
@@ -10098,7 +10112,7 @@
         <v>5</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>20</v>
@@ -10112,7 +10126,7 @@
         <v>5</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>20</v>
@@ -10126,7 +10140,7 @@
         <v>5</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>20</v>
@@ -10140,7 +10154,7 @@
         <v>5</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>20</v>
@@ -10154,7 +10168,7 @@
         <v>5</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>20</v>
@@ -10168,7 +10182,7 @@
         <v>5</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>20</v>
@@ -10182,7 +10196,7 @@
         <v>5</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>20</v>
@@ -10196,7 +10210,7 @@
         <v>5</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>20</v>
@@ -10210,7 +10224,7 @@
         <v>5</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>20</v>
@@ -10224,7 +10238,7 @@
         <v>5</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>20</v>
@@ -10238,7 +10252,7 @@
         <v>5</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>20</v>
@@ -10252,7 +10266,7 @@
         <v>5</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>20</v>
@@ -10266,7 +10280,7 @@
         <v>5</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>20</v>
@@ -10280,7 +10294,7 @@
         <v>5</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>20</v>
@@ -10294,7 +10308,7 @@
         <v>5</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>20</v>
@@ -10308,7 +10322,7 @@
         <v>5</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>20</v>
@@ -10322,7 +10336,7 @@
         <v>5</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>20</v>
@@ -10336,7 +10350,7 @@
         <v>5</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>20</v>
@@ -10364,7 +10378,7 @@
         <v>5</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>20</v>
@@ -10442,13 +10456,13 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C262" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C262" s="3" t="s">
-        <v>565</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>20</v>
@@ -10456,13 +10470,13 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C263" s="3" t="s">
         <v>897</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C263" s="3" t="s">
-        <v>898</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>7</v>
@@ -10470,13 +10484,13 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C264" s="3" t="s">
         <v>567</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C264" s="3" t="s">
-        <v>568</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>7</v>
@@ -10490,7 +10504,7 @@
         <v>5</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>7</v>
@@ -10518,7 +10532,7 @@
         <v>5</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>7</v>
@@ -10560,7 +10574,7 @@
         <v>5</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>7</v>
@@ -10574,7 +10588,7 @@
         <v>5</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>7</v>
@@ -10588,7 +10602,7 @@
         <v>5</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>7</v>
@@ -10602,7 +10616,7 @@
         <v>5</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>7</v>
@@ -10616,7 +10630,7 @@
         <v>5</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>7</v>
@@ -10630,7 +10644,7 @@
         <v>5</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>7</v>
@@ -10652,13 +10666,13 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C277" s="3" t="s">
         <v>585</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C277" s="3" t="s">
-        <v>586</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>7</v>
@@ -10666,13 +10680,13 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C278" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C278" s="3" t="s">
-        <v>589</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>7</v>
@@ -10680,13 +10694,13 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C279" s="3" t="s">
         <v>591</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C279" s="3" t="s">
-        <v>592</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>7</v>
@@ -10694,13 +10708,13 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C280" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C280" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>7</v>
@@ -10714,7 +10728,7 @@
         <v>5</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>7</v>
@@ -10722,13 +10736,13 @@
     </row>
     <row r="282" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C282" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C282" s="3" t="s">
-        <v>597</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>7</v>
@@ -10742,7 +10756,7 @@
         <v>5</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>7</v>
@@ -10750,13 +10764,13 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C284" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C284" s="3" t="s">
-        <v>601</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>7</v>
@@ -10806,13 +10820,13 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C288" s="3" t="s">
         <v>606</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C288" s="3" t="s">
-        <v>607</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>7</v>
@@ -10820,13 +10834,13 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C289" s="3" t="s">
         <v>609</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C289" s="3" t="s">
-        <v>610</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>7</v>
@@ -10834,13 +10848,13 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C290" s="3" t="s">
         <v>612</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C290" s="3" t="s">
-        <v>613</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>7</v>
@@ -10848,13 +10862,13 @@
     </row>
     <row r="291" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C291" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C291" s="3" t="s">
-        <v>364</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>7</v>
@@ -10862,13 +10876,13 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C292" s="3" t="s">
         <v>616</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C292" s="3" t="s">
-        <v>617</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>7</v>
@@ -10896,7 +10910,7 @@
         <v>5</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>20</v>
@@ -10924,7 +10938,7 @@
         <v>5</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>20</v>
@@ -10952,7 +10966,7 @@
         <v>5</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>20</v>
@@ -10980,7 +10994,7 @@
         <v>5</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>20</v>
@@ -10994,7 +11008,7 @@
         <v>5</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>20</v>
@@ -11134,7 +11148,7 @@
         <v>5</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>20</v>
@@ -11148,7 +11162,7 @@
         <v>5</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>20</v>
@@ -11162,7 +11176,7 @@
         <v>5</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>20</v>
@@ -11176,7 +11190,7 @@
         <v>5</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>20</v>
@@ -11246,7 +11260,7 @@
         <v>5</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>20</v>
@@ -11260,7 +11274,7 @@
         <v>5</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>20</v>
@@ -11274,7 +11288,7 @@
         <v>5</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>20</v>
@@ -11288,7 +11302,7 @@
         <v>5</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>20</v>
@@ -11400,7 +11414,7 @@
         <v>5</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>20</v>
@@ -11414,7 +11428,7 @@
         <v>5</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>20</v>
@@ -11428,7 +11442,7 @@
         <v>5</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D332" s="1" t="s">
         <v>20</v>
@@ -11442,7 +11456,7 @@
         <v>5</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>20</v>
@@ -11456,7 +11470,7 @@
         <v>5</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>20</v>
@@ -11540,7 +11554,7 @@
         <v>5</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>20</v>
@@ -11554,7 +11568,7 @@
         <v>5</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D341" s="1" t="s">
         <v>20</v>
@@ -11568,7 +11582,7 @@
         <v>5</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>20</v>
@@ -11652,7 +11666,7 @@
         <v>5</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>20</v>
@@ -11666,7 +11680,7 @@
         <v>5</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>20</v>
@@ -11680,7 +11694,7 @@
         <v>5</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>20</v>
@@ -11694,7 +11708,7 @@
         <v>5</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>20</v>
@@ -11708,7 +11722,7 @@
         <v>5</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>20</v>
@@ -11722,7 +11736,7 @@
         <v>5</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>20</v>
@@ -11736,7 +11750,7 @@
         <v>5</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>20</v>
@@ -11750,7 +11764,7 @@
         <v>5</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D355" s="1" t="s">
         <v>20</v>
@@ -11758,13 +11772,13 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C356" s="3" t="s">
         <v>685</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C356" s="3" t="s">
-        <v>686</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>7</v>
@@ -11786,13 +11800,13 @@
     </row>
     <row r="358" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C358" s="3" t="s">
         <v>689</v>
-      </c>
-      <c r="B358" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C358" s="3" t="s">
-        <v>690</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>20</v>
@@ -11800,13 +11814,13 @@
     </row>
     <row r="359" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C359" s="3" t="s">
         <v>692</v>
-      </c>
-      <c r="B359" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C359" s="3" t="s">
-        <v>693</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>20</v>
@@ -11814,13 +11828,13 @@
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C360" s="3" t="s">
         <v>695</v>
-      </c>
-      <c r="B360" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C360" s="3" t="s">
-        <v>696</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>7</v>
@@ -11834,7 +11848,7 @@
         <v>5</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>7</v>
@@ -11848,7 +11862,7 @@
         <v>5</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>7</v>
@@ -11862,7 +11876,7 @@
         <v>5</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>7</v>
@@ -11870,13 +11884,13 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C364" s="3" t="s">
         <v>703</v>
-      </c>
-      <c r="B364" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C364" s="3" t="s">
-        <v>704</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>7</v>
@@ -11884,13 +11898,13 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C365" s="3" t="s">
         <v>706</v>
-      </c>
-      <c r="B365" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C365" s="3" t="s">
-        <v>707</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>20</v>
@@ -11898,13 +11912,13 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C366" s="3" t="s">
         <v>709</v>
-      </c>
-      <c r="B366" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C366" s="3" t="s">
-        <v>710</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>20</v>
@@ -11912,13 +11926,13 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C367" s="3" t="s">
         <v>712</v>
-      </c>
-      <c r="B367" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C367" s="3" t="s">
-        <v>713</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>7</v>
@@ -11926,13 +11940,13 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C368" s="3" t="s">
         <v>715</v>
-      </c>
-      <c r="B368" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C368" s="3" t="s">
-        <v>716</v>
       </c>
       <c r="D368" s="2" t="s">
         <v>7</v>
@@ -11940,13 +11954,13 @@
     </row>
     <row r="369" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C369" s="3" t="s">
         <v>718</v>
-      </c>
-      <c r="B369" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C369" s="3" t="s">
-        <v>719</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>7</v>
@@ -11954,13 +11968,13 @@
     </row>
     <row r="370" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C370" s="3" t="s">
         <v>721</v>
-      </c>
-      <c r="B370" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C370" s="3" t="s">
-        <v>722</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>7</v>
@@ -11968,13 +11982,13 @@
     </row>
     <row r="371" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C371" s="3" t="s">
         <v>724</v>
-      </c>
-      <c r="B371" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C371" s="3" t="s">
-        <v>725</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>7</v>
@@ -11982,13 +11996,13 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C372" s="3" t="s">
         <v>727</v>
-      </c>
-      <c r="B372" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C372" s="3" t="s">
-        <v>728</v>
       </c>
       <c r="D372" s="2" t="s">
         <v>7</v>
@@ -11996,13 +12010,13 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C373" s="3" t="s">
         <v>730</v>
-      </c>
-      <c r="B373" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C373" s="3" t="s">
-        <v>731</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>7</v>
@@ -12010,13 +12024,13 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C374" s="3" t="s">
         <v>733</v>
-      </c>
-      <c r="B374" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C374" s="3" t="s">
-        <v>734</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>7</v>
@@ -12024,13 +12038,13 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C375" s="3" t="s">
         <v>736</v>
-      </c>
-      <c r="B375" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C375" s="3" t="s">
-        <v>737</v>
       </c>
       <c r="D375" s="2" t="s">
         <v>7</v>
@@ -12038,13 +12052,13 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C376" s="3" t="s">
         <v>739</v>
-      </c>
-      <c r="B376" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C376" s="3" t="s">
-        <v>740</v>
       </c>
       <c r="D376" s="2" t="s">
         <v>7</v>
@@ -12058,7 +12072,7 @@
         <v>5</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D377" s="2" t="s">
         <v>20</v>
@@ -12072,7 +12086,7 @@
         <v>5</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>20</v>
@@ -12108,13 +12122,13 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C381" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="B381" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C381" s="3" t="s">
-        <v>565</v>
       </c>
       <c r="D381" s="2" t="s">
         <v>20</v>
@@ -12128,7 +12142,7 @@
         <v>5</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>20</v>
@@ -12198,7 +12212,7 @@
         <v>5</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D387" s="2" t="s">
         <v>20</v>
@@ -12206,13 +12220,13 @@
     </row>
     <row r="388" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C388" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="B388" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C388" s="3" t="s">
-        <v>410</v>
       </c>
       <c r="D388" s="2" t="s">
         <v>20</v>
@@ -12226,7 +12240,7 @@
         <v>5</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D389" s="2" t="s">
         <v>7</v>
@@ -12262,13 +12276,13 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C392" s="3" t="s">
         <v>508</v>
-      </c>
-      <c r="B392" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C392" s="3" t="s">
-        <v>509</v>
       </c>
       <c r="D392" s="2" t="s">
         <v>7</v>
@@ -12276,13 +12290,13 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C393" s="3" t="s">
         <v>761</v>
-      </c>
-      <c r="B393" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C393" s="3" t="s">
-        <v>762</v>
       </c>
       <c r="D393" s="2" t="s">
         <v>7</v>
@@ -12296,7 +12310,7 @@
         <v>5</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D394" s="2" t="s">
         <v>7</v>
@@ -12324,7 +12338,7 @@
         <v>5</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D396" s="2" t="s">
         <v>7</v>
@@ -12332,13 +12346,13 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C397" s="3" t="s">
         <v>768</v>
-      </c>
-      <c r="B397" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C397" s="3" t="s">
-        <v>769</v>
       </c>
       <c r="D397" s="2" t="s">
         <v>7</v>
@@ -12346,13 +12360,13 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C398" s="3" t="s">
         <v>771</v>
-      </c>
-      <c r="B398" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C398" s="3" t="s">
-        <v>772</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>7</v>
@@ -12366,7 +12380,7 @@
         <v>5</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D399" s="2" t="s">
         <v>7</v>
@@ -12380,7 +12394,7 @@
         <v>5</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D400" s="2" t="s">
         <v>7</v>
@@ -12388,13 +12402,13 @@
     </row>
     <row r="401" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C401" s="3" t="s">
         <v>777</v>
-      </c>
-      <c r="B401" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C401" s="3" t="s">
-        <v>778</v>
       </c>
       <c r="D401" s="2" t="s">
         <v>7</v>
@@ -12416,13 +12430,13 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C403" s="3" t="s">
         <v>781</v>
-      </c>
-      <c r="B403" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C403" s="3" t="s">
-        <v>782</v>
       </c>
       <c r="D403" s="2" t="s">
         <v>7</v>
@@ -12430,13 +12444,13 @@
     </row>
     <row r="404" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C404" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="B404" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C404" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="D404" s="2" t="s">
         <v>7</v>
@@ -12444,13 +12458,13 @@
     </row>
     <row r="405" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C405" s="3" t="s">
         <v>785</v>
-      </c>
-      <c r="B405" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C405" s="3" t="s">
-        <v>786</v>
       </c>
       <c r="D405" s="2" t="s">
         <v>7</v>
@@ -12458,13 +12472,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C406" s="3" t="s">
         <v>788</v>
-      </c>
-      <c r="B406" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C406" s="3" t="s">
-        <v>789</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>7</v>
@@ -12472,13 +12486,13 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C407" s="3" t="s">
         <v>791</v>
-      </c>
-      <c r="B407" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C407" s="3" t="s">
-        <v>792</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>7</v>
@@ -12486,13 +12500,13 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C408" s="3" t="s">
         <v>794</v>
-      </c>
-      <c r="B408" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C408" s="3" t="s">
-        <v>795</v>
       </c>
       <c r="D408" s="2" t="s">
         <v>7</v>
@@ -12500,13 +12514,13 @@
     </row>
     <row r="409" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C409" s="3" t="s">
         <v>797</v>
-      </c>
-      <c r="B409" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C409" s="3" t="s">
-        <v>798</v>
       </c>
       <c r="D409" s="2" t="s">
         <v>7</v>
@@ -12514,13 +12528,13 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C410" s="3" t="s">
         <v>800</v>
-      </c>
-      <c r="B410" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C410" s="3" t="s">
-        <v>801</v>
       </c>
       <c r="D410" s="2" t="s">
         <v>7</v>
@@ -12534,7 +12548,7 @@
         <v>5</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D411" s="2" t="s">
         <v>20</v>
@@ -12548,7 +12562,7 @@
         <v>5</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D412" s="2" t="s">
         <v>20</v>
@@ -12562,7 +12576,7 @@
         <v>5</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>20</v>
@@ -12576,7 +12590,7 @@
         <v>5</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D414" s="2" t="s">
         <v>20</v>
@@ -12590,7 +12604,7 @@
         <v>5</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D415" s="2" t="s">
         <v>20</v>
@@ -12604,7 +12618,7 @@
         <v>5</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D416" s="2" t="s">
         <v>20</v>
@@ -12618,7 +12632,7 @@
         <v>5</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D417" s="2" t="s">
         <v>20</v>
@@ -12632,7 +12646,7 @@
         <v>5</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D418" s="2" t="s">
         <v>20</v>
@@ -12646,7 +12660,7 @@
         <v>5</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D419" s="2" t="s">
         <v>20</v>
@@ -12660,7 +12674,7 @@
         <v>5</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D420" s="2" t="s">
         <v>20</v>
@@ -12674,7 +12688,7 @@
         <v>5</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D421" s="2" t="s">
         <v>20</v>
@@ -12688,7 +12702,7 @@
         <v>5</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D422" s="2" t="s">
         <v>20</v>
@@ -12702,7 +12716,7 @@
         <v>5</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D423" s="2" t="s">
         <v>20</v>
@@ -12710,13 +12724,13 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C424" s="3" t="s">
         <v>819</v>
-      </c>
-      <c r="B424" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C424" s="3" t="s">
-        <v>820</v>
       </c>
       <c r="D424" s="2" t="s">
         <v>20</v>
@@ -12738,13 +12752,13 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C426" s="3" t="s">
         <v>823</v>
-      </c>
-      <c r="B426" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C426" s="3" t="s">
-        <v>824</v>
       </c>
       <c r="D426" s="2" t="s">
         <v>7</v>
@@ -12752,13 +12766,13 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C427" s="3" t="s">
         <v>826</v>
-      </c>
-      <c r="B427" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C427" s="3" t="s">
-        <v>827</v>
       </c>
       <c r="D427" s="2" t="s">
         <v>7</v>
@@ -12766,13 +12780,13 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C428" s="3" t="s">
         <v>829</v>
-      </c>
-      <c r="B428" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C428" s="3" t="s">
-        <v>830</v>
       </c>
       <c r="D428" s="2" t="s">
         <v>7</v>
@@ -12780,13 +12794,13 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C429" s="3" t="s">
         <v>832</v>
-      </c>
-      <c r="B429" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C429" s="3" t="s">
-        <v>833</v>
       </c>
       <c r="D429" s="2" t="s">
         <v>7</v>
@@ -12794,13 +12808,13 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C430" s="3" t="s">
         <v>835</v>
-      </c>
-      <c r="B430" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C430" s="3" t="s">
-        <v>836</v>
       </c>
       <c r="D430" s="2" t="s">
         <v>7</v>
@@ -12808,13 +12822,13 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C431" s="3" t="s">
         <v>838</v>
-      </c>
-      <c r="B431" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C431" s="3" t="s">
-        <v>839</v>
       </c>
       <c r="D431" s="2" t="s">
         <v>7</v>
@@ -12822,13 +12836,13 @@
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C432" s="3" t="s">
         <v>841</v>
-      </c>
-      <c r="B432" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C432" s="3" t="s">
-        <v>842</v>
       </c>
       <c r="D432" s="2" t="s">
         <v>7</v>
@@ -12836,13 +12850,13 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C433" s="3" t="s">
         <v>703</v>
-      </c>
-      <c r="B433" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C433" s="3" t="s">
-        <v>704</v>
       </c>
       <c r="D433" s="2" t="s">
         <v>7</v>
@@ -12850,13 +12864,13 @@
     </row>
     <row r="434" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C434" s="3" t="s">
         <v>845</v>
-      </c>
-      <c r="B434" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C434" s="3" t="s">
-        <v>846</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>7</v>
@@ -12878,13 +12892,13 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C436" s="3" t="s">
         <v>849</v>
-      </c>
-      <c r="B436" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C436" s="3" t="s">
-        <v>850</v>
       </c>
       <c r="D436" s="2" t="s">
         <v>7</v>
@@ -12892,13 +12906,13 @@
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C437" s="3" t="s">
         <v>852</v>
-      </c>
-      <c r="B437" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C437" s="3" t="s">
-        <v>853</v>
       </c>
       <c r="D437" s="2" t="s">
         <v>7</v>
@@ -12912,7 +12926,7 @@
         <v>5</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>7</v>
@@ -12920,13 +12934,13 @@
     </row>
     <row r="439" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C439" s="3" t="s">
         <v>857</v>
-      </c>
-      <c r="B439" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C439" s="3" t="s">
-        <v>858</v>
       </c>
       <c r="D439" s="2" t="s">
         <v>7</v>
@@ -12934,13 +12948,13 @@
     </row>
     <row r="440" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C440" s="3" t="s">
         <v>860</v>
-      </c>
-      <c r="B440" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C440" s="3" t="s">
-        <v>861</v>
       </c>
       <c r="D440" s="2" t="s">
         <v>7</v>
@@ -12954,7 +12968,7 @@
         <v>5</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D441" s="2" t="s">
         <v>7</v>
@@ -12962,13 +12976,13 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C442" s="3" t="s">
         <v>864</v>
-      </c>
-      <c r="B442" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C442" s="3" t="s">
-        <v>865</v>
       </c>
       <c r="D442" s="2" t="s">
         <v>7</v>
@@ -12976,13 +12990,13 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C443" s="3" t="s">
         <v>868</v>
-      </c>
-      <c r="B443" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C443" s="3" t="s">
-        <v>869</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>7</v>
@@ -12990,13 +13004,13 @@
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C444" s="3" t="s">
         <v>871</v>
-      </c>
-      <c r="B444" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C444" s="3" t="s">
-        <v>872</v>
       </c>
       <c r="D444" s="2" t="s">
         <v>7</v>
@@ -13004,13 +13018,13 @@
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C445" s="3" t="s">
         <v>874</v>
-      </c>
-      <c r="B445" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C445" s="3" t="s">
-        <v>875</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>7</v>
@@ -13018,13 +13032,13 @@
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C446" s="3" t="s">
         <v>876</v>
-      </c>
-      <c r="B446" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C446" s="3" t="s">
-        <v>877</v>
       </c>
       <c r="D446" s="2" t="s">
         <v>7</v>
@@ -13032,13 +13046,13 @@
     </row>
     <row r="447" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C447" s="3" t="s">
         <v>880</v>
-      </c>
-      <c r="B447" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C447" s="3" t="s">
-        <v>881</v>
       </c>
       <c r="D447" s="2" t="s">
         <v>7</v>
@@ -13046,13 +13060,13 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C448" s="3" t="s">
         <v>771</v>
-      </c>
-      <c r="B448" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C448" s="3" t="s">
-        <v>772</v>
       </c>
       <c r="D448" s="2" t="s">
         <v>7</v>
@@ -13066,7 +13080,7 @@
         <v>5</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D449" s="2" t="s">
         <v>7</v>
@@ -13088,13 +13102,13 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C451" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="B451" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C451" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="D451" s="2" t="s">
         <v>7</v>
@@ -13102,13 +13116,13 @@
     </row>
     <row r="452" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C452" s="3" t="s">
         <v>888</v>
-      </c>
-      <c r="B452" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C452" s="3" t="s">
-        <v>889</v>
       </c>
       <c r="D452" s="2" t="s">
         <v>7</v>
@@ -13116,13 +13130,13 @@
     </row>
     <row r="453" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C453" s="3" t="s">
         <v>891</v>
-      </c>
-      <c r="B453" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C453" s="3" t="s">
-        <v>892</v>
       </c>
       <c r="D453" s="2" t="s">
         <v>7</v>
@@ -13130,13 +13144,13 @@
     </row>
     <row r="454" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C454" s="3" t="s">
         <v>894</v>
-      </c>
-      <c r="B454" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C454" s="3" t="s">
-        <v>895</v>
       </c>
       <c r="D454" s="2" t="s">
         <v>7</v>
@@ -13150,10 +13164,24 @@
         <v>5</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D455" s="2" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A456" s="2">
+        <v>95802</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C456" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="D456" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E801BAE8-1683-4AC0-A5B8-903A1483CD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F894498-1DD3-4FCC-96F2-2497CBEC8416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2687" uniqueCount="951">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2742,7 +2742,157 @@
     <t>CONDULETE DE ALUMÍNIO, TIPO X, PARA ELETRODUTO DE AÇO GALVANIZADO DN 32 MM (1 1/4"), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2022</t>
   </si>
   <si>
-    <t>CONDULETE DE ALUMÍNIO, TIPO X, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+    <t>- Tomadas e Interruptores - Interruptores - Interruptor simples - 2 módulos</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO X, PARA ELETRODUTO DE AÇO GALVANIZADO DN 25 MM (1";), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>- Tomadas e Interruptores - Interruptores - Interruptor simples - 3 módulos</t>
+  </si>
+  <si>
+    <t>.S.O.S CAIXA DE PASSAGEM - EMBUTIR NO PISO - Alvenaria - 30x30x70 cm</t>
+  </si>
+  <si>
+    <t>- Luminárias LED - Refletores - 100W</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 1.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 1.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 1.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 1.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 1.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 10 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 10 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 10 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 10 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 10 MM², ANTI-CHAMA 450/750 V, PARA CIRCUITOS TERMINAIS - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 2.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 2.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 2.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 2.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 2.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 4 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 4 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 4 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 4 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 4 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 6 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 6 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 6 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 6 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 6 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Dispositivo de Comando - Relé fotoelétrico - 220V - 1000W c/ fotocélula</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva B - 10 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva C - 50 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR MONOPOLAR TIPO DIN, CORRENTE NOMINAL DE 50A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 40 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 380 V/220 V - DIN - Curva C - 40 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 40A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 40A - FORNECIMENTO E INSTALAÇÃO. AF_07/2026</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto pesado - 1.1/2" - Parede</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - Luminária Pública - Lâmpada 100W</t>
+  </si>
+  <si>
+    <t>Poste - Cônico duplo em Aço Galvanizado - 9 metros</t>
+  </si>
+  <si>
+    <t>POSTE DE AÇO CÔNICO CONTÍNUO CURVO DUPLO, FLANGEADO, H=9M - FORNECIMENTO E INSTALAÇÃO. AF_04/2025</t>
+  </si>
+  <si>
+    <t>Poste - Cônico em Aço Galvanizado - 9 metros</t>
+  </si>
+  <si>
+    <t>POSTE DE AÇO CÔNICO CONTÍNUO CURVO SIMPLES, FLANGEADO, H=9M - FORNECIMENTO E INSTALAÇÃO. AF_04/2025</t>
+  </si>
+  <si>
+    <t>Comp 1263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPORTE PARA 4 PÉTALAS PARA LUMINÁRIA DE ILUMINAÇÃO PÚBLICA - ( COMPOSIÇÃO REFERÊNCIA: AGETOP CIVIL 072369)  </t>
+  </si>
+  <si>
+    <t>- Luminárias LED - Iluminação pública - Poste de concreto 4 pétals</t>
+  </si>
+  <si>
+    <t>Comp 791</t>
+  </si>
+  <si>
+    <t>POSTE DE CONCRETO COM COMPRIMENTO NOMINAL DE 9 M, ENGASTAMENTO BASE CONCRETADA COM 1 M DE CONCRETO E 0,5 M DE SOLO . AF_11/2019 ( composição referencia: SINAPI 100603 01/2026)</t>
+  </si>
+  <si>
+    <t>Poste - Suporte - Suporte para 4 lumináriais tipo pétala</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 2,5mm</t>
   </si>
 </sst>
 </file>
@@ -2784,7 +2934,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2795,6 +2945,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3129,7 +3283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B456"/>
+  <dimension ref="A1:B496"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -6784,6 +6938,326 @@
         <v>7</v>
       </c>
     </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A457" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B457" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A458" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A459" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="B459" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A460" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A461" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A462" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A463" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="B463" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A464" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A465" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A466" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A467" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A468" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A469" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A470" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A471" s="5" t="s">
+        <v>916</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A472" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A473" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A474" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A475" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A476" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A477" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A478" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A479" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A480" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A481" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A482" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A483" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A484" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A485" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A486" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A487" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A488" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A489" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A490" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A491" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A492" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A493" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A494" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A495" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A496" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6791,7 +7265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D456"/>
+  <dimension ref="A1:D496"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -13178,10 +13652,570 @@
         <v>5</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D456" s="2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A457" s="2">
+        <v>91959</v>
+      </c>
+      <c r="B457" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C457" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D457" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A458" s="2">
+        <v>91967</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C458" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D458" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A459" s="2">
+        <v>97886</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D459" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A460" s="2">
+        <v>101657</v>
+      </c>
+      <c r="B460" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C460" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D460" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A461" s="2">
+        <v>91924</v>
+      </c>
+      <c r="B461" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C461" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D461" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A462" s="2">
+        <v>91924</v>
+      </c>
+      <c r="B462" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C462" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D462" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A463" s="2">
+        <v>91924</v>
+      </c>
+      <c r="B463" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C463" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D463" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A464" s="2">
+        <v>91924</v>
+      </c>
+      <c r="B464" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C464" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D464" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A465" s="2">
+        <v>91924</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C465" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D465" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A466" s="2">
+        <v>91932</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C466" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="D466" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A467" s="2">
+        <v>91932</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C467" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="D467" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A468" s="2">
+        <v>91932</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C468" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="D468" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A469" s="2">
+        <v>91932</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C469" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="D469" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A470" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C470" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D470" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A471" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B471" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C471" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D471" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A472" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B472" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C472" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D472" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A473" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B473" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C473" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D473" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A474" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B474" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C474" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D474" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A475" s="2">
+        <v>91928</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C475" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D475" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A476" s="2">
+        <v>91928</v>
+      </c>
+      <c r="B476" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C476" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D476" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A477" s="2">
+        <v>91928</v>
+      </c>
+      <c r="B477" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C477" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D477" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A478" s="2">
+        <v>91928</v>
+      </c>
+      <c r="B478" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C478" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D478" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A479" s="2">
+        <v>91928</v>
+      </c>
+      <c r="B479" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C479" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D479" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A480" s="2">
+        <v>91930</v>
+      </c>
+      <c r="B480" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C480" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="D480" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A481" s="2">
+        <v>91930</v>
+      </c>
+      <c r="B481" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C481" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="D481" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A482" s="2">
+        <v>91930</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C482" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="D482" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A483" s="2">
+        <v>91930</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C483" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="D483" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A484" s="2">
+        <v>91930</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C484" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="D484" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A485" s="2">
+        <v>101632</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C485" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D485" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A486" s="2">
+        <v>93653</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C486" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="D486" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A487" s="2">
+        <v>93659</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C487" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="D487" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A488" s="2">
+        <v>93672</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C488" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="D488" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A489" s="2">
+        <v>93672</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C489" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="D489" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A490" s="2">
+        <v>97667</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C490" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D490" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A491" s="2">
+        <v>101657</v>
+      </c>
+      <c r="B491" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C491" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D491" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A492" s="2">
+        <v>100621</v>
+      </c>
+      <c r="B492" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C492" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="D492" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A493" s="2">
+        <v>100620</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C493" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="D493" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A494" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C494" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D494" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A495" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="B495" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C495" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="D495" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A496" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B496" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C496" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D496" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F894498-1DD3-4FCC-96F2-2497CBEC8416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A5579D-9B20-4CA4-BBD8-39643B29419F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2687" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="960">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2893,6 +2893,33 @@
   </si>
   <si>
     <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 2,5mm</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - embutir - Barr. trif., disj geral, compacto - DIN - Ref. Moratori - Cap. 24 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE EMBUTIR, COM BARRAMENTO TRIFÁSICO, PARA 24 DISJUNTORES DIN 100A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - embutir - Sem barr. - DIN - Ref. Cemar - Cap. 16 disj. unip.</t>
+  </si>
+  <si>
+    <t>Comp 704</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE EMBUTIR, COM BARRAMENTO TRIFÁSICO, PARA 16 DISJUNTORES DIN 100A - FORNECIMENTO E INSTALAÇÃO. AF_10/2020  (COMPOSIÇÃO REFERÊNCIA: SINAPI 101883)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - embutir - Sem barr. - DIN - Ref. Cemar - Cap. 8 disj. unip.</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE LUZ EM PVC PARA 8 DISJUNTORES - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE EMBUTIR, COM BARRAMENTO TRIFÁSICO, PARA 12 DISJUNTORES DIN 100A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Quadro distrib. plástico - embutir - Barr. bif., - DIN - Ref. Hager - Cap. 12 disj. unip. - In Pente 100A</t>
   </si>
 </sst>
 </file>
@@ -3283,7 +3310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B496"/>
+  <dimension ref="A1:B500"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -7258,6 +7285,38 @@
         <v>20</v>
       </c>
     </row>
+    <row r="497" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A497" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="B497" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A498" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A499" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A500" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7265,7 +7324,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D496"/>
+  <dimension ref="A1:D500"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -14218,6 +14277,62 @@
         <v>20</v>
       </c>
     </row>
+    <row r="497" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A497" s="2">
+        <v>101879</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C497" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="D497" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A498" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="B498" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C498" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="D498" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A499" s="2">
+        <v>101872</v>
+      </c>
+      <c r="B499" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C499" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="D499" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A500" s="2">
+        <v>101875</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C500" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="D500" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A5579D-9B20-4CA4-BBD8-39643B29419F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2C4685-8766-44E1-BE99-ECE084952E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2776" uniqueCount="981">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2920,6 +2920,69 @@
   </si>
   <si>
     <t>Quadro distrib. plástico - embutir - Barr. bif., - DIN - Ref. Hager - Cap. 12 disj. unip. - In Pente 100A</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 4 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 1.5 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 2.5 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 25 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 25 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 25 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 25 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE ISOLADO, 25 MM², ANTI-CHAMA 450/750 V, INSTALADO EM ELETROCALHA OU PERFILADO - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto pesado - 3" - Piso</t>
+  </si>
+  <si>
+    <t>ELETRODUTO FLEXÍVEL CORRUGADO, PEAD, DN 90 (3"), PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 380 V/220 V - DIN - Curva C - 70 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>Comp 653</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 70A - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 93673 - 04/2023)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - embutir - Sem barr. - DIN - Ref. Moratori - Cap. 16 disj. unip.</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - embutir - Barr. trif., disj geral, compacto - DIN - Ref. Moratori - Cap. 48 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>Comp 1579</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE EMBUTIR, COM BARRAMENTO TRIFÁSICO, PARA 48 DISJUNTORES DIN 100A - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA SINAPI CÓD. 106023 08/2025)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - embutir - Sem barr. - DIN - Ref. Moratori - Cap. 4 disj. unip.</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE LUZ EM PVC PARA 4 DISJUNTORES - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 16 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE ISOLADO, 16 MM², ANTI-CHAMA 450/750 V, INSTALADO EM ELETROCALHA OU PERFILADO - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
   </si>
 </sst>
 </file>
@@ -3310,7 +3373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B500"/>
+  <dimension ref="A1:B513"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -7317,6 +7380,110 @@
         <v>7</v>
       </c>
     </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A501" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A502" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A503" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A504" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A505" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A506" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A507" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A508" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A509" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A510" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A511" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A512" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A513" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7324,7 +7491,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:D513"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -14333,6 +14500,188 @@
         <v>7</v>
       </c>
     </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A501" s="2">
+        <v>91928</v>
+      </c>
+      <c r="B501" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C501" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D501" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A502" s="2">
+        <v>91924</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C502" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D502" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A503" s="2">
+        <v>91926</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C503" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D503" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A504" s="2">
+        <v>101888</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C504" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="D504" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A505" s="2">
+        <v>101888</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C505" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="D505" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A506" s="2">
+        <v>101888</v>
+      </c>
+      <c r="B506" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C506" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="D506" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A507" s="2">
+        <v>101888</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C507" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="D507" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A508" s="2">
+        <v>97669</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C508" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="D508" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A509" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C509" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="D509" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A510" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C510" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="D510" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A511" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="B511" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C511" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="D511" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A512" s="2">
+        <v>101871</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C512" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="D512" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A513" s="2">
+        <v>101886</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C513" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="D513" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2C4685-8766-44E1-BE99-ECE084952E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186F3F62-E00F-4CE0-B94D-CE3E098F5715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2776" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="982">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2983,6 +2983,9 @@
   </si>
   <si>
     <t>CABO DE COBRE ISOLADO, 16 MM², ANTI-CHAMA 450/750 V, INSTALADO EM ELETROCALHA OU PERFILADO - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>- Tomadas e Interruptores - Interruptores - Interruptor simples - 1 módulo</t>
   </si>
 </sst>
 </file>
@@ -3373,7 +3376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B514"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -7484,6 +7487,14 @@
         <v>20</v>
       </c>
     </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A514" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7491,7 +7502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D513"/>
+  <dimension ref="A1:D514"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -14682,6 +14693,20 @@
         <v>20</v>
       </c>
     </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A514" s="2">
+        <v>91953</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C514" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D514" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186F3F62-E00F-4CE0-B94D-CE3E098F5715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06C85CC-A242-4B99-8B17-2E7E410B70B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="1017">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2986,6 +2986,111 @@
   </si>
   <si>
     <t>- Tomadas e Interruptores - Interruptores - Interruptor simples - 1 módulo</t>
+  </si>
+  <si>
+    <t>Bomba Hidráulica - Recalque - Schneider - Recalque - BC-92 S/T 1C 3/4CV R119</t>
+  </si>
+  <si>
+    <t>Comp 1440</t>
+  </si>
+  <si>
+    <t>BOMBA CENTRÍFUGA, TRIFÁSICA, 3/4 CV - FORNECIMENTO E INSTALAÇÃO. AF_12/2020 (COMPOSIÇÃO REFERÊNCIA: SINAPI 102118)</t>
+  </si>
+  <si>
+    <t>Metais - Hidrômetro individual - 1,5 m³/h - 3/4"</t>
+  </si>
+  <si>
+    <t>Comp 686</t>
+  </si>
+  <si>
+    <t>HIDRÔMETRO DN 3/4", 1,5 M3/H - FORNECIMENTO E INSTALAÇÃO. AF_03/2024 -( COMPOSIÇÃO REFERENCIA: SINAPI 95675)</t>
+  </si>
+  <si>
+    <t>Aço carbono - Bucha de redução concêntricas - 1 1/4"-1"</t>
+  </si>
+  <si>
+    <t>Comp 1439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA DE REDUÇÃO, EM FERRO GALVANIZADO, 1 1/4" X 1", CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 (COMPOSIÇÃO REFERÊNCIA: SINAPI 92925) </t>
+  </si>
+  <si>
+    <t>Metais - Registro esfera VS compacto soldável PVC - 25 mm</t>
+  </si>
+  <si>
+    <t>REGISTRO DE ESFERA, PVC, SOLDÁVEL, COM VOLANTE, DN 25 MM - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>Metais - Registro esfera VS compacto soldável PVC - 32 mm</t>
+  </si>
+  <si>
+    <t>REGISTRO DE ESFERA, PVC, SOLDÁVEL, COM VOLANTE, DN 32 MM - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>Metais - Registro esfera VS compacto soldável PVC - 40 mm</t>
+  </si>
+  <si>
+    <t>Metais - Registro esfera VS compacto soldável PVC - 50 mm</t>
+  </si>
+  <si>
+    <t>REGISTRO DE ESFERA, PVC, SOLDÁVEL, COM VOLANTE, DN 40 MM - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>REGISTRO DE ESFERA, PVC, SOLDÁVEL, COM VOLANTE, DN 50 MM - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tubos - 25 mm</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tubos - 32 mm</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tubos - 40 mm</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tubos - 50 mm</t>
+  </si>
+  <si>
+    <t>TUBO, PVC, SOLDÁVEL, DE 25MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>TUBO, PVC, SOLDÁVEL, DE 32MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>TUBO, PVC, SOLDÁVEL, DE 40MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>TUBO, PVC, SOLDÁVEL, DE 50MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>Metais - Registro de gaveta bruto ABNT - 3/4"</t>
+  </si>
+  <si>
+    <t>REGISTRO DE GAVETA BRUTO, LATÃO, ROSCÁVEL, 3/4" - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>Metais - Registro de pressão c/ canopla cromada - 3/4"</t>
+  </si>
+  <si>
+    <t>REGISTRO DE PRESSÃO BRUTO, LATÃO, ROSCÁVEL, 3/4", COM ACABAMENTO E CANOPLA CROMADOS - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>PVC Acessórios - Engate flexível cobre cromado com canopla - 1/2 - 30cm</t>
+  </si>
+  <si>
+    <t>ENGATE FLEXÍVEL EM INOX, 1/2 X 30CM - FORNECIMENTO E INSTALAÇÃO. AF_01/2020</t>
+  </si>
+  <si>
+    <t>PVC Acessórios - Engate flexível plástico - 1/2 - 30cm</t>
+  </si>
+  <si>
+    <t>ENGATE FLEXÍVEL EM PLÁSTICO BRANCO, 1/2" X 30CM - FORNECIMENTO E INSTALAÇÃO. AF_01/2020</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Adapt sold.curto c/bolsa-rosca p registro - 25 mm - 3/4"</t>
+  </si>
+  <si>
+    <t>ADAPTADOR CURTO COM BOLSA E ROSCA PARA REGISTRO, PVC, SOLDÁVEL, DN 25MM X 3/4, INSTALADO EM RAMAL OU SUB-RAMAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
   </si>
 </sst>
 </file>
@@ -3027,7 +3132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3041,7 +3146,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3376,7 +3480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B530"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -7064,7 +7168,7 @@
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A461" s="5" t="s">
+      <c r="A461" t="s">
         <v>905</v>
       </c>
       <c r="B461" s="1" t="s">
@@ -7072,7 +7176,7 @@
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A462" s="5" t="s">
+      <c r="A462" t="s">
         <v>906</v>
       </c>
       <c r="B462" s="1" t="s">
@@ -7080,7 +7184,7 @@
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A463" s="5" t="s">
+      <c r="A463" t="s">
         <v>907</v>
       </c>
       <c r="B463" s="1" t="s">
@@ -7088,7 +7192,7 @@
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A464" s="5" t="s">
+      <c r="A464" t="s">
         <v>908</v>
       </c>
       <c r="B464" s="1" t="s">
@@ -7096,7 +7200,7 @@
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A465" s="5" t="s">
+      <c r="A465" t="s">
         <v>909</v>
       </c>
       <c r="B465" s="1" t="s">
@@ -7104,7 +7208,7 @@
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A466" s="5" t="s">
+      <c r="A466" t="s">
         <v>910</v>
       </c>
       <c r="B466" s="1" t="s">
@@ -7112,7 +7216,7 @@
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A467" s="5" t="s">
+      <c r="A467" t="s">
         <v>911</v>
       </c>
       <c r="B467" s="1" t="s">
@@ -7120,7 +7224,7 @@
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A468" s="5" t="s">
+      <c r="A468" t="s">
         <v>912</v>
       </c>
       <c r="B468" s="1" t="s">
@@ -7128,7 +7232,7 @@
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A469" s="5" t="s">
+      <c r="A469" t="s">
         <v>913</v>
       </c>
       <c r="B469" s="1" t="s">
@@ -7136,7 +7240,7 @@
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A470" s="5" t="s">
+      <c r="A470" t="s">
         <v>915</v>
       </c>
       <c r="B470" s="1" t="s">
@@ -7144,7 +7248,7 @@
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A471" s="5" t="s">
+      <c r="A471" t="s">
         <v>916</v>
       </c>
       <c r="B471" s="1" t="s">
@@ -7152,7 +7256,7 @@
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A472" s="5" t="s">
+      <c r="A472" t="s">
         <v>917</v>
       </c>
       <c r="B472" s="1" t="s">
@@ -7160,7 +7264,7 @@
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A473" s="5" t="s">
+      <c r="A473" t="s">
         <v>918</v>
       </c>
       <c r="B473" s="1" t="s">
@@ -7168,7 +7272,7 @@
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A474" s="5" t="s">
+      <c r="A474" t="s">
         <v>919</v>
       </c>
       <c r="B474" s="1" t="s">
@@ -7176,7 +7280,7 @@
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A475" s="5" t="s">
+      <c r="A475" t="s">
         <v>920</v>
       </c>
       <c r="B475" s="1" t="s">
@@ -7184,7 +7288,7 @@
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A476" s="5" t="s">
+      <c r="A476" t="s">
         <v>921</v>
       </c>
       <c r="B476" s="1" t="s">
@@ -7192,7 +7296,7 @@
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A477" s="5" t="s">
+      <c r="A477" t="s">
         <v>922</v>
       </c>
       <c r="B477" s="1" t="s">
@@ -7200,7 +7304,7 @@
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A478" s="5" t="s">
+      <c r="A478" t="s">
         <v>923</v>
       </c>
       <c r="B478" s="1" t="s">
@@ -7208,7 +7312,7 @@
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A479" s="5" t="s">
+      <c r="A479" t="s">
         <v>924</v>
       </c>
       <c r="B479" s="1" t="s">
@@ -7216,7 +7320,7 @@
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A480" s="5" t="s">
+      <c r="A480" t="s">
         <v>925</v>
       </c>
       <c r="B480" s="1" t="s">
@@ -7224,7 +7328,7 @@
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A481" s="5" t="s">
+      <c r="A481" t="s">
         <v>926</v>
       </c>
       <c r="B481" s="1" t="s">
@@ -7232,7 +7336,7 @@
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A482" s="5" t="s">
+      <c r="A482" t="s">
         <v>927</v>
       </c>
       <c r="B482" s="1" t="s">
@@ -7240,7 +7344,7 @@
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A483" s="5" t="s">
+      <c r="A483" t="s">
         <v>928</v>
       </c>
       <c r="B483" s="1" t="s">
@@ -7248,7 +7352,7 @@
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A484" s="5" t="s">
+      <c r="A484" t="s">
         <v>929</v>
       </c>
       <c r="B484" s="1" t="s">
@@ -7256,7 +7360,7 @@
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A485" s="5" t="s">
+      <c r="A485" t="s">
         <v>930</v>
       </c>
       <c r="B485" s="1" t="s">
@@ -7492,6 +7596,134 @@
         <v>981</v>
       </c>
       <c r="B514" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A515" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A516" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A517" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A518" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A519" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A520" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A521" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A522" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A523" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A524" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A525" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A526" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A527" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A528" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A529" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A530" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B530" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -7502,7 +7734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D514"/>
+  <dimension ref="A1:D530"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -14707,6 +14939,230 @@
         <v>7</v>
       </c>
     </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A515" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C515" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="D515" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A516" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C516" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A517" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C517" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="D517" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A518" s="2">
+        <v>94489</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C518" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="D518" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A519" s="2">
+        <v>94490</v>
+      </c>
+      <c r="B519" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C519" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="D519" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A520" s="2">
+        <v>94491</v>
+      </c>
+      <c r="B520" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C520" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="D520" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A521" s="2">
+        <v>94492</v>
+      </c>
+      <c r="B521" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C521" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="D521" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A522" s="2">
+        <v>89402</v>
+      </c>
+      <c r="B522" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C522" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D522" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A523" s="2">
+        <v>89403</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C523" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D523" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A524" s="2">
+        <v>103978</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C524" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D524" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A525" s="2">
+        <v>103979</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C525" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D525" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A526" s="2">
+        <v>89353</v>
+      </c>
+      <c r="B526" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C526" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D526" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A527" s="2">
+        <v>89985</v>
+      </c>
+      <c r="B527" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C527" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D527" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A528" s="2">
+        <v>86886</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C528" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D528" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A529" s="2">
+        <v>86884</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C529" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D529" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A530" s="2">
+        <v>89383</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C530" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D530" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06C85CC-A242-4B99-8B17-2E7E410B70B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE96BF86-3AE2-4AD1-BCAA-3A8EBCBC88A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2881" uniqueCount="1024">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3091,6 +3091,27 @@
   </si>
   <si>
     <t>ADAPTADOR CURTO COM BOLSA E ROSCA PARA REGISTRO, PVC, SOLDÁVEL, DN 25MM X 3/4, INSTALADO EM RAMAL OU SUB-RAMAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Adapt sold. c/ flange livre p/ cx. d´água - 50 mm- 1.1/2"</t>
+  </si>
+  <si>
+    <t>ADAPTADOR COM FLANGE E ANEL DE VEDAÇÃO, PVC, SOLDÁVEL, DN 50 MM X 1 1/2", INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Adapt sold.curto c/bolsa-rosca p registro - 32 mm - 1"</t>
+  </si>
+  <si>
+    <t>ADAPTADOR CURTO COM BOLSA E ROSCA PARA REGISTRO, PVC, SOLDÁVEL, DN 32MM X 1, INSTALADO EM RAMAL OU SUB-RAMAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Adapt sold.curto c/bolsa-rosca p registro - 40 mm - 1.1/4"</t>
+  </si>
+  <si>
+    <t>ADAPTADOR CURTO COM BOLSA E ROSCA PARA REGISTRO, PVC, SOLDÁVEL, DN 40MM X 1.1/2", INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Adapt sold c/ flange fixo p cx. d´água - 40 mm - 1.1/4"</t>
   </si>
 </sst>
 </file>
@@ -3480,7 +3501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B534"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -7727,6 +7748,38 @@
         <v>7</v>
       </c>
     </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A531" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A532" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A533" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A534" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7734,7 +7787,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D530"/>
+  <dimension ref="A1:D533"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -15163,6 +15216,48 @@
         <v>7</v>
       </c>
     </row>
+    <row r="531" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A531" s="2">
+        <v>94706</v>
+      </c>
+      <c r="B531" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C531" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D531" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A532" s="2">
+        <v>89391</v>
+      </c>
+      <c r="B532" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C532" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D532" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A533" s="2">
+        <v>103994</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C533" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D533" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE96BF86-3AE2-4AD1-BCAA-3A8EBCBC88A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1834F3E5-9C41-4569-9E55-1B4725C37BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2881" uniqueCount="1024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2909" uniqueCount="1030">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3112,6 +3112,24 @@
   </si>
   <si>
     <t>PVC rígido soldável - Adapt sold c/ flange fixo p cx. d´água - 40 mm - 1.1/4"</t>
+  </si>
+  <si>
+    <t>ADAPTADOR COM FLANGE E ANEL DE VEDAÇÃO, PVC, SOLDÁVEL, DN 40 MM X 1 1/4", INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 95 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 95 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 95 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 95 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 50 mm² - Verde-amarelo</t>
   </si>
 </sst>
 </file>
@@ -3501,7 +3519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B534"/>
+  <dimension ref="A1:B539"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -7780,6 +7798,46 @@
         <v>7</v>
       </c>
     </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A535" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A536" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A537" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A538" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A539" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7787,7 +7845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D533"/>
+  <dimension ref="A1:D539"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -15258,6 +15316,90 @@
         <v>7</v>
       </c>
     </row>
+    <row r="534" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A534" s="2">
+        <v>94705</v>
+      </c>
+      <c r="B534" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C534" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D534" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A535" s="2">
+        <v>92992</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C535" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D535" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A536" s="2">
+        <v>92992</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C536" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D536" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A537" s="2">
+        <v>92992</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C537" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D537" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A538" s="2">
+        <v>92992</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C538" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D538" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A539" s="2">
+        <v>92988</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C539" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D539" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1834F3E5-9C41-4569-9E55-1B4725C37BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C47BDA1-88D2-4C5E-8951-1814288CA90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2909" uniqueCount="1030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="1031">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3130,6 +3130,9 @@
   </si>
   <si>
     <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 50 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 700 A - 50 kA</t>
   </si>
 </sst>
 </file>
@@ -3519,7 +3522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B539"/>
+  <dimension ref="A1:B540"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -7838,6 +7841,14 @@
         <v>20</v>
       </c>
     </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A540" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7845,7 +7856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D539"/>
+  <dimension ref="A1:D540"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -15400,6 +15411,20 @@
         <v>20</v>
       </c>
     </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A540" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B540" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C540" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="D540" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C47BDA1-88D2-4C5E-8951-1814288CA90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E180EF-2840-4FAE-9B35-4DCB55053346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="1031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="1033">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3133,6 +3133,12 @@
   </si>
   <si>
     <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 700 A - 50 kA</t>
+  </si>
+  <si>
+    <t>Comp 2049</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 700A, 50kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
   </si>
 </sst>
 </file>
@@ -15413,13 +15419,13 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A540" s="2" t="s">
-        <v>822</v>
+        <v>1031</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>823</v>
+        <v>1032</v>
       </c>
       <c r="D540" s="2" t="s">
         <v>7</v>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E180EF-2840-4FAE-9B35-4DCB55053346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864EB318-FFBB-4155-A67F-E14B421762F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3003" uniqueCount="1070">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3139,6 +3139,117 @@
   </si>
   <si>
     <t>DISJUNTOR CAIXA MOLDADA 700A, 50kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Tubo rígido c/ ponta lisa - 50 mm - 2"</t>
+  </si>
+  <si>
+    <t>TUBO PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 50 MM, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>TUBO PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 75 MM, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Tubo rígido c/ ponta lisa - 75 mm - 3"</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Joelho 45 - 50 mm</t>
+  </si>
+  <si>
+    <t>JOELHO 45 GRAUS, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>JOELHO 90 GRAUS, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Joelho 90 - 50 mm</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Luva simples - 50 mm</t>
+  </si>
+  <si>
+    <t>LUVA SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Tê sanitário - 50 mm - 50 mm</t>
+  </si>
+  <si>
+    <t>TE, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 50 X 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Junção simples - 50 mm - 50 mm</t>
+  </si>
+  <si>
+    <t>JUNÇÃO SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 50 X 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Terminal de ventilação - 50 mm</t>
+  </si>
+  <si>
+    <t>TERMINAL DE VENTILAÇÃO, PVC, SÉRIE NORMAL, ESGOTO PREDIAL, DN 50 MM, JUNTA SOLDÁVEL, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Luva simples - 75 mm</t>
+  </si>
+  <si>
+    <t>LUVA SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 75 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Joelho 45 - 75 mm</t>
+  </si>
+  <si>
+    <t>JOELHO 45 GRAUS, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 75 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Tê sanitário - 100 mm - 50 mm</t>
+  </si>
+  <si>
+    <t>TE, PVC, SÉRIE NORMAL, ESGOTO PREDIAL, DN 100 X 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Joelho 90 - 75 mm</t>
+  </si>
+  <si>
+    <t>JOELHO 90 GRAUS, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 75 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Junção simples - 75 mm - 50 mm</t>
+  </si>
+  <si>
+    <t>Comp 305</t>
+  </si>
+  <si>
+    <t>JUNÇÃO SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 75 X 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO.  (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 89861 - 04/2023)</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Terminal de ventilação - 75 mm</t>
+  </si>
+  <si>
+    <t>TERMINAL DE VENTILAÇÃO, PVC, SÉRIE NORMAL, ESGOTO PREDIAL, DN 75 MM, JUNTA SOLDÁVEL, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Tê sanitário - 100 mm - 75 mm</t>
+  </si>
+  <si>
+    <t>TE, PVC, SÉRIE NORMAL, ESGOTO PREDIAL, DN 100 X 75 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>Comp 101</t>
+  </si>
+  <si>
+    <t>REDUÇÃO EXCÊNTRICA, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 75 X 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 89549 - 04/2023)</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Redução excêntrica - 75 mm - 50 mm</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Tê sanitário - 75 mm - 50 mm</t>
+  </si>
+  <si>
+    <t>Comp 49</t>
+  </si>
+  <si>
+    <t>TE, PVC, SÉRIE NORMAL, ESGOTO PREDIAL, DN 75 X 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 104354 - 04/2023)</t>
   </si>
 </sst>
 </file>
@@ -3528,7 +3639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B540"/>
+  <dimension ref="A1:B557"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -7855,6 +7966,142 @@
         <v>7</v>
       </c>
     </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A541" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A542" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A543" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A544" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A545" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A546" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A547" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A548" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A549" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A550" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A551" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A552" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B552" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A553" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A554" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A555" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A556" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A557" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7862,7 +8109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D540"/>
+  <dimension ref="A1:D557"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -15431,6 +15678,244 @@
         <v>7</v>
       </c>
     </row>
+    <row r="541" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A541" s="2">
+        <v>89798</v>
+      </c>
+      <c r="B541" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C541" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D541" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A542" s="2">
+        <v>89799</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C542" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D542" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A543" s="2">
+        <v>89802</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C543" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D543" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A544" s="2">
+        <v>89801</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C544" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D544" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A545" s="2">
+        <v>89813</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C545" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D545" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A546" s="2">
+        <v>89825</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C546" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D546" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A547" s="2">
+        <v>89827</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C547" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D547" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A548" s="2">
+        <v>104348</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C548" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D548" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A549" s="2">
+        <v>89817</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C549" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D549" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A550" s="2">
+        <v>89806</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C550" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D550" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A551" s="2">
+        <v>104352</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C551" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D551" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A552" s="2">
+        <v>89805</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C552" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D552" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A553" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C553" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D553" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A554" s="2">
+        <v>104351</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C554" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D554" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A555" s="2">
+        <v>104354</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C555" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D555" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A556" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C556" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D556" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A557" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C557" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D557" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864EB318-FFBB-4155-A67F-E14B421762F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6841105-3F75-49D9-9097-E853E1878BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3003" uniqueCount="1070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3102" uniqueCount="1112">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3250,6 +3250,132 @@
   </si>
   <si>
     <t>TE, PVC, SÉRIE NORMAL, ESGOTO PREDIAL, DN 75 X 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 104354 - 04/2023)</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Tubo rígido c/ ponta lisa - 200 mm - 8"</t>
+  </si>
+  <si>
+    <t>Comp 402</t>
+  </si>
+  <si>
+    <t>TUBO PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 200 MM, FORNECIDO E INSTALADO EM SUBCOLETOR AÉREO DE ESGOTO SANITÁRIO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 89848 - 03/2025)</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Tubo rígido c/ ponta lisa - 100 mm - 4"</t>
+  </si>
+  <si>
+    <t>TUBO PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 100 MM, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Tubo rígido c/ ponta lisa - 40 mm</t>
+  </si>
+  <si>
+    <t>TUBO PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 40 MM, FORNECIDO E INSTALADO EM RAMAL DE DESCARGA OU RAMAL DE ESGOTO SANITÁRIO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>LUVA SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 40 MM, JUNTA SOLDÁVEL, FORNECIDO E INSTALADO EM RAMAL DE DESCARGA OU RAMAL DE ESGOTO SANITÁRIO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Luva - 40 mm</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Luva simples - 100 mm</t>
+  </si>
+  <si>
+    <t>LUVA SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 100 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Joelho 45 - 40 mm</t>
+  </si>
+  <si>
+    <t>JOELHO 45 GRAUS, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 40 MM, JUNTA SOLDÁVEL, FORNECIDO E INSTALADO EM RAMAL DE DESCARGA OU RAMAL DE ESGOTO SANITÁRIO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Joelho 90 - 40 mm</t>
+  </si>
+  <si>
+    <t>JOELHO 90 GRAUS, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 40 MM, JUNTA SOLDÁVEL, FORNECIDO E INSTALADO EM RAMAL DE DESCARGA OU RAMAL DE ESGOTO SANITÁRIO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Acessórios - Caixa sifonada - 150x150x50R</t>
+  </si>
+  <si>
+    <t>CAIXA SIFONADA, COM GRELHA QUADRADA, PVC, DN 150 X 150 X 50 MM, JUNTA SOLDÁVEL, FORNECIDA E INSTALADA EM RAMAL DE DESCARGA OU EM RAMAL DE ESGOTO SANITÁRIO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Junção simples - 100 mm - 50 mm</t>
+  </si>
+  <si>
+    <t>Comp 46</t>
+  </si>
+  <si>
+    <t>JUNÇÃO SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 100 X 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO.  (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 89861 - 04/2023)</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Joelho 90 - 100 mm</t>
+  </si>
+  <si>
+    <t>JOELHO 90 GRAUS, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 100 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>Caixas de Passagem - Caixa de inspeção esgoto simples - CE- 60x60 cm</t>
+  </si>
+  <si>
+    <t>CAIXA ENTERRADA HIDRÁULICA RETANGULAR EM ALVENARIA COM TIJOLOS CERÂMICOS MACIÇOS, DIMENSÕES INTERNAS: 0,6X0,6X0,6 M PARA REDE DE ESGOTO. AF_12/2020</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Junção simples - 100 mm- 100 mm</t>
+  </si>
+  <si>
+    <t>JUNÇÃO SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 100 X 100 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM RAMAL DE DESCARGA OU RAMAL DE ESGOTO SANITÁRIO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Luva simples - 200 mm</t>
+  </si>
+  <si>
+    <t>Comp 687</t>
+  </si>
+  <si>
+    <t>LUVA SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 200 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022 (COMPOSIÇÃO REFERÊNCIA : SINAPI 89821)</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Joelho 45 - 100 mm</t>
+  </si>
+  <si>
+    <t>JOELHO 45 GRAUS, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 100 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>CURVA CURTA 90 GRAUS, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 40 MM, JUNTA SOLDÁVEL, FORNECIDO E INSTALADO EM RAMAL DE DESCARGA OU RAMAL DE ESGOTO SANITÁRIO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Curva 90 curta - 40 mm</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Curva 90 curta - 50 mm</t>
+  </si>
+  <si>
+    <t>CURVA CURTA 90 GRAUS, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 50 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>Caixas de Passagem - Caixa de inspeção esgoto simples - CE- 80 x 80 cm</t>
+  </si>
+  <si>
+    <t>CAIXA DE GORDURA SIMPLES (CAPACIDADE: 36L), RETANGULAR, EM ALVENARIA COM TIJOLOS CERÂMICOS MACIÇOS, DIMENSÕES INTERNAS = 0,2X0,4 M, ALTURA INTERNA = 0,8 M. AF_12/2020</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Junção simples - 100 mm - 75 mm</t>
+  </si>
+  <si>
+    <t>Comp 47</t>
+  </si>
+  <si>
+    <t>JUNÇÃO SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 100 X 75 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM RAMAL DE DESCARGA OU RAMAL DE ESGOTO SANITÁRIO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 89797 - 04/2023)</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Junção simples - 40 mm x 40 mm</t>
+  </si>
+  <si>
+    <t>JUNÇÃO SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 40 MM, JUNTA SOLDÁVEL, FORNECIDO E INSTALADO EM RAMAL DE DESCARGA OU RAMAL DE ESGOTO SANITÁRIO. AF_08/2022</t>
   </si>
 </sst>
 </file>
@@ -3639,7 +3765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B557"/>
+  <dimension ref="A1:B576"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -8102,6 +8228,158 @@
         <v>7</v>
       </c>
     </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A558" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A559" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A560" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A561" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A562" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A563" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A564" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A565" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A566" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A567" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A568" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A569" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A570" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A571" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A572" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A573" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A574" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A575" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A576" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8109,7 +8387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D557"/>
+  <dimension ref="A1:D576"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -15916,6 +16194,272 @@
         <v>7</v>
       </c>
     </row>
+    <row r="558" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A558" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B558" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C558" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D558" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A559" s="2">
+        <v>89800</v>
+      </c>
+      <c r="B559" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D559" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A560" s="2">
+        <v>89711</v>
+      </c>
+      <c r="B560" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C560" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D560" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A561" s="2">
+        <v>89752</v>
+      </c>
+      <c r="B561" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C561" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D561" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A562" s="2">
+        <v>89821</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C562" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D562" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A563" s="2">
+        <v>89726</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C563" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D563" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A564" s="2">
+        <v>89724</v>
+      </c>
+      <c r="B564" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C564" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D564" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A565" s="2">
+        <v>104328</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C565" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D565" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A566" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B566" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C566" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D566" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A567" s="2">
+        <v>89809</v>
+      </c>
+      <c r="B567" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C567" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D567" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A568" s="2">
+        <v>97902</v>
+      </c>
+      <c r="B568" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C568" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D568" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A569" s="2">
+        <v>89797</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D569" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A570" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B570" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C570" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D570" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A571" s="2">
+        <v>89810</v>
+      </c>
+      <c r="B571" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C571" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D571" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A572" s="2">
+        <v>89728</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C572" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D572" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A573" s="2">
+        <v>89803</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C573" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D573" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A574" s="2">
+        <v>98104</v>
+      </c>
+      <c r="B574" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C574" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D574" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A575" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B575" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C575" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D575" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A576" s="2">
+        <v>89783</v>
+      </c>
+      <c r="B576" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C576" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D576" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6841105-3F75-49D9-9097-E853E1878BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C92E7F9-2D76-439E-A44E-9F22AFE555A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3102" uniqueCount="1112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3175" uniqueCount="1143">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3360,9 +3360,6 @@
     <t>Caixas de Passagem - Caixa de inspeção esgoto simples - CE- 80 x 80 cm</t>
   </si>
   <si>
-    <t>CAIXA DE GORDURA SIMPLES (CAPACIDADE: 36L), RETANGULAR, EM ALVENARIA COM TIJOLOS CERÂMICOS MACIÇOS, DIMENSÕES INTERNAS = 0,2X0,4 M, ALTURA INTERNA = 0,8 M. AF_12/2020</t>
-  </si>
-  <si>
     <t>PVC Esgoto - Junção simples - 100 mm - 75 mm</t>
   </si>
   <si>
@@ -3376,6 +3373,102 @@
   </si>
   <si>
     <t>JUNÇÃO SIMPLES, PVC, SERIE NORMAL, ESGOTO PREDIAL, DN 40 MM, JUNTA SOLDÁVEL, FORNECIDO E INSTALADO EM RAMAL DE DESCARGA OU RAMAL DE ESGOTO SANITÁRIO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>CAIXA ENTERRADA HIDRÁULICA RETANGULAR EM ALVENARIA COM TIJOLOS CERÂMICOS MACIÇOS, DIMENSÕES INTERNAS: 0,8X0,8X0,6 M PARA REDE DE ESGOTO. AF_12/2020</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Tubo rígido c/ ponta lisa - 150 mm - 6"</t>
+  </si>
+  <si>
+    <t>TUBO PVC, SÉRIE R, ÁGUA PLUVIAL, DN 150 MM, FORNECIDO E INSTALADO EM CONDUTORES VERTICAIS DE ÁGUAS PLUVIAIS. AF_06/2022</t>
+  </si>
+  <si>
+    <t>Calha metálica - Calha retangular - 300 mm x 300 mm - DU 100</t>
+  </si>
+  <si>
+    <t>CALHA EM CHAPA DE AÇO GALVANIZADO NÚMERO 24, DESENVOLVIMENTO DE 100 CM, INCLUSO TRANSPORTE VERTICAL. AF_07/2019</t>
+  </si>
+  <si>
+    <t>Calha metálica - Calha retangular - 200 mm x 100 mm - D50</t>
+  </si>
+  <si>
+    <t>CALHA EM CHAPA DE AÇO GALVANIZADO NÚMERO 24, DESENVOLVIMENTO DE 50 CM, INCLUSO TRANSPORTE VERTICAL. AF_07/2019</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Luva simples - 150 mm</t>
+  </si>
+  <si>
+    <t>LUVA SIMPLES, PVC, SERIE R, ÁGUA PLUVIAL, DN 150 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM CONDUTORES VERTICAIS DE ÁGUAS PLUVIAIS. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Joelho 90 - 150 mm</t>
+  </si>
+  <si>
+    <t>JOELHO 90 GRAUS, PVC, SERIE R, ÁGUA PLUVIAL, DN 150 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM CONDUTORES VERTICAIS DE ÁGUAS PLUVIAIS. AF_06/2022</t>
+  </si>
+  <si>
+    <t>CAIXA ENTERRADA HIDRÁULICA RETANGULAR EM ALVENARIA COM TIJOLOS CERÂMICOS MACIÇOS, DIMENSÕES INTERNAS: 0,6X0,6X0,6 M PARA REDE DE DRENAGEM. AF_12/2020</t>
+  </si>
+  <si>
+    <t>Caixas de Passagem - Caixa de areia pluvial sem grelha - CA- 60x60cm</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Terminal de ventilação - 100 mm</t>
+  </si>
+  <si>
+    <t>TERMINAL DE VENTILAÇÃO, PVC, SÉRIE NORMAL, ESGOTO PREDIAL, DN 100 MM, JUNTA SOLDÁVEL, FORNECIDO E INSTALADO EM PRUMADA DE ESGOTO SANITÁRIO OU VENTILAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC Acessórios - Ralo abacaxi - 100mm</t>
+  </si>
+  <si>
+    <t>Comp 1662</t>
+  </si>
+  <si>
+    <t>INSTALACAO DE RALO TIPO GRELHA EM CALHAS E  LAJE IMPERMEABILIZADA 100MM (COMPOSIÇÃO DE REFERÊNCIA: SBC 055897 - 03/2023)</t>
+  </si>
+  <si>
+    <t>PVC Acessórios - Ralo abacaxi - 150mm</t>
+  </si>
+  <si>
+    <t>Comp 1663</t>
+  </si>
+  <si>
+    <t>INSTALACAO DE RALO TIPO GRELHA EM CALHA E LAJE IMPERMEABILIZADA 150MM (COMPOSIÇÃO DE REFERÊNCIA: SBC 055897 - 03/2023)</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Junção simples - 150 mm - 100 mm</t>
+  </si>
+  <si>
+    <t>JUNÇÃO SIMPLES, PVC, SERIE R, ÁGUA PLUVIAL, DN 150 X 100 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM CONDUTORES VERTICAIS DE ÁGUAS PLUVIAIS. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Tê sanitário - 100 mm - 100 mm</t>
+  </si>
+  <si>
+    <t>TÊ, PVC, SERIE R, ÁGUA PLUVIAL, DN 100 X 100 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM CONDUTORES VERTICAIS DE ÁGUAS PLUVIAIS. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Curva 90 longa - 100 mm</t>
+  </si>
+  <si>
+    <t>CURVA 90 GRAUS, PVC, SERIE R, ÁGUA PLUVIAL, DN 100 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM CONDUTORES VERTICAIS DE ÁGUAS PLUVIAIS. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Joelho 45 - 150 mm</t>
+  </si>
+  <si>
+    <t>JOELHO 45 GRAUS, PVC, SERIE R, ÁGUA PLUVIAL, DN 150 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM CONDUTORES VERTICAIS DE ÁGUAS PLUVIAIS. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC Esgoto - Curva 90 longa - 150 mm</t>
+  </si>
+  <si>
+    <t>Comp 1204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURVA 90 GRAUS, PVC, SERIE R, ÁGUA PLUVIAL, DN 150 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM CONDUTORES VERTICAIS DE ÁGUAS PLUVIAIS. AF_06/2022 - (COMPOSIÇÃO REFERÊNCIA:  SINAPI 95695  05/25) </t>
   </si>
 </sst>
 </file>
@@ -3765,7 +3858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B576"/>
+  <dimension ref="A1:B590"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -8366,7 +8459,7 @@
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B575" s="1" t="s">
         <v>7</v>
@@ -8374,9 +8467,121 @@
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A576" s="3" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B576" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A577" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A578" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A579" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A580" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A581" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A582" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A583" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A584" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A585" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A586" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A587" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A588" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A589" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A590" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B590" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -8387,7 +8592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D576"/>
+  <dimension ref="A1:D590"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -16418,15 +16623,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="574" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A574" s="2">
-        <v>98104</v>
+        <v>97903</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C574" s="3" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="D574" s="2" t="s">
         <v>7</v>
@@ -16434,13 +16639,13 @@
     </row>
     <row r="575" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A575" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B575" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C575" s="3" t="s">
         <v>1108</v>
-      </c>
-      <c r="B575" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C575" s="3" t="s">
-        <v>1109</v>
       </c>
       <c r="D575" s="2" t="s">
         <v>7</v>
@@ -16454,9 +16659,205 @@
         <v>5</v>
       </c>
       <c r="C576" s="3" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D576" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A577" s="2">
+        <v>89580</v>
+      </c>
+      <c r="B577" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C577" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D577" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A578" s="2">
+        <v>94229</v>
+      </c>
+      <c r="B578" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C578" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D578" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A579" s="2">
+        <v>94228</v>
+      </c>
+      <c r="B579" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C579" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D579" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A580" s="2">
+        <v>89677</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C580" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D580" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A581" s="2">
+        <v>89590</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D581" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A582" s="2">
+        <v>99253</v>
+      </c>
+      <c r="B582" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C582" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D582" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A583" s="2">
+        <v>104356</v>
+      </c>
+      <c r="B583" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C583" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D583" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A584" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B584" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C584" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D584" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A585" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B585" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C585" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D585" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A586" s="2">
+        <v>89699</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C586" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D586" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A587" s="2">
+        <v>89693</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C587" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D587" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A588" s="2">
+        <v>95695</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C588" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D588" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A589" s="2">
+        <v>89591</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C589" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D589" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A590" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C590" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D590" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C92E7F9-2D76-439E-A44E-9F22AFE555A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7712F1E6-BF09-4BC5-A43E-084F61E2E5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3175" uniqueCount="1143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3221" uniqueCount="1162">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3469,6 +3469,63 @@
   </si>
   <si>
     <t xml:space="preserve">CURVA 90 GRAUS, PVC, SERIE R, ÁGUA PLUVIAL, DN 150 MM, JUNTA ELÁSTICA, FORNECIDO E INSTALADO EM CONDUTORES VERTICAIS DE ÁGUAS PLUVIAIS. AF_06/2022 - (COMPOSIÇÃO REFERÊNCIA:  SINAPI 95695  05/25) </t>
+  </si>
+  <si>
+    <t>Aparelho - Torneira de Jardim - 25 mm x 1/2"</t>
+  </si>
+  <si>
+    <t>Comp 304</t>
+  </si>
+  <si>
+    <t>TORNEIRA PARA JARDIM  (COMPOSIÇÃO DE REFERÊNCIA: ORSE - 06/2022)</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Curva 90 soldável - 25 mm</t>
+  </si>
+  <si>
+    <t>CURVA 90 GRAUS, PVC, SOLDÁVEL, DN 25MM, INSTALADO EM RAMAL OU SUB-RAMAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>JOELHO 90 GRAUS COM BUCHA DE LATÃO, PVC, SOLDÁVEL, DN 25MM, X 1/2 INSTALADO EM RAMAL OU SUB-RAMAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC soldável azul c/ bucha latão - Joelho de redução 90º soldável com bucha de latão - 25 mm- 1/2"</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Luva de redução soldável - 32 mm - 25 mm</t>
+  </si>
+  <si>
+    <t>LUVA DE REDUÇÃO, PVC, SOLDÁVEL, DN 32MM X 25MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tê 90 soldável - 32 mm</t>
+  </si>
+  <si>
+    <t>TE, PVC, SOLDÁVEL, DN 32MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Curva 90 soldável - 32 mm</t>
+  </si>
+  <si>
+    <t>CURVA 90 GRAUS, PVC, SOLDÁVEL, DN 32MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Joelho 45 soldável - 32 mm</t>
+  </si>
+  <si>
+    <t>JOELHO 45 GRAUS, PVC, SOLDÁVEL, DN 32MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tê de redução 90 soldável - 32 mm - 25 mm</t>
+  </si>
+  <si>
+    <t>TÊ DE REDUÇÃO, PVC, SOLDÁVEL, DN 32MM X 25MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Joelho 45 soldável - 25 mm</t>
+  </si>
+  <si>
+    <t>JOELHO 45 GRAUS, PVC, SOLDÁVEL, DN 25MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
   </si>
 </sst>
 </file>
@@ -3858,7 +3915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B590"/>
+  <dimension ref="A1:B599"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -8585,6 +8642,78 @@
         <v>7</v>
       </c>
     </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A591" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A592" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A593" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A594" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A595" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A596" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A597" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A598" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A599" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8592,7 +8721,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D590"/>
+  <dimension ref="A1:D599"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -16455,7 +16584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A562" s="2">
         <v>89821</v>
       </c>
@@ -16623,7 +16752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A574" s="2">
         <v>97903</v>
       </c>
@@ -16858,6 +16987,132 @@
         <v>1142</v>
       </c>
       <c r="D590" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A591" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B591" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C591" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D591" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A592" s="2">
+        <v>89364</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C592" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D592" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A593" s="2">
+        <v>90373</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C593" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D593" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A594" s="2">
+        <v>89426</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C594" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D594" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A595" s="2">
+        <v>89443</v>
+      </c>
+      <c r="B595" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C595" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D595" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A596" s="2">
+        <v>89415</v>
+      </c>
+      <c r="B596" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C596" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D596" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A597" s="2">
+        <v>89414</v>
+      </c>
+      <c r="B597" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C597" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D597" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A598" s="2">
+        <v>89445</v>
+      </c>
+      <c r="B598" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C598" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D598" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A599" s="2">
+        <v>89409</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C599" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D599" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7712F1E6-BF09-4BC5-A43E-084F61E2E5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF4B425-0E68-4BA6-AA4C-E4F0D48F03DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3221" uniqueCount="1162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3247" uniqueCount="1172">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3526,6 +3526,36 @@
   </si>
   <si>
     <t>JOELHO 45 GRAUS, PVC, SOLDÁVEL, DN 25MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Tubo de aço galvanizado - 65 mm - 2.1/2"</t>
+  </si>
+  <si>
+    <t>TUBO DE AÇO GALVANIZADO COM COSTURA, CLASSE MÉDIA, DN 65 (2 1/2"), CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Tubo de aço galvanizado - 25 mm - 1"</t>
+  </si>
+  <si>
+    <t>TUBO DE AÇO GALVANIZADO COM COSTURA, CLASSE MÉDIA, DN 25 (1"), CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Incêndio - Iluminação de emergência - Autônoma 30 LED's 100 lúmens</t>
+  </si>
+  <si>
+    <t>Incêndio - Iluminação de emergência - Autônoma 30 LED's 80 lúmens</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA DE EMERGÊNCIA, COM 30 LÂMPADAS LED DE 2 W, SEM REATOR - FORNECIMENTO E INSTALAÇÃO. AF_09/2024</t>
+  </si>
+  <si>
+    <t>Incêndio - Alarme de incêndio - Central de Alarme e Detecção</t>
+  </si>
+  <si>
+    <t>Comp 51</t>
+  </si>
+  <si>
+    <t>CENTRAL DE ALARME ENDEREÇÁVEL PARA SISTEMA DE COMBATE A INCÊNDIO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: FDE 09.05.097 - 04/2022)</t>
   </si>
 </sst>
 </file>
@@ -3915,7 +3945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B599"/>
+  <dimension ref="A1:B604"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -8714,6 +8744,46 @@
         <v>7</v>
       </c>
     </row>
+    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A600" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A601" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A602" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A603" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A604" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8721,7 +8791,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D599"/>
+  <dimension ref="A1:D604"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -17116,6 +17186,76 @@
         <v>7</v>
       </c>
     </row>
+    <row r="600" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A600" s="2">
+        <v>92367</v>
+      </c>
+      <c r="B600" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C600" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D600" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A601" s="2">
+        <v>97498</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C601" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D601" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A602" s="2">
+        <v>97599</v>
+      </c>
+      <c r="B602" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C602" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D602" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A603" s="2">
+        <v>97599</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C603" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D603" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A604" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B604" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C604" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D604" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF4B425-0E68-4BA6-AA4C-E4F0D48F03DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB28720-00B3-4AE3-876A-81B1D824601D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3247" uniqueCount="1172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3366" uniqueCount="1214">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3556,6 +3556,132 @@
   </si>
   <si>
     <t>CENTRAL DE ALARME ENDEREÇÁVEL PARA SISTEMA DE COMBATE A INCÊNDIO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: FDE 09.05.097 - 04/2022)</t>
+  </si>
+  <si>
+    <t>Incêndio - Extintor portátil - Extintor PQS 6kg ABC</t>
+  </si>
+  <si>
+    <t>EXTINTOR DE INCÊNDIO PORTÁTIL COM CARGA DE PQS DE 6 KG, CLASSE BC - FORNECIMENTO E INSTALAÇÃO. AF_01/2026_PE</t>
+  </si>
+  <si>
+    <t>Comp 93</t>
+  </si>
+  <si>
+    <t>SIRENE AUDIO-VISUAL 12 A 24V - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SBC 055530 - 03/2025)</t>
+  </si>
+  <si>
+    <t>Incêndio - Alarme de incêndio - Avisador Sonoro</t>
+  </si>
+  <si>
+    <t>Incêndio - Alarme de incêndio - Quadro Metálico de Comando de Bombas</t>
+  </si>
+  <si>
+    <t>Comp 1380</t>
+  </si>
+  <si>
+    <t>QUADRO DE COMANDO COM FLANGE, 100X60X25CM, PARA BOMBAS  (COMPOSIÇÃO DE REFERÊNCIA: FDE 09.05.089 - 04/2022)</t>
+  </si>
+  <si>
+    <t>Incêndio - Alarme de incêndio - Acionador de bomba convencional com botão liga/desliga</t>
+  </si>
+  <si>
+    <t>Comp 1675</t>
+  </si>
+  <si>
+    <t>BOTOEIRA PARA ACIONAMENTO DA BOMBA DE INCÊNDIO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: CPOS 50.01.090 - 03/2018)</t>
+  </si>
+  <si>
+    <t>Incêndio - Alarme de incêndio - Acionador manual de alarme de incêndio c/ sirene endereçável</t>
+  </si>
+  <si>
+    <t>Comp 1674</t>
+  </si>
+  <si>
+    <t>BOTOEIRA PARA ACIONAMENTO DO SISTEMA DE ALARME DE INCÊNDIO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: CPOS 50.01.090 - 03/2018)</t>
+  </si>
+  <si>
+    <t>Incêndio - Sinalização de emergência - Placa fotoluminescente rota de fuga seta para cima de PVC 24x12cm</t>
+  </si>
+  <si>
+    <t>Incêndio - Sinalização de emergência - Placa fotoluminescente rota de fuga seta para direita de PVC 24x12cm</t>
+  </si>
+  <si>
+    <t>Incêndio - Sinalização de emergência - Placa fotoluminescente saída seta para esquerda de PVC 24x12cm</t>
+  </si>
+  <si>
+    <t>Incêndio - Sinalização de emergência - Placa fotoluminescente saída de PVC 24x12cm</t>
+  </si>
+  <si>
+    <t>Comp 52</t>
+  </si>
+  <si>
+    <t>SINALIZAÇÃO DE SEGURANÇA CONTRA INCÊNDIO (SINALIZAÇÃO DE EMERGÊNCIA) - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: ORSE 7321 - 10/2018)</t>
+  </si>
+  <si>
+    <t>Incêndio - Sinalização de emergência - Placa fotoluminescente extintor de PVC 15x15cm</t>
+  </si>
+  <si>
+    <t>Incêndio - Sinalização de emergência - Placa fotoluminescente alarme de incêndio de PVC 15x20cm</t>
+  </si>
+  <si>
+    <t>Incêndio - Sinalização de emergência - Placa fotoluminescente bomba de incêndio de PVC 15x20cm</t>
+  </si>
+  <si>
+    <t>Incêndio - Sinalização de emergência - Placa fotoluminescente sirene de PVC 20x20cm</t>
+  </si>
+  <si>
+    <t>Incêndio - Sinalização de emergência - Placa fotoluminescente central de alarme de detecção de PVC 24 x 12cm</t>
+  </si>
+  <si>
+    <t>Comp 94</t>
+  </si>
+  <si>
+    <t>SINALIZAÇÃO DE SEGURANÇA CONTRA INCÊNDIO (SINALIZAÇÃO DE EQUIPAMENTO DE COMBATE A INCÊNDIO) - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: ORSE 7321 - 10/2018)</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Cotovelo 90 - 2.1/2"</t>
+  </si>
+  <si>
+    <t>JOELHO 90 GRAUS, EM FERRO GALVANIZADO, DN 65 (2 1/2"), CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>NIPLE, EM FERRO GALVANIZADO, DN 65 (2 1/2"), CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Niple duplo - 2.1/2"</t>
+  </si>
+  <si>
+    <t>NIPLE, EM FERRO GALVANIZADO, DN 25 (1"), CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Niple duplo - 1"</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - União ass. de ferro conico macho-fêmea - 2.1/2"</t>
+  </si>
+  <si>
+    <t>UNIÃO, EM FERRO GALVANIZADO, DN 65 (2 1/2"), CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>REGISTRO DE GAVETA BRUTO, LATÃO, ROSCÁVEL, 2 1/2" - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>Metais - Registro bruto de gaveta industrial - 2.1/2"</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Tê - 1"</t>
+  </si>
+  <si>
+    <t>TÊ, EM FERRO GALVANIZADO, CONEXÃO ROSQUEADA, DN 25 (1"), INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Incêndio - Mangueiras - 1.1/2 " 15 m</t>
+  </si>
+  <si>
+    <t>Comp 87</t>
+  </si>
+  <si>
+    <t>ABRIGO PARA HIDRANTE EM CHAPA DE AÇO, 75X45X17CM, PORTA COM VISOR "INCÊNDIO", INCLUSIVE REGISTRO DE GAVETA 2 1/2", ESGUICHO REGULÁVEL, 1 1/2X13MM, REDUÇÃO FIXA TIPO STORZ, CHAVE STORZ E MANGUEIRA 30M, TIPO 1, 1 1/2" - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: SINAPI 72283 - 09/2019)</t>
   </si>
 </sst>
 </file>
@@ -3945,7 +4071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B604"/>
+  <dimension ref="A1:B625"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -8784,6 +8910,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A605" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A606" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A607" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A608" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A609" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A610" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A611" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A612" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A613" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A614" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A615" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A616" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A617" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A618" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A619" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A620" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A621" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A622" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A623" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A624" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A625" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8791,7 +9085,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D604"/>
+  <dimension ref="A1:D625"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -17256,6 +17550,300 @@
         <v>7</v>
       </c>
     </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A605" s="2">
+        <v>101909</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C605" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D605" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A606" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C606" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D606" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A607" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C607" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D607" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A608" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C608" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D608" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A609" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C609" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D609" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A610" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C610" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D610" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A611" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C611" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D611" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A612" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C612" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D612" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A613" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C613" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D613" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A614" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C614" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D614" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A615" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C615" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D615" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A616" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C616" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D616" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A617" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C617" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D617" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A618" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C618" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D618" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A619" s="2">
+        <v>92390</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C619" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D619" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A620" s="2">
+        <v>92377</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C620" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D620" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A621" s="2">
+        <v>92369</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C621" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D621" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A622" s="2">
+        <v>92896</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D622" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A623" s="2">
+        <v>94499</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D623" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A624" s="2">
+        <v>92637</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C624" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D624" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A625" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C625" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D625" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB28720-00B3-4AE3-876A-81B1D824601D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091AD085-7562-4762-BA87-11E7D5A463F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3366" uniqueCount="1214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="1223">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3682,6 +3682,33 @@
   </si>
   <si>
     <t>ABRIGO PARA HIDRANTE EM CHAPA DE AÇO, 75X45X17CM, PORTA COM VISOR "INCÊNDIO", INCLUSIVE REGISTRO DE GAVETA 2 1/2", ESGUICHO REGULÁVEL, 1 1/2X13MM, REDUÇÃO FIXA TIPO STORZ, CHAVE STORZ E MANGUEIRA 30M, TIPO 1, 1 1/2" - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: SINAPI 72283 - 09/2019)</t>
+  </si>
+  <si>
+    <t>Metais - Registro bruto de gaveta industrial - 1"</t>
+  </si>
+  <si>
+    <t>REGISTRO DE GAVETA BRUTO, LATÃO, ROSCÁVEL, 1" - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Tê - 2.1/2"</t>
+  </si>
+  <si>
+    <t>TÊ, EM FERRO GALVANIZADO, CONEXÃO ROSQUEADA, DN 65 (2 1/2"), INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Cotovelo 90 - 1"</t>
+  </si>
+  <si>
+    <t>JOELHO 90 GRAUS, EM FERRO GALVANIZADO, DN 25 (1"), CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Tê de redução - 2.1/2" x 1"</t>
+  </si>
+  <si>
+    <t>Comp 1233</t>
+  </si>
+  <si>
+    <t>TÊ DE REDUÇÃO EM FERRO GALVANIZADO, CONEXÃO ROSQUEADA,  2 1/2" X  1" INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE E SPRINKLER - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 (COMPOSIÇÃO REFERÊNCIA: SINAPI 92642 - 04/2023)</t>
   </si>
 </sst>
 </file>
@@ -4071,7 +4098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B629"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -9078,6 +9105,38 @@
         <v>7</v>
       </c>
     </row>
+    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A626" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A627" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A628" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A629" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -9085,7 +9144,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D625"/>
+  <dimension ref="A1:D629"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -17844,6 +17903,62 @@
         <v>7</v>
       </c>
     </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A626" s="2">
+        <v>94495</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C626" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D626" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A627" s="2">
+        <v>92642</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C627" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D627" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A628" s="2">
+        <v>92382</v>
+      </c>
+      <c r="B628" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C628" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D628" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A629" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C629" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D629" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091AD085-7562-4762-BA87-11E7D5A463F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F1276B-66C3-4832-838B-E1AAFD03FD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="1223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3425" uniqueCount="1238">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3675,9 +3675,6 @@
     <t>TÊ, EM FERRO GALVANIZADO, CONEXÃO ROSQUEADA, DN 25 (1"), INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
   </si>
   <si>
-    <t>Incêndio - Mangueiras - 1.1/2 " 15 m</t>
-  </si>
-  <si>
     <t>Comp 87</t>
   </si>
   <si>
@@ -3709,6 +3706,54 @@
   </si>
   <si>
     <t>TÊ DE REDUÇÃO EM FERRO GALVANIZADO, CONEXÃO ROSQUEADA,  2 1/2" X  1" INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE E SPRINKLER - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 (COMPOSIÇÃO REFERÊNCIA: SINAPI 92642 - 04/2023)</t>
+  </si>
+  <si>
+    <t>Incêndio - Caixa para abrigo de mangueiras - 75 x 45 x 17 cm</t>
+  </si>
+  <si>
+    <t>Incêndio - Sinalização de emergência - Placa fotoluminescente hidrante de PVC 15x15cm</t>
+  </si>
+  <si>
+    <t>Metais - Pressostato - 3/4"</t>
+  </si>
+  <si>
+    <t>Comp 89</t>
+  </si>
+  <si>
+    <t>PRESSOSTATO ALTA/BAIXA COM REARME MANUAL (COMPOSIÇÃO DE REFERÊNCIA: SBC (055700) 07/2023)</t>
+  </si>
+  <si>
+    <t>Metais - Válvula de retenção vertical - 2.1/2"</t>
+  </si>
+  <si>
+    <t>VÁLVULA DE RETENÇÃO VERTICAL, DE BRONZE, ROSCÁVEL, 2 1/2" - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>Bomba Hidráulica - Incêndio - WDM Pumps Brasil - HE 3 I - 7,5 CV - R191</t>
+  </si>
+  <si>
+    <t>Comp 118</t>
+  </si>
+  <si>
+    <t>BOMBA CENTRÍFUGA, TRIFÁSICA, 7,5 CV - FORNECIMENTO E INSTALAÇÃO. AF_12/2020 (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 102122 - 03/2025)</t>
+  </si>
+  <si>
+    <t>Bomba Jockey - Bomba schneider - BT4-05 79mm - 1/2CV</t>
+  </si>
+  <si>
+    <t>BOMBA CENTRÍFUGA, MONOFÁSICA, 0,5 CV OU 0,49 HP, HM 6 A 20 M, Q 1,2 A 8,3 M3/H - FORNECIMENTO E INSTALAÇÃO. AF_11/2025_PS</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Luva macho - fêmea - 1"</t>
+  </si>
+  <si>
+    <t>LUVA, EM FERRO GALVANIZADO, DN 25 (1"), CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Metais - Manômetro - 3/4"</t>
+  </si>
+  <si>
+    <t>MANÔMETRO 0 A 200 PSI (0 A 14 KGF/CM2), D = 50MM - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
   </si>
 </sst>
 </file>
@@ -4098,7 +4143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B629"/>
+  <dimension ref="A1:B636"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -9099,7 +9144,7 @@
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A625" s="3" t="s">
-        <v>1211</v>
+        <v>1222</v>
       </c>
       <c r="B625" s="1" t="s">
         <v>7</v>
@@ -9107,7 +9152,7 @@
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A626" s="3" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B626" s="1" t="s">
         <v>7</v>
@@ -9115,7 +9160,7 @@
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A627" s="3" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B627" s="1" t="s">
         <v>7</v>
@@ -9123,7 +9168,7 @@
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A628" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B628" s="1" t="s">
         <v>7</v>
@@ -9131,9 +9176,65 @@
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A629" s="3" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B629" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A630" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A631" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A632" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A633" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A634" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A635" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A636" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B636" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -9144,7 +9245,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D629"/>
+  <dimension ref="A1:D636"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -17891,13 +17992,13 @@
     </row>
     <row r="625" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A625" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C625" s="3" t="s">
         <v>1212</v>
-      </c>
-      <c r="B625" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C625" s="3" t="s">
-        <v>1213</v>
       </c>
       <c r="D625" s="2" t="s">
         <v>7</v>
@@ -17911,7 +18012,7 @@
         <v>5</v>
       </c>
       <c r="C626" s="3" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D626" s="2" t="s">
         <v>7</v>
@@ -17925,7 +18026,7 @@
         <v>5</v>
       </c>
       <c r="C627" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D627" s="2" t="s">
         <v>7</v>
@@ -17939,7 +18040,7 @@
         <v>5</v>
       </c>
       <c r="C628" s="3" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D628" s="2" t="s">
         <v>7</v>
@@ -17947,15 +18048,113 @@
     </row>
     <row r="629" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A629" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C629" s="3" t="s">
         <v>1221</v>
       </c>
-      <c r="B629" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C629" s="3" t="s">
-        <v>1222</v>
-      </c>
       <c r="D629" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A630" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C630" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D630" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A631" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B631" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C631" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D631" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A632" s="2">
+        <v>103009</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C632" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D632" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A633" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B633" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C633" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D633" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A634" s="2">
+        <v>102111</v>
+      </c>
+      <c r="B634" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C634" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D634" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A635" s="2">
+        <v>92370</v>
+      </c>
+      <c r="B635" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C635" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D635" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A636" s="2">
+        <v>101917</v>
+      </c>
+      <c r="B636" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C636" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D636" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F1276B-66C3-4832-838B-E1AAFD03FD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6033F5-3B37-4FE1-834F-F8A4DDA721F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3425" uniqueCount="1238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="1258">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3754,6 +3754,66 @@
   </si>
   <si>
     <t>MANÔMETRO 0 A 200 PSI (0 A 14 KGF/CM2), D = 50MM - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Aço carbono - Redução concêntricas - 1"-3/4"</t>
+  </si>
+  <si>
+    <t>Comp 2007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REDUCAO CONCENTRICA ACO CARBONO DN 1 x 3/4""  - (COMPOSIÇÃO REFERÊNCIA: SBC 055106-02/2026) </t>
+  </si>
+  <si>
+    <t>Metais - Válvula de Esfera - 3/4"</t>
+  </si>
+  <si>
+    <t>VÁLVULA DE ESFERA BRUTA, BRONZE, ROSCÁVEL, 3/4&amp;#39;&amp;#39; - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>VÁLVULA DE RETENÇÃO HORIZONTAL, DE BRONZE, ROSCÁVEL, 2 1/2" - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>Metais - Válvula de retenção vertical - 1"</t>
+  </si>
+  <si>
+    <t>Metais - Válvula de retenção horiz c/ portinhola - 2.1/2"</t>
+  </si>
+  <si>
+    <t>VÁLVULA DE RETENÇÃO VERTICAL, DE BRONZE, ROSCÁVEL, 1" - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>Metais - Vaso de Expansão - Vaso de Expansão 18L</t>
+  </si>
+  <si>
+    <t>Comp 683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TANQUE DE PRESSÃO CAPACIDADE DE 18 LITROS (P/ INCÊNDIO) (COMPOSIÇÃO REFERÊNCIA:  ORSE 13313) </t>
+  </si>
+  <si>
+    <t>Incêndio - Tampão de ferro fundido para passeio com inscrição "hidrante" com telar - 70x60 - cm</t>
+  </si>
+  <si>
+    <t>Comp 85</t>
+  </si>
+  <si>
+    <t>HIDRANTE DE RECALQUE COM CAIXA EM ALVENARIA DE BLOCO CERÂMICO 60X40X50CM, REVESTIDA INTERNAMENTE COM ARGAMASSA (CIMENTO E AREIA, TRAÇO 1:4) E=2,0CM, TAMPAO FOFO SIMPLES COM BASE CLASSE A15 CARGA MAX 1,5 T, 400 X 500 MM, COM INSCRICAO INCENDIO E FUNDO DE BRITA , INCLUSIVE REGISTRO ANGULAR 45 GRAUS, TAMPÃO CEGO, NIPLE DUPLO E VÁLVULA DE RETENÇÃO - ESCAVAÇÃO, CONFECÇÃO, FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 74104/1 E 83448 - 12/2017)</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Bucha de redução - 2.1/2" x 1"</t>
+  </si>
+  <si>
+    <t>Comp 1189</t>
+  </si>
+  <si>
+    <t>LUVA DE REDUÇÃO, EM FERRO GALVANIZADO, 2 1/2" X 1", CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2020-(COMPOSIÇÃO REFERÊNCIA: SINAPI 92935)</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Curva macho - fêmea - 2.1/2"</t>
+  </si>
+  <si>
+    <t>CURVA 90 GRAUS, EM AÇO, CONEXÃO SOLDADA, DN 65 (2 1/2"), INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
   </si>
 </sst>
 </file>
@@ -4143,7 +4203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B636"/>
+  <dimension ref="A1:B644"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -9238,6 +9298,70 @@
         <v>7</v>
       </c>
     </row>
+    <row r="637" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A637" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A638" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A639" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A640" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A641" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A642" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A643" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A644" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -9245,7 +9369,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D636"/>
+  <dimension ref="A1:D644"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -18158,6 +18282,118 @@
         <v>7</v>
       </c>
     </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A637" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B637" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C637" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D637" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A638" s="2">
+        <v>95249</v>
+      </c>
+      <c r="B638" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C638" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D638" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A639" s="2">
+        <v>99624</v>
+      </c>
+      <c r="B639" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C639" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D639" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A640" s="2">
+        <v>99629</v>
+      </c>
+      <c r="B640" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D640" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A641" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C641" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D641" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A642" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B642" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D642" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A643" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B643" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C643" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D643" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A644" s="2">
+        <v>97488</v>
+      </c>
+      <c r="B644" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C644" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D644" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6033F5-3B37-4FE1-834F-F8A4DDA721F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995D518E-6CC6-4499-A78C-AC95D72F943B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="1258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3475" uniqueCount="1260">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3814,6 +3814,12 @@
   </si>
   <si>
     <t>CURVA 90 GRAUS, EM AÇO, CONEXÃO SOLDADA, DN 65 (2 1/2"), INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Comp 74</t>
+  </si>
+  <si>
+    <t>PINTURA DE PISO PARA SINALIZAÇÃO (1,00 X 1,00 M) DE EXTINTOR DE INCÊNDIO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA - SEINFRA CEARÁ C4649 - 03/2016)</t>
   </si>
 </sst>
 </file>
@@ -4203,7 +4209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B644"/>
+  <dimension ref="A1:B645"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -9362,6 +9368,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="645" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A645" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -9369,7 +9383,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D644"/>
+  <dimension ref="A1:D645"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -18394,6 +18408,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="645" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A645" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B645" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C645" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D645" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995D518E-6CC6-4499-A78C-AC95D72F943B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910A15F2-C2D3-44B6-923D-A932E1DA10A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3475" uniqueCount="1260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3541" uniqueCount="1285">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3820,6 +3820,81 @@
   </si>
   <si>
     <t>PINTURA DE PISO PARA SINALIZAÇÃO (1,00 X 1,00 M) DE EXTINTOR DE INCÊNDIO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA - SEINFRA CEARÁ C4649 - 03/2016)</t>
+  </si>
+  <si>
+    <t>Cobre - Tubos de cobre - 15 mm</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE RÍGIDO, DN 15 MM, CLASSE E, SEM ISOLAMENTO, INSTALADO EM RAMAL E SUB-RAMAL DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_04/2022</t>
+  </si>
+  <si>
+    <t>Cobre - Tubos de cobre - 22 mm</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE RÍGIDO, DN 22 MM, CLASSE A, SEM ISOLAMENTO, INSTALADO EM PRUMADA DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_04/2022</t>
+  </si>
+  <si>
+    <t>Cobre - Cotovelo bolsa - bolsa - 15 mm</t>
+  </si>
+  <si>
+    <t>COTOVELO EM COBRE, DN 15 MM, 90 GRAUS, SEM ANEL DE SOLDA, INSTALADO EM RAMAL E SUB-RAMAL DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_04/2022</t>
+  </si>
+  <si>
+    <t>CURVA EM COBRE, DN 15 MM, 45 GRAUS, SEM ANEL DE SOLDA, BOLSA X BOLSA, INSTALADO EM RAMAL E SUB-RAMAL DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_04/2022</t>
+  </si>
+  <si>
+    <t>Cobre - Curva 45 bolsa - bolsa - 15 mm</t>
+  </si>
+  <si>
+    <t>Cobre - Tê c/ redução central - 22 mm x 15 mm x 22 mm</t>
+  </si>
+  <si>
+    <t>Comp 2008</t>
+  </si>
+  <si>
+    <t>TE COM REDUÇÃO DE COBRE 22MM X 15MM X 22MM  INSTALADO EM RAMAIS E SUB-RAMAIS DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_10/2020(COMPOSIÇÃO REFERÊNCIA: SINAPI 92642 - 04/2023)</t>
+  </si>
+  <si>
+    <t>BUCHA DE REDUÇÃO EM COBRE, DN 22 MM X 15 MM, SEM ANEL DE SOLDA, PONTA X BOLSA, INSTALADO EM RAMAL E SUB-RAMAL DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_04/2022</t>
+  </si>
+  <si>
+    <t>Cobre - Bucha de redução ponta-bolsa - 22 mm x 15 mm</t>
+  </si>
+  <si>
+    <t>Cobre - Cotovelo bolsa - bolsa - 22 mm</t>
+  </si>
+  <si>
+    <t>COTOVELO EM COBRE, DN 22 MM, 90 GRAUS, SEM ANEL DE SOLDA, INSTALADO EM RAMAL E SUB-RAMAL DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_04/2022</t>
+  </si>
+  <si>
+    <t>Cobre - Cotovelo bolsa x bolsa c/ rosca interna - 15 mm x 1/2"</t>
+  </si>
+  <si>
+    <t>COTOVELO EM BRONZE/LATÃO, DN 15 MM X 1/2", 90 GRAUS, SEM ANEL DE SOLDA, BOLSA X ROSCA F, INSTALADO EM RAMAL E SUB-RAMAL DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_04/2022</t>
+  </si>
+  <si>
+    <t>Gás - Registro rápido - 1/2" x terminal Ø 11,80mm - para mangueira 3/8</t>
+  </si>
+  <si>
+    <t>Cobre - Curva 45 bolsa - bolsa - 22 mm</t>
+  </si>
+  <si>
+    <t>CURVA EM COBRE, DN 22 MM, 45 GRAUS, SEM ANEL DE SOLDA, BOLSA X BOLSA, INSTALADO EM RAMAL E SUB-RAMAL DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_04/2022</t>
+  </si>
+  <si>
+    <t>Cobre - Tê bolsa x bolsa x bolsa - 22 mm</t>
+  </si>
+  <si>
+    <t>Cobre - Tê bolsaXbolsaXbolsa - 22 mm</t>
+  </si>
+  <si>
+    <t>TE EM COBRE, DN 22 MM, SEM ANEL DE SOLDA, INSTALADO EM RAMAL E SUB-RAMAL DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_04/2022</t>
+  </si>
+  <si>
+    <t>REGISTRO OU REGULADOR DE GÁS DE COZINHA - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>Gás - Regulador de alta pressão GLP c/ segurança OPSO - Regulagem externa - 3/4" NPT f x 3/4" NPT f</t>
   </si>
 </sst>
 </file>
@@ -4209,7 +4284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B645"/>
+  <dimension ref="A1:B658"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -9376,6 +9451,110 @@
         <v>7</v>
       </c>
     </row>
+    <row r="646" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A646" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A647" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A648" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A649" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A650" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A651" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A652" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A653" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A654" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A655" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A656" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A657" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A658" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -9383,7 +9562,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D645"/>
+  <dimension ref="A1:D658"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -18422,6 +18601,188 @@
         <v>7</v>
       </c>
     </row>
+    <row r="646" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A646" s="2">
+        <v>103802</v>
+      </c>
+      <c r="B646" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D646" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A647" s="2">
+        <v>97335</v>
+      </c>
+      <c r="B647" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C647" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D647" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A648" s="2">
+        <v>103805</v>
+      </c>
+      <c r="B648" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C648" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D648" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A649" s="2">
+        <v>103806</v>
+      </c>
+      <c r="B649" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C649" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D649" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A650" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C650" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D650" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A651" s="2">
+        <v>103823</v>
+      </c>
+      <c r="B651" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C651" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D651" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A652" s="2">
+        <v>103808</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C652" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D652" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A653" s="2">
+        <v>103807</v>
+      </c>
+      <c r="B653" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C653" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D653" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A654" s="2">
+        <v>103029</v>
+      </c>
+      <c r="B654" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D654" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A655" s="2">
+        <v>103809</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D655" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A656" s="2">
+        <v>103833</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D656" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A657" s="2">
+        <v>103833</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D657" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A658" s="2">
+        <v>103029</v>
+      </c>
+      <c r="B658" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D658" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910A15F2-C2D3-44B6-923D-A932E1DA10A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F75EC8-28A7-4DCA-9E3C-9C63B4BADE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3541" uniqueCount="1285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3551" uniqueCount="1289">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3768,9 +3768,6 @@
     <t>Metais - Válvula de Esfera - 3/4"</t>
   </si>
   <si>
-    <t>VÁLVULA DE ESFERA BRUTA, BRONZE, ROSCÁVEL, 3/4&amp;#39;&amp;#39; - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
-  </si>
-  <si>
     <t>VÁLVULA DE RETENÇÃO HORIZONTAL, DE BRONZE, ROSCÁVEL, 2 1/2" - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
   </si>
   <si>
@@ -3876,6 +3873,9 @@
     <t>Gás - Registro rápido - 1/2" x terminal Ø 11,80mm - para mangueira 3/8</t>
   </si>
   <si>
+    <t>REGISTRO DE GAVETA BRUTO, LATÃO, ROSCÁVEL, 1/2" - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
     <t>Cobre - Curva 45 bolsa - bolsa - 22 mm</t>
   </si>
   <si>
@@ -3895,6 +3895,18 @@
   </si>
   <si>
     <t>Gás - Regulador de alta pressão GLP c/ segurança OPSO - Regulagem externa - 3/4" NPT f x 3/4" NPT f</t>
+  </si>
+  <si>
+    <t>Metais - Registro de gaveta bruto ABNT - 1/2"</t>
+  </si>
+  <si>
+    <t>VÁLVULA DE ESFERA BRUTA, BRONZE, ROSCÁVEL, 3/4"" - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>Cobre - Conector bolsa - ponta - 15 mm x 1/2"</t>
+  </si>
+  <si>
+    <t>CONECTOR EM BRONZE/LATÃO, DN 15 MM X 1/2", SEM ANEL DE SOLDA, BOLSA X ROSCA F, INSTALADO EM RAMAL E SUB-RAMAL DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_04/2022</t>
   </si>
 </sst>
 </file>
@@ -4284,7 +4296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B658"/>
+  <dimension ref="A1:B660"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -9397,7 +9409,7 @@
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A639" s="3" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B639" s="1" t="s">
         <v>7</v>
@@ -9405,7 +9417,7 @@
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A640" s="3" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B640" s="1" t="s">
         <v>7</v>
@@ -9413,7 +9425,7 @@
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A641" s="3" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B641" s="1" t="s">
         <v>7</v>
@@ -9421,7 +9433,7 @@
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A642" s="3" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B642" s="1" t="s">
         <v>7</v>
@@ -9429,7 +9441,7 @@
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A643" s="3" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B643" s="1" t="s">
         <v>7</v>
@@ -9437,7 +9449,7 @@
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A644" s="3" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B644" s="1" t="s">
         <v>7</v>
@@ -9453,7 +9465,7 @@
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A646" s="3" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B646" s="1" t="s">
         <v>20</v>
@@ -9461,7 +9473,7 @@
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A647" s="3" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B647" s="1" t="s">
         <v>20</v>
@@ -9469,7 +9481,7 @@
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A648" s="3" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B648" s="1" t="s">
         <v>7</v>
@@ -9477,7 +9489,7 @@
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A649" s="3" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B649" s="1" t="s">
         <v>7</v>
@@ -9485,7 +9497,7 @@
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A650" s="3" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B650" s="1" t="s">
         <v>7</v>
@@ -9493,7 +9505,7 @@
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A651" s="3" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B651" s="1" t="s">
         <v>7</v>
@@ -9501,7 +9513,7 @@
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A652" s="3" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B652" s="1" t="s">
         <v>7</v>
@@ -9509,7 +9521,7 @@
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A653" s="3" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B653" s="1" t="s">
         <v>7</v>
@@ -9517,7 +9529,7 @@
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A654" s="3" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B654" s="1" t="s">
         <v>7</v>
@@ -9552,6 +9564,22 @@
         <v>1284</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A659" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A660" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B660" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -9562,7 +9590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D658"/>
+  <dimension ref="A1:D660"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -18497,7 +18525,7 @@
         <v>5</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>1242</v>
+        <v>1286</v>
       </c>
       <c r="D638" s="2" t="s">
         <v>7</v>
@@ -18511,7 +18539,7 @@
         <v>5</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="D639" s="2" t="s">
         <v>7</v>
@@ -18525,7 +18553,7 @@
         <v>5</v>
       </c>
       <c r="C640" s="3" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D640" s="2" t="s">
         <v>7</v>
@@ -18533,13 +18561,13 @@
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A641" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C641" s="3" t="s">
         <v>1248</v>
-      </c>
-      <c r="B641" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C641" s="3" t="s">
-        <v>1249</v>
       </c>
       <c r="D641" s="2" t="s">
         <v>7</v>
@@ -18547,13 +18575,13 @@
     </row>
     <row r="642" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A642" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B642" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C642" s="3" t="s">
         <v>1251</v>
-      </c>
-      <c r="B642" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C642" s="3" t="s">
-        <v>1252</v>
       </c>
       <c r="D642" s="2" t="s">
         <v>7</v>
@@ -18561,13 +18589,13 @@
     </row>
     <row r="643" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A643" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B643" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C643" s="3" t="s">
         <v>1254</v>
-      </c>
-      <c r="B643" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C643" s="3" t="s">
-        <v>1255</v>
       </c>
       <c r="D643" s="2" t="s">
         <v>7</v>
@@ -18581,7 +18609,7 @@
         <v>5</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D644" s="2" t="s">
         <v>7</v>
@@ -18589,13 +18617,13 @@
     </row>
     <row r="645" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A645" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B645" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C645" s="3" t="s">
         <v>1258</v>
-      </c>
-      <c r="B645" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C645" s="3" t="s">
-        <v>1259</v>
       </c>
       <c r="D645" s="2" t="s">
         <v>7</v>
@@ -18609,7 +18637,7 @@
         <v>5</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="D646" s="2" t="s">
         <v>20</v>
@@ -18623,7 +18651,7 @@
         <v>5</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D647" s="2" t="s">
         <v>20</v>
@@ -18637,7 +18665,7 @@
         <v>5</v>
       </c>
       <c r="C648" s="3" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D648" s="2" t="s">
         <v>7</v>
@@ -18651,7 +18679,7 @@
         <v>5</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D649" s="2" t="s">
         <v>7</v>
@@ -18659,13 +18687,13 @@
     </row>
     <row r="650" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A650" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C650" s="3" t="s">
         <v>1269</v>
-      </c>
-      <c r="B650" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C650" s="3" t="s">
-        <v>1270</v>
       </c>
       <c r="D650" s="2" t="s">
         <v>7</v>
@@ -18679,7 +18707,7 @@
         <v>5</v>
       </c>
       <c r="C651" s="3" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="D651" s="2" t="s">
         <v>7</v>
@@ -18693,7 +18721,7 @@
         <v>5</v>
       </c>
       <c r="C652" s="3" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D652" s="2" t="s">
         <v>7</v>
@@ -18707,7 +18735,7 @@
         <v>5</v>
       </c>
       <c r="C653" s="3" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="D653" s="2" t="s">
         <v>7</v>
@@ -18780,6 +18808,34 @@
         <v>1283</v>
       </c>
       <c r="D658" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A659" s="2">
+        <v>89352</v>
+      </c>
+      <c r="B659" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D659" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A660" s="2">
+        <v>103818</v>
+      </c>
+      <c r="B660" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D660" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F75EC8-28A7-4DCA-9E3C-9C63B4BADE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0382BDC6-3C66-4F17-A3AD-C193B75BCB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3551" uniqueCount="1289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3647" uniqueCount="1334">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3907,6 +3907,141 @@
   </si>
   <si>
     <t>CONECTOR EM BRONZE/LATÃO, DN 15 MM X 1/2", SEM ANEL DE SOLDA, BOLSA X ROSCA F, INSTALADO EM RAMAL E SUB-RAMAL DE GÁS COMBUSTÍVEL - FORNECIMENTO E INSTALAÇÃO. AF_04/2022</t>
+  </si>
+  <si>
+    <t>Comp 2050</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE TETRAPOLAR, ISOLADO EM PVC, 0,6/1KV, 2,5MM2 PARA CIRCUITO DE FORÇA, FORNECIMENTO DE MATERIAL (COMPOSIÇÃO REFERÊNCIA: SBC 063003 03/2026)</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Cabo PP Tetrapolar Isol.PVC - 0,6/1KV - #2.5 mm²</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Cabo PP Tetrapolar Isol.PVC - 0,6/1KV - #4.0 mm²</t>
+  </si>
+  <si>
+    <t>Comp 2051</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE TETRAPOLAR, ISOLADO EM PVC, 0,6/1KV, 4MM2 PARA CIRCUITO DE FORÇA, FORNECIMENTO DE MATERIAL (COMPOSIÇÃO REFERÊNCIA: SBC 063003 03/2026)</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 3/8"</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE FLEXÍVEL, DN 3/8", COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR-CONDICIONADO - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 5/8"</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE FLEXÍVEL, DN 5/8", COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR-CONDICIONADO - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Comp 68</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE FLEXÍVEL, DN 7/8, COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR CONDICIONADO COM CONDENSADORA CENTRAL FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA COD 161006 IOPES 05/2023)</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 7/8"</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 1/4"</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE FLEXÍVEL, DN 1/4", COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR-CONDICIONADO - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 1/2"</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE FLEXÍVEL, DN 1/2", COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR-CONDICIONADO - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>JOELHO 90 GRAUS, PVC, SOLDÁVEL, DN 25MM, INSTALADO EM DRENO DE AR-CONDICIONADO - FORNECIMENTO E INSTALAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Joelho 90º soldável - 25 mm</t>
+  </si>
+  <si>
+    <t>Comp 2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Caixa de passagem para condicionamento de ar tipo Split, com saída de dreno (COMPOSIÇÃO REFERENCIA:  CPOS/CDHU  43.20.130 -01/2026) </t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Caixa de distribuição - Caixa de passagem com dreno - saída central</t>
+  </si>
+  <si>
+    <t>TE, PVC, SOLDÁVEL, DN 25MM, INSTALADO EM DRENO DE AR-CONDICIONADO - FORNECIMENTO E INSTALAÇÃO. AF_08/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tê 90 soldável - 25 mm</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Evaporadora Teto/Piso - Evaporadora Split Piso Teto - Carrier - 42ZQVD48C5 - 48000 BTU/h - 6,0 kW</t>
+  </si>
+  <si>
+    <t>Comp 2021</t>
+  </si>
+  <si>
+    <t>Ar Condicionado Split Piso Teto - Carrier - 42ZQVD48C5 - 48000 BTU/h - 6,0 kW- (COMPOSIÇÃO DE REFERENCIA CÓDIGO 070389 SBC  07/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Condensadora Split - Condensadora Piso-Teto - Gree - GULD60W1/NhA-S - B - 60.000 BTU/h</t>
+  </si>
+  <si>
+    <t>Comp 1328</t>
+  </si>
+  <si>
+    <t>AR CONDICIONADO PISO TETO - 60000 BTU/h - 16,41 kW- (COMPOSIÇÃO DE REFERENCIA CÓDIGO 070389 SBC  07/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Condensadora Split - Condensadora Piso-Teto - Gree - GULD56W1/NhA-S - 57.000 BTU/h</t>
+  </si>
+  <si>
+    <t>Comp 1500</t>
+  </si>
+  <si>
+    <t>Ar-Condicionado Inverter Piso Teto R-32 Gree G-Prime Compact 57.000 BTUs Só Frio 220V Monofásico - FORNECIMENTO E INSTALAÇÃO. HCM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI (103252) 09/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Condensadora Split - Condensadora Split - Carrier - 38TVCD24515MC - 24000 BTU/h</t>
+  </si>
+  <si>
+    <t>Comp 2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ar-Condicionado  Cassete  1 Via 24000 BTUs  Só Frio 220v - FORNECIMENTO E INSTALAÇÃO. AF_11/2021 - (COMPOSIÇÃO REFERÊNCIA: SINAPI 103253) </t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Condensadora Split - Condensadora Split - Gree - D6DNA2A - 12000 BTU/h - 3,51 kW</t>
+  </si>
+  <si>
+    <t>Comp 1733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ar-condicionado Split 12.000 BTUs Gree Inverter Só Frio 220v - GWC12ATB - FORNECIMENTO E INSTALAÇÃO. AF_11/2021 - (COMPOSIÇÃO REFERÊNCIA: SINAPI 103253) </t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Condensadora Split - Condensadora Split - Gree - D6DNA2A - 18000 BTU/h - 5,27 kW</t>
+  </si>
+  <si>
+    <t>Comp 1732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ar-Condicionado Inverter Split Hi Wall G-Top Auto Wi-Fi Gree 18.000 BTUs Só Frio 220V - GWC18ATD - FORNECIMENTO E INSTALAÇÃO. AF_11/2021 - (COMPOSIÇÃO REFERÊNCIA: SINAPI 103253) </t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Condensadora Split - Condensadora Split - Gree - D6DNA2A - 27000 BTU/h - 7,91 kW</t>
+  </si>
+  <si>
+    <t>Comp 2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ar-Condicionado Inverter Split Hi Wall  27.000 BTUs Só Frio 220V - GWC27ATE - FORNECIMENTO E INSTALAÇÃO. AF_11/2021 - (COMPOSIÇÃO REFERÊNCIA: SINAPI 103253) </t>
   </si>
 </sst>
 </file>
@@ -4296,7 +4431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B660"/>
+  <dimension ref="A1:B677"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -9583,6 +9718,142 @@
         <v>7</v>
       </c>
     </row>
+    <row r="661" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A661" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A662" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A663" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A664" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A665" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A666" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A667" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A668" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A669" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A670" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A671" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A672" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A673" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A674" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A675" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A676" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A677" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -9590,7 +9861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D660"/>
+  <dimension ref="A1:D677"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -18839,6 +19110,244 @@
         <v>7</v>
       </c>
     </row>
+    <row r="661" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A661" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C661" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D661" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A662" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B662" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D662" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A663" s="2">
+        <v>97328</v>
+      </c>
+      <c r="B663" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D663" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A664" s="2">
+        <v>97330</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D664" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A665" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B665" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D665" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A666" s="2">
+        <v>97327</v>
+      </c>
+      <c r="B666" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D666" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A667" s="2">
+        <v>97329</v>
+      </c>
+      <c r="B667" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D667" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A668" s="2">
+        <v>89866</v>
+      </c>
+      <c r="B668" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D668" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A669" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B669" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D669" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A670" s="2">
+        <v>89869</v>
+      </c>
+      <c r="B670" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D670" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A671" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B671" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D671" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A672" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D672" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A673" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D673" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A674" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B674" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D674" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A675" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C675" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D675" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A676" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B676" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C676" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D676" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A677" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C677" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D677" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0382BDC6-3C66-4F17-A3AD-C193B75BCB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6281B1F8-E38C-47FD-A12A-FD2297EC38DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3647" uniqueCount="1334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3749" uniqueCount="1386">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4042,6 +4042,162 @@
   </si>
   <si>
     <t xml:space="preserve">Ar-Condicionado Inverter Split Hi Wall  27.000 BTUs Só Frio 220V - GWC27ATE - FORNECIMENTO E INSTALAÇÃO. AF_11/2021 - (COMPOSIÇÃO REFERÊNCIA: SINAPI 103253) </t>
+  </si>
+  <si>
+    <t>Condutos Ar condicionado - Duto de alumínio - 4"</t>
+  </si>
+  <si>
+    <t>Comp 54</t>
+  </si>
+  <si>
+    <t>DUTO ALUMINIZADO FLEXIVEL  4" . (COMPOSIÇÃO REFERENCIA 070475 SBC)</t>
+  </si>
+  <si>
+    <t>Condutos Ar condicionado - Duto de alumínio - 6"</t>
+  </si>
+  <si>
+    <t>Comp 1241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUTO ALUMINIZADO FLEXIVEL  6" . (COMPOSIÇÃO REFERENCIA 070475 SBC) </t>
+  </si>
+  <si>
+    <t>Condutos Ar condicionado - Duto de alumínio - 5"</t>
+  </si>
+  <si>
+    <t>Comp 583</t>
+  </si>
+  <si>
+    <t>DUTO ALUMINIZADO FLEXIVEL  5" . (COMPOSIÇÃO REFERENCIA 070475 SBC)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Ventilador Maxx - Ventilador ACI 150 + Filbox Red 150 - G4+F8 - 560 m³/h</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Ventilador Maxx - Ventilador ACI 125 + Filbox Red 125 - G4+F8 - 390 m³/h</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Exaustor - Ventilador Helicocentrífugo Mixvent | TD-4000/355</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Exaustor - Grelha Metálica Fixa - 6"</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Exaustor - Grelha Metálica Fixa - 5"</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Coifa - Coifa de Centro com filtro Metálico Removível em Aço Inox 150x100 ANSI 304</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Chaminé em Aço Galvanizado - Chapeu Circular com Aneis - 30Ø</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Exaustor - DF2 - Difusor - 5"</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Exaustor - Exaustor Sonora 10</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Exaustor - DF2 - Difusor - 6"</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Ventilador Maxx - Ventilador ACI 100 + Filbox Red 100 - G4+F8 - 275 m³/h</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Exaustor - Grelha Metálica Fixa - 4"</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Exaustor - DF2 - Difusor - 4"</t>
+  </si>
+  <si>
+    <t>Condutos Ar condicionado - Duto Aço Galvanizado - 30cm</t>
+  </si>
+  <si>
+    <t>Comp 2039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBO DE AÇO GALVANIZADO COM COSTURA, CLASSE MÉDIA, DN 300 (12"), CONEXÃO ROSQUEADA - FORNECIMENTO E INSTALAÇÃO. AF_01/2026 - ( COMPOSIÇÃO REFERÊNCIA:  SINAPI 101927 01/2026) </t>
+  </si>
+  <si>
+    <t>Comp 1722</t>
+  </si>
+  <si>
+    <t>DIFUSOR CAPTADOR DE AR CIRCULAR VENTIDEC DVK 100 - 4"- FORNECIMENTO E INSTALAÇÃO - (COMPOSIÇÃO DE REFERÊNCIA: 070928 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>Comp 1307</t>
+  </si>
+  <si>
+    <t>GRELHA METÁLICA FIXA C/TELA ANTI-INSETO - 4" (COMPOSIÇÃO DE REFERÊNCIA: 070928 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>Comp 1243</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VENTILADOR ACI 100 + FILBOX RED 100 (G4 + F8)  - (COMPOSIÇÃO DE REFERÊNCIA: 070852 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>Comp 1695</t>
+  </si>
+  <si>
+    <t>DIFUSOR CAPTADOR DE AR CIRCULAR VENTIDEC DVK 150 - 6" - FORNECIMENTO E INSTALAÇÃO - (COMPOSIÇÃO DE REFERÊNCIA: 070928 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>Comp 1282</t>
+  </si>
+  <si>
+    <t>Exaustor Sonora 10 (COMPOSIÇÃO DE REFERENCIA CÓDIGO 070389 SBC  07/2023)</t>
+  </si>
+  <si>
+    <t>Comp 1694</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DIFUSOR CAPTADOR DE AR CIRCULAR VENTIDEC DVK 125 - 5" - FORNECIMENTO E INSTALAÇÃO - (COMPOSIÇÃO DE REFERÊNCIA: 070928 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>UM</t>
+  </si>
+  <si>
+    <t>Comp 2017</t>
+  </si>
+  <si>
+    <t>Chapeu Circular com Aneis - 30Ø - (COMPOSIÇÃO REFERÊNCIA: SBC 073400 - 02/2026)</t>
+  </si>
+  <si>
+    <t>Comp 2015</t>
+  </si>
+  <si>
+    <t>COIFA EM AÇO INOX - (COMPOSIÇÃO REFERÊNCIA: SBC 073400 - 02/2026)</t>
+  </si>
+  <si>
+    <t>Comp 1480</t>
+  </si>
+  <si>
+    <t>GRELHA METÁLICA FIXA C/TELA ANTI-INSETO - 5" (COMPOSIÇÃO DE REFERÊNCIA: 070928 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>Comp 1481</t>
+  </si>
+  <si>
+    <t>GRELHA METÁLICA FIXA C/TELA ANTI-INSETO - 6" (COMPOSIÇÃO DE REFERÊNCIA: 070928 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>Comp 2016</t>
+  </si>
+  <si>
+    <t>Ventilador Helicocentrífugo Mixvent | TD-4000/355 (COMPOSIÇÃO DE REFERENCIA CÓDIGO 070389 SBC  07/2023)</t>
+  </si>
+  <si>
+    <t>Comp 1719</t>
+  </si>
+  <si>
+    <t>VENTILADOR ACI 125 + FILBOX RED 125 (G4 + F8)  - (COMPOSIÇÃO DE REFERÊNCIA: 070852 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>Comp 1721</t>
+  </si>
+  <si>
+    <t>VENTILADOR ACI 150 + FILBOX RED 150 (G4 + F8)  - (COMPOSIÇÃO DE REFERÊNCIA: 070852 SBC 06/2024)</t>
   </si>
 </sst>
 </file>
@@ -4431,7 +4587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B677"/>
+  <dimension ref="A1:B694"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -9854,6 +10010,142 @@
         <v>7</v>
       </c>
     </row>
+    <row r="678" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A678" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A679" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A680" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A681" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A682" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A683" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A684" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A685" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A686" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A687" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A688" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A689" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A690" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A691" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A692" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A693" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A694" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -9861,7 +10153,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D677"/>
+  <dimension ref="A1:D694"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -19348,6 +19640,244 @@
         <v>7</v>
       </c>
     </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A678" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C678" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D678" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A679" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B679" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C679" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D679" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A680" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B680" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C680" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D680" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A681" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B681" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C681" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D681" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A682" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B682" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C682" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D682" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A683" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B683" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C683" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D683" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A684" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B684" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C684" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D684" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A685" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C685" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D685" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A686" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C686" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D686" s="2" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A687" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C687" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D687" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A688" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C688" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D688" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A689" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B689" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C689" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D689" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A690" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B690" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C690" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D690" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A691" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C691" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D691" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A692" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C692" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D692" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A693" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C693" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D693" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A694" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C694" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D694" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6281B1F8-E38C-47FD-A12A-FD2297EC38DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023242F9-5264-4F40-9067-CD75F632375F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3749" uniqueCount="1386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3899" uniqueCount="1461">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4198,6 +4198,231 @@
   </si>
   <si>
     <t>VENTILADOR ACI 150 + FILBOX RED 150 (G4 + F8)  - (COMPOSIÇÃO DE REFERÊNCIA: 070852 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>Comp 67</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 3/4"</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE FLEXÍVEL, DN 3/4, COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR CONDICIONADO COM CONDENSADORA CENTRAL FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA COD 97334 SINAPI 05/2023)</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 1 1/8"</t>
+  </si>
+  <si>
+    <t>Comp 121</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE FLEXÍVEL, DN 1 1/8", COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR CONDICIONADO COM CONDENSADORA CENTRAL FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA COD 161006 IOPES 05/2023)</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 1 5/8"</t>
+  </si>
+  <si>
+    <t>Comp 123</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE FLEXÍVEL, DN 1 5/8", COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR CONDICIONADO COM CONDENSADORA CENTRAL FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA COD 161006 IOPES 05/2023)</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 1 3/8"</t>
+  </si>
+  <si>
+    <t>Comp 941</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE RIGIDO, DN 1.3/8, COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR CONDICIONADO COM CONDENSADORA CENTRAL FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA COD 161008 IOPES 08/2023)</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 1 1/2"</t>
+  </si>
+  <si>
+    <t>Comp 119</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE FLEXÍVEL, DN 1 1/2, COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR CONDICIONADO COM CONDENSADORA CENTRAL FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA COD 161006 IOPES 05/2023)</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 1 1/4"</t>
+  </si>
+  <si>
+    <t>Comp 120</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE FLEXÍVEL, DN 1 1/4", COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR CONDICIONADO COM CONDENSADORA CENTRAL FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA COD 161006 IOPES 05/2023)</t>
+  </si>
+  <si>
+    <t>Segmento de duto - Tubo de cobre flexível - 1"</t>
+  </si>
+  <si>
+    <t>Comp 1099</t>
+  </si>
+  <si>
+    <t>TUBO EM COBRE FLEXÍVEL, DN 1", COM ISOLAMENTO, INSTALADO EM RAMAL DE ALIMENTAÇÃO DE AR CONDICIONADO COM CONDENSADORA CENTRAL FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA COD 161006 IOPES 05/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - DAIKIN - Evaporadora DAIKIN - FXAQ63AVM</t>
+  </si>
+  <si>
+    <t>Comp 1511</t>
+  </si>
+  <si>
+    <t>EVAPORADORA VRV DAIKIN HI-WALL (PAREDE), 2,5 HP, 24200 BTUS/H, CICLO FRIO IPER - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI (103252) 09/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Válvula de esfera - 3/8"</t>
+  </si>
+  <si>
+    <t>Comp 633</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERA TIPO GBC 3/8" PARA FLUÍDO REFRIGERANTE NA ENTRADA E SAIDA DOS EQUIPAMENTOS (COMPOSIÇÃO DE REFERÊNCIA: 070305 SBC 02/2024)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Válvula de esfera - 5/8"</t>
+  </si>
+  <si>
+    <t>Comp 634</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERA TIPO GBC 5/8" PARA FLUÍDO REFRIGERANTE NA ENTRADA E SAIDA DOS EQUIPAMENTOS (COMPOSIÇÃO DE REFERÊNCIA: 070305 SBC 02/2024)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Válvula de esfera - 1/2"</t>
+  </si>
+  <si>
+    <t>Comp 632</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERA TIPO GBC 1/2" PARA FLUÍDO REFRIGERANTE NA ENTRADA E SAIDA DOS EQUIPAMENTOS (COMPOSIÇÃO DE REFERÊNCIA: 070305 SBC 02/2024)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Válvula de esfera - 1/4"</t>
+  </si>
+  <si>
+    <t>Comp 315</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERA TIPO GBC 1/4" PARA FLUÍDO REFRIGERANTE NA ENTRADA E SAIDA DOS EQUIPAMENTOS (COMPOSIÇÃO DE REFERÊNCIA: 070305 SBC 02/2024)</t>
+  </si>
+  <si>
+    <t>Comp 1510</t>
+  </si>
+  <si>
+    <t>EVAPORADORA VRV DAIKIN HI-WALL (PAREDE), 2 HP, 19100 BTUS/H, IPER CICLO FRIO - FORNECIMENTO E INSTALAÇÃO. HCM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI (103252) 09/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - DAIKIN - Evaporadora DAIKIN - FXAQ50AVM</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - DAIKIN - Evaporadora DAIKIN - FXAQ40AVM</t>
+  </si>
+  <si>
+    <t>Comp 1509</t>
+  </si>
+  <si>
+    <t>EVAPORADORA VRV DAIKIN HI-WALL (PAREDE), 1,6 HP, 15400 BTUS/H, CICLO FRIO IPER - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI (103252) 09/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Evaporadora Teto/Piso - Evaporadora Split Piso Teto - DAIKIN - FXHQ-140BMV - 59100 BTU/h</t>
+  </si>
+  <si>
+    <t>Comp 1515</t>
+  </si>
+  <si>
+    <t>EVAPORADORA VRV PISO/TETO 59100 BTU'S IPER- (COMPOSIÇÃO DE REFERENCIA CÓDIGO 070389 SBC 07/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Condensadora VRF - VRF - RXQ18TATL - 171000 BTU/h - 220V,60HZ - 15,4 kW</t>
+  </si>
+  <si>
+    <t>Comp 1506</t>
+  </si>
+  <si>
+    <t>UNIDADE CONDENSADORA VRV INOVA 18HP SÓ FRIO 220V IPER - DAIKIN  (COMPOSIÇÃO DE REFERÊNCIA: SBC (070905) 07/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Evaporadora Cassete 2 vias - 24200 BTU/h - 2,5 HP- DAIKIN - 220 V, 60 Hz - FXCQ63BVM</t>
+  </si>
+  <si>
+    <t>Comp 1512</t>
+  </si>
+  <si>
+    <t>EVAPORADORA VRV DAIKIN, CASSETE  2 VIAS, 2,5HP, 24200 BTU/H, CICLO FRIO IPER - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI (103268) 09/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Evaporadora Teto/Piso - Evaporadora Split Piso Teto - DAIKIN - FXHQ-100MAVE - 38200 BTU/h</t>
+  </si>
+  <si>
+    <t>Comp 1513</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Evaporadora Teto/Piso - Evaporadora Split Piso Teto - DAIKIN - FXHQ-63MAVE - 24200 BTU/h</t>
+  </si>
+  <si>
+    <t>Comp 1516</t>
+  </si>
+  <si>
+    <t>EVAPORADORA VRV PISO/TETO 38200 BTU'S IPER - (COMPOSIÇÃO DE REFERENCIA CÓDIGO 070389 SBC 07/2023)</t>
+  </si>
+  <si>
+    <t>EVAPORADORA VRV PISO/TETO 24200 BTU'S IPER - (COMPOSIÇÃO DE REFERENCIA CÓDIGO 070389 SBC 07/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Condensadora VRF - VRF - RXQ12TATL - 114000 BTU/h - 220V,60HZ - 8,82 kW</t>
+  </si>
+  <si>
+    <t>Comp 1504</t>
+  </si>
+  <si>
+    <t>UNIDADE CONDENSADORA VRV INOVA 12HP 220V IPER - DAIKIN  (COMPOSIÇÃO DE REFERÊNCIA: SBC (070905) 07/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Evaporadora Teto/Piso - Evaporadora Split Piso Teto - DAIKIN - FXHQ-125BMV - 48100 BTU/h</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Condensadora VRF - VRF - RXQ14TATL</t>
+  </si>
+  <si>
+    <t>Comp 1514</t>
+  </si>
+  <si>
+    <t>EVAPORADORA VRV PISO/TETO 48100 BTU&amp;#39;S IPER - (COMPOSIÇÃO DE REFERENCIA CÓDIGO 070389 SBC 07/2023)</t>
+  </si>
+  <si>
+    <t>Comp 1451</t>
+  </si>
+  <si>
+    <t>UNIDADE CONDENSADORA VRV INOVA 14HP SÓ FRIO 220V - DAIKIN IPER (COMPOSIÇÃO DE REFERÊNCIA: SBC (070905) 07/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Condensadora VRF - VRF - RXQ16TATL - 154000 BTU/h - 220V,60HZ - 45 kW</t>
+  </si>
+  <si>
+    <t>Comp 1505</t>
+  </si>
+  <si>
+    <t>UNIDADE CONDENSADORA VRV INOVA 16HP SÓ FRIO 220V IPER - DAIKIN  (COMPOSIÇÃO DE REFERÊNCIA: SBC (070905) 07/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - Condensadora VRF - VRF - RXQ20TATL - 191000 BTU/h - 220V,60HZ - 56 kW</t>
+  </si>
+  <si>
+    <t>Comp 1507</t>
+  </si>
+  <si>
+    <t>UNIDADE CONDENSADORA VRV INOVA 20HP SO FRIO 220V IPER - DAIKIN (COMPOSIÇÃO DE REFERÊNCIA: SBC (070907) 07/2023)</t>
+  </si>
+  <si>
+    <t>Equipamentos Ar condicionado - DAIKIN - Evaporadora DAIKIN - FXAQ32AVM</t>
+  </si>
+  <si>
+    <t>Comp 1508</t>
+  </si>
+  <si>
+    <t>EVAPORADORA VRV DAIKIN HI-WALL (PAREDE), 1,25 HP, 12300 BTUS/H, CICLO FRIO IPER - FORNECIMENTO E INSTALAÇÃO. HCM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI (103252) 09/2023)</t>
   </si>
 </sst>
 </file>
@@ -4587,7 +4812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B694"/>
+  <dimension ref="A1:B719"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -10146,6 +10371,206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="695" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A695" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A696" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A697" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A698" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A699" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A700" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A701" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A702" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A703" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A704" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A705" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A706" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A707" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A708" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A709" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A710" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A711" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A712" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A713" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A714" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A715" s="3" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A716" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A717" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A718" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A719" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B719" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -10153,7 +10578,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D694"/>
+  <dimension ref="A1:D719"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -19878,6 +20303,356 @@
         <v>7</v>
       </c>
     </row>
+    <row r="695" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A695" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C695" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D695" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A696" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C696" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D696" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A697" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B697" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C697" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D697" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A698" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C698" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D698" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A699" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C699" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D699" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A700" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B700" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C700" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D700" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A701" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C701" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D701" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A702" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C702" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D702" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A703" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C703" s="3" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D703" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A704" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C704" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D704" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A705" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C705" s="3" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D705" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A706" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C706" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D706" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A707" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B707" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C707" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D707" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A708" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C708" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D708" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A709" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C709" s="3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D709" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A710" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B710" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C710" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D710" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A711" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B711" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C711" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D711" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A712" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B712" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C712" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D712" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A713" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C713" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D713" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A714" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B714" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C714" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D714" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A715" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B715" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C715" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D715" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A716" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B716" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C716" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D716" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A717" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C717" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D717" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A718" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B718" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C718" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D718" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A719" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B719" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C719" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D719" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023242F9-5264-4F40-9067-CD75F632375F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686D8FF9-E5F5-4D24-BCEA-280BB01B277B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3899" uniqueCount="1461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="1493">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4423,6 +4423,102 @@
   </si>
   <si>
     <t>EVAPORADORA VRV DAIKIN HI-WALL (PAREDE), 1,25 HP, 12300 BTUS/H, CICLO FRIO IPER - FORNECIMENTO E INSTALAÇÃO. HCM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI (103252) 09/2023)</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Curva 90 soldável - 40 mm</t>
+  </si>
+  <si>
+    <t>CURVA 90 GRAUS, PVC, SOLDÁVEL, DN 40MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>VÁLVULA DE RETENÇÃO HORIZONTAL, DE BRONZE, ROSCÁVEL, 1 1/4" - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>Metais - Válvula de retenção horiz c/ portinhola - 1.1/4"</t>
+  </si>
+  <si>
+    <t>PVC misto soldável - Luva soldável c/ rosca - 25 mm -3/4"</t>
+  </si>
+  <si>
+    <t>LUVA COM BUCHA DE LATÃO, PVC, SOLDÁVEL, DN 25MM X 3/4, INSTALADO EM RAMAL OU SUB-RAMAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Torneira de bóia - 3/4"</t>
+  </si>
+  <si>
+    <t>TORNEIRA DE BOIA PARA CAIXA D&amp;#39;ÁGUA, ROSCÁVEL, 3/4" - FORNECIMENTO E INSTALAÇÃO. AF_08/2021</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tê 90 soldável - 40 mm</t>
+  </si>
+  <si>
+    <t>TE, PVC, SOLDÁVEL, DN 40MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Luva soldável - 32 mm</t>
+  </si>
+  <si>
+    <t>LUVA, PVC, SOLDÁVEL, DN 32MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Adapt sold c/ flange fixo p cx. d´água - 25 mm - 3/4"</t>
+  </si>
+  <si>
+    <t>ADAPTADOR COM FLANGE E ANEL DE VEDAÇÃO, PVC, SOLDÁVEL, DN 25 MM X 3/4", INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Adapt sold c/ flange fixo p cx. d´água - 32 mm - 1"</t>
+  </si>
+  <si>
+    <t>ADAPTADOR COM FLANGE E ANEL DE VEDAÇÃO, PVC, SOLDÁVEL, DN 32 MM X 1", INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - União soldável - 25 mm</t>
+  </si>
+  <si>
+    <t>UNIÃO, PVC, SOLDÁVEL, DN 25MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - União soldável - 32 mm</t>
+  </si>
+  <si>
+    <t>UNIÃO, PVC, SOLDÁVEL, DN 32MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - União soldável - 40 mm</t>
+  </si>
+  <si>
+    <t>UNIÃO, PVC, SOLDÁVEL, DN 40MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC soldável azul c/ bucha latão - Tê red.90 sold c/ bucha latão B central - 25 mm -1/2"</t>
+  </si>
+  <si>
+    <t>TÊ COM BUCHA DE LATÃO NA BOLSA CENTRAL, PVC, SOLDÁVEL, DN 25MM X 1/2, INSTALADO EM RAMAL OU SUB-RAMAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Curva 90 soldável - 50 mm</t>
+  </si>
+  <si>
+    <t>CURVA 90 GRAUS, PVC, SOLDÁVEL, DN 50MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tê 90 soldável - 50 mm</t>
+  </si>
+  <si>
+    <t>TE, PVC, SOLDÁVEL, DN 50MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Bucha de redução sold. longa - 50 mm - 25 mm</t>
+  </si>
+  <si>
+    <t>BUCHA DE REDUÇÃO PVC, SOLDÁVEL, LONGA, DN 50 X 25 MM, INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Luva soldável - 50 mm</t>
+  </si>
+  <si>
+    <t>LUVA, PVC, SOLDÁVEL, DN 50MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
   </si>
 </sst>
 </file>
@@ -4812,7 +4908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B719"/>
+  <dimension ref="A1:B736"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -10571,6 +10667,142 @@
         <v>7</v>
       </c>
     </row>
+    <row r="720" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A720" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A721" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A722" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A723" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B723" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A724" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A725" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B725" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A726" s="3" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B726" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A727" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B727" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A728" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B728" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A729" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B729" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A730" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B730" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A731" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B731" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A732" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A733" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B733" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A734" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B734" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A735" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B735" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A736" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -10578,7 +10810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D719"/>
+  <dimension ref="A1:D736"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -20653,6 +20885,244 @@
         <v>7</v>
       </c>
     </row>
+    <row r="720" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A720" s="2">
+        <v>103982</v>
+      </c>
+      <c r="B720" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C720" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D720" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A721" s="2">
+        <v>99621</v>
+      </c>
+      <c r="B721" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C721" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D721" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A722" s="2">
+        <v>89381</v>
+      </c>
+      <c r="B722" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C722" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D722" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A723" s="2">
+        <v>94796</v>
+      </c>
+      <c r="B723" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C723" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D723" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A724" s="2">
+        <v>104011</v>
+      </c>
+      <c r="B724" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C724" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D724" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A725" s="2">
+        <v>89431</v>
+      </c>
+      <c r="B725" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C725" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D725" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A726" s="2">
+        <v>94703</v>
+      </c>
+      <c r="B726" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C726" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D726" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A727" s="2">
+        <v>94704</v>
+      </c>
+      <c r="B727" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C727" s="3" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D727" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A728" s="2">
+        <v>89428</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C728" s="3" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D728" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A729" s="2">
+        <v>89435</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C729" s="3" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D729" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="730" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A730" s="2">
+        <v>103990</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C730" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D730" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A731" s="2">
+        <v>89396</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C731" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D731" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A732" s="2">
+        <v>103986</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C732" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D732" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A733" s="2">
+        <v>104004</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C733" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D733" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="734" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A734" s="2">
+        <v>105234</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C734" s="3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D734" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A735" s="2">
+        <v>103995</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C735" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D735" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A736" s="2">
+        <v>103982</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C736" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D736" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686D8FF9-E5F5-4D24-BCEA-280BB01B277B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9784C65F-3705-4A8B-A805-8283B127A5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="1493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3994" uniqueCount="1499">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4519,6 +4519,24 @@
   </si>
   <si>
     <t>LUVA, PVC, SOLDÁVEL, DN 50MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tê de redução 90 soldável - 50 mm - 25 mm</t>
+  </si>
+  <si>
+    <t>TÊ DE REDUÇÃO, PVC, SOLDÁVEL, DN 50MM X 25MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Bucha de redução sold. longa - 50 mm - 32 mm</t>
+  </si>
+  <si>
+    <t>BUCHA DE REDUÇÃO PVC, SOLDÁVEL, LONGA, DN 50 X 32 MM, INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
+  </si>
+  <si>
+    <t>PVC soldável azul c/ bucha latão - Joelho 90º soldável com bucha de latão - 25 mm - 3/4"</t>
+  </si>
+  <si>
+    <t>JOELHO 90 GRAUS COM BUCHA DE LATÃO, PVC, SOLDÁVEL, DN 25 MM X 3/4", INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
   </si>
 </sst>
 </file>
@@ -4908,7 +4926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B736"/>
+  <dimension ref="A1:B738"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -10797,9 +10815,25 @@
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A736" s="3" t="s">
-        <v>1461</v>
+        <v>1493</v>
       </c>
       <c r="B736" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A737" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A738" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B738" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -10810,7 +10844,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D736"/>
+  <dimension ref="A1:D738"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -21109,17 +21143,45 @@
         <v>7</v>
       </c>
     </row>
-    <row r="736" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A736" s="2">
-        <v>103982</v>
+        <v>104006</v>
       </c>
       <c r="B736" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C736" s="3" t="s">
-        <v>1462</v>
+        <v>1494</v>
       </c>
       <c r="D736" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="737" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A737" s="2">
+        <v>105228</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C737" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D737" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="738" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A738" s="2">
+        <v>94672</v>
+      </c>
+      <c r="B738" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C738" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D738" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9784C65F-3705-4A8B-A805-8283B127A5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C7BF4A-821B-48A3-B437-BA9B271A8A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3994" uniqueCount="1499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4052" uniqueCount="1519">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4537,6 +4537,66 @@
   </si>
   <si>
     <t>JOELHO 90 GRAUS COM BUCHA DE LATÃO, PVC, SOLDÁVEL, DN 25 MM X 3/4", INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
+  </si>
+  <si>
+    <t>Bomba Hidráulica - Incêndio - WDM Pumps Brasil - QE 3 I - 10 CV - R191</t>
+  </si>
+  <si>
+    <t>BOMBA CENTRÍFUGA, TRIFÁSICA, 10 CV OU 9,86 HP, HM 85 A 140 M, Q 4,2 A 14,9 M3/H - FORNECIMENTO E INSTALAÇÃO. AF_11/2025_PS</t>
+  </si>
+  <si>
+    <t>Bomba Jockey - Bomba schneider - BC-92 S/T AV 150mm - 1.5CV</t>
+  </si>
+  <si>
+    <t>BOMBA CENTRÍFUGA, TRIFÁSICA, 1,5 CV OU 1,48 HP, HM 10 A 70 M, Q 1,8 A 5,3 M3/H - FORNECIMENTO E INSTALAÇÃO. AF_11/2025_PS</t>
+  </si>
+  <si>
+    <t>Metais - Registro de gaveta bruto ABNT - 1"</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Bucha de redução - 1.1/4" x 1"</t>
+  </si>
+  <si>
+    <t>LUVA DE REDUÇÃO, EM FERRO GALVANIZADO, 1 1/4" X 1", CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Bucha de redução - 1" x 1/2"</t>
+  </si>
+  <si>
+    <t>LUVA DE REDUÇÃO, EM FERRO GALVANIZADO, 1" X 1/2", CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Bucha de redução - 2.1/2" x 1.1/4"</t>
+  </si>
+  <si>
+    <t>Comp 878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA DE REDUÇÃO, EM FERRO GALVANIZADO, 2 1/2" X 1 1/4", CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - ( COMPOSIÇÃO REFERÊNCIA SINAPI 92934) </t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Luva de redução - 1" x 1/2"</t>
+  </si>
+  <si>
+    <t>Metais - Pressostato - 1"</t>
+  </si>
+  <si>
+    <t>Metais - Manômetro - 1"</t>
+  </si>
+  <si>
+    <t>Comp 908</t>
+  </si>
+  <si>
+    <t>Tanque de pressão capacidade 25 lt (p/incendio) (COMPOSIÇÃO REFERÊNCIA:  ORSE 13313)</t>
+  </si>
+  <si>
+    <t>Metais - Tanque de Pressão - Tanque de Pressão 25L</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Adapt. p/ cx. d´agua de concreto 150 mm - 2.1/2"</t>
+  </si>
+  <si>
+    <t>ADAPTADOR COM FLANGES LIVRES, PVC, SOLDÁVEL, DN 75 MM X 2 1/2", INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
   </si>
 </sst>
 </file>
@@ -4926,7 +4986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B738"/>
+  <dimension ref="A1:B749"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -10837,6 +10897,94 @@
         <v>7</v>
       </c>
     </row>
+    <row r="739" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A739" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A740" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A741" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A742" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A743" s="3" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A744" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A745" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A746" s="3" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A747" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A748" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A749" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -10844,7 +10992,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D738"/>
+  <dimension ref="A1:D749"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -21185,6 +21333,160 @@
         <v>7</v>
       </c>
     </row>
+    <row r="739" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A739" s="2">
+        <v>102122</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C739" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D739" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="740" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A740" s="2">
+        <v>102115</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C740" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D740" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="741" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A741" s="2">
+        <v>94495</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C741" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D741" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="742" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A742" s="2">
+        <v>92925</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C742" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D742" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="743" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A743" s="2">
+        <v>92918</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C743" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D743" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="744" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A744" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C744" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D744" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="745" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A745" s="2">
+        <v>92918</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C745" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D745" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="746" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A746" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C746" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D746" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="747" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A747" s="2">
+        <v>101917</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C747" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D747" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="748" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A748" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C748" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D748" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="749" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A749" s="2">
+        <v>94713</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C749" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D749" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C7BF4A-821B-48A3-B437-BA9B271A8A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C8E5D9-71CE-4C20-ACB5-F8AD24069DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4052" uniqueCount="1519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4094" uniqueCount="1533">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4597,6 +4597,48 @@
   </si>
   <si>
     <t>ADAPTADOR COM FLANGES LIVRES, PVC, SOLDÁVEL, DN 75 MM X 2 1/2", INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 4 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - ref. Pirastic Ecoplus BWF Flexível - 1.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 2P+T 10A - Alta</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 3 - 2P+T 20A - Baixa</t>
+  </si>
+  <si>
+    <t>TOMADA BAIXA DE EMBUTIR (3 MÓDULOS), 2P+T 10 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva C - 16 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 380 V/220 V - DIN - Curva C - 63 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 63A - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 93673 - 04/2023)</t>
+  </si>
+  <si>
+    <t>Comp 290</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor unipolar termomagnético - 220 V/127 V - DIN - Curva C - 40 A - 5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR MONOPOLAR TIPO DIN, CORRENTE NOMINAL DE 40A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Cruzeta 90° - 100x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Comp 710</t>
+  </si>
+  <si>
+    <t>CRUZETA HORIZONTAL PARA ELETROCALHA 100X100MM (COMPOSIÇÃO DE REFERÊNCIA: 063746 SBC 06/2024)</t>
   </si>
 </sst>
 </file>
@@ -4638,7 +4680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4651,6 +4693,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4986,7 +5031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B749"/>
+  <dimension ref="A1:B757"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -10985,6 +11030,70 @@
         <v>7</v>
       </c>
     </row>
+    <row r="750" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A750" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B750" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A751" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B751" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A752" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B752" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A753" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A754" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A755" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A756" s="3" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A757" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -10992,7 +11101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D749"/>
+  <dimension ref="A1:D757"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -21487,6 +21596,118 @@
         <v>7</v>
       </c>
     </row>
+    <row r="750" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A750" s="1">
+        <v>91928</v>
+      </c>
+      <c r="B750" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C750" t="s">
+        <v>548</v>
+      </c>
+      <c r="D750" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="751" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A751" s="1">
+        <v>91924</v>
+      </c>
+      <c r="B751" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C751" t="s">
+        <v>536</v>
+      </c>
+      <c r="D751" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="752" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A752" s="2">
+        <v>91992</v>
+      </c>
+      <c r="B752" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C752" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D752" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A753" s="2">
+        <v>92016</v>
+      </c>
+      <c r="B753" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C753" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D753" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="754" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A754" s="2">
+        <v>93661</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C754" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D754" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="755" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A755" s="5" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B755" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C755" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D755" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="756" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A756" s="2">
+        <v>93658</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C756" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D756" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="757" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A757" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B757" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C757" s="3" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D757" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C8E5D9-71CE-4C20-ACB5-F8AD24069DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4B3714-2B74-4E90-90C6-8D92CF6B9A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4094" uniqueCount="1533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4099" uniqueCount="1534">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4639,6 +4639,9 @@
   </si>
   <si>
     <t>CRUZETA HORIZONTAL PARA ELETROCALHA 100X100MM (COMPOSIÇÃO DE REFERÊNCIA: 063746 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Caixa PVC octogonal - 4"x4"</t>
   </si>
 </sst>
 </file>
@@ -5031,7 +5034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B757"/>
+  <dimension ref="A1:B758"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -11094,6 +11097,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="758" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A758" s="3" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -11101,7 +11112,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D757"/>
+  <dimension ref="A1:D758"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -21708,6 +21719,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="758" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A758" s="2">
+        <v>91936</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C758" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D758" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4B3714-2B74-4E90-90C6-8D92CF6B9A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BC709B-3064-49FB-AFCE-FB857FCBEEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4099" uniqueCount="1534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4171" uniqueCount="1550">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4642,6 +4642,54 @@
   </si>
   <si>
     <t>Acessórios p/ eletrodutos - Caixa PVC octogonal - 4"x4"</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 1.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 1.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 1.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 1.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 1.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 2.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 2.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 2.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 2.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 2.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 2.5 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva B - 20 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 380 V/220 V - DIN - Curva C - 100 A - 13 kA</t>
+  </si>
+  <si>
+    <t>Comp 328</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE EMBUTIR, COM BARRAMENTO TRIFÁSICO, PARA 42 DISJUNTORES DIN 100A - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101881 - 04/2023)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - embutir - Barr. trif., disj geral, compacto - DIN - Cap. 42 disj. unip. - In barr. 100 A</t>
   </si>
 </sst>
 </file>
@@ -5034,7 +5082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B758"/>
+  <dimension ref="A1:B772"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -11105,6 +11153,118 @@
         <v>7</v>
       </c>
     </row>
+    <row r="759" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A759" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B759" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A760" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B760" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A761" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A762" s="3" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A763" s="3" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A764" s="3" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A765" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B765" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A766" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B766" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A767" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A768" s="3" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A769" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A770" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B770" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A771" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B771" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A772" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B772" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -11112,7 +11272,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D758"/>
+  <dimension ref="A1:D772"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -21733,6 +21893,202 @@
         <v>7</v>
       </c>
     </row>
+    <row r="759" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A759" s="2">
+        <v>91925</v>
+      </c>
+      <c r="B759" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C759" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D759" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="760" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A760" s="2">
+        <v>91925</v>
+      </c>
+      <c r="B760" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C760" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D760" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="761" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A761" s="2">
+        <v>91925</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C761" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D761" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="762" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A762" s="2">
+        <v>91925</v>
+      </c>
+      <c r="B762" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C762" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D762" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="763" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A763" s="2">
+        <v>91925</v>
+      </c>
+      <c r="B763" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C763" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D763" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="764" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A764" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B764" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C764" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D764" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="765" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A765" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B765" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C765" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D765" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="766" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A766" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B766" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C766" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D766" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="767" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A767" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B767" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C767" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D767" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="768" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A768" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B768" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C768" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D768" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="769" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A769" s="2">
+        <v>91927</v>
+      </c>
+      <c r="B769" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C769" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D769" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="770" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A770" s="2">
+        <v>93662</v>
+      </c>
+      <c r="B770" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C770" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D770" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="771" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A771" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B771" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C771" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D771" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="772" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A772" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B772" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C772" s="3" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D772" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BC709B-3064-49FB-AFCE-FB857FCBEEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A81F7F-E9EC-4B77-B150-174EE8C4EC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4171" uniqueCount="1550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4235" uniqueCount="1569">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4690,6 +4690,63 @@
   </si>
   <si>
     <t>Quadro distrib. chapa pintada - embutir - Barr. trif., disj geral, compacto - DIN - Cap. 42 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>.Soprano - Quadro de Distribuição ABS - Embutir - 36 polos DIN - cód. 05129.0036.11</t>
+  </si>
+  <si>
+    <t>Comp 2052</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE EMBUTIR, COM BARRAMENTO TRIFÁSICO, PARA 36 DISJUNTORES DIN 100A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025 (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 106022 - 04/2026)</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Condulete PVC 5 entradas - Condulete PVC 5 entradas</t>
+  </si>
+  <si>
+    <t>CONDULETE DE ALUMÍNIO, TIPO X, PARA ELETRODUTO DE AÇO GALVANIZADO DN 20 MM (3/4&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 4 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 4 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 4 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva C - 25 A - 25 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 380 V/220 V - DIN - Curva C - 63 A - 10 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - sobrepor - Tampa PVC p/ condulete - Interruptor 1 tecla simples</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Interruptor 1 tecla simples e tomada hexagonal - NBR14136</t>
+  </si>
+  <si>
+    <t>INTERRUPTOR SIMPLES (1 MÓDULO) COM 1 TOMADA DE EMBUTIR 2P+T 10 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Comp 2054</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 4x4" - Placa cega</t>
+  </si>
+  <si>
+    <t>CAIXA DE PASSAGEM PLASTICA DE 4X4 PAREDE DE CONCRETO COM TAMPA REMOVIVEL E ESPAÇADOR DE 12CM (COMPOSIÇÃO DE REFERÊNCIA: FDE 09.06.055 - 01/2026)</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC encaixe - Eletroduto, vara 3,0m - 3/4"</t>
+  </si>
+  <si>
+    <t>ELETRODUTO RÍGIDO ROSCÁVEL, PVC, DN 25 MM (3/4"), PARA CIRCUITOS TERMINAIS, INSTALADO EM PAREDE - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC flexível - Eletroduto leve - 1" - Parede</t>
   </si>
 </sst>
 </file>
@@ -5082,7 +5139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B772"/>
+  <dimension ref="A1:B784"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -11265,6 +11322,102 @@
         <v>7</v>
       </c>
     </row>
+    <row r="773" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A773" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B773" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A774" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B774" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A775" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B775" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A776" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A777" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A778" s="3" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B778" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A779" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B779" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A780" s="3" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B780" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A781" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B781" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A782" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B782" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A783" s="3" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B783" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A784" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B784" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -11272,7 +11425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D772"/>
+  <dimension ref="A1:D784"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -22089,6 +22242,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="773" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A773" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B773" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C773" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D773" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="774" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A774" s="2">
+        <v>95801</v>
+      </c>
+      <c r="B774" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C774" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D774" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="775" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A775" s="2">
+        <v>91929</v>
+      </c>
+      <c r="B775" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C775" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D775" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="776" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A776" s="2">
+        <v>91929</v>
+      </c>
+      <c r="B776" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C776" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D776" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="777" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A777" s="2">
+        <v>91929</v>
+      </c>
+      <c r="B777" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C777" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D777" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A778" s="2">
+        <v>93663</v>
+      </c>
+      <c r="B778" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C778" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D778" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A779" s="5" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B779" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C779" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D779" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A780" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B780" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C780" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="D780" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A781" s="2">
+        <v>92023</v>
+      </c>
+      <c r="B781" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C781" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D781" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A782" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B782" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C782" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D782" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A783" s="2">
+        <v>91871</v>
+      </c>
+      <c r="B783" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C783" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D783" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A784" s="2">
+        <v>91856</v>
+      </c>
+      <c r="B784" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C784" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D784" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A81F7F-E9EC-4B77-B150-174EE8C4EC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C268CD-4C23-4D5E-8D08-EBAB324F2F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4235" uniqueCount="1569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="1568">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4702,9 +4702,6 @@
   </si>
   <si>
     <t>Acessórios p/ eletrodutos - Condulete PVC 5 entradas - Condulete PVC 5 entradas</t>
-  </si>
-  <si>
-    <t>CONDULETE DE ALUMÍNIO, TIPO X, PARA ELETRODUTO DE AÇO GALVANIZADO DN 20 MM (3/4&amp;#39;&amp;#39;), APARENTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
   </si>
   <si>
     <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 4 mm² - Branco</t>
@@ -5139,7 +5136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B784"/>
+  <dimension ref="A1:B783"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -8204,7 +8201,7 @@
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>20</v>
@@ -8212,7 +8209,7 @@
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384" s="3" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>20</v>
@@ -8220,7 +8217,7 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>20</v>
@@ -8228,7 +8225,7 @@
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" s="3" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>20</v>
@@ -8236,7 +8233,7 @@
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>20</v>
@@ -8244,15 +8241,15 @@
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>7</v>
@@ -8260,7 +8257,7 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>7</v>
@@ -8268,7 +8265,7 @@
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>7</v>
@@ -8276,7 +8273,7 @@
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>7</v>
@@ -8284,7 +8281,7 @@
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>7</v>
@@ -8292,7 +8289,7 @@
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>7</v>
@@ -8300,7 +8297,7 @@
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>7</v>
@@ -8308,7 +8305,7 @@
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" s="3" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>7</v>
@@ -8316,7 +8313,7 @@
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>7</v>
@@ -8324,7 +8321,7 @@
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" s="3" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>7</v>
@@ -8332,7 +8329,7 @@
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B399" s="1" t="s">
         <v>7</v>
@@ -8340,7 +8337,7 @@
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>7</v>
@@ -8348,7 +8345,7 @@
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>7</v>
@@ -8356,7 +8353,7 @@
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>7</v>
@@ -8364,7 +8361,7 @@
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>7</v>
@@ -8372,7 +8369,7 @@
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>7</v>
@@ -8380,7 +8377,7 @@
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>7</v>
@@ -8388,7 +8385,7 @@
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>7</v>
@@ -8396,7 +8393,7 @@
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>7</v>
@@ -8404,7 +8401,7 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" s="3" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B408" s="1" t="s">
         <v>7</v>
@@ -8412,7 +8409,7 @@
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B409" s="1" t="s">
         <v>7</v>
@@ -8420,15 +8417,15 @@
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>20</v>
@@ -8436,7 +8433,7 @@
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>20</v>
@@ -8444,7 +8441,7 @@
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>20</v>
@@ -8452,7 +8449,7 @@
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" s="3" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B414" s="1" t="s">
         <v>20</v>
@@ -8460,7 +8457,7 @@
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>20</v>
@@ -8468,7 +8465,7 @@
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>20</v>
@@ -8476,7 +8473,7 @@
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>20</v>
@@ -8484,7 +8481,7 @@
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>20</v>
@@ -8492,7 +8489,7 @@
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>20</v>
@@ -8500,7 +8497,7 @@
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>20</v>
@@ -8508,7 +8505,7 @@
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>20</v>
@@ -8516,7 +8513,7 @@
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" s="3" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>20</v>
@@ -8524,7 +8521,7 @@
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>20</v>
@@ -8532,7 +8529,7 @@
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>20</v>
@@ -8540,15 +8537,15 @@
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" s="3" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>7</v>
@@ -8556,7 +8553,7 @@
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>7</v>
@@ -8564,7 +8561,7 @@
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" s="3" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>7</v>
@@ -8572,7 +8569,7 @@
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>7</v>
@@ -8580,7 +8577,7 @@
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430" s="3" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>7</v>
@@ -8588,7 +8585,7 @@
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>7</v>
@@ -8596,7 +8593,7 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" s="3" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>7</v>
@@ -8604,7 +8601,7 @@
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>7</v>
@@ -8612,7 +8609,7 @@
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" s="3" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>7</v>
@@ -8620,7 +8617,7 @@
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>7</v>
@@ -8628,7 +8625,7 @@
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" s="3" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>7</v>
@@ -8636,7 +8633,7 @@
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>7</v>
@@ -8644,7 +8641,7 @@
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438" s="3" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>7</v>
@@ -8652,7 +8649,7 @@
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>7</v>
@@ -8660,7 +8657,7 @@
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" s="3" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>7</v>
@@ -8668,7 +8665,7 @@
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>7</v>
@@ -8676,7 +8673,7 @@
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" s="3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>7</v>
@@ -8684,7 +8681,7 @@
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>7</v>
@@ -8692,7 +8689,7 @@
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444" s="3" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>7</v>
@@ -8700,7 +8697,7 @@
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>7</v>
@@ -8708,7 +8705,7 @@
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" s="3" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>7</v>
@@ -8716,7 +8713,7 @@
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>7</v>
@@ -8724,7 +8721,7 @@
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>7</v>
@@ -8732,7 +8729,7 @@
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>7</v>
@@ -8740,7 +8737,7 @@
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>7</v>
@@ -8748,7 +8745,7 @@
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>7</v>
@@ -8756,7 +8753,7 @@
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>7</v>
@@ -8764,7 +8761,7 @@
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>7</v>
@@ -8772,63 +8769,63 @@
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456" s="3" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A457" s="3" t="s">
-        <v>900</v>
+      <c r="A457" s="4" t="s">
+        <v>902</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A458" s="4" t="s">
-        <v>902</v>
+      <c r="A458" s="3" t="s">
+        <v>903</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A459" s="3" t="s">
-        <v>903</v>
+      <c r="A459" s="4" t="s">
+        <v>904</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A460" s="4" t="s">
-        <v>904</v>
+      <c r="A460" t="s">
+        <v>905</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>20</v>
@@ -8836,7 +8833,7 @@
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>20</v>
@@ -8844,7 +8841,7 @@
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>20</v>
@@ -8852,7 +8849,7 @@
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>20</v>
@@ -8860,7 +8857,7 @@
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>20</v>
@@ -8868,7 +8865,7 @@
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>20</v>
@@ -8876,7 +8873,7 @@
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>20</v>
@@ -8884,7 +8881,7 @@
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>20</v>
@@ -8892,7 +8889,7 @@
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>20</v>
@@ -8900,7 +8897,7 @@
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>20</v>
@@ -8908,7 +8905,7 @@
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B471" s="1" t="s">
         <v>20</v>
@@ -8916,7 +8913,7 @@
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>20</v>
@@ -8924,7 +8921,7 @@
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>20</v>
@@ -8932,7 +8929,7 @@
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>20</v>
@@ -8940,7 +8937,7 @@
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B475" s="1" t="s">
         <v>20</v>
@@ -8948,7 +8945,7 @@
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>20</v>
@@ -8956,7 +8953,7 @@
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>20</v>
@@ -8964,7 +8961,7 @@
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B478" s="1" t="s">
         <v>20</v>
@@ -8972,7 +8969,7 @@
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>20</v>
@@ -8980,7 +8977,7 @@
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B480" s="1" t="s">
         <v>20</v>
@@ -8988,7 +8985,7 @@
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B481" s="1" t="s">
         <v>20</v>
@@ -8996,7 +8993,7 @@
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>20</v>
@@ -9004,7 +9001,7 @@
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>20</v>
@@ -9012,15 +9009,15 @@
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A485" t="s">
-        <v>930</v>
+      <c r="A485" s="3" t="s">
+        <v>931</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>7</v>
@@ -9028,7 +9025,7 @@
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486" s="3" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>7</v>
@@ -9036,7 +9033,7 @@
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>7</v>
@@ -9044,7 +9041,7 @@
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488" s="3" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>7</v>
@@ -9052,23 +9049,23 @@
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A490" s="3" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>7</v>
@@ -9076,7 +9073,7 @@
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492" s="3" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>7</v>
@@ -9084,7 +9081,7 @@
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>7</v>
@@ -9092,7 +9089,7 @@
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494" s="3" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>7</v>
@@ -9100,23 +9097,23 @@
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A496" s="3" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="497" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>7</v>
@@ -9124,7 +9121,7 @@
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498" s="3" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>7</v>
@@ -9132,7 +9129,7 @@
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="B499" s="1" t="s">
         <v>7</v>
@@ -9140,15 +9137,15 @@
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B501" s="1" t="s">
         <v>20</v>
@@ -9156,7 +9153,7 @@
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B502" s="1" t="s">
         <v>20</v>
@@ -9164,7 +9161,7 @@
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>20</v>
@@ -9172,7 +9169,7 @@
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504" s="3" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>20</v>
@@ -9180,7 +9177,7 @@
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B505" s="1" t="s">
         <v>20</v>
@@ -9188,7 +9185,7 @@
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506" s="3" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>20</v>
@@ -9196,7 +9193,7 @@
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>20</v>
@@ -9204,31 +9201,31 @@
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508" s="3" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="B509" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A510" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B510" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="511" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B511" s="1" t="s">
         <v>7</v>
@@ -9236,23 +9233,23 @@
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512" s="3" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514" s="3" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B514" s="1" t="s">
         <v>7</v>
@@ -9260,7 +9257,7 @@
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="B515" s="1" t="s">
         <v>7</v>
@@ -9268,7 +9265,7 @@
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516" s="3" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="B516" s="1" t="s">
         <v>7</v>
@@ -9276,7 +9273,7 @@
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B517" s="1" t="s">
         <v>7</v>
@@ -9284,7 +9281,7 @@
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518" s="3" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B518" s="1" t="s">
         <v>7</v>
@@ -9292,7 +9289,7 @@
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B519" s="1" t="s">
         <v>7</v>
@@ -9300,7 +9297,7 @@
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A520" s="3" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B520" s="1" t="s">
         <v>7</v>
@@ -9308,15 +9305,15 @@
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522" s="3" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B522" s="1" t="s">
         <v>20</v>
@@ -9324,7 +9321,7 @@
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B523" s="1" t="s">
         <v>20</v>
@@ -9332,7 +9329,7 @@
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524" s="3" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>20</v>
@@ -9340,15 +9337,15 @@
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526" s="3" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>7</v>
@@ -9356,7 +9353,7 @@
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>7</v>
@@ -9364,7 +9361,7 @@
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528" s="3" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>7</v>
@@ -9372,7 +9369,7 @@
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B529" s="1" t="s">
         <v>7</v>
@@ -9380,7 +9377,7 @@
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A530" s="3" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>7</v>
@@ -9388,7 +9385,7 @@
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>7</v>
@@ -9396,7 +9393,7 @@
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A532" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>7</v>
@@ -9404,7 +9401,7 @@
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>7</v>
@@ -9412,15 +9409,15 @@
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A534" s="3" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>20</v>
@@ -9428,7 +9425,7 @@
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A536" s="3" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>20</v>
@@ -9436,7 +9433,7 @@
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B537" s="1" t="s">
         <v>20</v>
@@ -9444,7 +9441,7 @@
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A538" s="3" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>20</v>
@@ -9452,23 +9449,23 @@
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A540" s="3" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B541" s="1" t="s">
         <v>20</v>
@@ -9476,15 +9473,15 @@
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A542" s="3" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="B543" s="1" t="s">
         <v>7</v>
@@ -9492,7 +9489,7 @@
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A544" s="3" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B544" s="1" t="s">
         <v>7</v>
@@ -9500,7 +9497,7 @@
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B545" s="1" t="s">
         <v>7</v>
@@ -9508,7 +9505,7 @@
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A546" s="3" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B546" s="1" t="s">
         <v>7</v>
@@ -9516,7 +9513,7 @@
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B547" s="1" t="s">
         <v>7</v>
@@ -9524,7 +9521,7 @@
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A548" s="3" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B548" s="1" t="s">
         <v>7</v>
@@ -9532,7 +9529,7 @@
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B549" s="1" t="s">
         <v>7</v>
@@ -9540,7 +9537,7 @@
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A550" s="3" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>7</v>
@@ -9548,7 +9545,7 @@
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>7</v>
@@ -9556,7 +9553,7 @@
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A552" s="3" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>7</v>
@@ -9564,7 +9561,7 @@
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="B553" s="1" t="s">
         <v>7</v>
@@ -9572,7 +9569,7 @@
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A554" s="3" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B554" s="1" t="s">
         <v>7</v>
@@ -9580,7 +9577,7 @@
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="B555" s="1" t="s">
         <v>7</v>
@@ -9588,7 +9585,7 @@
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A556" s="3" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B556" s="1" t="s">
         <v>7</v>
@@ -9596,15 +9593,15 @@
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A558" s="3" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="B558" s="1" t="s">
         <v>20</v>
@@ -9612,7 +9609,7 @@
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B559" s="1" t="s">
         <v>20</v>
@@ -9620,15 +9617,15 @@
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A560" s="3" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B561" s="1" t="s">
         <v>7</v>
@@ -9636,7 +9633,7 @@
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A562" s="3" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B562" s="1" t="s">
         <v>7</v>
@@ -9644,7 +9641,7 @@
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B563" s="1" t="s">
         <v>7</v>
@@ -9652,7 +9649,7 @@
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A564" s="3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B564" s="1" t="s">
         <v>7</v>
@@ -9660,7 +9657,7 @@
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B565" s="1" t="s">
         <v>7</v>
@@ -9668,7 +9665,7 @@
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A566" s="3" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>7</v>
@@ -9676,7 +9673,7 @@
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B567" s="1" t="s">
         <v>7</v>
@@ -9684,7 +9681,7 @@
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A568" s="3" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B568" s="1" t="s">
         <v>7</v>
@@ -9692,7 +9689,7 @@
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B569" s="1" t="s">
         <v>7</v>
@@ -9700,7 +9697,7 @@
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A570" s="3" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="B570" s="1" t="s">
         <v>7</v>
@@ -9708,7 +9705,7 @@
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="B571" s="1" t="s">
         <v>7</v>
@@ -9716,7 +9713,7 @@
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A572" s="3" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B572" s="1" t="s">
         <v>7</v>
@@ -9724,7 +9721,7 @@
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B573" s="1" t="s">
         <v>7</v>
@@ -9732,7 +9729,7 @@
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A574" s="3" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B574" s="1" t="s">
         <v>7</v>
@@ -9740,7 +9737,7 @@
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B575" s="1" t="s">
         <v>7</v>
@@ -9748,15 +9745,15 @@
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A576" s="3" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B577" s="1" t="s">
         <v>20</v>
@@ -9764,7 +9761,7 @@
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A578" s="3" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="B578" s="1" t="s">
         <v>20</v>
@@ -9772,15 +9769,15 @@
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A580" s="3" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B580" s="1" t="s">
         <v>7</v>
@@ -9788,7 +9785,7 @@
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="B581" s="1" t="s">
         <v>7</v>
@@ -9796,7 +9793,7 @@
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A582" s="3" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B582" s="1" t="s">
         <v>7</v>
@@ -9804,7 +9801,7 @@
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B583" s="1" t="s">
         <v>7</v>
@@ -9812,7 +9809,7 @@
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A584" s="3" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="B584" s="1" t="s">
         <v>7</v>
@@ -9820,7 +9817,7 @@
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="B585" s="1" t="s">
         <v>7</v>
@@ -9828,7 +9825,7 @@
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A586" s="3" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B586" s="1" t="s">
         <v>7</v>
@@ -9836,7 +9833,7 @@
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A587" s="3" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B587" s="1" t="s">
         <v>7</v>
@@ -9844,7 +9841,7 @@
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A588" s="3" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B588" s="1" t="s">
         <v>7</v>
@@ -9852,7 +9849,7 @@
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B589" s="1" t="s">
         <v>7</v>
@@ -9860,7 +9857,7 @@
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A590" s="3" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="B590" s="1" t="s">
         <v>7</v>
@@ -9868,7 +9865,7 @@
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="B591" s="1" t="s">
         <v>7</v>
@@ -9876,7 +9873,7 @@
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A592" s="3" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="B592" s="1" t="s">
         <v>7</v>
@@ -9884,7 +9881,7 @@
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B593" s="1" t="s">
         <v>7</v>
@@ -9892,7 +9889,7 @@
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A594" s="3" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="B594" s="1" t="s">
         <v>7</v>
@@ -9900,7 +9897,7 @@
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A595" s="3" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B595" s="1" t="s">
         <v>7</v>
@@ -9908,7 +9905,7 @@
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A596" s="3" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="B596" s="1" t="s">
         <v>7</v>
@@ -9916,7 +9913,7 @@
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A597" s="3" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B597" s="1" t="s">
         <v>7</v>
@@ -9924,7 +9921,7 @@
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A598" s="3" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B598" s="1" t="s">
         <v>7</v>
@@ -9932,15 +9929,15 @@
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A599" s="3" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A600" s="3" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="B600" s="1" t="s">
         <v>20</v>
@@ -9948,15 +9945,15 @@
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A601" s="3" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A602" s="3" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B602" s="1" t="s">
         <v>7</v>
@@ -9964,7 +9961,7 @@
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A603" s="3" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B603" s="1" t="s">
         <v>7</v>
@@ -9972,7 +9969,7 @@
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A604" s="3" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="B604" s="1" t="s">
         <v>7</v>
@@ -9980,7 +9977,7 @@
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A605" s="3" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="B605" s="1" t="s">
         <v>7</v>
@@ -9988,7 +9985,7 @@
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A606" s="3" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B606" s="1" t="s">
         <v>7</v>
@@ -9996,7 +9993,7 @@
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A607" s="3" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="B607" s="1" t="s">
         <v>7</v>
@@ -10004,7 +10001,7 @@
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A608" s="3" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="B608" s="1" t="s">
         <v>7</v>
@@ -10012,7 +10009,7 @@
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A609" s="3" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="B609" s="1" t="s">
         <v>7</v>
@@ -10020,7 +10017,7 @@
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A610" s="3" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B610" s="1" t="s">
         <v>7</v>
@@ -10028,7 +10025,7 @@
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A611" s="3" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B611" s="1" t="s">
         <v>7</v>
@@ -10036,7 +10033,7 @@
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A612" s="3" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B612" s="1" t="s">
         <v>7</v>
@@ -10044,7 +10041,7 @@
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A613" s="3" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="B613" s="1" t="s">
         <v>7</v>
@@ -10052,7 +10049,7 @@
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A614" s="3" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B614" s="1" t="s">
         <v>7</v>
@@ -10060,7 +10057,7 @@
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A615" s="3" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B615" s="1" t="s">
         <v>7</v>
@@ -10068,7 +10065,7 @@
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A616" s="3" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B616" s="1" t="s">
         <v>7</v>
@@ -10076,7 +10073,7 @@
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A617" s="3" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B617" s="1" t="s">
         <v>7</v>
@@ -10084,7 +10081,7 @@
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A618" s="3" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="B618" s="1" t="s">
         <v>7</v>
@@ -10092,7 +10089,7 @@
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A619" s="3" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="B619" s="1" t="s">
         <v>7</v>
@@ -10100,7 +10097,7 @@
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A620" s="3" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="B620" s="1" t="s">
         <v>7</v>
@@ -10108,7 +10105,7 @@
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A621" s="3" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B621" s="1" t="s">
         <v>7</v>
@@ -10116,7 +10113,7 @@
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A622" s="3" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="B622" s="1" t="s">
         <v>7</v>
@@ -10124,7 +10121,7 @@
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A623" s="3" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B623" s="1" t="s">
         <v>7</v>
@@ -10132,7 +10129,7 @@
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A624" s="3" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="B624" s="1" t="s">
         <v>7</v>
@@ -10140,7 +10137,7 @@
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A625" s="3" t="s">
-        <v>1222</v>
+        <v>1213</v>
       </c>
       <c r="B625" s="1" t="s">
         <v>7</v>
@@ -10148,7 +10145,7 @@
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A626" s="3" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="B626" s="1" t="s">
         <v>7</v>
@@ -10156,7 +10153,7 @@
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A627" s="3" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="B627" s="1" t="s">
         <v>7</v>
@@ -10164,7 +10161,7 @@
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A628" s="3" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B628" s="1" t="s">
         <v>7</v>
@@ -10172,7 +10169,7 @@
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A629" s="3" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="B629" s="1" t="s">
         <v>7</v>
@@ -10180,7 +10177,7 @@
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A630" s="3" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B630" s="1" t="s">
         <v>7</v>
@@ -10188,7 +10185,7 @@
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A631" s="3" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="B631" s="1" t="s">
         <v>7</v>
@@ -10196,7 +10193,7 @@
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A632" s="3" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="B632" s="1" t="s">
         <v>7</v>
@@ -10204,7 +10201,7 @@
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A633" s="3" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="B633" s="1" t="s">
         <v>7</v>
@@ -10212,7 +10209,7 @@
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A634" s="3" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B634" s="1" t="s">
         <v>7</v>
@@ -10220,7 +10217,7 @@
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A635" s="3" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B635" s="1" t="s">
         <v>7</v>
@@ -10228,7 +10225,7 @@
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A636" s="3" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="B636" s="1" t="s">
         <v>7</v>
@@ -10236,7 +10233,7 @@
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A637" s="3" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="B637" s="1" t="s">
         <v>7</v>
@@ -10244,7 +10241,7 @@
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A638" s="3" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="B638" s="1" t="s">
         <v>7</v>
@@ -10252,7 +10249,7 @@
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A639" s="3" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B639" s="1" t="s">
         <v>7</v>
@@ -10260,7 +10257,7 @@
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A640" s="3" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="B640" s="1" t="s">
         <v>7</v>
@@ -10268,7 +10265,7 @@
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A641" s="3" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="B641" s="1" t="s">
         <v>7</v>
@@ -10276,7 +10273,7 @@
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A642" s="3" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="B642" s="1" t="s">
         <v>7</v>
@@ -10284,7 +10281,7 @@
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A643" s="3" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="B643" s="1" t="s">
         <v>7</v>
@@ -10292,7 +10289,7 @@
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A644" s="3" t="s">
-        <v>1255</v>
+        <v>1172</v>
       </c>
       <c r="B644" s="1" t="s">
         <v>7</v>
@@ -10300,15 +10297,15 @@
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A645" s="3" t="s">
-        <v>1172</v>
+        <v>1259</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A646" s="3" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="B646" s="1" t="s">
         <v>20</v>
@@ -10316,15 +10313,15 @@
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A647" s="3" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A648" s="3" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="B648" s="1" t="s">
         <v>7</v>
@@ -10332,7 +10329,7 @@
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A649" s="3" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B649" s="1" t="s">
         <v>7</v>
@@ -10340,7 +10337,7 @@
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A650" s="3" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="B650" s="1" t="s">
         <v>7</v>
@@ -10348,7 +10345,7 @@
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A651" s="3" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B651" s="1" t="s">
         <v>7</v>
@@ -10356,7 +10353,7 @@
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A652" s="3" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="B652" s="1" t="s">
         <v>7</v>
@@ -10364,7 +10361,7 @@
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A653" s="3" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="B653" s="1" t="s">
         <v>7</v>
@@ -10372,7 +10369,7 @@
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A654" s="3" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="B654" s="1" t="s">
         <v>7</v>
@@ -10380,7 +10377,7 @@
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A655" s="3" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="B655" s="1" t="s">
         <v>7</v>
@@ -10388,7 +10385,7 @@
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A656" s="3" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B656" s="1" t="s">
         <v>7</v>
@@ -10396,7 +10393,7 @@
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A657" s="3" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="B657" s="1" t="s">
         <v>7</v>
@@ -10404,7 +10401,7 @@
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A658" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B658" s="1" t="s">
         <v>7</v>
@@ -10412,7 +10409,7 @@
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A659" s="3" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="B659" s="1" t="s">
         <v>7</v>
@@ -10420,15 +10417,15 @@
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A660" s="3" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A661" s="3" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B661" s="1" t="s">
         <v>20</v>
@@ -10436,7 +10433,7 @@
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A662" s="3" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="B662" s="1" t="s">
         <v>20</v>
@@ -10444,7 +10441,7 @@
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A663" s="3" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="B663" s="1" t="s">
         <v>20</v>
@@ -10452,7 +10449,7 @@
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A664" s="3" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="B664" s="1" t="s">
         <v>20</v>
@@ -10460,7 +10457,7 @@
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A665" s="3" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B665" s="1" t="s">
         <v>20</v>
@@ -10468,7 +10465,7 @@
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A666" s="3" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="B666" s="1" t="s">
         <v>20</v>
@@ -10476,15 +10473,15 @@
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A667" s="3" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A668" s="3" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="B668" s="1" t="s">
         <v>7</v>
@@ -10492,7 +10489,7 @@
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A669" s="3" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="B669" s="1" t="s">
         <v>7</v>
@@ -10500,7 +10497,7 @@
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A670" s="3" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B670" s="1" t="s">
         <v>7</v>
@@ -10508,7 +10505,7 @@
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A671" s="3" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="B671" s="1" t="s">
         <v>7</v>
@@ -10516,7 +10513,7 @@
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A672" s="3" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="B672" s="1" t="s">
         <v>7</v>
@@ -10524,7 +10521,7 @@
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A673" s="3" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="B673" s="1" t="s">
         <v>7</v>
@@ -10532,7 +10529,7 @@
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A674" s="3" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="B674" s="1" t="s">
         <v>7</v>
@@ -10540,7 +10537,7 @@
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A675" s="3" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="B675" s="1" t="s">
         <v>7</v>
@@ -10548,7 +10545,7 @@
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A676" s="3" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="B676" s="1" t="s">
         <v>7</v>
@@ -10556,15 +10553,15 @@
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A677" s="3" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A678" s="3" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="B678" s="1" t="s">
         <v>20</v>
@@ -10572,7 +10569,7 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A679" s="3" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="B679" s="1" t="s">
         <v>20</v>
@@ -10580,7 +10577,7 @@
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A680" s="3" t="s">
-        <v>1340</v>
+        <v>1356</v>
       </c>
       <c r="B680" s="1" t="s">
         <v>20</v>
@@ -10588,15 +10585,15 @@
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A681" s="3" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A682" s="3" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B682" s="1" t="s">
         <v>7</v>
@@ -10604,7 +10601,7 @@
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A683" s="3" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B683" s="1" t="s">
         <v>7</v>
@@ -10612,7 +10609,7 @@
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A684" s="3" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B684" s="1" t="s">
         <v>7</v>
@@ -10620,7 +10617,7 @@
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A685" s="3" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B685" s="1" t="s">
         <v>7</v>
@@ -10628,7 +10625,7 @@
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A686" s="3" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B686" s="1" t="s">
         <v>7</v>
@@ -10636,7 +10633,7 @@
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A687" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B687" s="1" t="s">
         <v>7</v>
@@ -10644,7 +10641,7 @@
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A688" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B688" s="1" t="s">
         <v>7</v>
@@ -10652,7 +10649,7 @@
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A689" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B689" s="1" t="s">
         <v>7</v>
@@ -10660,7 +10657,7 @@
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A690" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B690" s="1" t="s">
         <v>7</v>
@@ -10668,7 +10665,7 @@
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A691" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B691" s="1" t="s">
         <v>7</v>
@@ -10676,7 +10673,7 @@
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A692" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="B692" s="1" t="s">
         <v>7</v>
@@ -10684,7 +10681,7 @@
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A693" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B693" s="1" t="s">
         <v>7</v>
@@ -10692,15 +10689,15 @@
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A694" s="3" t="s">
-        <v>1343</v>
+        <v>1387</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A695" s="3" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="B695" s="1" t="s">
         <v>20</v>
@@ -10708,7 +10705,7 @@
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A696" s="3" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="B696" s="1" t="s">
         <v>20</v>
@@ -10716,7 +10713,7 @@
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A697" s="3" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="B697" s="1" t="s">
         <v>20</v>
@@ -10724,7 +10721,7 @@
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A698" s="3" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="B698" s="1" t="s">
         <v>20</v>
@@ -10732,7 +10729,7 @@
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A699" s="3" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="B699" s="1" t="s">
         <v>20</v>
@@ -10740,7 +10737,7 @@
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A700" s="3" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="B700" s="1" t="s">
         <v>20</v>
@@ -10748,15 +10745,15 @@
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A701" s="3" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A702" s="3" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="B702" s="1" t="s">
         <v>7</v>
@@ -10764,7 +10761,7 @@
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A703" s="3" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="B703" s="1" t="s">
         <v>7</v>
@@ -10772,7 +10769,7 @@
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A704" s="3" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="B704" s="1" t="s">
         <v>7</v>
@@ -10780,7 +10777,7 @@
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A705" s="3" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="B705" s="1" t="s">
         <v>7</v>
@@ -10788,7 +10785,7 @@
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A706" s="3" t="s">
-        <v>1419</v>
+        <v>1424</v>
       </c>
       <c r="B706" s="1" t="s">
         <v>7</v>
@@ -10796,7 +10793,7 @@
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A707" s="3" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B707" s="1" t="s">
         <v>7</v>
@@ -10804,7 +10801,7 @@
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A708" s="3" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="B708" s="1" t="s">
         <v>7</v>
@@ -10812,7 +10809,7 @@
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A709" s="3" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="B709" s="1" t="s">
         <v>7</v>
@@ -10820,7 +10817,7 @@
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A710" s="3" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="B710" s="1" t="s">
         <v>7</v>
@@ -10828,7 +10825,7 @@
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A711" s="3" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="B711" s="1" t="s">
         <v>7</v>
@@ -10836,7 +10833,7 @@
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A712" s="3" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="B712" s="1" t="s">
         <v>7</v>
@@ -10844,7 +10841,7 @@
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A713" s="3" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="B713" s="1" t="s">
         <v>7</v>
@@ -10852,7 +10849,7 @@
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A714" s="3" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="B714" s="1" t="s">
         <v>7</v>
@@ -10860,7 +10857,7 @@
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A715" s="3" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B715" s="1" t="s">
         <v>7</v>
@@ -10868,7 +10865,7 @@
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A716" s="3" t="s">
-        <v>1447</v>
+        <v>1452</v>
       </c>
       <c r="B716" s="1" t="s">
         <v>7</v>
@@ -10876,7 +10873,7 @@
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A717" s="3" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="B717" s="1" t="s">
         <v>7</v>
@@ -10884,7 +10881,7 @@
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A718" s="3" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="B718" s="1" t="s">
         <v>7</v>
@@ -10892,7 +10889,7 @@
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A719" s="3" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
       <c r="B719" s="1" t="s">
         <v>7</v>
@@ -10900,7 +10897,7 @@
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A720" s="3" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
       <c r="B720" s="1" t="s">
         <v>7</v>
@@ -10908,7 +10905,7 @@
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A721" s="3" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B721" s="1" t="s">
         <v>7</v>
@@ -10916,7 +10913,7 @@
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A722" s="3" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="B722" s="1" t="s">
         <v>7</v>
@@ -10924,7 +10921,7 @@
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A723" s="3" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="B723" s="1" t="s">
         <v>7</v>
@@ -10932,7 +10929,7 @@
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A724" s="3" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B724" s="1" t="s">
         <v>7</v>
@@ -10940,7 +10937,7 @@
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A725" s="3" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B725" s="1" t="s">
         <v>7</v>
@@ -10948,7 +10945,7 @@
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A726" s="3" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="B726" s="1" t="s">
         <v>7</v>
@@ -10956,7 +10953,7 @@
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A727" s="3" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="B727" s="1" t="s">
         <v>7</v>
@@ -10964,7 +10961,7 @@
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A728" s="3" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="B728" s="1" t="s">
         <v>7</v>
@@ -10972,7 +10969,7 @@
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A729" s="3" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="B729" s="1" t="s">
         <v>7</v>
@@ -10980,7 +10977,7 @@
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A730" s="3" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="B730" s="1" t="s">
         <v>7</v>
@@ -10988,7 +10985,7 @@
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A731" s="3" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="B731" s="1" t="s">
         <v>7</v>
@@ -10996,7 +10993,7 @@
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A732" s="3" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="B732" s="1" t="s">
         <v>7</v>
@@ -11004,7 +11001,7 @@
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A733" s="3" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="B733" s="1" t="s">
         <v>7</v>
@@ -11012,7 +11009,7 @@
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A734" s="3" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="B734" s="1" t="s">
         <v>7</v>
@@ -11020,7 +11017,7 @@
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A735" s="3" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="B735" s="1" t="s">
         <v>7</v>
@@ -11028,7 +11025,7 @@
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A736" s="3" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="B736" s="1" t="s">
         <v>7</v>
@@ -11036,7 +11033,7 @@
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A737" s="3" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B737" s="1" t="s">
         <v>7</v>
@@ -11044,15 +11041,15 @@
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A738" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="B738" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B738" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A739" s="3" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="B739" s="2" t="s">
         <v>7</v>
@@ -11060,7 +11057,7 @@
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A740" s="3" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B740" s="2" t="s">
         <v>7</v>
@@ -11068,7 +11065,7 @@
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A741" s="3" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>7</v>
@@ -11076,7 +11073,7 @@
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A742" s="3" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="B742" s="2" t="s">
         <v>7</v>
@@ -11084,7 +11081,7 @@
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A743" s="3" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="B743" s="2" t="s">
         <v>7</v>
@@ -11092,7 +11089,7 @@
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A744" s="3" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="B744" s="2" t="s">
         <v>7</v>
@@ -11100,7 +11097,7 @@
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A745" s="3" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B745" s="2" t="s">
         <v>7</v>
@@ -11108,7 +11105,7 @@
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A746" s="3" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B746" s="2" t="s">
         <v>7</v>
@@ -11116,7 +11113,7 @@
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A747" s="3" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="B747" s="2" t="s">
         <v>7</v>
@@ -11124,7 +11121,7 @@
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A748" s="3" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B748" s="2" t="s">
         <v>7</v>
@@ -11132,15 +11129,15 @@
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A749" s="3" t="s">
-        <v>1517</v>
-      </c>
-      <c r="B749" s="2" t="s">
-        <v>7</v>
+        <v>1519</v>
+      </c>
+      <c r="B749" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A750" s="3" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B750" s="1" t="s">
         <v>20</v>
@@ -11148,15 +11145,15 @@
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A751" s="3" t="s">
-        <v>1520</v>
-      </c>
-      <c r="B751" s="1" t="s">
-        <v>20</v>
+        <v>1521</v>
+      </c>
+      <c r="B751" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A752" s="3" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B752" s="2" t="s">
         <v>7</v>
@@ -11164,7 +11161,7 @@
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A753" s="3" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="B753" s="2" t="s">
         <v>7</v>
@@ -11172,7 +11169,7 @@
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A754" s="3" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B754" s="2" t="s">
         <v>7</v>
@@ -11180,7 +11177,7 @@
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A755" s="3" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
       <c r="B755" s="2" t="s">
         <v>7</v>
@@ -11188,7 +11185,7 @@
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A756" s="3" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="B756" s="2" t="s">
         <v>7</v>
@@ -11196,7 +11193,7 @@
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A757" s="3" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
       <c r="B757" s="2" t="s">
         <v>7</v>
@@ -11204,15 +11201,15 @@
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A758" s="3" t="s">
-        <v>1533</v>
-      </c>
-      <c r="B758" s="2" t="s">
-        <v>7</v>
+        <v>1534</v>
+      </c>
+      <c r="B758" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A759" s="3" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B759" s="1" t="s">
         <v>20</v>
@@ -11220,7 +11217,7 @@
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A760" s="3" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B760" s="1" t="s">
         <v>20</v>
@@ -11228,7 +11225,7 @@
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A761" s="3" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B761" s="1" t="s">
         <v>20</v>
@@ -11236,7 +11233,7 @@
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A762" s="3" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B762" s="1" t="s">
         <v>20</v>
@@ -11244,7 +11241,7 @@
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A763" s="3" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B763" s="1" t="s">
         <v>20</v>
@@ -11252,7 +11249,7 @@
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A764" s="3" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B764" s="1" t="s">
         <v>20</v>
@@ -11260,7 +11257,7 @@
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A765" s="3" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B765" s="1" t="s">
         <v>20</v>
@@ -11268,7 +11265,7 @@
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A766" s="3" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B766" s="1" t="s">
         <v>20</v>
@@ -11276,7 +11273,7 @@
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A767" s="3" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B767" s="1" t="s">
         <v>20</v>
@@ -11284,7 +11281,7 @@
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A768" s="3" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B768" s="1" t="s">
         <v>20</v>
@@ -11292,15 +11289,15 @@
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A769" s="3" t="s">
-        <v>1544</v>
-      </c>
-      <c r="B769" s="1" t="s">
-        <v>20</v>
+        <v>1545</v>
+      </c>
+      <c r="B769" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A770" s="3" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B770" s="2" t="s">
         <v>7</v>
@@ -11308,7 +11305,7 @@
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A771" s="3" t="s">
-        <v>1546</v>
+        <v>1549</v>
       </c>
       <c r="B771" s="2" t="s">
         <v>7</v>
@@ -11316,7 +11313,7 @@
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A772" s="3" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B772" s="2" t="s">
         <v>7</v>
@@ -11324,7 +11321,7 @@
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A773" s="3" t="s">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="B773" s="2" t="s">
         <v>7</v>
@@ -11332,10 +11329,10 @@
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A774" s="3" t="s">
-        <v>1553</v>
-      </c>
-      <c r="B774" s="2" t="s">
-        <v>7</v>
+        <v>1554</v>
+      </c>
+      <c r="B774" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.3">
@@ -11358,8 +11355,8 @@
       <c r="A777" s="3" t="s">
         <v>1557</v>
       </c>
-      <c r="B777" s="1" t="s">
-        <v>20</v>
+      <c r="B777" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.3">
@@ -11388,7 +11385,7 @@
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A781" s="3" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="B781" s="2" t="s">
         <v>7</v>
@@ -11396,25 +11393,17 @@
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A782" s="3" t="s">
-        <v>1564</v>
-      </c>
-      <c r="B782" s="2" t="s">
-        <v>7</v>
+        <v>1565</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A783" s="3" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B783" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="784" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A784" s="3" t="s">
-        <v>1568</v>
-      </c>
-      <c r="B784" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -11425,7 +11414,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D784"/>
+  <dimension ref="A1:D783"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -16782,29 +16771,29 @@
         <v>20</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A383" s="2">
-        <v>91836</v>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A383" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D383" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A384" s="2" t="s">
-        <v>67</v>
+    <row r="384" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A384" s="2">
+        <v>97667</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D384" s="2" t="s">
         <v>20</v>
@@ -16812,13 +16801,13 @@
     </row>
     <row r="385" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A385" s="2">
-        <v>97667</v>
+        <v>97670</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D385" s="2" t="s">
         <v>20</v>
@@ -16826,55 +16815,55 @@
     </row>
     <row r="386" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A386" s="2">
-        <v>97670</v>
+        <v>97668</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>101</v>
+        <v>741</v>
       </c>
       <c r="D386" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A387" s="2">
-        <v>97668</v>
+      <c r="A387" s="2" t="s">
+        <v>408</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>741</v>
+        <v>409</v>
       </c>
       <c r="D387" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="388" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A388" s="2" t="s">
-        <v>408</v>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A388" s="2">
+        <v>98308</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>409</v>
+        <v>755</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" s="2">
-        <v>98308</v>
+        <v>93661</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>755</v>
+        <v>118</v>
       </c>
       <c r="D389" s="2" t="s">
         <v>7</v>
@@ -16882,27 +16871,27 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" s="2">
-        <v>93661</v>
+        <v>93655</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D390" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A391" s="2">
-        <v>93655</v>
+      <c r="A391" s="2" t="s">
+        <v>507</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>112</v>
+        <v>508</v>
       </c>
       <c r="D391" s="2" t="s">
         <v>7</v>
@@ -16910,27 +16899,27 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
-        <v>507</v>
+        <v>760</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>508</v>
+        <v>761</v>
       </c>
       <c r="D392" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A393" s="2" t="s">
-        <v>760</v>
+      <c r="A393" s="2">
+        <v>93662</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>761</v>
+        <v>315</v>
       </c>
       <c r="D393" s="2" t="s">
         <v>7</v>
@@ -16938,13 +16927,13 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" s="2">
-        <v>93662</v>
+        <v>93671</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>315</v>
+        <v>121</v>
       </c>
       <c r="D394" s="2" t="s">
         <v>7</v>
@@ -16952,27 +16941,27 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" s="2">
-        <v>93671</v>
+        <v>101658</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>121</v>
+        <v>765</v>
       </c>
       <c r="D395" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A396" s="2">
-        <v>101658</v>
+      <c r="A396" s="2" t="s">
+        <v>767</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D396" s="2" t="s">
         <v>7</v>
@@ -16980,27 +16969,27 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="D397" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A398" s="2" t="s">
-        <v>770</v>
+      <c r="A398" s="2">
+        <v>93656</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>7</v>
@@ -17008,41 +16997,41 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A399" s="2">
-        <v>93656</v>
+        <v>93664</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>773</v>
+        <v>326</v>
       </c>
       <c r="D399" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A400" s="2">
-        <v>93664</v>
+    <row r="400" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A400" s="2" t="s">
+        <v>776</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>326</v>
+        <v>777</v>
       </c>
       <c r="D400" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="401" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
-        <v>776</v>
+        <v>192</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>777</v>
+        <v>193</v>
       </c>
       <c r="D401" s="2" t="s">
         <v>7</v>
@@ -17050,27 +17039,27 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
-        <v>192</v>
+        <v>780</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>193</v>
+        <v>781</v>
       </c>
       <c r="D402" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
-        <v>780</v>
+        <v>320</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>781</v>
+        <v>321</v>
       </c>
       <c r="D403" s="2" t="s">
         <v>7</v>
@@ -17078,27 +17067,27 @@
     </row>
     <row r="404" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
-        <v>320</v>
+        <v>784</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>321</v>
+        <v>785</v>
       </c>
       <c r="D404" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="405" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="D405" s="2" t="s">
         <v>7</v>
@@ -17106,13 +17095,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>7</v>
@@ -17120,58 +17109,58 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D408" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="409" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D409" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A410" s="2" t="s">
-        <v>799</v>
+    <row r="410" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A410" s="2">
+        <v>93000</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -17218,13 +17207,13 @@
     </row>
     <row r="414" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A414" s="2">
-        <v>93000</v>
+        <v>92994</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>805</v>
+        <v>436</v>
       </c>
       <c r="D414" s="2" t="s">
         <v>20</v>
@@ -17288,13 +17277,13 @@
     </row>
     <row r="419" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A419" s="2">
-        <v>92994</v>
+        <v>92990</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="D419" s="2" t="s">
         <v>20</v>
@@ -17302,27 +17291,27 @@
     </row>
     <row r="420" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A420" s="2">
-        <v>92990</v>
+        <v>92988</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>442</v>
+        <v>372</v>
       </c>
       <c r="D420" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A421" s="2">
-        <v>92988</v>
+        <v>102990</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>372</v>
+        <v>814</v>
       </c>
       <c r="D421" s="2" t="s">
         <v>20</v>
@@ -17330,69 +17319,69 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A422" s="2">
-        <v>102990</v>
+        <v>102991</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D422" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A423" s="2">
-        <v>102991</v>
+      <c r="A423" s="2" t="s">
+        <v>818</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D423" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A424" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="B424" s="2" t="s">
-        <v>68</v>
+    <row r="424" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A424" s="1">
+        <v>97670</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>819</v>
-      </c>
-      <c r="D424" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="425" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A425" s="1">
-        <v>97670</v>
-      </c>
-      <c r="B425" s="1" t="s">
-        <v>5</v>
+        <v>101</v>
+      </c>
+      <c r="D424" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A425" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D425" s="1" t="s">
-        <v>20</v>
+        <v>823</v>
+      </c>
+      <c r="D425" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D426" s="2" t="s">
         <v>7</v>
@@ -17400,13 +17389,13 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D427" s="2" t="s">
         <v>7</v>
@@ -17414,13 +17403,13 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D428" s="2" t="s">
         <v>7</v>
@@ -17428,13 +17417,13 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C429" s="3" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D429" s="2" t="s">
         <v>7</v>
@@ -17442,13 +17431,13 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="D430" s="2" t="s">
         <v>7</v>
@@ -17456,13 +17445,13 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D431" s="2" t="s">
         <v>7</v>
@@ -17470,55 +17459,55 @@
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
-        <v>840</v>
+        <v>702</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>841</v>
+        <v>703</v>
       </c>
       <c r="D432" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
-        <v>702</v>
+        <v>844</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>703</v>
+        <v>845</v>
       </c>
       <c r="D433" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A434" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="B434" s="2" t="s">
-        <v>68</v>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A434" s="2">
+        <v>93671</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>845</v>
+        <v>121</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A435" s="2">
-        <v>93671</v>
-      </c>
-      <c r="B435" s="1" t="s">
-        <v>5</v>
+      <c r="A435" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>121</v>
+        <v>849</v>
       </c>
       <c r="D435" s="2" t="s">
         <v>7</v>
@@ -17526,41 +17515,41 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D436" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A437" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B437" s="2" t="s">
-        <v>68</v>
+      <c r="A437" s="2">
+        <v>93653</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D437" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A438" s="2">
-        <v>93653</v>
-      </c>
-      <c r="B438" s="1" t="s">
-        <v>5</v>
+    <row r="438" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A438" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>7</v>
@@ -17568,41 +17557,41 @@
     </row>
     <row r="439" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D439" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="440" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A440" s="2" t="s">
-        <v>859</v>
-      </c>
-      <c r="B440" s="2" t="s">
-        <v>68</v>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A440" s="2">
+        <v>93675</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D440" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A441" s="2">
-        <v>93675</v>
-      </c>
-      <c r="B441" s="1" t="s">
-        <v>5</v>
+      <c r="A441" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D441" s="2" t="s">
         <v>7</v>
@@ -17610,13 +17599,13 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D442" s="2" t="s">
         <v>7</v>
@@ -17624,13 +17613,13 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>7</v>
@@ -17638,13 +17627,13 @@
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D444" s="2" t="s">
         <v>7</v>
@@ -17652,69 +17641,69 @@
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D446" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
-        <v>879</v>
+        <v>770</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>880</v>
+        <v>771</v>
       </c>
       <c r="D447" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A448" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="B448" s="2" t="s">
-        <v>68</v>
+    <row r="448" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A448" s="2">
+        <v>100562</v>
+      </c>
+      <c r="B448" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>771</v>
+        <v>883</v>
       </c>
       <c r="D448" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A449" s="2">
-        <v>100562</v>
-      </c>
-      <c r="B449" s="1" t="s">
-        <v>5</v>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A449" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>883</v>
+        <v>152</v>
       </c>
       <c r="D449" s="2" t="s">
         <v>7</v>
@@ -17722,27 +17711,27 @@
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
-        <v>151</v>
+        <v>305</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C450" s="3" t="s">
-        <v>152</v>
+        <v>306</v>
       </c>
       <c r="D450" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
-        <v>305</v>
+        <v>887</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>306</v>
+        <v>888</v>
       </c>
       <c r="D451" s="2" t="s">
         <v>7</v>
@@ -17750,13 +17739,13 @@
     </row>
     <row r="452" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="D452" s="2" t="s">
         <v>7</v>
@@ -17764,55 +17753,55 @@
     </row>
     <row r="453" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D453" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="454" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A454" s="2" t="s">
-        <v>893</v>
+      <c r="A454" s="2">
+        <v>92988</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C454" s="3" t="s">
-        <v>894</v>
+        <v>372</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="455" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A455" s="2">
-        <v>92988</v>
+        <v>95802</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>372</v>
+        <v>901</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="456" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A456" s="2">
-        <v>95802</v>
+        <v>91959</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>901</v>
+        <v>301</v>
       </c>
       <c r="D456" s="2" t="s">
         <v>7</v>
@@ -17820,41 +17809,41 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A457" s="2">
-        <v>91959</v>
+        <v>91967</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C457" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D457" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A458" s="2">
-        <v>91967</v>
+        <v>97886</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C458" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D458" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="459" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A459" s="2">
-        <v>97886</v>
+        <v>101657</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C459" s="3" t="s">
-        <v>295</v>
+        <v>328</v>
       </c>
       <c r="D459" s="2" t="s">
         <v>7</v>
@@ -17862,16 +17851,16 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A460" s="2">
-        <v>101657</v>
+        <v>91924</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C460" s="3" t="s">
-        <v>328</v>
+        <v>536</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.3">
@@ -17932,13 +17921,13 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A465" s="2">
-        <v>91924</v>
+        <v>91932</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C465" s="3" t="s">
-        <v>536</v>
+        <v>914</v>
       </c>
       <c r="D465" s="2" t="s">
         <v>20</v>
@@ -17988,13 +17977,13 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A469" s="2">
-        <v>91932</v>
+        <v>91926</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C469" s="3" t="s">
-        <v>914</v>
+        <v>543</v>
       </c>
       <c r="D469" s="2" t="s">
         <v>20</v>
@@ -18058,13 +18047,13 @@
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A474" s="2">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D474" s="2" t="s">
         <v>20</v>
@@ -18128,13 +18117,13 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A479" s="2">
-        <v>91928</v>
+        <v>91930</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>548</v>
+        <v>682</v>
       </c>
       <c r="D479" s="2" t="s">
         <v>20</v>
@@ -18198,27 +18187,27 @@
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A484" s="2">
-        <v>91930</v>
+        <v>101632</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C484" s="3" t="s">
-        <v>682</v>
+        <v>323</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A485" s="2">
-        <v>101632</v>
-      </c>
-      <c r="B485" s="2" t="s">
+        <v>93653</v>
+      </c>
+      <c r="B485" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C485" s="3" t="s">
-        <v>323</v>
+        <v>854</v>
       </c>
       <c r="D485" s="2" t="s">
         <v>7</v>
@@ -18226,13 +18215,13 @@
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A486" s="2">
-        <v>93653</v>
+        <v>93659</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C486" s="3" t="s">
-        <v>854</v>
+        <v>933</v>
       </c>
       <c r="D486" s="2" t="s">
         <v>7</v>
@@ -18240,13 +18229,13 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A487" s="2">
-        <v>93659</v>
+        <v>93672</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C487" s="3" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="D487" s="2" t="s">
         <v>7</v>
@@ -18260,49 +18249,49 @@
         <v>5</v>
       </c>
       <c r="C488" s="3" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D488" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A489" s="2">
-        <v>93672</v>
-      </c>
-      <c r="B489" s="1" t="s">
+        <v>97667</v>
+      </c>
+      <c r="B489" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C489" s="3" t="s">
-        <v>937</v>
+        <v>89</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="490" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A490" s="2">
-        <v>97667</v>
+        <v>101657</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C490" s="3" t="s">
-        <v>89</v>
+        <v>328</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A491" s="2">
-        <v>101657</v>
+        <v>100621</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C491" s="3" t="s">
-        <v>328</v>
+        <v>941</v>
       </c>
       <c r="D491" s="2" t="s">
         <v>7</v>
@@ -18310,139 +18299,139 @@
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A492" s="2">
-        <v>100621</v>
+        <v>100620</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C492" s="3" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="D492" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A493" s="2">
-        <v>100620</v>
+      <c r="A493" s="2" t="s">
+        <v>944</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C493" s="3" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="D493" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A494" s="2" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C494" s="3" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D494" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="495" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A495" s="2" t="s">
-        <v>947</v>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A495" s="2">
+        <v>91927</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C495" s="3" t="s">
-        <v>948</v>
+        <v>39</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A496" s="2">
-        <v>91927</v>
+        <v>101879</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C496" s="3" t="s">
-        <v>39</v>
+        <v>952</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="497" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A497" s="2">
-        <v>101879</v>
+      <c r="A497" s="2" t="s">
+        <v>954</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C497" s="3" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D497" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="498" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A498" s="2" t="s">
-        <v>954</v>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A498" s="2">
+        <v>101872</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D498" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A499" s="2">
-        <v>101872</v>
+        <v>101875</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D499" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="500" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A500" s="2">
-        <v>101875</v>
+        <v>91928</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>958</v>
+        <v>548</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A501" s="2">
-        <v>91928</v>
+        <v>91924</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C501" s="3" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="D501" s="2" t="s">
         <v>20</v>
@@ -18450,27 +18439,27 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A502" s="2">
-        <v>91924</v>
+        <v>91926</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C502" s="3" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="D502" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A503" s="2">
-        <v>91926</v>
+        <v>101888</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>543</v>
+        <v>967</v>
       </c>
       <c r="D503" s="2" t="s">
         <v>20</v>
@@ -18520,41 +18509,41 @@
     </row>
     <row r="507" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A507" s="2">
-        <v>101888</v>
+        <v>97669</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D507" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="508" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A508" s="2">
-        <v>97669</v>
+      <c r="A508" s="2" t="s">
+        <v>971</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C508" s="3" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="509" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A509" s="2" t="s">
-        <v>971</v>
+        <v>954</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>972</v>
+        <v>955</v>
       </c>
       <c r="D509" s="2" t="s">
         <v>7</v>
@@ -18562,69 +18551,69 @@
     </row>
     <row r="510" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A510" s="2" t="s">
-        <v>954</v>
+        <v>975</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="D510" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="511" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A511" s="2" t="s">
-        <v>975</v>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A511" s="2">
+        <v>101871</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D511" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A512" s="2">
-        <v>101871</v>
+        <v>101886</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C512" s="3" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="513" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A513" s="2">
-        <v>101886</v>
+        <v>91953</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C513" s="3" t="s">
-        <v>980</v>
+        <v>140</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A514" s="2">
-        <v>91953</v>
+      <c r="A514" s="2" t="s">
+        <v>983</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C514" s="3" t="s">
-        <v>140</v>
+        <v>984</v>
       </c>
       <c r="D514" s="2" t="s">
         <v>7</v>
@@ -18632,41 +18621,41 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A515" s="2" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D515" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A516" s="2" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="D516" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="517" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A517" s="2" t="s">
-        <v>989</v>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A517" s="2">
+        <v>94489</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D517" s="2" t="s">
         <v>7</v>
@@ -18674,13 +18663,13 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A518" s="2">
-        <v>94489</v>
+        <v>94490</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C518" s="3" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D518" s="2" t="s">
         <v>7</v>
@@ -18688,13 +18677,13 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A519" s="2">
-        <v>94490</v>
+        <v>94491</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C519" s="3" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="D519" s="2" t="s">
         <v>7</v>
@@ -18702,13 +18691,13 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A520" s="2">
-        <v>94491</v>
+        <v>94492</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C520" s="3" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D520" s="2" t="s">
         <v>7</v>
@@ -18716,27 +18705,27 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A521" s="2">
-        <v>94492</v>
+        <v>89402</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C521" s="3" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A522" s="2">
-        <v>89402</v>
+        <v>89403</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C522" s="3" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D522" s="2" t="s">
         <v>20</v>
@@ -18744,13 +18733,13 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A523" s="2">
-        <v>89403</v>
+        <v>103978</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C523" s="3" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D523" s="2" t="s">
         <v>20</v>
@@ -18758,13 +18747,13 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A524" s="2">
-        <v>103978</v>
+        <v>103979</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D524" s="2" t="s">
         <v>20</v>
@@ -18772,41 +18761,41 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A525" s="2">
-        <v>103979</v>
+        <v>89353</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D525" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A526" s="2">
-        <v>89353</v>
+        <v>89985</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C526" s="3" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D526" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="527" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A527" s="2">
-        <v>89985</v>
+        <v>86886</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C527" s="3" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D527" s="2" t="s">
         <v>7</v>
@@ -18814,27 +18803,27 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A528" s="2">
-        <v>86886</v>
+        <v>86884</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C528" s="3" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="D528" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A529" s="2">
-        <v>86884</v>
+        <v>89383</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C529" s="3" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="D529" s="2" t="s">
         <v>7</v>
@@ -18842,13 +18831,13 @@
     </row>
     <row r="530" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A530" s="2">
-        <v>89383</v>
+        <v>94706</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>7</v>
@@ -18856,13 +18845,13 @@
     </row>
     <row r="531" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A531" s="2">
-        <v>94706</v>
+        <v>89391</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D531" s="2" t="s">
         <v>7</v>
@@ -18870,13 +18859,13 @@
     </row>
     <row r="532" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A532" s="2">
-        <v>89391</v>
+        <v>103994</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C532" s="3" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="D532" s="2" t="s">
         <v>7</v>
@@ -18884,13 +18873,13 @@
     </row>
     <row r="533" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A533" s="2">
-        <v>103994</v>
+        <v>94705</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C533" s="3" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="D533" s="2" t="s">
         <v>7</v>
@@ -18898,16 +18887,16 @@
     </row>
     <row r="534" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A534" s="2">
-        <v>94705</v>
+        <v>92992</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C534" s="3" t="s">
-        <v>1024</v>
+        <v>370</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="535" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -18954,55 +18943,55 @@
     </row>
     <row r="538" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A538" s="2">
-        <v>92992</v>
+        <v>92988</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C538" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D538" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="539" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A539" s="2">
-        <v>92988</v>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A539" s="2" t="s">
+        <v>1031</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C539" s="3" t="s">
-        <v>372</v>
+        <v>1032</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A540" s="2" t="s">
-        <v>1031</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A540" s="2">
+        <v>89798</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="541" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A541" s="2">
-        <v>89798</v>
+        <v>89799</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C541" s="3" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D541" s="2" t="s">
         <v>20</v>
@@ -19010,27 +18999,27 @@
     </row>
     <row r="542" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A542" s="2">
-        <v>89799</v>
+        <v>89802</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="543" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A543" s="2">
-        <v>89802</v>
+        <v>89801</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C543" s="3" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D543" s="2" t="s">
         <v>7</v>
@@ -19038,13 +19027,13 @@
     </row>
     <row r="544" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A544" s="2">
-        <v>89801</v>
+        <v>89813</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C544" s="3" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D544" s="2" t="s">
         <v>7</v>
@@ -19052,13 +19041,13 @@
     </row>
     <row r="545" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A545" s="2">
-        <v>89813</v>
+        <v>89825</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C545" s="3" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D545" s="2" t="s">
         <v>7</v>
@@ -19066,13 +19055,13 @@
     </row>
     <row r="546" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A546" s="2">
-        <v>89825</v>
+        <v>89827</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C546" s="3" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D546" s="2" t="s">
         <v>7</v>
@@ -19080,13 +19069,13 @@
     </row>
     <row r="547" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A547" s="2">
-        <v>89827</v>
+        <v>104348</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C547" s="3" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D547" s="2" t="s">
         <v>7</v>
@@ -19094,13 +19083,13 @@
     </row>
     <row r="548" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A548" s="2">
-        <v>104348</v>
+        <v>89817</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D548" s="2" t="s">
         <v>7</v>
@@ -19108,13 +19097,13 @@
     </row>
     <row r="549" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A549" s="2">
-        <v>89817</v>
+        <v>89806</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C549" s="3" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D549" s="2" t="s">
         <v>7</v>
@@ -19122,13 +19111,13 @@
     </row>
     <row r="550" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A550" s="2">
-        <v>89806</v>
+        <v>104352</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C550" s="3" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="D550" s="2" t="s">
         <v>7</v>
@@ -19136,41 +19125,41 @@
     </row>
     <row r="551" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A551" s="2">
-        <v>104352</v>
+        <v>89805</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C551" s="3" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="D551" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="552" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A552" s="2">
-        <v>89805</v>
+      <c r="A552" s="2" t="s">
+        <v>1058</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C552" s="3" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="D552" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="553" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A553" s="2" t="s">
-        <v>1058</v>
+      <c r="A553" s="2">
+        <v>104351</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C553" s="3" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D553" s="2" t="s">
         <v>7</v>
@@ -19178,27 +19167,27 @@
     </row>
     <row r="554" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A554" s="2">
-        <v>104351</v>
+        <v>104354</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C554" s="3" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D554" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="555" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A555" s="2">
-        <v>104354</v>
+      <c r="A555" s="2" t="s">
+        <v>1064</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C555" s="3" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D555" s="2" t="s">
         <v>7</v>
@@ -19206,13 +19195,13 @@
     </row>
     <row r="556" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A556" s="2" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C556" s="3" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="D556" s="2" t="s">
         <v>7</v>
@@ -19220,27 +19209,27 @@
     </row>
     <row r="557" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A557" s="2" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C557" s="3" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="558" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A558" s="2" t="s">
-        <v>1071</v>
+      <c r="A558" s="2">
+        <v>89800</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C558" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="D558" s="2" t="s">
         <v>20</v>
@@ -19248,13 +19237,13 @@
     </row>
     <row r="559" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A559" s="2">
-        <v>89800</v>
+        <v>89711</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C559" s="3" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D559" s="2" t="s">
         <v>20</v>
@@ -19262,27 +19251,27 @@
     </row>
     <row r="560" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A560" s="2">
-        <v>89711</v>
+        <v>89752</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C560" s="3" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="561" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A561" s="2">
-        <v>89752</v>
+        <v>89821</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C561" s="3" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="D561" s="2" t="s">
         <v>7</v>
@@ -19290,13 +19279,13 @@
     </row>
     <row r="562" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A562" s="2">
-        <v>89821</v>
+        <v>89726</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C562" s="3" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="D562" s="2" t="s">
         <v>7</v>
@@ -19304,13 +19293,13 @@
     </row>
     <row r="563" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A563" s="2">
-        <v>89726</v>
+        <v>89724</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C563" s="3" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="D563" s="2" t="s">
         <v>7</v>
@@ -19318,41 +19307,41 @@
     </row>
     <row r="564" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A564" s="2">
-        <v>89724</v>
+        <v>104328</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C564" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="D564" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="565" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A565" s="2">
-        <v>104328</v>
+      <c r="A565" s="2" t="s">
+        <v>1088</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C565" s="3" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="D565" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="566" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A566" s="2" t="s">
-        <v>1088</v>
+      <c r="A566" s="2">
+        <v>89809</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C566" s="3" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="D566" s="2" t="s">
         <v>7</v>
@@ -19360,13 +19349,13 @@
     </row>
     <row r="567" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A567" s="2">
-        <v>89809</v>
+        <v>97902</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C567" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="D567" s="2" t="s">
         <v>7</v>
@@ -19374,41 +19363,41 @@
     </row>
     <row r="568" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A568" s="2">
-        <v>97902</v>
+        <v>89797</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="D568" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="569" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A569" s="2">
-        <v>89797</v>
+      <c r="A569" s="2" t="s">
+        <v>1097</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C569" s="3" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D569" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="570" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A570" s="2" t="s">
-        <v>1097</v>
+      <c r="A570" s="2">
+        <v>89810</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C570" s="3" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D570" s="2" t="s">
         <v>7</v>
@@ -19416,13 +19405,13 @@
     </row>
     <row r="571" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A571" s="2">
-        <v>89810</v>
+        <v>89728</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C571" s="3" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D571" s="2" t="s">
         <v>7</v>
@@ -19430,13 +19419,13 @@
     </row>
     <row r="572" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A572" s="2">
-        <v>89728</v>
+        <v>89803</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C572" s="3" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="D572" s="2" t="s">
         <v>7</v>
@@ -19444,69 +19433,69 @@
     </row>
     <row r="573" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A573" s="2">
-        <v>89803</v>
+        <v>97903</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C573" s="3" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="D573" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="574" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A574" s="2">
-        <v>97903</v>
+      <c r="A574" s="2" t="s">
+        <v>1107</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C574" s="3" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="D574" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="575" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A575" s="2" t="s">
-        <v>1107</v>
+      <c r="A575" s="2">
+        <v>89783</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D575" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="576" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A576" s="2">
-        <v>89783</v>
+        <v>89580</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C576" s="3" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A577" s="2">
-        <v>89580</v>
+        <v>94229</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="D577" s="2" t="s">
         <v>20</v>
@@ -19514,41 +19503,41 @@
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A578" s="2">
-        <v>94229</v>
+        <v>94228</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="D578" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A579" s="2">
-        <v>94228</v>
+        <v>89677</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C579" s="3" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="580" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A580" s="2">
-        <v>89677</v>
+        <v>89590</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C580" s="3" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D580" s="2" t="s">
         <v>7</v>
@@ -19556,13 +19545,13 @@
     </row>
     <row r="581" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A581" s="2">
-        <v>89590</v>
+        <v>99253</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C581" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D581" s="2" t="s">
         <v>7</v>
@@ -19570,27 +19559,27 @@
     </row>
     <row r="582" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A582" s="2">
-        <v>99253</v>
+        <v>104356</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C582" s="3" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D582" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="583" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A583" s="2">
-        <v>104356</v>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A583" s="2" t="s">
+        <v>1127</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="D583" s="2" t="s">
         <v>7</v>
@@ -19598,27 +19587,27 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A584" s="2" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="D584" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A585" s="2" t="s">
-        <v>1130</v>
+    <row r="585" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A585" s="2">
+        <v>89699</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C585" s="3" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="D585" s="2" t="s">
         <v>7</v>
@@ -19626,13 +19615,13 @@
     </row>
     <row r="586" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A586" s="2">
-        <v>89699</v>
+        <v>89693</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C586" s="3" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="D586" s="2" t="s">
         <v>7</v>
@@ -19640,13 +19629,13 @@
     </row>
     <row r="587" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A587" s="2">
-        <v>89693</v>
+        <v>95695</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C587" s="3" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="D587" s="2" t="s">
         <v>7</v>
@@ -19654,69 +19643,69 @@
     </row>
     <row r="588" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A588" s="2">
-        <v>95695</v>
+        <v>89591</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C588" s="3" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D588" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="589" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A589" s="2">
-        <v>89591</v>
+      <c r="A589" s="2" t="s">
+        <v>1141</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C589" s="3" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="D589" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="590" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A590" s="2" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C590" s="3" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="D590" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A591" s="2" t="s">
-        <v>1144</v>
+      <c r="A591" s="2">
+        <v>89364</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C591" s="3" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D591" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A592" s="2">
-        <v>89364</v>
+        <v>90373</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C592" s="3" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D592" s="2" t="s">
         <v>7</v>
@@ -19724,27 +19713,27 @@
     </row>
     <row r="593" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A593" s="2">
-        <v>90373</v>
+        <v>89426</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C593" s="3" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="D593" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="594" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A594" s="2">
-        <v>89426</v>
+        <v>89443</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C594" s="3" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D594" s="2" t="s">
         <v>7</v>
@@ -19752,13 +19741,13 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A595" s="2">
-        <v>89443</v>
+        <v>89415</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C595" s="3" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="D595" s="2" t="s">
         <v>7</v>
@@ -19766,86 +19755,86 @@
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A596" s="2">
-        <v>89415</v>
+        <v>89414</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C596" s="3" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D596" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A597" s="2">
-        <v>89414</v>
+        <v>89445</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C597" s="3" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D597" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="598" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A598" s="2">
-        <v>89445</v>
+        <v>89409</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C598" s="3" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D598" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A599" s="2">
-        <v>89409</v>
+        <v>92367</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C599" s="3" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="D599" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="600" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A600" s="2">
-        <v>92367</v>
+        <v>97498</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C600" s="3" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="D600" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="601" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A601" s="2">
-        <v>97498</v>
+        <v>97599</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="D601" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.3">
@@ -19862,43 +19851,43 @@
         <v>7</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A603" s="2">
-        <v>97599</v>
+    <row r="603" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A603" s="2" t="s">
+        <v>1170</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C603" s="3" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="D603" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="604" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A604" s="2" t="s">
-        <v>1170</v>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A604" s="2">
+        <v>101909</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C604" s="3" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D604" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A605" s="2">
-        <v>101909</v>
+      <c r="A605" s="2" t="s">
+        <v>1174</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C605" s="3" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D605" s="2" t="s">
         <v>7</v>
@@ -19906,27 +19895,27 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A606" s="2" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C606" s="3" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="D606" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A607" s="2" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C607" s="3" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="D607" s="2" t="s">
         <v>7</v>
@@ -19934,13 +19923,13 @@
     </row>
     <row r="608" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A608" s="2" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C608" s="3" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="D608" s="2" t="s">
         <v>7</v>
@@ -19948,13 +19937,13 @@
     </row>
     <row r="609" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A609" s="2" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C609" s="3" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="D609" s="2" t="s">
         <v>7</v>
@@ -20004,13 +19993,13 @@
     </row>
     <row r="613" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A613" s="2" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C613" s="3" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="D613" s="2" t="s">
         <v>7</v>
@@ -20073,14 +20062,14 @@
       </c>
     </row>
     <row r="618" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A618" s="2" t="s">
-        <v>1197</v>
+      <c r="A618" s="2">
+        <v>92390</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C618" s="3" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="D618" s="2" t="s">
         <v>7</v>
@@ -20088,13 +20077,13 @@
     </row>
     <row r="619" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A619" s="2">
-        <v>92390</v>
+        <v>92377</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C619" s="3" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D619" s="2" t="s">
         <v>7</v>
@@ -20102,13 +20091,13 @@
     </row>
     <row r="620" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A620" s="2">
-        <v>92377</v>
+        <v>92369</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C620" s="3" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="D620" s="2" t="s">
         <v>7</v>
@@ -20116,83 +20105,83 @@
     </row>
     <row r="621" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A621" s="2">
-        <v>92369</v>
+        <v>92896</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C621" s="3" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="D621" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="622" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A622" s="2">
-        <v>92896</v>
+        <v>94499</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C622" s="3" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D622" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A623" s="2">
-        <v>94499</v>
+        <v>92637</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C623" s="3" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="D623" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="624" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A624" s="2">
-        <v>92637</v>
+    <row r="624" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A624" s="2" t="s">
+        <v>1211</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C624" s="3" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="D624" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="625" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A625" s="2" t="s">
-        <v>1211</v>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A625" s="2">
+        <v>94495</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C625" s="3" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="D625" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A626" s="2">
-        <v>94495</v>
+        <v>92642</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C626" s="3" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="D626" s="2" t="s">
         <v>7</v>
@@ -20200,27 +20189,27 @@
     </row>
     <row r="627" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A627" s="2">
-        <v>92642</v>
+        <v>92382</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C627" s="3" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D627" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="628" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A628" s="2">
-        <v>92382</v>
+      <c r="A628" s="2" t="s">
+        <v>1220</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C628" s="3" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="D628" s="2" t="s">
         <v>7</v>
@@ -20228,125 +20217,125 @@
     </row>
     <row r="629" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A629" s="2" t="s">
-        <v>1220</v>
+        <v>1197</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C629" s="3" t="s">
-        <v>1221</v>
+        <v>1198</v>
       </c>
       <c r="D629" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="630" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A630" s="2" t="s">
-        <v>1197</v>
+        <v>1225</v>
       </c>
       <c r="B630" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C630" s="3" t="s">
-        <v>1198</v>
+        <v>1226</v>
       </c>
       <c r="D630" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A631" s="2" t="s">
-        <v>1225</v>
+      <c r="A631" s="2">
+        <v>103009</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="D631" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A632" s="2">
-        <v>103009</v>
+      <c r="A632" s="2" t="s">
+        <v>1230</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="D632" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A633" s="2" t="s">
-        <v>1230</v>
+      <c r="A633" s="2">
+        <v>102111</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D633" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A634" s="2">
-        <v>102111</v>
+        <v>92370</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C634" s="3" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D634" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="635" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A635" s="2">
-        <v>92370</v>
+        <v>101917</v>
       </c>
       <c r="B635" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C635" s="3" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="D635" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A636" s="2">
-        <v>101917</v>
+      <c r="A636" s="2" t="s">
+        <v>1239</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C636" s="3" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="D636" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A637" s="2" t="s">
-        <v>1239</v>
+      <c r="A637" s="2">
+        <v>95249</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C637" s="3" t="s">
-        <v>1240</v>
+        <v>1286</v>
       </c>
       <c r="D637" s="2" t="s">
         <v>7</v>
@@ -20354,13 +20343,13 @@
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A638" s="2">
-        <v>95249</v>
+        <v>99624</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>1286</v>
+        <v>1242</v>
       </c>
       <c r="D638" s="2" t="s">
         <v>7</v>
@@ -20368,111 +20357,111 @@
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A639" s="2">
-        <v>99624</v>
+        <v>99629</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="D639" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A640" s="2">
-        <v>99629</v>
+      <c r="A640" s="2" t="s">
+        <v>1247</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C640" s="3" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="D640" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A641" s="2" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C641" s="3" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="D641" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="642" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A642" s="2" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C642" s="3" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="D642" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="643" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A643" s="2" t="s">
-        <v>1253</v>
+      <c r="A643" s="2">
+        <v>97488</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C643" s="3" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="D643" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="644" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A644" s="2">
-        <v>97488</v>
+      <c r="A644" s="2" t="s">
+        <v>1257</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="D644" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="645" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A645" s="2" t="s">
-        <v>1257</v>
+      <c r="A645" s="2">
+        <v>103802</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C645" s="3" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="D645" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="646" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A646" s="2">
-        <v>103802</v>
+        <v>97335</v>
       </c>
       <c r="B646" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="D646" s="2" t="s">
         <v>20</v>
@@ -20480,55 +20469,55 @@
     </row>
     <row r="647" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A647" s="2">
-        <v>97335</v>
+        <v>103805</v>
       </c>
       <c r="B647" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="648" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A648" s="2">
-        <v>103805</v>
+        <v>103806</v>
       </c>
       <c r="B648" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C648" s="3" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="D648" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="649" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A649" s="2">
-        <v>103806</v>
+      <c r="A649" s="2" t="s">
+        <v>1268</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="D649" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="650" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A650" s="2" t="s">
-        <v>1268</v>
+      <c r="A650" s="2">
+        <v>103823</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C650" s="3" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D650" s="2" t="s">
         <v>7</v>
@@ -20536,13 +20525,13 @@
     </row>
     <row r="651" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A651" s="2">
-        <v>103823</v>
+        <v>103808</v>
       </c>
       <c r="B651" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C651" s="3" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="D651" s="2" t="s">
         <v>7</v>
@@ -20550,41 +20539,41 @@
     </row>
     <row r="652" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A652" s="2">
-        <v>103808</v>
+        <v>103807</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C652" s="3" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="D652" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="653" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A653" s="2">
-        <v>103807</v>
+        <v>103029</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C653" s="3" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="D653" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A654" s="2">
-        <v>103029</v>
+        <v>103809</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C654" s="3" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="D654" s="2" t="s">
         <v>7</v>
@@ -20592,13 +20581,13 @@
     </row>
     <row r="655" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A655" s="2">
-        <v>103809</v>
+        <v>103833</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C655" s="3" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="D655" s="2" t="s">
         <v>7</v>
@@ -20618,15 +20607,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="657" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A657" s="2">
-        <v>103833</v>
+        <v>103029</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C657" s="3" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="D657" s="2" t="s">
         <v>7</v>
@@ -20634,69 +20623,69 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A658" s="2">
-        <v>103029</v>
+        <v>89352</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C658" s="3" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="D658" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A659" s="2">
-        <v>89352</v>
+        <v>103818</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C659" s="3" t="s">
-        <v>1277</v>
+        <v>1288</v>
       </c>
       <c r="D659" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="660" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A660" s="2">
-        <v>103818</v>
+      <c r="A660" s="2" t="s">
+        <v>1289</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C660" s="3" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="D660" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="661" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A661" s="2" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C661" s="3" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="D661" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="662" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A662" s="2" t="s">
-        <v>1293</v>
+      <c r="A662" s="2">
+        <v>97328</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C662" s="3" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D662" s="2" t="s">
         <v>20</v>
@@ -20704,41 +20693,41 @@
     </row>
     <row r="663" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A663" s="2">
-        <v>97328</v>
+        <v>97330</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C663" s="3" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="D663" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="664" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A664" s="2">
-        <v>97330</v>
+      <c r="A664" s="2" t="s">
+        <v>1299</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C664" s="3" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="D664" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="665" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A665" s="2" t="s">
-        <v>1299</v>
+      <c r="A665" s="2">
+        <v>97327</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="D665" s="2" t="s">
         <v>20</v>
@@ -20746,69 +20735,69 @@
     </row>
     <row r="666" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A666" s="2">
-        <v>97327</v>
+        <v>97329</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C666" s="3" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="D666" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="667" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A667" s="2">
-        <v>97329</v>
+        <v>89866</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C667" s="3" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="D667" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A668" s="2">
-        <v>89866</v>
+      <c r="A668" s="2" t="s">
+        <v>1308</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C668" s="3" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="D668" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A669" s="2" t="s">
-        <v>1308</v>
+      <c r="A669" s="2">
+        <v>89869</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D669" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A670" s="2">
-        <v>89869</v>
+      <c r="A670" s="2" t="s">
+        <v>1314</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C670" s="3" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="D670" s="2" t="s">
         <v>7</v>
@@ -20816,27 +20805,27 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A671" s="2" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="B671" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C671" s="3" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="D671" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A672" s="2" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="B672" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C672" s="3" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="D672" s="2" t="s">
         <v>7</v>
@@ -20844,13 +20833,13 @@
     </row>
     <row r="673" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A673" s="2" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C673" s="3" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="D673" s="2" t="s">
         <v>7</v>
@@ -20858,13 +20847,13 @@
     </row>
     <row r="674" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A674" s="2" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C674" s="3" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="D674" s="2" t="s">
         <v>7</v>
@@ -20872,13 +20861,13 @@
     </row>
     <row r="675" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A675" s="2" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C675" s="3" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="D675" s="2" t="s">
         <v>7</v>
@@ -20886,41 +20875,41 @@
     </row>
     <row r="676" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A676" s="2" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="B676" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C676" s="3" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="D676" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="677" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A677" s="2" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="B677" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C677" s="3" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="D677" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A678" s="2" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="B678" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C678" s="3" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="D678" s="2" t="s">
         <v>20</v>
@@ -20928,27 +20917,27 @@
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A679" s="2" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C679" s="3" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="D679" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A680" s="2" t="s">
-        <v>1341</v>
+        <v>1357</v>
       </c>
       <c r="B680" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C680" s="3" t="s">
-        <v>1342</v>
+        <v>1358</v>
       </c>
       <c r="D680" s="2" t="s">
         <v>20</v>
@@ -20956,27 +20945,27 @@
     </row>
     <row r="681" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A681" s="2" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="B681" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C681" s="3" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="D681" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="682" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A682" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="B682" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C682" s="3" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="D682" s="2" t="s">
         <v>7</v>
@@ -20984,69 +20973,69 @@
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A683" s="2" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B683" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C683" s="3" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="D683" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A684" s="2" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="B684" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C684" s="3" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="D684" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="685" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A685" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B685" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C685" s="3" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="D685" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A686" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="B686" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C686" s="3" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="D686" s="2" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-    <row r="687" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A687" s="2" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="B687" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C687" s="3" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="D687" s="2" t="s">
         <v>7</v>
@@ -21054,13 +21043,13 @@
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A688" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C688" s="3" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="D688" s="2" t="s">
         <v>7</v>
@@ -21068,13 +21057,13 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A689" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="B689" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C689" s="3" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="D689" s="2" t="s">
         <v>7</v>
@@ -21082,13 +21071,13 @@
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A690" s="2" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C690" s="3" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="D690" s="2" t="s">
         <v>7</v>
@@ -21096,13 +21085,13 @@
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A691" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="B691" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C691" s="3" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="D691" s="2" t="s">
         <v>7</v>
@@ -21110,13 +21099,13 @@
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A692" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B692" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C692" s="3" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="D692" s="2" t="s">
         <v>7</v>
@@ -21124,41 +21113,41 @@
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A693" s="2" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C693" s="3" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="D693" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A694" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="B694" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C694" s="3" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="D694" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="695" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A695" s="2" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="B695" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C695" s="3" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="D695" s="2" t="s">
         <v>20</v>
@@ -21166,13 +21155,13 @@
     </row>
     <row r="696" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A696" s="2" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="B696" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C696" s="3" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="D696" s="2" t="s">
         <v>20</v>
@@ -21180,13 +21169,13 @@
     </row>
     <row r="697" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A697" s="2" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="B697" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C697" s="3" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="D697" s="2" t="s">
         <v>20</v>
@@ -21194,13 +21183,13 @@
     </row>
     <row r="698" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A698" s="2" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="B698" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C698" s="3" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="D698" s="2" t="s">
         <v>20</v>
@@ -21208,13 +21197,13 @@
     </row>
     <row r="699" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A699" s="2" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="B699" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C699" s="3" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="D699" s="2" t="s">
         <v>20</v>
@@ -21222,13 +21211,13 @@
     </row>
     <row r="700" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A700" s="2" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="B700" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C700" s="3" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="D700" s="2" t="s">
         <v>20</v>
@@ -21236,27 +21225,27 @@
     </row>
     <row r="701" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A701" s="2" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="B701" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C701" s="3" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D701" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="702" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A702" s="2" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="B702" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C702" s="3" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="D702" s="2" t="s">
         <v>7</v>
@@ -21264,13 +21253,13 @@
     </row>
     <row r="703" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A703" s="2" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="B703" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C703" s="3" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="D703" s="2" t="s">
         <v>7</v>
@@ -21278,13 +21267,13 @@
     </row>
     <row r="704" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A704" s="2" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="B704" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C704" s="3" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="D704" s="2" t="s">
         <v>7</v>
@@ -21292,13 +21281,13 @@
     </row>
     <row r="705" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A705" s="2" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="B705" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C705" s="3" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="D705" s="2" t="s">
         <v>7</v>
@@ -21306,13 +21295,13 @@
     </row>
     <row r="706" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A706" s="2" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="B706" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C706" s="3" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="D706" s="2" t="s">
         <v>7</v>
@@ -21320,27 +21309,27 @@
     </row>
     <row r="707" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A707" s="2" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="B707" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C707" s="3" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="D707" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="708" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A708" s="2" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="B708" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C708" s="3" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="D708" s="2" t="s">
         <v>7</v>
@@ -21348,41 +21337,41 @@
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A709" s="2" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="B709" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C709" s="3" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="D709" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A710" s="2" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="B710" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C710" s="3" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="D710" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="711" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A711" s="2" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="B711" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C711" s="3" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="D711" s="2" t="s">
         <v>7</v>
@@ -21390,13 +21379,13 @@
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A712" s="2" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="B712" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C712" s="3" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="D712" s="2" t="s">
         <v>7</v>
@@ -21404,13 +21393,13 @@
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A713" s="2" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="B713" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C713" s="3" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="D713" s="2" t="s">
         <v>7</v>
@@ -21418,13 +21407,13 @@
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A714" s="2" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="B714" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C714" s="3" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="D714" s="2" t="s">
         <v>7</v>
@@ -21432,13 +21421,13 @@
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A715" s="2" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="B715" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C715" s="3" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="D715" s="2" t="s">
         <v>7</v>
@@ -21446,13 +21435,13 @@
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A716" s="2" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="B716" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C716" s="3" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="D716" s="2" t="s">
         <v>7</v>
@@ -21460,41 +21449,41 @@
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A717" s="2" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="B717" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C717" s="3" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="D717" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A718" s="2" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="B718" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C718" s="3" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="D718" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="719" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A719" s="2" t="s">
-        <v>1459</v>
+    <row r="719" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A719" s="2">
+        <v>103982</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C719" s="3" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="D719" s="2" t="s">
         <v>7</v>
@@ -21502,41 +21491,41 @@
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A720" s="2">
-        <v>103982</v>
+        <v>99621</v>
       </c>
       <c r="B720" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C720" s="3" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="D720" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A721" s="2">
-        <v>99621</v>
+        <v>89381</v>
       </c>
       <c r="B721" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C721" s="3" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="D721" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="722" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A722" s="2">
-        <v>89381</v>
+        <v>94796</v>
       </c>
       <c r="B722" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C722" s="3" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="D722" s="2" t="s">
         <v>7</v>
@@ -21544,13 +21533,13 @@
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A723" s="2">
-        <v>94796</v>
+        <v>104011</v>
       </c>
       <c r="B723" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C723" s="3" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="D723" s="2" t="s">
         <v>7</v>
@@ -21558,27 +21547,27 @@
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A724" s="2">
-        <v>104011</v>
+        <v>89431</v>
       </c>
       <c r="B724" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C724" s="3" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="D724" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A725" s="2">
-        <v>89431</v>
+        <v>94703</v>
       </c>
       <c r="B725" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C725" s="3" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="D725" s="2" t="s">
         <v>7</v>
@@ -21586,27 +21575,27 @@
     </row>
     <row r="726" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A726" s="2">
-        <v>94703</v>
+        <v>94704</v>
       </c>
       <c r="B726" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C726" s="3" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="D726" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="727" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A727" s="2">
-        <v>94704</v>
+        <v>89428</v>
       </c>
       <c r="B727" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C727" s="3" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="D727" s="2" t="s">
         <v>7</v>
@@ -21614,13 +21603,13 @@
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A728" s="2">
-        <v>89428</v>
+        <v>89435</v>
       </c>
       <c r="B728" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C728" s="3" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="D728" s="2" t="s">
         <v>7</v>
@@ -21628,41 +21617,41 @@
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A729" s="2">
-        <v>89435</v>
+        <v>103990</v>
       </c>
       <c r="B729" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C729" s="3" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="D729" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="730" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A730" s="2">
-        <v>103990</v>
+        <v>89396</v>
       </c>
       <c r="B730" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C730" s="3" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="D730" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="731" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A731" s="2">
-        <v>89396</v>
+        <v>103986</v>
       </c>
       <c r="B731" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C731" s="3" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="D731" s="2" t="s">
         <v>7</v>
@@ -21670,55 +21659,55 @@
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A732" s="2">
-        <v>103986</v>
+        <v>104004</v>
       </c>
       <c r="B732" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C732" s="3" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="D732" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="733" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A733" s="2">
-        <v>104004</v>
+        <v>105234</v>
       </c>
       <c r="B733" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C733" s="3" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="D733" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="734" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A734" s="2">
-        <v>105234</v>
+        <v>103995</v>
       </c>
       <c r="B734" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C734" s="3" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="D734" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="735" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A735" s="2">
-        <v>103995</v>
+        <v>104006</v>
       </c>
       <c r="B735" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C735" s="3" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="D735" s="2" t="s">
         <v>7</v>
@@ -21726,13 +21715,13 @@
     </row>
     <row r="736" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A736" s="2">
-        <v>104006</v>
+        <v>105228</v>
       </c>
       <c r="B736" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C736" s="3" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="D736" s="2" t="s">
         <v>7</v>
@@ -21740,27 +21729,27 @@
     </row>
     <row r="737" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A737" s="2">
-        <v>105228</v>
+        <v>94672</v>
       </c>
       <c r="B737" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C737" s="3" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="D737" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="738" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A738" s="2">
-        <v>94672</v>
+        <v>102122</v>
       </c>
       <c r="B738" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C738" s="3" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="D738" s="2" t="s">
         <v>7</v>
@@ -21768,13 +21757,13 @@
     </row>
     <row r="739" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A739" s="2">
-        <v>102122</v>
+        <v>102115</v>
       </c>
       <c r="B739" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C739" s="3" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="D739" s="2" t="s">
         <v>7</v>
@@ -21782,27 +21771,27 @@
     </row>
     <row r="740" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A740" s="2">
-        <v>102115</v>
+        <v>94495</v>
       </c>
       <c r="B740" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C740" s="3" t="s">
-        <v>1502</v>
+        <v>1214</v>
       </c>
       <c r="D740" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A741" s="2">
-        <v>94495</v>
+        <v>92925</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C741" s="3" t="s">
-        <v>1214</v>
+        <v>1505</v>
       </c>
       <c r="D741" s="2" t="s">
         <v>7</v>
@@ -21810,153 +21799,153 @@
     </row>
     <row r="742" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A742" s="2">
-        <v>92925</v>
+        <v>92918</v>
       </c>
       <c r="B742" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C742" s="3" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="D742" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="743" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A743" s="2">
+      <c r="A743" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C743" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D743" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="744" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A744" s="2">
         <v>92918</v>
       </c>
-      <c r="B743" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C743" s="3" t="s">
+      <c r="B744" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C744" s="3" t="s">
         <v>1507</v>
       </c>
-      <c r="D743" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="744" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A744" s="2" t="s">
-        <v>1509</v>
-      </c>
-      <c r="B744" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C744" s="3" t="s">
-        <v>1510</v>
-      </c>
       <c r="D744" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="745" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A745" s="2">
-        <v>92918</v>
+    <row r="745" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A745" s="2" t="s">
+        <v>1225</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C745" s="3" t="s">
-        <v>1507</v>
+        <v>1226</v>
       </c>
       <c r="D745" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A746" s="2" t="s">
-        <v>1225</v>
+      <c r="A746" s="2">
+        <v>101917</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C746" s="3" t="s">
-        <v>1226</v>
+        <v>1237</v>
       </c>
       <c r="D746" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A747" s="2">
-        <v>101917</v>
+      <c r="A747" s="2" t="s">
+        <v>1514</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C747" s="3" t="s">
-        <v>1237</v>
+        <v>1515</v>
       </c>
       <c r="D747" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="748" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A748" s="2" t="s">
-        <v>1514</v>
+    <row r="748" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A748" s="2">
+        <v>94713</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C748" s="3" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
       <c r="D748" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="749" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A749" s="2">
-        <v>94713</v>
-      </c>
-      <c r="B749" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C749" s="3" t="s">
-        <v>1518</v>
+    <row r="749" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A749" s="1">
+        <v>91928</v>
+      </c>
+      <c r="B749" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C749" t="s">
+        <v>548</v>
       </c>
       <c r="D749" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A750" s="1">
-        <v>91928</v>
+        <v>91924</v>
       </c>
       <c r="B750" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C750" t="s">
-        <v>548</v>
-      </c>
-      <c r="D750" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D750" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="751" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A751" s="1">
-        <v>91924</v>
+      <c r="A751" s="2">
+        <v>91992</v>
       </c>
       <c r="B751" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C751" t="s">
-        <v>536</v>
-      </c>
-      <c r="D751" s="1" t="s">
-        <v>20</v>
+      <c r="C751" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D751" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A752" s="2">
-        <v>91992</v>
+        <v>92016</v>
       </c>
       <c r="B752" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C752" s="3" t="s">
-        <v>338</v>
+        <v>1523</v>
       </c>
       <c r="D752" s="2" t="s">
         <v>7</v>
@@ -21964,69 +21953,69 @@
     </row>
     <row r="753" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A753" s="2">
-        <v>92016</v>
-      </c>
-      <c r="B753" s="1" t="s">
+        <v>93661</v>
+      </c>
+      <c r="B753" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C753" s="3" t="s">
-        <v>1523</v>
+        <v>118</v>
       </c>
       <c r="D753" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="754" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A754" s="2">
-        <v>93661</v>
-      </c>
-      <c r="B754" s="2" t="s">
-        <v>5</v>
+    <row r="754" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A754" s="5" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B754" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="C754" s="3" t="s">
-        <v>118</v>
+        <v>1526</v>
       </c>
       <c r="D754" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="755" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A755" s="5" t="s">
-        <v>1527</v>
-      </c>
-      <c r="B755" s="5" t="s">
-        <v>68</v>
+    <row r="755" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A755" s="2">
+        <v>93658</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C755" s="3" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="D755" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A756" s="2">
-        <v>93658</v>
-      </c>
-      <c r="B756" s="2" t="s">
-        <v>5</v>
+      <c r="A756" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B756" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="C756" s="3" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="D756" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="757" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A757" s="2" t="s">
-        <v>1531</v>
-      </c>
-      <c r="B757" s="5" t="s">
-        <v>68</v>
+      <c r="A757" s="2">
+        <v>91936</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C757" s="3" t="s">
-        <v>1532</v>
+        <v>303</v>
       </c>
       <c r="D757" s="2" t="s">
         <v>7</v>
@@ -22034,16 +22023,16 @@
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A758" s="2">
-        <v>91936</v>
+        <v>91925</v>
       </c>
       <c r="B758" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C758" s="3" t="s">
-        <v>303</v>
+        <v>19</v>
       </c>
       <c r="D758" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.3">
@@ -22104,13 +22093,13 @@
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A763" s="2">
-        <v>91925</v>
+        <v>91927</v>
       </c>
       <c r="B763" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C763" s="3" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D763" s="2" t="s">
         <v>20</v>
@@ -22188,27 +22177,27 @@
     </row>
     <row r="769" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A769" s="2">
-        <v>91927</v>
+        <v>93662</v>
       </c>
       <c r="B769" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C769" s="3" t="s">
-        <v>39</v>
+        <v>315</v>
       </c>
       <c r="D769" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="770" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A770" s="2">
-        <v>93662</v>
-      </c>
-      <c r="B770" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="770" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A770" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B770" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="C770" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D770" s="2" t="s">
         <v>7</v>
@@ -22216,13 +22205,13 @@
     </row>
     <row r="771" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A771" s="2" t="s">
-        <v>317</v>
+        <v>1547</v>
       </c>
       <c r="B771" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C771" s="3" t="s">
-        <v>318</v>
+        <v>1548</v>
       </c>
       <c r="D771" s="2" t="s">
         <v>7</v>
@@ -22230,44 +22219,44 @@
     </row>
     <row r="772" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A772" s="2" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="B772" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C772" s="3" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="D772" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="773" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A773" s="2" t="s">
-        <v>1551</v>
-      </c>
-      <c r="B773" s="5" t="s">
-        <v>68</v>
+      <c r="A773" s="2">
+        <v>95801</v>
+      </c>
+      <c r="B773" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C773" s="3" t="s">
-        <v>1552</v>
+        <v>421</v>
       </c>
       <c r="D773" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="774" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A774" s="2">
-        <v>95801</v>
+        <v>91929</v>
       </c>
       <c r="B774" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C774" s="3" t="s">
-        <v>1554</v>
+        <v>50</v>
       </c>
       <c r="D774" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="775" spans="1:4" x14ac:dyDescent="0.3">
@@ -22300,113 +22289,99 @@
     </row>
     <row r="777" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A777" s="2">
-        <v>91929</v>
+        <v>93663</v>
       </c>
       <c r="B777" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C777" s="3" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="D777" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="778" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A778" s="2">
-        <v>93663</v>
-      </c>
-      <c r="B778" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A778" s="5" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B778" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="C778" s="3" t="s">
-        <v>116</v>
+        <v>1526</v>
       </c>
       <c r="D778" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="779" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A779" s="5" t="s">
-        <v>1527</v>
-      </c>
-      <c r="B779" s="5" t="s">
+      <c r="A779" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B779" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C779" s="3" t="s">
-        <v>1526</v>
+        <v>492</v>
       </c>
       <c r="D779" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="780" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A780" s="2" t="s">
-        <v>491</v>
+      <c r="A780" s="2">
+        <v>92023</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C780" s="3" t="s">
-        <v>492</v>
+        <v>1561</v>
       </c>
       <c r="D780" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="781" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A781" s="2">
-        <v>92023</v>
+      <c r="A781" s="2" t="s">
+        <v>1562</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C781" s="3" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="D781" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="782" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A782" s="2" t="s">
-        <v>1563</v>
+      <c r="A782" s="2">
+        <v>91871</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C782" s="3" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="D782" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="783" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A783" s="2">
-        <v>91871</v>
+        <v>91856</v>
       </c>
       <c r="B783" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C783" s="3" t="s">
-        <v>1567</v>
+        <v>96</v>
       </c>
       <c r="D783" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="784" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A784" s="2">
-        <v>91856</v>
-      </c>
-      <c r="B784" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C784" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D784" s="2" t="s">
         <v>20</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C268CD-4C23-4D5E-8D08-EBAB324F2F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A795973-50BD-4E8D-A39C-1BE4077EC8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="1568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="1575">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4744,6 +4744,27 @@
   </si>
   <si>
     <t>Eletroduto PVC flexível - Eletroduto leve - 1" - Parede</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Bipolar Termomagnético - norma DIN - Curva C - 16 A - 3 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Bipolar Termomagnético - norma DIN - Curva C - 20 A - 3 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Bipolar Termomagnético - norma DIN - Curva C - 32 A - 3 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 63 A - 6 kA</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Arandela - 40 W</t>
+  </si>
+  <si>
+    <t>Comp 2055</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA ARANDELA SOBREPOR EXTERNA, COM 1 LÂMPADA LED DE 40 W, SEM REATOR - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97607 - 09/2024))</t>
   </si>
 </sst>
 </file>
@@ -5136,7 +5157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B783"/>
+  <dimension ref="A1:B788"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -10495,7 +10516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A670" s="3" t="s">
         <v>1313</v>
       </c>
@@ -10503,7 +10524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A671" s="3" t="s">
         <v>1316</v>
       </c>
@@ -10511,7 +10532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A672" s="3" t="s">
         <v>1319</v>
       </c>
@@ -10799,7 +10820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A708" s="3" t="s">
         <v>1428</v>
       </c>
@@ -10815,7 +10836,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A710" s="3" t="s">
         <v>1434</v>
       </c>
@@ -10823,7 +10844,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A711" s="3" t="s">
         <v>1437</v>
       </c>
@@ -10831,7 +10852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A712" s="3" t="s">
         <v>1439</v>
       </c>
@@ -10847,7 +10868,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A714" s="3" t="s">
         <v>1446</v>
       </c>
@@ -11405,6 +11426,46 @@
       </c>
       <c r="B783" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A784" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B784" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A785" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B785" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A786" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B786" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A787" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B787" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A788" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B788" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -11414,7 +11475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D783"/>
+  <dimension ref="A1:D788"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -22385,6 +22446,76 @@
         <v>20</v>
       </c>
     </row>
+    <row r="784" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A784" s="2">
+        <v>93661</v>
+      </c>
+      <c r="B784" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C784" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D784" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A785" s="2">
+        <v>93662</v>
+      </c>
+      <c r="B785" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C785" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D785" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A786" s="2">
+        <v>93664</v>
+      </c>
+      <c r="B786" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C786" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D786" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A787" s="5" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B787" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C787" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D787" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A788" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B788" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C788" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D788" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A795973-50BD-4E8D-A39C-1BE4077EC8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F08338-0AE8-4FA3-9AA0-F41A3C35F67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="1575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="1574">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2272,9 +2272,6 @@
   </si>
   <si>
     <t>Eletroduto PVC flexível - Eletroduto leve - 1" - Forro</t>
-  </si>
-  <si>
-    <t>ELETRODUTO FLEXÍVEL CORRUGADO, PEAD, DN 32 MM (1"), PARA CIRCUITOS TERMINAIS, INSTALADO EM FORRO - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
   </si>
   <si>
     <t>Cabeamento estruturado - óptico - Cabo ótico - interna - 1</t>
@@ -6180,7 +6177,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>281</v>
       </c>
@@ -6188,7 +6185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>282</v>
       </c>
@@ -8190,7 +8187,7 @@
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>20</v>
@@ -8198,7 +8195,7 @@
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" s="3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>20</v>
@@ -8206,7 +8203,7 @@
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>20</v>
@@ -8214,7 +8211,7 @@
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>20</v>
@@ -8222,7 +8219,7 @@
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>20</v>
@@ -8230,7 +8227,7 @@
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>20</v>
@@ -8238,7 +8235,7 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>20</v>
@@ -8246,7 +8243,7 @@
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>20</v>
@@ -8254,7 +8251,7 @@
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>20</v>
@@ -8262,7 +8259,7 @@
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>7</v>
@@ -8270,7 +8267,7 @@
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>7</v>
@@ -8278,7 +8275,7 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>7</v>
@@ -8286,7 +8283,7 @@
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>7</v>
@@ -8294,7 +8291,7 @@
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>7</v>
@@ -8302,7 +8299,7 @@
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>7</v>
@@ -8310,7 +8307,7 @@
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>7</v>
@@ -8318,7 +8315,7 @@
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>7</v>
@@ -8326,7 +8323,7 @@
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>7</v>
@@ -8334,7 +8331,7 @@
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>7</v>
@@ -8342,7 +8339,7 @@
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>7</v>
@@ -8350,7 +8347,7 @@
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B399" s="1" t="s">
         <v>7</v>
@@ -8358,7 +8355,7 @@
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>7</v>
@@ -8366,7 +8363,7 @@
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>7</v>
@@ -8374,7 +8371,7 @@
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>7</v>
@@ -8382,7 +8379,7 @@
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>7</v>
@@ -8390,7 +8387,7 @@
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>7</v>
@@ -8398,7 +8395,7 @@
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>7</v>
@@ -8406,7 +8403,7 @@
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>7</v>
@@ -8414,7 +8411,7 @@
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>7</v>
@@ -8422,7 +8419,7 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B408" s="1" t="s">
         <v>7</v>
@@ -8430,7 +8427,7 @@
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B409" s="1" t="s">
         <v>7</v>
@@ -8438,7 +8435,7 @@
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B410" s="1" t="s">
         <v>20</v>
@@ -8446,7 +8443,7 @@
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>20</v>
@@ -8454,7 +8451,7 @@
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>20</v>
@@ -8462,7 +8459,7 @@
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>20</v>
@@ -8470,7 +8467,7 @@
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B414" s="1" t="s">
         <v>20</v>
@@ -8478,7 +8475,7 @@
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>20</v>
@@ -8486,7 +8483,7 @@
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>20</v>
@@ -8494,7 +8491,7 @@
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>20</v>
@@ -8502,7 +8499,7 @@
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>20</v>
@@ -8510,7 +8507,7 @@
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>20</v>
@@ -8518,7 +8515,7 @@
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>20</v>
@@ -8526,7 +8523,7 @@
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>20</v>
@@ -8534,7 +8531,7 @@
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>20</v>
@@ -8542,7 +8539,7 @@
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>20</v>
@@ -8550,7 +8547,7 @@
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>20</v>
@@ -8558,7 +8555,7 @@
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>7</v>
@@ -8566,7 +8563,7 @@
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" s="3" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>7</v>
@@ -8574,7 +8571,7 @@
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>7</v>
@@ -8582,7 +8579,7 @@
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" s="3" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>7</v>
@@ -8590,7 +8587,7 @@
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>7</v>
@@ -8598,7 +8595,7 @@
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>7</v>
@@ -8606,7 +8603,7 @@
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>7</v>
@@ -8614,7 +8611,7 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" s="3" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>7</v>
@@ -8622,7 +8619,7 @@
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>7</v>
@@ -8630,7 +8627,7 @@
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>7</v>
@@ -8638,7 +8635,7 @@
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>7</v>
@@ -8646,7 +8643,7 @@
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" s="3" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>7</v>
@@ -8654,7 +8651,7 @@
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>7</v>
@@ -8662,7 +8659,7 @@
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>7</v>
@@ -8670,7 +8667,7 @@
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>7</v>
@@ -8678,7 +8675,7 @@
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>7</v>
@@ -8686,7 +8683,7 @@
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>7</v>
@@ -8694,7 +8691,7 @@
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>7</v>
@@ -8702,7 +8699,7 @@
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>7</v>
@@ -8710,7 +8707,7 @@
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444" s="3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>7</v>
@@ -8718,7 +8715,7 @@
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>7</v>
@@ -8726,7 +8723,7 @@
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>7</v>
@@ -8734,7 +8731,7 @@
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>7</v>
@@ -8742,7 +8739,7 @@
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>7</v>
@@ -8750,7 +8747,7 @@
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>7</v>
@@ -8758,7 +8755,7 @@
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>7</v>
@@ -8766,7 +8763,7 @@
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>7</v>
@@ -8774,7 +8771,7 @@
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>7</v>
@@ -8782,7 +8779,7 @@
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>7</v>
@@ -8790,7 +8787,7 @@
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>20</v>
@@ -8798,7 +8795,7 @@
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>7</v>
@@ -8806,7 +8803,7 @@
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>7</v>
@@ -8814,7 +8811,7 @@
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>7</v>
@@ -8822,7 +8819,7 @@
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>7</v>
@@ -8830,7 +8827,7 @@
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>7</v>
@@ -8838,7 +8835,7 @@
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>20</v>
@@ -8846,7 +8843,7 @@
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>20</v>
@@ -8854,7 +8851,7 @@
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>20</v>
@@ -8862,7 +8859,7 @@
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>20</v>
@@ -8870,7 +8867,7 @@
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>20</v>
@@ -8878,7 +8875,7 @@
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>20</v>
@@ -8886,7 +8883,7 @@
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>20</v>
@@ -8894,7 +8891,7 @@
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>20</v>
@@ -8902,7 +8899,7 @@
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>20</v>
@@ -8910,7 +8907,7 @@
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>20</v>
@@ -8918,7 +8915,7 @@
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>20</v>
@@ -8926,7 +8923,7 @@
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B471" s="1" t="s">
         <v>20</v>
@@ -8934,7 +8931,7 @@
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>20</v>
@@ -8942,7 +8939,7 @@
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>20</v>
@@ -8950,7 +8947,7 @@
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>20</v>
@@ -8958,7 +8955,7 @@
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B475" s="1" t="s">
         <v>20</v>
@@ -8966,7 +8963,7 @@
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>20</v>
@@ -8974,7 +8971,7 @@
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>20</v>
@@ -8982,7 +8979,7 @@
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B478" s="1" t="s">
         <v>20</v>
@@ -8990,7 +8987,7 @@
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>20</v>
@@ -8998,7 +8995,7 @@
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B480" s="1" t="s">
         <v>20</v>
@@ -9006,7 +9003,7 @@
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B481" s="1" t="s">
         <v>20</v>
@@ -9014,7 +9011,7 @@
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>20</v>
@@ -9022,7 +9019,7 @@
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>20</v>
@@ -9030,7 +9027,7 @@
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>7</v>
@@ -9038,7 +9035,7 @@
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>7</v>
@@ -9046,7 +9043,7 @@
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>7</v>
@@ -9054,7 +9051,7 @@
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>7</v>
@@ -9062,7 +9059,7 @@
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>7</v>
@@ -9070,7 +9067,7 @@
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>20</v>
@@ -9078,7 +9075,7 @@
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A490" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>7</v>
@@ -9086,7 +9083,7 @@
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>7</v>
@@ -9094,7 +9091,7 @@
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>7</v>
@@ -9102,7 +9099,7 @@
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>7</v>
@@ -9110,7 +9107,7 @@
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>7</v>
@@ -9118,7 +9115,7 @@
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>20</v>
@@ -9126,7 +9123,7 @@
     </row>
     <row r="496" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A496" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>7</v>
@@ -9134,7 +9131,7 @@
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>7</v>
@@ -9142,7 +9139,7 @@
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498" s="3" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>7</v>
@@ -9150,7 +9147,7 @@
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B499" s="1" t="s">
         <v>7</v>
@@ -9158,7 +9155,7 @@
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>20</v>
@@ -9166,7 +9163,7 @@
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B501" s="1" t="s">
         <v>20</v>
@@ -9174,7 +9171,7 @@
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502" s="3" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B502" s="1" t="s">
         <v>20</v>
@@ -9182,7 +9179,7 @@
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>20</v>
@@ -9190,7 +9187,7 @@
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504" s="3" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>20</v>
@@ -9198,7 +9195,7 @@
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B505" s="1" t="s">
         <v>20</v>
@@ -9206,7 +9203,7 @@
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>20</v>
@@ -9214,7 +9211,7 @@
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>20</v>
@@ -9222,7 +9219,7 @@
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B508" s="1" t="s">
         <v>7</v>
@@ -9230,7 +9227,7 @@
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B509" s="1" t="s">
         <v>7</v>
@@ -9238,7 +9235,7 @@
     </row>
     <row r="510" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A510" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B510" s="1" t="s">
         <v>7</v>
@@ -9246,7 +9243,7 @@
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B511" s="1" t="s">
         <v>7</v>
@@ -9254,7 +9251,7 @@
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512" s="3" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B512" s="1" t="s">
         <v>20</v>
@@ -9262,7 +9259,7 @@
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B513" s="1" t="s">
         <v>7</v>
@@ -9270,7 +9267,7 @@
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514" s="3" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B514" s="1" t="s">
         <v>7</v>
@@ -9278,7 +9275,7 @@
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B515" s="1" t="s">
         <v>7</v>
@@ -9286,7 +9283,7 @@
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B516" s="1" t="s">
         <v>7</v>
@@ -9294,7 +9291,7 @@
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B517" s="1" t="s">
         <v>7</v>
@@ -9302,7 +9299,7 @@
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B518" s="1" t="s">
         <v>7</v>
@@ -9310,7 +9307,7 @@
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B519" s="1" t="s">
         <v>7</v>
@@ -9318,7 +9315,7 @@
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A520" s="3" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B520" s="1" t="s">
         <v>7</v>
@@ -9326,7 +9323,7 @@
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B521" s="1" t="s">
         <v>20</v>
@@ -9334,7 +9331,7 @@
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B522" s="1" t="s">
         <v>20</v>
@@ -9342,7 +9339,7 @@
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B523" s="1" t="s">
         <v>20</v>
@@ -9350,7 +9347,7 @@
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>20</v>
@@ -9358,7 +9355,7 @@
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B525" s="1" t="s">
         <v>7</v>
@@ -9366,7 +9363,7 @@
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>7</v>
@@ -9374,7 +9371,7 @@
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>7</v>
@@ -9382,7 +9379,7 @@
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>7</v>
@@ -9390,7 +9387,7 @@
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B529" s="1" t="s">
         <v>7</v>
@@ -9398,7 +9395,7 @@
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A530" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>7</v>
@@ -9406,7 +9403,7 @@
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>7</v>
@@ -9414,7 +9411,7 @@
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A532" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>7</v>
@@ -9422,7 +9419,7 @@
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>7</v>
@@ -9430,7 +9427,7 @@
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A534" s="3" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>20</v>
@@ -9438,7 +9435,7 @@
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>20</v>
@@ -9446,7 +9443,7 @@
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A536" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>20</v>
@@ -9454,7 +9451,7 @@
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B537" s="1" t="s">
         <v>20</v>
@@ -9462,7 +9459,7 @@
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A538" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>20</v>
@@ -9470,7 +9467,7 @@
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B539" s="1" t="s">
         <v>7</v>
@@ -9478,7 +9475,7 @@
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A540" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B540" s="1" t="s">
         <v>20</v>
@@ -9486,7 +9483,7 @@
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B541" s="1" t="s">
         <v>20</v>
@@ -9494,7 +9491,7 @@
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A542" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B542" s="1" t="s">
         <v>7</v>
@@ -9502,7 +9499,7 @@
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B543" s="1" t="s">
         <v>7</v>
@@ -9510,7 +9507,7 @@
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A544" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B544" s="1" t="s">
         <v>7</v>
@@ -9518,7 +9515,7 @@
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B545" s="1" t="s">
         <v>7</v>
@@ -9526,7 +9523,7 @@
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A546" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B546" s="1" t="s">
         <v>7</v>
@@ -9534,7 +9531,7 @@
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B547" s="1" t="s">
         <v>7</v>
@@ -9542,7 +9539,7 @@
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A548" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B548" s="1" t="s">
         <v>7</v>
@@ -9550,7 +9547,7 @@
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B549" s="1" t="s">
         <v>7</v>
@@ -9558,7 +9555,7 @@
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A550" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>7</v>
@@ -9566,7 +9563,7 @@
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>7</v>
@@ -9574,7 +9571,7 @@
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A552" s="3" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>7</v>
@@ -9582,7 +9579,7 @@
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B553" s="1" t="s">
         <v>7</v>
@@ -9590,7 +9587,7 @@
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A554" s="3" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B554" s="1" t="s">
         <v>7</v>
@@ -9598,7 +9595,7 @@
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B555" s="1" t="s">
         <v>7</v>
@@ -9606,7 +9603,7 @@
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A556" s="3" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B556" s="1" t="s">
         <v>7</v>
@@ -9614,7 +9611,7 @@
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B557" s="1" t="s">
         <v>20</v>
@@ -9622,7 +9619,7 @@
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A558" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B558" s="1" t="s">
         <v>20</v>
@@ -9630,7 +9627,7 @@
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B559" s="1" t="s">
         <v>20</v>
@@ -9638,7 +9635,7 @@
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A560" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B560" s="1" t="s">
         <v>7</v>
@@ -9646,7 +9643,7 @@
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B561" s="1" t="s">
         <v>7</v>
@@ -9654,7 +9651,7 @@
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A562" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B562" s="1" t="s">
         <v>7</v>
@@ -9662,7 +9659,7 @@
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B563" s="1" t="s">
         <v>7</v>
@@ -9670,7 +9667,7 @@
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A564" s="3" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B564" s="1" t="s">
         <v>7</v>
@@ -9678,7 +9675,7 @@
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B565" s="1" t="s">
         <v>7</v>
@@ -9686,7 +9683,7 @@
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A566" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>7</v>
@@ -9694,7 +9691,7 @@
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B567" s="1" t="s">
         <v>7</v>
@@ -9702,7 +9699,7 @@
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A568" s="3" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B568" s="1" t="s">
         <v>7</v>
@@ -9710,7 +9707,7 @@
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B569" s="1" t="s">
         <v>7</v>
@@ -9718,7 +9715,7 @@
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A570" s="3" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B570" s="1" t="s">
         <v>7</v>
@@ -9726,7 +9723,7 @@
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B571" s="1" t="s">
         <v>7</v>
@@ -9734,7 +9731,7 @@
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A572" s="3" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B572" s="1" t="s">
         <v>7</v>
@@ -9742,7 +9739,7 @@
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B573" s="1" t="s">
         <v>7</v>
@@ -9750,7 +9747,7 @@
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A574" s="3" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B574" s="1" t="s">
         <v>7</v>
@@ -9758,7 +9755,7 @@
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B575" s="1" t="s">
         <v>7</v>
@@ -9766,7 +9763,7 @@
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A576" s="3" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B576" s="1" t="s">
         <v>20</v>
@@ -9774,7 +9771,7 @@
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B577" s="1" t="s">
         <v>20</v>
@@ -9782,7 +9779,7 @@
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A578" s="3" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B578" s="1" t="s">
         <v>20</v>
@@ -9790,7 +9787,7 @@
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B579" s="1" t="s">
         <v>7</v>
@@ -9798,7 +9795,7 @@
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A580" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B580" s="1" t="s">
         <v>7</v>
@@ -9806,7 +9803,7 @@
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B581" s="1" t="s">
         <v>7</v>
@@ -9814,7 +9811,7 @@
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A582" s="3" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B582" s="1" t="s">
         <v>7</v>
@@ -9822,7 +9819,7 @@
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B583" s="1" t="s">
         <v>7</v>
@@ -9830,7 +9827,7 @@
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A584" s="3" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B584" s="1" t="s">
         <v>7</v>
@@ -9838,7 +9835,7 @@
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B585" s="1" t="s">
         <v>7</v>
@@ -9846,7 +9843,7 @@
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A586" s="3" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B586" s="1" t="s">
         <v>7</v>
@@ -9854,7 +9851,7 @@
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A587" s="3" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B587" s="1" t="s">
         <v>7</v>
@@ -9862,7 +9859,7 @@
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A588" s="3" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B588" s="1" t="s">
         <v>7</v>
@@ -9870,7 +9867,7 @@
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B589" s="1" t="s">
         <v>7</v>
@@ -9878,7 +9875,7 @@
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A590" s="3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B590" s="1" t="s">
         <v>7</v>
@@ -9886,7 +9883,7 @@
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B591" s="1" t="s">
         <v>7</v>
@@ -9894,7 +9891,7 @@
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A592" s="3" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B592" s="1" t="s">
         <v>7</v>
@@ -9902,7 +9899,7 @@
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B593" s="1" t="s">
         <v>7</v>
@@ -9910,7 +9907,7 @@
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A594" s="3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B594" s="1" t="s">
         <v>7</v>
@@ -9918,7 +9915,7 @@
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A595" s="3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B595" s="1" t="s">
         <v>7</v>
@@ -9926,7 +9923,7 @@
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A596" s="3" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B596" s="1" t="s">
         <v>7</v>
@@ -9934,7 +9931,7 @@
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A597" s="3" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B597" s="1" t="s">
         <v>7</v>
@@ -9942,7 +9939,7 @@
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A598" s="3" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B598" s="1" t="s">
         <v>7</v>
@@ -9950,7 +9947,7 @@
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A599" s="3" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B599" s="1" t="s">
         <v>20</v>
@@ -9958,7 +9955,7 @@
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A600" s="3" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B600" s="1" t="s">
         <v>20</v>
@@ -9966,7 +9963,7 @@
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A601" s="3" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B601" s="1" t="s">
         <v>7</v>
@@ -9974,7 +9971,7 @@
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A602" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B602" s="1" t="s">
         <v>7</v>
@@ -9982,7 +9979,7 @@
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A603" s="3" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B603" s="1" t="s">
         <v>7</v>
@@ -9990,7 +9987,7 @@
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A604" s="3" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B604" s="1" t="s">
         <v>7</v>
@@ -9998,7 +9995,7 @@
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A605" s="3" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B605" s="1" t="s">
         <v>7</v>
@@ -10006,7 +10003,7 @@
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A606" s="3" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B606" s="1" t="s">
         <v>7</v>
@@ -10014,7 +10011,7 @@
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A607" s="3" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B607" s="1" t="s">
         <v>7</v>
@@ -10022,7 +10019,7 @@
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A608" s="3" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B608" s="1" t="s">
         <v>7</v>
@@ -10030,7 +10027,7 @@
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A609" s="3" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B609" s="1" t="s">
         <v>7</v>
@@ -10038,7 +10035,7 @@
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A610" s="3" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B610" s="1" t="s">
         <v>7</v>
@@ -10046,7 +10043,7 @@
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A611" s="3" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B611" s="1" t="s">
         <v>7</v>
@@ -10054,7 +10051,7 @@
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A612" s="3" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B612" s="1" t="s">
         <v>7</v>
@@ -10062,7 +10059,7 @@
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A613" s="3" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B613" s="1" t="s">
         <v>7</v>
@@ -10070,7 +10067,7 @@
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A614" s="3" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B614" s="1" t="s">
         <v>7</v>
@@ -10078,7 +10075,7 @@
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A615" s="3" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B615" s="1" t="s">
         <v>7</v>
@@ -10086,7 +10083,7 @@
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A616" s="3" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B616" s="1" t="s">
         <v>7</v>
@@ -10094,7 +10091,7 @@
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A617" s="3" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B617" s="1" t="s">
         <v>7</v>
@@ -10102,7 +10099,7 @@
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A618" s="3" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B618" s="1" t="s">
         <v>7</v>
@@ -10110,7 +10107,7 @@
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A619" s="3" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B619" s="1" t="s">
         <v>7</v>
@@ -10118,7 +10115,7 @@
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A620" s="3" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B620" s="1" t="s">
         <v>7</v>
@@ -10126,7 +10123,7 @@
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A621" s="3" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B621" s="1" t="s">
         <v>7</v>
@@ -10134,7 +10131,7 @@
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A622" s="3" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B622" s="1" t="s">
         <v>7</v>
@@ -10142,7 +10139,7 @@
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A623" s="3" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B623" s="1" t="s">
         <v>7</v>
@@ -10150,7 +10147,7 @@
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A624" s="3" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B624" s="1" t="s">
         <v>7</v>
@@ -10158,7 +10155,7 @@
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A625" s="3" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B625" s="1" t="s">
         <v>7</v>
@@ -10166,7 +10163,7 @@
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A626" s="3" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B626" s="1" t="s">
         <v>7</v>
@@ -10174,7 +10171,7 @@
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A627" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B627" s="1" t="s">
         <v>7</v>
@@ -10182,7 +10179,7 @@
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A628" s="3" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B628" s="1" t="s">
         <v>7</v>
@@ -10190,7 +10187,7 @@
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A629" s="3" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="B629" s="1" t="s">
         <v>7</v>
@@ -10198,7 +10195,7 @@
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A630" s="3" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B630" s="1" t="s">
         <v>7</v>
@@ -10206,7 +10203,7 @@
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A631" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B631" s="1" t="s">
         <v>7</v>
@@ -10214,7 +10211,7 @@
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A632" s="3" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B632" s="1" t="s">
         <v>7</v>
@@ -10222,7 +10219,7 @@
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A633" s="3" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B633" s="1" t="s">
         <v>7</v>
@@ -10230,7 +10227,7 @@
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A634" s="3" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B634" s="1" t="s">
         <v>7</v>
@@ -10238,7 +10235,7 @@
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A635" s="3" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B635" s="1" t="s">
         <v>7</v>
@@ -10246,7 +10243,7 @@
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A636" s="3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B636" s="1" t="s">
         <v>7</v>
@@ -10254,7 +10251,7 @@
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A637" s="3" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B637" s="1" t="s">
         <v>7</v>
@@ -10262,7 +10259,7 @@
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A638" s="3" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B638" s="1" t="s">
         <v>7</v>
@@ -10270,7 +10267,7 @@
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A639" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B639" s="1" t="s">
         <v>7</v>
@@ -10278,7 +10275,7 @@
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A640" s="3" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B640" s="1" t="s">
         <v>7</v>
@@ -10286,7 +10283,7 @@
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A641" s="3" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B641" s="1" t="s">
         <v>7</v>
@@ -10294,7 +10291,7 @@
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A642" s="3" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B642" s="1" t="s">
         <v>7</v>
@@ -10302,7 +10299,7 @@
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A643" s="3" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B643" s="1" t="s">
         <v>7</v>
@@ -10310,7 +10307,7 @@
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A644" s="3" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B644" s="1" t="s">
         <v>7</v>
@@ -10318,7 +10315,7 @@
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A645" s="3" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B645" s="1" t="s">
         <v>20</v>
@@ -10326,7 +10323,7 @@
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A646" s="3" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B646" s="1" t="s">
         <v>20</v>
@@ -10334,7 +10331,7 @@
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A647" s="3" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="B647" s="1" t="s">
         <v>7</v>
@@ -10342,7 +10339,7 @@
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A648" s="3" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B648" s="1" t="s">
         <v>7</v>
@@ -10350,7 +10347,7 @@
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A649" s="3" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B649" s="1" t="s">
         <v>7</v>
@@ -10358,7 +10355,7 @@
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A650" s="3" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B650" s="1" t="s">
         <v>7</v>
@@ -10366,7 +10363,7 @@
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A651" s="3" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B651" s="1" t="s">
         <v>7</v>
@@ -10374,7 +10371,7 @@
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A652" s="3" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B652" s="1" t="s">
         <v>7</v>
@@ -10382,7 +10379,7 @@
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A653" s="3" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B653" s="1" t="s">
         <v>7</v>
@@ -10390,7 +10387,7 @@
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A654" s="3" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B654" s="1" t="s">
         <v>7</v>
@@ -10398,7 +10395,7 @@
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A655" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B655" s="1" t="s">
         <v>7</v>
@@ -10406,7 +10403,7 @@
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A656" s="3" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B656" s="1" t="s">
         <v>7</v>
@@ -10414,7 +10411,7 @@
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A657" s="3" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B657" s="1" t="s">
         <v>7</v>
@@ -10422,7 +10419,7 @@
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A658" s="3" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B658" s="1" t="s">
         <v>7</v>
@@ -10430,7 +10427,7 @@
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A659" s="3" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B659" s="1" t="s">
         <v>7</v>
@@ -10438,7 +10435,7 @@
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A660" s="3" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B660" s="1" t="s">
         <v>20</v>
@@ -10446,7 +10443,7 @@
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A661" s="3" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B661" s="1" t="s">
         <v>20</v>
@@ -10454,7 +10451,7 @@
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A662" s="3" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B662" s="1" t="s">
         <v>20</v>
@@ -10462,7 +10459,7 @@
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A663" s="3" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B663" s="1" t="s">
         <v>20</v>
@@ -10470,7 +10467,7 @@
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A664" s="3" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B664" s="1" t="s">
         <v>20</v>
@@ -10478,7 +10475,7 @@
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A665" s="3" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B665" s="1" t="s">
         <v>20</v>
@@ -10486,7 +10483,7 @@
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A666" s="3" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B666" s="1" t="s">
         <v>20</v>
@@ -10494,7 +10491,7 @@
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A667" s="3" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B667" s="1" t="s">
         <v>7</v>
@@ -10502,7 +10499,7 @@
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A668" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B668" s="1" t="s">
         <v>7</v>
@@ -10510,7 +10507,7 @@
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A669" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="B669" s="1" t="s">
         <v>7</v>
@@ -10518,7 +10515,7 @@
     </row>
     <row r="670" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A670" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B670" s="1" t="s">
         <v>7</v>
@@ -10526,7 +10523,7 @@
     </row>
     <row r="671" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A671" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B671" s="1" t="s">
         <v>7</v>
@@ -10534,7 +10531,7 @@
     </row>
     <row r="672" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A672" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B672" s="1" t="s">
         <v>7</v>
@@ -10542,7 +10539,7 @@
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A673" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B673" s="1" t="s">
         <v>7</v>
@@ -10550,7 +10547,7 @@
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A674" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B674" s="1" t="s">
         <v>7</v>
@@ -10558,7 +10555,7 @@
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A675" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B675" s="1" t="s">
         <v>7</v>
@@ -10566,7 +10563,7 @@
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A676" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B676" s="1" t="s">
         <v>7</v>
@@ -10574,7 +10571,7 @@
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A677" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B677" s="1" t="s">
         <v>20</v>
@@ -10582,7 +10579,7 @@
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A678" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B678" s="1" t="s">
         <v>20</v>
@@ -10590,7 +10587,7 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A679" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B679" s="1" t="s">
         <v>20</v>
@@ -10598,7 +10595,7 @@
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A680" s="3" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B680" s="1" t="s">
         <v>20</v>
@@ -10606,7 +10603,7 @@
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A681" s="3" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B681" s="1" t="s">
         <v>7</v>
@@ -10614,7 +10611,7 @@
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A682" s="3" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B682" s="1" t="s">
         <v>7</v>
@@ -10622,7 +10619,7 @@
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A683" s="3" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B683" s="1" t="s">
         <v>7</v>
@@ -10630,7 +10627,7 @@
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A684" s="3" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B684" s="1" t="s">
         <v>7</v>
@@ -10638,7 +10635,7 @@
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A685" s="3" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B685" s="1" t="s">
         <v>7</v>
@@ -10646,7 +10643,7 @@
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A686" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B686" s="1" t="s">
         <v>7</v>
@@ -10654,7 +10651,7 @@
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A687" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B687" s="1" t="s">
         <v>7</v>
@@ -10662,7 +10659,7 @@
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A688" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B688" s="1" t="s">
         <v>7</v>
@@ -10670,7 +10667,7 @@
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A689" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B689" s="1" t="s">
         <v>7</v>
@@ -10678,7 +10675,7 @@
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A690" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B690" s="1" t="s">
         <v>7</v>
@@ -10686,7 +10683,7 @@
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A691" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="B691" s="1" t="s">
         <v>7</v>
@@ -10694,7 +10691,7 @@
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A692" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B692" s="1" t="s">
         <v>7</v>
@@ -10702,7 +10699,7 @@
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A693" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B693" s="1" t="s">
         <v>7</v>
@@ -10710,7 +10707,7 @@
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A694" s="3" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B694" s="1" t="s">
         <v>20</v>
@@ -10718,7 +10715,7 @@
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A695" s="3" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B695" s="1" t="s">
         <v>20</v>
@@ -10726,7 +10723,7 @@
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A696" s="3" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B696" s="1" t="s">
         <v>20</v>
@@ -10734,7 +10731,7 @@
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A697" s="3" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B697" s="1" t="s">
         <v>20</v>
@@ -10742,7 +10739,7 @@
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A698" s="3" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B698" s="1" t="s">
         <v>20</v>
@@ -10750,7 +10747,7 @@
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A699" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B699" s="1" t="s">
         <v>20</v>
@@ -10758,7 +10755,7 @@
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A700" s="3" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B700" s="1" t="s">
         <v>20</v>
@@ -10766,7 +10763,7 @@
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A701" s="3" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B701" s="1" t="s">
         <v>7</v>
@@ -10774,7 +10771,7 @@
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A702" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B702" s="1" t="s">
         <v>7</v>
@@ -10782,7 +10779,7 @@
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A703" s="3" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B703" s="1" t="s">
         <v>7</v>
@@ -10790,7 +10787,7 @@
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A704" s="3" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B704" s="1" t="s">
         <v>7</v>
@@ -10798,7 +10795,7 @@
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A705" s="3" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B705" s="1" t="s">
         <v>7</v>
@@ -10806,7 +10803,7 @@
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A706" s="3" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B706" s="1" t="s">
         <v>7</v>
@@ -10814,7 +10811,7 @@
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A707" s="3" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B707" s="1" t="s">
         <v>7</v>
@@ -10822,7 +10819,7 @@
     </row>
     <row r="708" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A708" s="3" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B708" s="1" t="s">
         <v>7</v>
@@ -10830,7 +10827,7 @@
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A709" s="3" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B709" s="1" t="s">
         <v>7</v>
@@ -10838,7 +10835,7 @@
     </row>
     <row r="710" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A710" s="3" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B710" s="1" t="s">
         <v>7</v>
@@ -10846,7 +10843,7 @@
     </row>
     <row r="711" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A711" s="3" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B711" s="1" t="s">
         <v>7</v>
@@ -10854,7 +10851,7 @@
     </row>
     <row r="712" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A712" s="3" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B712" s="1" t="s">
         <v>7</v>
@@ -10862,7 +10859,7 @@
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A713" s="3" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B713" s="1" t="s">
         <v>7</v>
@@ -10870,7 +10867,7 @@
     </row>
     <row r="714" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A714" s="3" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B714" s="1" t="s">
         <v>7</v>
@@ -10878,7 +10875,7 @@
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A715" s="3" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B715" s="1" t="s">
         <v>7</v>
@@ -10886,7 +10883,7 @@
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A716" s="3" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B716" s="1" t="s">
         <v>7</v>
@@ -10894,7 +10891,7 @@
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A717" s="3" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B717" s="1" t="s">
         <v>7</v>
@@ -10902,7 +10899,7 @@
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A718" s="3" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B718" s="1" t="s">
         <v>7</v>
@@ -10910,7 +10907,7 @@
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A719" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B719" s="1" t="s">
         <v>7</v>
@@ -10918,7 +10915,7 @@
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A720" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B720" s="1" t="s">
         <v>7</v>
@@ -10926,7 +10923,7 @@
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A721" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B721" s="1" t="s">
         <v>7</v>
@@ -10934,7 +10931,7 @@
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A722" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B722" s="1" t="s">
         <v>7</v>
@@ -10942,7 +10939,7 @@
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A723" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B723" s="1" t="s">
         <v>7</v>
@@ -10950,7 +10947,7 @@
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A724" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B724" s="1" t="s">
         <v>7</v>
@@ -10958,7 +10955,7 @@
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A725" s="3" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B725" s="1" t="s">
         <v>7</v>
@@ -10966,7 +10963,7 @@
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A726" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B726" s="1" t="s">
         <v>7</v>
@@ -10974,7 +10971,7 @@
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A727" s="3" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B727" s="1" t="s">
         <v>7</v>
@@ -10982,7 +10979,7 @@
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A728" s="3" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B728" s="1" t="s">
         <v>7</v>
@@ -10990,7 +10987,7 @@
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A729" s="3" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="B729" s="1" t="s">
         <v>7</v>
@@ -10998,7 +10995,7 @@
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A730" s="3" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B730" s="1" t="s">
         <v>7</v>
@@ -11006,7 +11003,7 @@
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A731" s="3" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B731" s="1" t="s">
         <v>7</v>
@@ -11014,7 +11011,7 @@
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A732" s="3" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B732" s="1" t="s">
         <v>7</v>
@@ -11022,7 +11019,7 @@
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A733" s="3" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="B733" s="1" t="s">
         <v>7</v>
@@ -11030,7 +11027,7 @@
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A734" s="3" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="B734" s="1" t="s">
         <v>7</v>
@@ -11038,7 +11035,7 @@
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A735" s="3" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="B735" s="1" t="s">
         <v>7</v>
@@ -11046,7 +11043,7 @@
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A736" s="3" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="B736" s="1" t="s">
         <v>7</v>
@@ -11054,7 +11051,7 @@
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A737" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="B737" s="1" t="s">
         <v>7</v>
@@ -11062,7 +11059,7 @@
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A738" s="3" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B738" s="2" t="s">
         <v>7</v>
@@ -11070,7 +11067,7 @@
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A739" s="3" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B739" s="2" t="s">
         <v>7</v>
@@ -11078,7 +11075,7 @@
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A740" s="3" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B740" s="2" t="s">
         <v>7</v>
@@ -11086,7 +11083,7 @@
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A741" s="3" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>7</v>
@@ -11094,7 +11091,7 @@
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A742" s="3" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B742" s="2" t="s">
         <v>7</v>
@@ -11102,7 +11099,7 @@
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A743" s="3" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B743" s="2" t="s">
         <v>7</v>
@@ -11110,7 +11107,7 @@
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A744" s="3" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B744" s="2" t="s">
         <v>7</v>
@@ -11118,7 +11115,7 @@
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A745" s="3" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B745" s="2" t="s">
         <v>7</v>
@@ -11126,7 +11123,7 @@
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A746" s="3" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B746" s="2" t="s">
         <v>7</v>
@@ -11134,7 +11131,7 @@
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A747" s="3" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B747" s="2" t="s">
         <v>7</v>
@@ -11142,7 +11139,7 @@
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A748" s="3" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B748" s="2" t="s">
         <v>7</v>
@@ -11150,7 +11147,7 @@
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A749" s="3" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B749" s="1" t="s">
         <v>20</v>
@@ -11158,7 +11155,7 @@
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A750" s="3" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="B750" s="1" t="s">
         <v>20</v>
@@ -11166,7 +11163,7 @@
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A751" s="3" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B751" s="2" t="s">
         <v>7</v>
@@ -11174,7 +11171,7 @@
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A752" s="3" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B752" s="2" t="s">
         <v>7</v>
@@ -11182,7 +11179,7 @@
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A753" s="3" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="B753" s="2" t="s">
         <v>7</v>
@@ -11190,7 +11187,7 @@
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A754" s="3" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B754" s="2" t="s">
         <v>7</v>
@@ -11198,7 +11195,7 @@
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A755" s="3" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B755" s="2" t="s">
         <v>7</v>
@@ -11206,7 +11203,7 @@
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A756" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B756" s="2" t="s">
         <v>7</v>
@@ -11214,7 +11211,7 @@
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A757" s="3" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B757" s="2" t="s">
         <v>7</v>
@@ -11222,7 +11219,7 @@
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A758" s="3" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="B758" s="1" t="s">
         <v>20</v>
@@ -11230,7 +11227,7 @@
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A759" s="3" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="B759" s="1" t="s">
         <v>20</v>
@@ -11238,7 +11235,7 @@
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A760" s="3" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B760" s="1" t="s">
         <v>20</v>
@@ -11246,7 +11243,7 @@
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A761" s="3" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B761" s="1" t="s">
         <v>20</v>
@@ -11254,7 +11251,7 @@
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A762" s="3" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B762" s="1" t="s">
         <v>20</v>
@@ -11262,7 +11259,7 @@
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A763" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B763" s="1" t="s">
         <v>20</v>
@@ -11270,7 +11267,7 @@
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A764" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B764" s="1" t="s">
         <v>20</v>
@@ -11278,7 +11275,7 @@
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A765" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B765" s="1" t="s">
         <v>20</v>
@@ -11286,7 +11283,7 @@
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A766" s="3" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B766" s="1" t="s">
         <v>20</v>
@@ -11294,7 +11291,7 @@
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A767" s="3" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="B767" s="1" t="s">
         <v>20</v>
@@ -11302,7 +11299,7 @@
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A768" s="3" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B768" s="1" t="s">
         <v>20</v>
@@ -11310,7 +11307,7 @@
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A769" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="B769" s="2" t="s">
         <v>7</v>
@@ -11318,7 +11315,7 @@
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A770" s="3" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B770" s="2" t="s">
         <v>7</v>
@@ -11326,7 +11323,7 @@
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A771" s="3" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B771" s="2" t="s">
         <v>7</v>
@@ -11334,7 +11331,7 @@
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A772" s="3" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B772" s="2" t="s">
         <v>7</v>
@@ -11342,7 +11339,7 @@
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A773" s="3" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B773" s="2" t="s">
         <v>7</v>
@@ -11350,7 +11347,7 @@
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A774" s="3" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B774" s="1" t="s">
         <v>20</v>
@@ -11358,7 +11355,7 @@
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A775" s="3" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B775" s="1" t="s">
         <v>20</v>
@@ -11366,7 +11363,7 @@
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A776" s="3" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B776" s="1" t="s">
         <v>20</v>
@@ -11374,7 +11371,7 @@
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A777" s="3" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="B777" s="2" t="s">
         <v>7</v>
@@ -11382,7 +11379,7 @@
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A778" s="3" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B778" s="2" t="s">
         <v>7</v>
@@ -11390,7 +11387,7 @@
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A779" s="3" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B779" s="2" t="s">
         <v>7</v>
@@ -11398,7 +11395,7 @@
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A780" s="3" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="B780" s="2" t="s">
         <v>7</v>
@@ -11406,7 +11403,7 @@
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A781" s="3" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B781" s="2" t="s">
         <v>7</v>
@@ -11414,7 +11411,7 @@
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A782" s="3" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B782" s="1" t="s">
         <v>20</v>
@@ -11422,7 +11419,7 @@
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A783" s="3" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B783" s="1" t="s">
         <v>20</v>
@@ -11430,7 +11427,7 @@
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A784" s="3" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B784" s="2" t="s">
         <v>7</v>
@@ -11438,7 +11435,7 @@
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A785" s="3" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B785" s="2" t="s">
         <v>7</v>
@@ -11446,7 +11443,7 @@
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A786" s="3" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="B786" s="2" t="s">
         <v>7</v>
@@ -11454,7 +11451,7 @@
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A787" s="3" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B787" s="2" t="s">
         <v>7</v>
@@ -11462,7 +11459,7 @@
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A788" s="3" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B788" s="2" t="s">
         <v>7</v>
@@ -13144,7 +13141,7 @@
         <v>5</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>7</v>
@@ -15154,13 +15151,13 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C263" s="3" t="s">
         <v>896</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C263" s="3" t="s">
-        <v>897</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>7</v>
@@ -16764,13 +16761,13 @@
     </row>
     <row r="378" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A378" s="2">
-        <v>91838</v>
+        <v>91836</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>744</v>
+        <v>91</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>20</v>
@@ -16826,7 +16823,7 @@
         <v>5</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>20</v>
@@ -16910,7 +16907,7 @@
         <v>5</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D388" s="2" t="s">
         <v>7</v>
@@ -16960,13 +16957,13 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C392" s="3" t="s">
         <v>760</v>
-      </c>
-      <c r="B392" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C392" s="3" t="s">
-        <v>761</v>
       </c>
       <c r="D392" s="2" t="s">
         <v>7</v>
@@ -17008,7 +17005,7 @@
         <v>5</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D395" s="2" t="s">
         <v>7</v>
@@ -17016,13 +17013,13 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C396" s="3" t="s">
         <v>767</v>
-      </c>
-      <c r="B396" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C396" s="3" t="s">
-        <v>768</v>
       </c>
       <c r="D396" s="2" t="s">
         <v>7</v>
@@ -17030,13 +17027,13 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C397" s="3" t="s">
         <v>770</v>
-      </c>
-      <c r="B397" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C397" s="3" t="s">
-        <v>771</v>
       </c>
       <c r="D397" s="2" t="s">
         <v>7</v>
@@ -17050,7 +17047,7 @@
         <v>5</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>7</v>
@@ -17072,13 +17069,13 @@
     </row>
     <row r="400" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C400" s="3" t="s">
         <v>776</v>
-      </c>
-      <c r="B400" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C400" s="3" t="s">
-        <v>777</v>
       </c>
       <c r="D400" s="2" t="s">
         <v>7</v>
@@ -17100,13 +17097,13 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C402" s="3" t="s">
         <v>780</v>
-      </c>
-      <c r="B402" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C402" s="3" t="s">
-        <v>781</v>
       </c>
       <c r="D402" s="2" t="s">
         <v>7</v>
@@ -17128,13 +17125,13 @@
     </row>
     <row r="404" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C404" s="3" t="s">
         <v>784</v>
-      </c>
-      <c r="B404" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C404" s="3" t="s">
-        <v>785</v>
       </c>
       <c r="D404" s="2" t="s">
         <v>7</v>
@@ -17142,13 +17139,13 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C405" s="3" t="s">
         <v>787</v>
-      </c>
-      <c r="B405" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C405" s="3" t="s">
-        <v>788</v>
       </c>
       <c r="D405" s="2" t="s">
         <v>7</v>
@@ -17156,13 +17153,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C406" s="3" t="s">
         <v>790</v>
-      </c>
-      <c r="B406" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C406" s="3" t="s">
-        <v>791</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>7</v>
@@ -17170,13 +17167,13 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C407" s="3" t="s">
         <v>793</v>
-      </c>
-      <c r="B407" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C407" s="3" t="s">
-        <v>794</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>7</v>
@@ -17184,13 +17181,13 @@
     </row>
     <row r="408" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C408" s="3" t="s">
         <v>796</v>
-      </c>
-      <c r="B408" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C408" s="3" t="s">
-        <v>797</v>
       </c>
       <c r="D408" s="2" t="s">
         <v>7</v>
@@ -17198,13 +17195,13 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C409" s="3" t="s">
         <v>799</v>
-      </c>
-      <c r="B409" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C409" s="3" t="s">
-        <v>800</v>
       </c>
       <c r="D409" s="2" t="s">
         <v>7</v>
@@ -17218,7 +17215,7 @@
         <v>5</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D410" s="2" t="s">
         <v>20</v>
@@ -17232,7 +17229,7 @@
         <v>5</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D411" s="2" t="s">
         <v>20</v>
@@ -17246,7 +17243,7 @@
         <v>5</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D412" s="2" t="s">
         <v>20</v>
@@ -17260,7 +17257,7 @@
         <v>5</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>20</v>
@@ -17372,7 +17369,7 @@
         <v>5</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D421" s="2" t="s">
         <v>20</v>
@@ -17386,7 +17383,7 @@
         <v>5</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D422" s="2" t="s">
         <v>20</v>
@@ -17394,13 +17391,13 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C423" s="3" t="s">
         <v>818</v>
-      </c>
-      <c r="B423" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C423" s="3" t="s">
-        <v>819</v>
       </c>
       <c r="D423" s="2" t="s">
         <v>20</v>
@@ -17422,13 +17419,13 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C425" s="3" t="s">
         <v>822</v>
-      </c>
-      <c r="B425" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C425" s="3" t="s">
-        <v>823</v>
       </c>
       <c r="D425" s="2" t="s">
         <v>7</v>
@@ -17436,13 +17433,13 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C426" s="3" t="s">
         <v>825</v>
-      </c>
-      <c r="B426" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C426" s="3" t="s">
-        <v>826</v>
       </c>
       <c r="D426" s="2" t="s">
         <v>7</v>
@@ -17450,13 +17447,13 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C427" s="3" t="s">
         <v>828</v>
-      </c>
-      <c r="B427" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C427" s="3" t="s">
-        <v>829</v>
       </c>
       <c r="D427" s="2" t="s">
         <v>7</v>
@@ -17464,13 +17461,13 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C428" s="3" t="s">
         <v>831</v>
-      </c>
-      <c r="B428" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C428" s="3" t="s">
-        <v>832</v>
       </c>
       <c r="D428" s="2" t="s">
         <v>7</v>
@@ -17478,13 +17475,13 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C429" s="3" t="s">
         <v>834</v>
-      </c>
-      <c r="B429" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C429" s="3" t="s">
-        <v>835</v>
       </c>
       <c r="D429" s="2" t="s">
         <v>7</v>
@@ -17492,13 +17489,13 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C430" s="3" t="s">
         <v>837</v>
-      </c>
-      <c r="B430" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C430" s="3" t="s">
-        <v>838</v>
       </c>
       <c r="D430" s="2" t="s">
         <v>7</v>
@@ -17506,13 +17503,13 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C431" s="3" t="s">
         <v>840</v>
-      </c>
-      <c r="B431" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C431" s="3" t="s">
-        <v>841</v>
       </c>
       <c r="D431" s="2" t="s">
         <v>7</v>
@@ -17534,13 +17531,13 @@
     </row>
     <row r="433" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C433" s="3" t="s">
         <v>844</v>
-      </c>
-      <c r="B433" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C433" s="3" t="s">
-        <v>845</v>
       </c>
       <c r="D433" s="2" t="s">
         <v>7</v>
@@ -17562,13 +17559,13 @@
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C435" s="3" t="s">
         <v>848</v>
-      </c>
-      <c r="B435" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C435" s="3" t="s">
-        <v>849</v>
       </c>
       <c r="D435" s="2" t="s">
         <v>7</v>
@@ -17576,13 +17573,13 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C436" s="3" t="s">
         <v>851</v>
-      </c>
-      <c r="B436" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C436" s="3" t="s">
-        <v>852</v>
       </c>
       <c r="D436" s="2" t="s">
         <v>7</v>
@@ -17596,7 +17593,7 @@
         <v>5</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D437" s="2" t="s">
         <v>7</v>
@@ -17604,13 +17601,13 @@
     </row>
     <row r="438" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C438" s="3" t="s">
         <v>856</v>
-      </c>
-      <c r="B438" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C438" s="3" t="s">
-        <v>857</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>7</v>
@@ -17618,13 +17615,13 @@
     </row>
     <row r="439" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C439" s="3" t="s">
         <v>859</v>
-      </c>
-      <c r="B439" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C439" s="3" t="s">
-        <v>860</v>
       </c>
       <c r="D439" s="2" t="s">
         <v>7</v>
@@ -17638,7 +17635,7 @@
         <v>5</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D440" s="2" t="s">
         <v>7</v>
@@ -17646,13 +17643,13 @@
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C441" s="3" t="s">
         <v>863</v>
-      </c>
-      <c r="B441" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C441" s="3" t="s">
-        <v>864</v>
       </c>
       <c r="D441" s="2" t="s">
         <v>7</v>
@@ -17660,13 +17657,13 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C442" s="3" t="s">
         <v>867</v>
-      </c>
-      <c r="B442" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C442" s="3" t="s">
-        <v>868</v>
       </c>
       <c r="D442" s="2" t="s">
         <v>7</v>
@@ -17674,13 +17671,13 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C443" s="3" t="s">
         <v>870</v>
-      </c>
-      <c r="B443" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C443" s="3" t="s">
-        <v>871</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>7</v>
@@ -17688,13 +17685,13 @@
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C444" s="3" t="s">
         <v>873</v>
-      </c>
-      <c r="B444" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C444" s="3" t="s">
-        <v>874</v>
       </c>
       <c r="D444" s="2" t="s">
         <v>7</v>
@@ -17702,13 +17699,13 @@
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C445" s="3" t="s">
         <v>875</v>
-      </c>
-      <c r="B445" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C445" s="3" t="s">
-        <v>876</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>7</v>
@@ -17716,13 +17713,13 @@
     </row>
     <row r="446" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C446" s="3" t="s">
         <v>879</v>
-      </c>
-      <c r="B446" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C446" s="3" t="s">
-        <v>880</v>
       </c>
       <c r="D446" s="2" t="s">
         <v>7</v>
@@ -17730,13 +17727,13 @@
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C447" s="3" t="s">
         <v>770</v>
-      </c>
-      <c r="B447" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C447" s="3" t="s">
-        <v>771</v>
       </c>
       <c r="D447" s="2" t="s">
         <v>7</v>
@@ -17750,7 +17747,7 @@
         <v>5</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D448" s="2" t="s">
         <v>7</v>
@@ -17786,13 +17783,13 @@
     </row>
     <row r="451" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C451" s="3" t="s">
         <v>887</v>
-      </c>
-      <c r="B451" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C451" s="3" t="s">
-        <v>888</v>
       </c>
       <c r="D451" s="2" t="s">
         <v>7</v>
@@ -17800,13 +17797,13 @@
     </row>
     <row r="452" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C452" s="3" t="s">
         <v>890</v>
-      </c>
-      <c r="B452" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C452" s="3" t="s">
-        <v>891</v>
       </c>
       <c r="D452" s="2" t="s">
         <v>7</v>
@@ -17814,13 +17811,13 @@
     </row>
     <row r="453" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C453" s="3" t="s">
         <v>893</v>
-      </c>
-      <c r="B453" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C453" s="3" t="s">
-        <v>894</v>
       </c>
       <c r="D453" s="2" t="s">
         <v>7</v>
@@ -17848,7 +17845,7 @@
         <v>5</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D455" s="2" t="s">
         <v>7</v>
@@ -17988,7 +17985,7 @@
         <v>5</v>
       </c>
       <c r="C465" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D465" s="2" t="s">
         <v>20</v>
@@ -18002,7 +17999,7 @@
         <v>5</v>
       </c>
       <c r="C466" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D466" s="2" t="s">
         <v>20</v>
@@ -18016,7 +18013,7 @@
         <v>5</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D467" s="2" t="s">
         <v>20</v>
@@ -18030,7 +18027,7 @@
         <v>5</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D468" s="2" t="s">
         <v>20</v>
@@ -18268,7 +18265,7 @@
         <v>5</v>
       </c>
       <c r="C485" s="3" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D485" s="2" t="s">
         <v>7</v>
@@ -18282,7 +18279,7 @@
         <v>5</v>
       </c>
       <c r="C486" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D486" s="2" t="s">
         <v>7</v>
@@ -18296,7 +18293,7 @@
         <v>5</v>
       </c>
       <c r="C487" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D487" s="2" t="s">
         <v>7</v>
@@ -18310,7 +18307,7 @@
         <v>5</v>
       </c>
       <c r="C488" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D488" s="2" t="s">
         <v>7</v>
@@ -18352,7 +18349,7 @@
         <v>5</v>
       </c>
       <c r="C491" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D491" s="2" t="s">
         <v>7</v>
@@ -18366,7 +18363,7 @@
         <v>5</v>
       </c>
       <c r="C492" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D492" s="2" t="s">
         <v>7</v>
@@ -18374,13 +18371,13 @@
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A493" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C493" s="3" t="s">
         <v>944</v>
-      </c>
-      <c r="B493" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C493" s="3" t="s">
-        <v>945</v>
       </c>
       <c r="D493" s="2" t="s">
         <v>7</v>
@@ -18388,13 +18385,13 @@
     </row>
     <row r="494" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A494" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C494" s="3" t="s">
         <v>947</v>
-      </c>
-      <c r="B494" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C494" s="3" t="s">
-        <v>948</v>
       </c>
       <c r="D494" s="2" t="s">
         <v>7</v>
@@ -18422,7 +18419,7 @@
         <v>5</v>
       </c>
       <c r="C496" s="3" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="D496" s="2" t="s">
         <v>7</v>
@@ -18430,13 +18427,13 @@
     </row>
     <row r="497" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A497" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C497" s="3" t="s">
         <v>954</v>
-      </c>
-      <c r="B497" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C497" s="3" t="s">
-        <v>955</v>
       </c>
       <c r="D497" s="2" t="s">
         <v>7</v>
@@ -18450,7 +18447,7 @@
         <v>5</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="D498" s="2" t="s">
         <v>7</v>
@@ -18464,7 +18461,7 @@
         <v>5</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D499" s="2" t="s">
         <v>7</v>
@@ -18520,7 +18517,7 @@
         <v>5</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D503" s="2" t="s">
         <v>20</v>
@@ -18534,7 +18531,7 @@
         <v>5</v>
       </c>
       <c r="C504" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D504" s="2" t="s">
         <v>20</v>
@@ -18548,7 +18545,7 @@
         <v>5</v>
       </c>
       <c r="C505" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D505" s="2" t="s">
         <v>20</v>
@@ -18562,7 +18559,7 @@
         <v>5</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D506" s="2" t="s">
         <v>20</v>
@@ -18576,7 +18573,7 @@
         <v>5</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D507" s="2" t="s">
         <v>20</v>
@@ -18584,13 +18581,13 @@
     </row>
     <row r="508" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A508" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C508" s="3" t="s">
         <v>971</v>
-      </c>
-      <c r="B508" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C508" s="3" t="s">
-        <v>972</v>
       </c>
       <c r="D508" s="2" t="s">
         <v>7</v>
@@ -18598,13 +18595,13 @@
     </row>
     <row r="509" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A509" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C509" s="3" t="s">
         <v>954</v>
-      </c>
-      <c r="B509" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C509" s="3" t="s">
-        <v>955</v>
       </c>
       <c r="D509" s="2" t="s">
         <v>7</v>
@@ -18612,13 +18609,13 @@
     </row>
     <row r="510" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A510" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C510" s="3" t="s">
         <v>975</v>
-      </c>
-      <c r="B510" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C510" s="3" t="s">
-        <v>976</v>
       </c>
       <c r="D510" s="2" t="s">
         <v>7</v>
@@ -18632,7 +18629,7 @@
         <v>5</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D511" s="2" t="s">
         <v>7</v>
@@ -18646,7 +18643,7 @@
         <v>5</v>
       </c>
       <c r="C512" s="3" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D512" s="2" t="s">
         <v>20</v>
@@ -18668,13 +18665,13 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A514" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C514" s="3" t="s">
         <v>983</v>
-      </c>
-      <c r="B514" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C514" s="3" t="s">
-        <v>984</v>
       </c>
       <c r="D514" s="2" t="s">
         <v>7</v>
@@ -18682,13 +18679,13 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A515" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C515" s="3" t="s">
         <v>986</v>
-      </c>
-      <c r="B515" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C515" s="3" t="s">
-        <v>987</v>
       </c>
       <c r="D515" s="2" t="s">
         <v>7</v>
@@ -18696,13 +18693,13 @@
     </row>
     <row r="516" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A516" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C516" s="3" t="s">
         <v>989</v>
-      </c>
-      <c r="B516" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C516" s="3" t="s">
-        <v>990</v>
       </c>
       <c r="D516" s="2" t="s">
         <v>7</v>
@@ -18716,7 +18713,7 @@
         <v>5</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D517" s="2" t="s">
         <v>7</v>
@@ -18730,7 +18727,7 @@
         <v>5</v>
       </c>
       <c r="C518" s="3" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D518" s="2" t="s">
         <v>7</v>
@@ -18744,7 +18741,7 @@
         <v>5</v>
       </c>
       <c r="C519" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D519" s="2" t="s">
         <v>7</v>
@@ -18758,7 +18755,7 @@
         <v>5</v>
       </c>
       <c r="C520" s="3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D520" s="2" t="s">
         <v>7</v>
@@ -18772,7 +18769,7 @@
         <v>5</v>
       </c>
       <c r="C521" s="3" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D521" s="2" t="s">
         <v>20</v>
@@ -18786,7 +18783,7 @@
         <v>5</v>
       </c>
       <c r="C522" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D522" s="2" t="s">
         <v>20</v>
@@ -18800,7 +18797,7 @@
         <v>5</v>
       </c>
       <c r="C523" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D523" s="2" t="s">
         <v>20</v>
@@ -18814,7 +18811,7 @@
         <v>5</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D524" s="2" t="s">
         <v>20</v>
@@ -18828,7 +18825,7 @@
         <v>5</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D525" s="2" t="s">
         <v>7</v>
@@ -18842,7 +18839,7 @@
         <v>5</v>
       </c>
       <c r="C526" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="D526" s="2" t="s">
         <v>7</v>
@@ -18856,7 +18853,7 @@
         <v>5</v>
       </c>
       <c r="C527" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D527" s="2" t="s">
         <v>7</v>
@@ -18870,7 +18867,7 @@
         <v>5</v>
       </c>
       <c r="C528" s="3" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D528" s="2" t="s">
         <v>7</v>
@@ -18884,7 +18881,7 @@
         <v>5</v>
       </c>
       <c r="C529" s="3" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D529" s="2" t="s">
         <v>7</v>
@@ -18898,7 +18895,7 @@
         <v>5</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>7</v>
@@ -18912,7 +18909,7 @@
         <v>5</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="D531" s="2" t="s">
         <v>7</v>
@@ -18926,7 +18923,7 @@
         <v>5</v>
       </c>
       <c r="C532" s="3" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D532" s="2" t="s">
         <v>7</v>
@@ -18940,7 +18937,7 @@
         <v>5</v>
       </c>
       <c r="C533" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="D533" s="2" t="s">
         <v>7</v>
@@ -19018,13 +19015,13 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A539" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C539" s="3" t="s">
         <v>1031</v>
-      </c>
-      <c r="B539" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C539" s="3" t="s">
-        <v>1032</v>
       </c>
       <c r="D539" s="2" t="s">
         <v>7</v>
@@ -19038,7 +19035,7 @@
         <v>5</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D540" s="2" t="s">
         <v>20</v>
@@ -19052,7 +19049,7 @@
         <v>5</v>
       </c>
       <c r="C541" s="3" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="D541" s="2" t="s">
         <v>20</v>
@@ -19066,7 +19063,7 @@
         <v>5</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D542" s="2" t="s">
         <v>7</v>
@@ -19080,7 +19077,7 @@
         <v>5</v>
       </c>
       <c r="C543" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D543" s="2" t="s">
         <v>7</v>
@@ -19094,7 +19091,7 @@
         <v>5</v>
       </c>
       <c r="C544" s="3" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D544" s="2" t="s">
         <v>7</v>
@@ -19108,7 +19105,7 @@
         <v>5</v>
       </c>
       <c r="C545" s="3" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D545" s="2" t="s">
         <v>7</v>
@@ -19122,7 +19119,7 @@
         <v>5</v>
       </c>
       <c r="C546" s="3" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="D546" s="2" t="s">
         <v>7</v>
@@ -19136,7 +19133,7 @@
         <v>5</v>
       </c>
       <c r="C547" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D547" s="2" t="s">
         <v>7</v>
@@ -19150,7 +19147,7 @@
         <v>5</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D548" s="2" t="s">
         <v>7</v>
@@ -19164,7 +19161,7 @@
         <v>5</v>
       </c>
       <c r="C549" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D549" s="2" t="s">
         <v>7</v>
@@ -19178,7 +19175,7 @@
         <v>5</v>
       </c>
       <c r="C550" s="3" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="D550" s="2" t="s">
         <v>7</v>
@@ -19192,7 +19189,7 @@
         <v>5</v>
       </c>
       <c r="C551" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D551" s="2" t="s">
         <v>7</v>
@@ -19200,13 +19197,13 @@
     </row>
     <row r="552" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A552" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C552" s="3" t="s">
         <v>1058</v>
-      </c>
-      <c r="B552" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C552" s="3" t="s">
-        <v>1059</v>
       </c>
       <c r="D552" s="2" t="s">
         <v>7</v>
@@ -19220,7 +19217,7 @@
         <v>5</v>
       </c>
       <c r="C553" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D553" s="2" t="s">
         <v>7</v>
@@ -19234,7 +19231,7 @@
         <v>5</v>
       </c>
       <c r="C554" s="3" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="D554" s="2" t="s">
         <v>7</v>
@@ -19242,13 +19239,13 @@
     </row>
     <row r="555" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A555" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C555" s="3" t="s">
         <v>1064</v>
-      </c>
-      <c r="B555" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C555" s="3" t="s">
-        <v>1065</v>
       </c>
       <c r="D555" s="2" t="s">
         <v>7</v>
@@ -19256,13 +19253,13 @@
     </row>
     <row r="556" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A556" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C556" s="3" t="s">
         <v>1068</v>
-      </c>
-      <c r="B556" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C556" s="3" t="s">
-        <v>1069</v>
       </c>
       <c r="D556" s="2" t="s">
         <v>7</v>
@@ -19270,13 +19267,13 @@
     </row>
     <row r="557" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A557" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C557" s="3" t="s">
         <v>1071</v>
-      </c>
-      <c r="B557" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C557" s="3" t="s">
-        <v>1072</v>
       </c>
       <c r="D557" s="2" t="s">
         <v>20</v>
@@ -19290,7 +19287,7 @@
         <v>5</v>
       </c>
       <c r="C558" s="3" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D558" s="2" t="s">
         <v>20</v>
@@ -19304,7 +19301,7 @@
         <v>5</v>
       </c>
       <c r="C559" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="D559" s="2" t="s">
         <v>20</v>
@@ -19318,7 +19315,7 @@
         <v>5</v>
       </c>
       <c r="C560" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="D560" s="2" t="s">
         <v>7</v>
@@ -19332,7 +19329,7 @@
         <v>5</v>
       </c>
       <c r="C561" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="D561" s="2" t="s">
         <v>7</v>
@@ -19346,7 +19343,7 @@
         <v>5</v>
       </c>
       <c r="C562" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D562" s="2" t="s">
         <v>7</v>
@@ -19360,7 +19357,7 @@
         <v>5</v>
       </c>
       <c r="C563" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D563" s="2" t="s">
         <v>7</v>
@@ -19374,7 +19371,7 @@
         <v>5</v>
       </c>
       <c r="C564" s="3" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D564" s="2" t="s">
         <v>7</v>
@@ -19382,13 +19379,13 @@
     </row>
     <row r="565" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A565" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C565" s="3" t="s">
         <v>1088</v>
-      </c>
-      <c r="B565" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C565" s="3" t="s">
-        <v>1089</v>
       </c>
       <c r="D565" s="2" t="s">
         <v>7</v>
@@ -19402,7 +19399,7 @@
         <v>5</v>
       </c>
       <c r="C566" s="3" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="D566" s="2" t="s">
         <v>7</v>
@@ -19416,7 +19413,7 @@
         <v>5</v>
       </c>
       <c r="C567" s="3" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D567" s="2" t="s">
         <v>7</v>
@@ -19430,7 +19427,7 @@
         <v>5</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="D568" s="2" t="s">
         <v>7</v>
@@ -19438,13 +19435,13 @@
     </row>
     <row r="569" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A569" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C569" s="3" t="s">
         <v>1097</v>
-      </c>
-      <c r="B569" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C569" s="3" t="s">
-        <v>1098</v>
       </c>
       <c r="D569" s="2" t="s">
         <v>7</v>
@@ -19458,7 +19455,7 @@
         <v>5</v>
       </c>
       <c r="C570" s="3" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D570" s="2" t="s">
         <v>7</v>
@@ -19472,7 +19469,7 @@
         <v>5</v>
       </c>
       <c r="C571" s="3" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D571" s="2" t="s">
         <v>7</v>
@@ -19486,7 +19483,7 @@
         <v>5</v>
       </c>
       <c r="C572" s="3" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D572" s="2" t="s">
         <v>7</v>
@@ -19500,7 +19497,7 @@
         <v>5</v>
       </c>
       <c r="C573" s="3" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D573" s="2" t="s">
         <v>7</v>
@@ -19508,13 +19505,13 @@
     </row>
     <row r="574" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A574" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B574" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C574" s="3" t="s">
         <v>1107</v>
-      </c>
-      <c r="B574" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C574" s="3" t="s">
-        <v>1108</v>
       </c>
       <c r="D574" s="2" t="s">
         <v>7</v>
@@ -19528,7 +19525,7 @@
         <v>5</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D575" s="2" t="s">
         <v>7</v>
@@ -19542,7 +19539,7 @@
         <v>5</v>
       </c>
       <c r="C576" s="3" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D576" s="2" t="s">
         <v>20</v>
@@ -19556,7 +19553,7 @@
         <v>5</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D577" s="2" t="s">
         <v>20</v>
@@ -19570,7 +19567,7 @@
         <v>5</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D578" s="2" t="s">
         <v>20</v>
@@ -19584,7 +19581,7 @@
         <v>5</v>
       </c>
       <c r="C579" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D579" s="2" t="s">
         <v>7</v>
@@ -19598,7 +19595,7 @@
         <v>5</v>
       </c>
       <c r="C580" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D580" s="2" t="s">
         <v>7</v>
@@ -19612,7 +19609,7 @@
         <v>5</v>
       </c>
       <c r="C581" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D581" s="2" t="s">
         <v>7</v>
@@ -19626,7 +19623,7 @@
         <v>5</v>
       </c>
       <c r="C582" s="3" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D582" s="2" t="s">
         <v>7</v>
@@ -19634,13 +19631,13 @@
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A583" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B583" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C583" s="3" t="s">
         <v>1127</v>
-      </c>
-      <c r="B583" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C583" s="3" t="s">
-        <v>1128</v>
       </c>
       <c r="D583" s="2" t="s">
         <v>7</v>
@@ -19648,13 +19645,13 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A584" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B584" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C584" s="3" t="s">
         <v>1130</v>
-      </c>
-      <c r="B584" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C584" s="3" t="s">
-        <v>1131</v>
       </c>
       <c r="D584" s="2" t="s">
         <v>7</v>
@@ -19668,7 +19665,7 @@
         <v>5</v>
       </c>
       <c r="C585" s="3" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D585" s="2" t="s">
         <v>7</v>
@@ -19682,7 +19679,7 @@
         <v>5</v>
       </c>
       <c r="C586" s="3" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D586" s="2" t="s">
         <v>7</v>
@@ -19696,7 +19693,7 @@
         <v>5</v>
       </c>
       <c r="C587" s="3" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D587" s="2" t="s">
         <v>7</v>
@@ -19710,7 +19707,7 @@
         <v>5</v>
       </c>
       <c r="C588" s="3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D588" s="2" t="s">
         <v>7</v>
@@ -19718,13 +19715,13 @@
     </row>
     <row r="589" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A589" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C589" s="3" t="s">
         <v>1141</v>
-      </c>
-      <c r="B589" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C589" s="3" t="s">
-        <v>1142</v>
       </c>
       <c r="D589" s="2" t="s">
         <v>7</v>
@@ -19732,13 +19729,13 @@
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A590" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C590" s="3" t="s">
         <v>1144</v>
-      </c>
-      <c r="B590" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C590" s="3" t="s">
-        <v>1145</v>
       </c>
       <c r="D590" s="2" t="s">
         <v>7</v>
@@ -19752,7 +19749,7 @@
         <v>5</v>
       </c>
       <c r="C591" s="3" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D591" s="2" t="s">
         <v>7</v>
@@ -19766,7 +19763,7 @@
         <v>68</v>
       </c>
       <c r="C592" s="3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D592" s="2" t="s">
         <v>7</v>
@@ -19780,7 +19777,7 @@
         <v>5</v>
       </c>
       <c r="C593" s="3" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D593" s="2" t="s">
         <v>7</v>
@@ -19794,7 +19791,7 @@
         <v>5</v>
       </c>
       <c r="C594" s="3" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D594" s="2" t="s">
         <v>7</v>
@@ -19808,7 +19805,7 @@
         <v>5</v>
       </c>
       <c r="C595" s="3" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D595" s="2" t="s">
         <v>7</v>
@@ -19822,7 +19819,7 @@
         <v>5</v>
       </c>
       <c r="C596" s="3" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D596" s="2" t="s">
         <v>7</v>
@@ -19836,7 +19833,7 @@
         <v>5</v>
       </c>
       <c r="C597" s="3" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D597" s="2" t="s">
         <v>7</v>
@@ -19850,7 +19847,7 @@
         <v>5</v>
       </c>
       <c r="C598" s="3" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="D598" s="2" t="s">
         <v>7</v>
@@ -19864,7 +19861,7 @@
         <v>5</v>
       </c>
       <c r="C599" s="3" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D599" s="2" t="s">
         <v>20</v>
@@ -19878,7 +19875,7 @@
         <v>5</v>
       </c>
       <c r="C600" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D600" s="2" t="s">
         <v>20</v>
@@ -19892,7 +19889,7 @@
         <v>5</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D601" s="2" t="s">
         <v>7</v>
@@ -19906,7 +19903,7 @@
         <v>5</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D602" s="2" t="s">
         <v>7</v>
@@ -19914,13 +19911,13 @@
     </row>
     <row r="603" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A603" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C603" s="3" t="s">
         <v>1170</v>
-      </c>
-      <c r="B603" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C603" s="3" t="s">
-        <v>1171</v>
       </c>
       <c r="D603" s="2" t="s">
         <v>7</v>
@@ -19934,7 +19931,7 @@
         <v>5</v>
       </c>
       <c r="C604" s="3" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D604" s="2" t="s">
         <v>7</v>
@@ -19942,13 +19939,13 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A605" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C605" s="3" t="s">
         <v>1174</v>
-      </c>
-      <c r="B605" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C605" s="3" t="s">
-        <v>1175</v>
       </c>
       <c r="D605" s="2" t="s">
         <v>7</v>
@@ -19956,13 +19953,13 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A606" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C606" s="3" t="s">
         <v>1178</v>
-      </c>
-      <c r="B606" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C606" s="3" t="s">
-        <v>1179</v>
       </c>
       <c r="D606" s="2" t="s">
         <v>7</v>
@@ -19970,13 +19967,13 @@
     </row>
     <row r="607" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A607" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C607" s="3" t="s">
         <v>1181</v>
-      </c>
-      <c r="B607" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C607" s="3" t="s">
-        <v>1182</v>
       </c>
       <c r="D607" s="2" t="s">
         <v>7</v>
@@ -19984,13 +19981,13 @@
     </row>
     <row r="608" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A608" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C608" s="3" t="s">
         <v>1184</v>
-      </c>
-      <c r="B608" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C608" s="3" t="s">
-        <v>1185</v>
       </c>
       <c r="D608" s="2" t="s">
         <v>7</v>
@@ -19998,13 +19995,13 @@
     </row>
     <row r="609" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A609" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C609" s="3" t="s">
         <v>1190</v>
-      </c>
-      <c r="B609" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C609" s="3" t="s">
-        <v>1191</v>
       </c>
       <c r="D609" s="2" t="s">
         <v>7</v>
@@ -20012,13 +20009,13 @@
     </row>
     <row r="610" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A610" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C610" s="3" t="s">
         <v>1190</v>
-      </c>
-      <c r="B610" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C610" s="3" t="s">
-        <v>1191</v>
       </c>
       <c r="D610" s="2" t="s">
         <v>7</v>
@@ -20026,13 +20023,13 @@
     </row>
     <row r="611" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A611" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C611" s="3" t="s">
         <v>1190</v>
-      </c>
-      <c r="B611" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C611" s="3" t="s">
-        <v>1191</v>
       </c>
       <c r="D611" s="2" t="s">
         <v>7</v>
@@ -20040,13 +20037,13 @@
     </row>
     <row r="612" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A612" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C612" s="3" t="s">
         <v>1190</v>
-      </c>
-      <c r="B612" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C612" s="3" t="s">
-        <v>1191</v>
       </c>
       <c r="D612" s="2" t="s">
         <v>7</v>
@@ -20054,13 +20051,13 @@
     </row>
     <row r="613" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A613" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C613" s="3" t="s">
         <v>1197</v>
-      </c>
-      <c r="B613" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C613" s="3" t="s">
-        <v>1198</v>
       </c>
       <c r="D613" s="2" t="s">
         <v>7</v>
@@ -20068,13 +20065,13 @@
     </row>
     <row r="614" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A614" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C614" s="3" t="s">
         <v>1197</v>
-      </c>
-      <c r="B614" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C614" s="3" t="s">
-        <v>1198</v>
       </c>
       <c r="D614" s="2" t="s">
         <v>7</v>
@@ -20082,13 +20079,13 @@
     </row>
     <row r="615" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A615" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C615" s="3" t="s">
         <v>1197</v>
-      </c>
-      <c r="B615" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C615" s="3" t="s">
-        <v>1198</v>
       </c>
       <c r="D615" s="2" t="s">
         <v>7</v>
@@ -20096,13 +20093,13 @@
     </row>
     <row r="616" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A616" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C616" s="3" t="s">
         <v>1197</v>
-      </c>
-      <c r="B616" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C616" s="3" t="s">
-        <v>1198</v>
       </c>
       <c r="D616" s="2" t="s">
         <v>7</v>
@@ -20110,13 +20107,13 @@
     </row>
     <row r="617" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A617" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C617" s="3" t="s">
         <v>1197</v>
-      </c>
-      <c r="B617" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C617" s="3" t="s">
-        <v>1198</v>
       </c>
       <c r="D617" s="2" t="s">
         <v>7</v>
@@ -20130,7 +20127,7 @@
         <v>5</v>
       </c>
       <c r="C618" s="3" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D618" s="2" t="s">
         <v>7</v>
@@ -20144,7 +20141,7 @@
         <v>5</v>
       </c>
       <c r="C619" s="3" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="D619" s="2" t="s">
         <v>7</v>
@@ -20158,7 +20155,7 @@
         <v>5</v>
       </c>
       <c r="C620" s="3" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D620" s="2" t="s">
         <v>7</v>
@@ -20172,7 +20169,7 @@
         <v>5</v>
       </c>
       <c r="C621" s="3" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D621" s="2" t="s">
         <v>7</v>
@@ -20186,7 +20183,7 @@
         <v>5</v>
       </c>
       <c r="C622" s="3" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D622" s="2" t="s">
         <v>7</v>
@@ -20200,7 +20197,7 @@
         <v>5</v>
       </c>
       <c r="C623" s="3" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D623" s="2" t="s">
         <v>7</v>
@@ -20208,13 +20205,13 @@
     </row>
     <row r="624" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A624" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C624" s="3" t="s">
         <v>1211</v>
-      </c>
-      <c r="B624" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C624" s="3" t="s">
-        <v>1212</v>
       </c>
       <c r="D624" s="2" t="s">
         <v>7</v>
@@ -20228,7 +20225,7 @@
         <v>5</v>
       </c>
       <c r="C625" s="3" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D625" s="2" t="s">
         <v>7</v>
@@ -20242,7 +20239,7 @@
         <v>5</v>
       </c>
       <c r="C626" s="3" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D626" s="2" t="s">
         <v>7</v>
@@ -20256,7 +20253,7 @@
         <v>5</v>
       </c>
       <c r="C627" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D627" s="2" t="s">
         <v>7</v>
@@ -20264,13 +20261,13 @@
     </row>
     <row r="628" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A628" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B628" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C628" s="3" t="s">
         <v>1220</v>
-      </c>
-      <c r="B628" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C628" s="3" t="s">
-        <v>1221</v>
       </c>
       <c r="D628" s="2" t="s">
         <v>7</v>
@@ -20278,13 +20275,13 @@
     </row>
     <row r="629" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A629" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C629" s="3" t="s">
         <v>1197</v>
-      </c>
-      <c r="B629" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C629" s="3" t="s">
-        <v>1198</v>
       </c>
       <c r="D629" s="2" t="s">
         <v>7</v>
@@ -20292,13 +20289,13 @@
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A630" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C630" s="3" t="s">
         <v>1225</v>
-      </c>
-      <c r="B630" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C630" s="3" t="s">
-        <v>1226</v>
       </c>
       <c r="D630" s="2" t="s">
         <v>7</v>
@@ -20312,7 +20309,7 @@
         <v>5</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D631" s="2" t="s">
         <v>7</v>
@@ -20320,13 +20317,13 @@
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A632" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C632" s="3" t="s">
         <v>1230</v>
-      </c>
-      <c r="B632" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C632" s="3" t="s">
-        <v>1231</v>
       </c>
       <c r="D632" s="2" t="s">
         <v>7</v>
@@ -20340,7 +20337,7 @@
         <v>5</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="D633" s="2" t="s">
         <v>7</v>
@@ -20354,7 +20351,7 @@
         <v>5</v>
       </c>
       <c r="C634" s="3" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="D634" s="2" t="s">
         <v>7</v>
@@ -20368,7 +20365,7 @@
         <v>5</v>
       </c>
       <c r="C635" s="3" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="D635" s="2" t="s">
         <v>7</v>
@@ -20376,13 +20373,13 @@
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A636" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B636" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C636" s="3" t="s">
         <v>1239</v>
-      </c>
-      <c r="B636" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C636" s="3" t="s">
-        <v>1240</v>
       </c>
       <c r="D636" s="2" t="s">
         <v>7</v>
@@ -20396,7 +20393,7 @@
         <v>5</v>
       </c>
       <c r="C637" s="3" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D637" s="2" t="s">
         <v>7</v>
@@ -20410,7 +20407,7 @@
         <v>5</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D638" s="2" t="s">
         <v>7</v>
@@ -20424,7 +20421,7 @@
         <v>5</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D639" s="2" t="s">
         <v>7</v>
@@ -20432,13 +20429,13 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A640" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B640" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C640" s="3" t="s">
         <v>1247</v>
-      </c>
-      <c r="B640" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C640" s="3" t="s">
-        <v>1248</v>
       </c>
       <c r="D640" s="2" t="s">
         <v>7</v>
@@ -20446,13 +20443,13 @@
     </row>
     <row r="641" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A641" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C641" s="3" t="s">
         <v>1250</v>
-      </c>
-      <c r="B641" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C641" s="3" t="s">
-        <v>1251</v>
       </c>
       <c r="D641" s="2" t="s">
         <v>7</v>
@@ -20460,13 +20457,13 @@
     </row>
     <row r="642" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A642" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B642" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C642" s="3" t="s">
         <v>1253</v>
-      </c>
-      <c r="B642" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C642" s="3" t="s">
-        <v>1254</v>
       </c>
       <c r="D642" s="2" t="s">
         <v>7</v>
@@ -20480,7 +20477,7 @@
         <v>5</v>
       </c>
       <c r="C643" s="3" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="D643" s="2" t="s">
         <v>7</v>
@@ -20488,13 +20485,13 @@
     </row>
     <row r="644" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A644" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B644" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C644" s="3" t="s">
         <v>1257</v>
-      </c>
-      <c r="B644" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C644" s="3" t="s">
-        <v>1258</v>
       </c>
       <c r="D644" s="2" t="s">
         <v>7</v>
@@ -20508,7 +20505,7 @@
         <v>5</v>
       </c>
       <c r="C645" s="3" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D645" s="2" t="s">
         <v>20</v>
@@ -20522,7 +20519,7 @@
         <v>5</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D646" s="2" t="s">
         <v>20</v>
@@ -20536,7 +20533,7 @@
         <v>5</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D647" s="2" t="s">
         <v>7</v>
@@ -20550,7 +20547,7 @@
         <v>5</v>
       </c>
       <c r="C648" s="3" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D648" s="2" t="s">
         <v>7</v>
@@ -20558,13 +20555,13 @@
     </row>
     <row r="649" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A649" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B649" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C649" s="3" t="s">
         <v>1268</v>
-      </c>
-      <c r="B649" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C649" s="3" t="s">
-        <v>1269</v>
       </c>
       <c r="D649" s="2" t="s">
         <v>7</v>
@@ -20578,7 +20575,7 @@
         <v>5</v>
       </c>
       <c r="C650" s="3" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D650" s="2" t="s">
         <v>7</v>
@@ -20592,7 +20589,7 @@
         <v>5</v>
       </c>
       <c r="C651" s="3" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="D651" s="2" t="s">
         <v>7</v>
@@ -20606,7 +20603,7 @@
         <v>5</v>
       </c>
       <c r="C652" s="3" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D652" s="2" t="s">
         <v>7</v>
@@ -20620,7 +20617,7 @@
         <v>5</v>
       </c>
       <c r="C653" s="3" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D653" s="2" t="s">
         <v>7</v>
@@ -20634,7 +20631,7 @@
         <v>5</v>
       </c>
       <c r="C654" s="3" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="D654" s="2" t="s">
         <v>7</v>
@@ -20648,7 +20645,7 @@
         <v>5</v>
       </c>
       <c r="C655" s="3" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D655" s="2" t="s">
         <v>7</v>
@@ -20662,7 +20659,7 @@
         <v>5</v>
       </c>
       <c r="C656" s="3" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D656" s="2" t="s">
         <v>7</v>
@@ -20676,7 +20673,7 @@
         <v>5</v>
       </c>
       <c r="C657" s="3" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D657" s="2" t="s">
         <v>7</v>
@@ -20690,7 +20687,7 @@
         <v>5</v>
       </c>
       <c r="C658" s="3" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="D658" s="2" t="s">
         <v>7</v>
@@ -20704,7 +20701,7 @@
         <v>5</v>
       </c>
       <c r="C659" s="3" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D659" s="2" t="s">
         <v>7</v>
@@ -20712,13 +20709,13 @@
     </row>
     <row r="660" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A660" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B660" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C660" s="3" t="s">
         <v>1289</v>
-      </c>
-      <c r="B660" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C660" s="3" t="s">
-        <v>1290</v>
       </c>
       <c r="D660" s="2" t="s">
         <v>20</v>
@@ -20726,13 +20723,13 @@
     </row>
     <row r="661" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A661" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C661" s="3" t="s">
         <v>1293</v>
-      </c>
-      <c r="B661" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C661" s="3" t="s">
-        <v>1294</v>
       </c>
       <c r="D661" s="2" t="s">
         <v>20</v>
@@ -20746,7 +20743,7 @@
         <v>5</v>
       </c>
       <c r="C662" s="3" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D662" s="2" t="s">
         <v>20</v>
@@ -20760,7 +20757,7 @@
         <v>5</v>
       </c>
       <c r="C663" s="3" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D663" s="2" t="s">
         <v>20</v>
@@ -20768,13 +20765,13 @@
     </row>
     <row r="664" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A664" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C664" s="3" t="s">
         <v>1299</v>
-      </c>
-      <c r="B664" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C664" s="3" t="s">
-        <v>1300</v>
       </c>
       <c r="D664" s="2" t="s">
         <v>20</v>
@@ -20788,7 +20785,7 @@
         <v>5</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D665" s="2" t="s">
         <v>20</v>
@@ -20802,7 +20799,7 @@
         <v>5</v>
       </c>
       <c r="C666" s="3" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D666" s="2" t="s">
         <v>20</v>
@@ -20816,7 +20813,7 @@
         <v>5</v>
       </c>
       <c r="C667" s="3" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D667" s="2" t="s">
         <v>7</v>
@@ -20824,13 +20821,13 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A668" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B668" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C668" s="3" t="s">
         <v>1308</v>
-      </c>
-      <c r="B668" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C668" s="3" t="s">
-        <v>1309</v>
       </c>
       <c r="D668" s="2" t="s">
         <v>7</v>
@@ -20844,7 +20841,7 @@
         <v>5</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="D669" s="2" t="s">
         <v>7</v>
@@ -20852,13 +20849,13 @@
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A670" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B670" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C670" s="3" t="s">
         <v>1314</v>
-      </c>
-      <c r="B670" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C670" s="3" t="s">
-        <v>1315</v>
       </c>
       <c r="D670" s="2" t="s">
         <v>7</v>
@@ -20866,13 +20863,13 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A671" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B671" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C671" s="3" t="s">
         <v>1317</v>
-      </c>
-      <c r="B671" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C671" s="3" t="s">
-        <v>1318</v>
       </c>
       <c r="D671" s="2" t="s">
         <v>7</v>
@@ -20880,13 +20877,13 @@
     </row>
     <row r="672" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A672" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C672" s="3" t="s">
         <v>1320</v>
-      </c>
-      <c r="B672" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C672" s="3" t="s">
-        <v>1321</v>
       </c>
       <c r="D672" s="2" t="s">
         <v>7</v>
@@ -20894,13 +20891,13 @@
     </row>
     <row r="673" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A673" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C673" s="3" t="s">
         <v>1323</v>
-      </c>
-      <c r="B673" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C673" s="3" t="s">
-        <v>1324</v>
       </c>
       <c r="D673" s="2" t="s">
         <v>7</v>
@@ -20908,13 +20905,13 @@
     </row>
     <row r="674" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A674" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B674" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C674" s="3" t="s">
         <v>1326</v>
-      </c>
-      <c r="B674" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C674" s="3" t="s">
-        <v>1327</v>
       </c>
       <c r="D674" s="2" t="s">
         <v>7</v>
@@ -20922,13 +20919,13 @@
     </row>
     <row r="675" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A675" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C675" s="3" t="s">
         <v>1329</v>
-      </c>
-      <c r="B675" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C675" s="3" t="s">
-        <v>1330</v>
       </c>
       <c r="D675" s="2" t="s">
         <v>7</v>
@@ -20936,13 +20933,13 @@
     </row>
     <row r="676" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A676" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B676" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C676" s="3" t="s">
         <v>1332</v>
-      </c>
-      <c r="B676" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C676" s="3" t="s">
-        <v>1333</v>
       </c>
       <c r="D676" s="2" t="s">
         <v>7</v>
@@ -20950,13 +20947,13 @@
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A677" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C677" s="3" t="s">
         <v>1335</v>
-      </c>
-      <c r="B677" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C677" s="3" t="s">
-        <v>1336</v>
       </c>
       <c r="D677" s="2" t="s">
         <v>20</v>
@@ -20964,13 +20961,13 @@
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A678" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C678" s="3" t="s">
         <v>1338</v>
-      </c>
-      <c r="B678" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C678" s="3" t="s">
-        <v>1339</v>
       </c>
       <c r="D678" s="2" t="s">
         <v>20</v>
@@ -20978,13 +20975,13 @@
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A679" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B679" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C679" s="3" t="s">
         <v>1341</v>
-      </c>
-      <c r="B679" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C679" s="3" t="s">
-        <v>1342</v>
       </c>
       <c r="D679" s="2" t="s">
         <v>20</v>
@@ -20992,13 +20989,13 @@
     </row>
     <row r="680" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A680" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B680" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C680" s="3" t="s">
         <v>1357</v>
-      </c>
-      <c r="B680" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C680" s="3" t="s">
-        <v>1358</v>
       </c>
       <c r="D680" s="2" t="s">
         <v>20</v>
@@ -21006,13 +21003,13 @@
     </row>
     <row r="681" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A681" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B681" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C681" s="3" t="s">
         <v>1359</v>
-      </c>
-      <c r="B681" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C681" s="3" t="s">
-        <v>1360</v>
       </c>
       <c r="D681" s="2" t="s">
         <v>7</v>
@@ -21020,13 +21017,13 @@
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A682" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B682" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C682" s="3" t="s">
         <v>1361</v>
-      </c>
-      <c r="B682" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C682" s="3" t="s">
-        <v>1362</v>
       </c>
       <c r="D682" s="2" t="s">
         <v>7</v>
@@ -21034,13 +21031,13 @@
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A683" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B683" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C683" s="3" t="s">
         <v>1363</v>
-      </c>
-      <c r="B683" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C683" s="3" t="s">
-        <v>1364</v>
       </c>
       <c r="D683" s="2" t="s">
         <v>7</v>
@@ -21048,13 +21045,13 @@
     </row>
     <row r="684" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A684" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B684" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C684" s="3" t="s">
         <v>1365</v>
-      </c>
-      <c r="B684" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C684" s="3" t="s">
-        <v>1366</v>
       </c>
       <c r="D684" s="2" t="s">
         <v>7</v>
@@ -21062,27 +21059,27 @@
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A685" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C685" s="3" t="s">
         <v>1367</v>
       </c>
-      <c r="B685" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C685" s="3" t="s">
-        <v>1368</v>
-      </c>
       <c r="D685" s="2" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="686" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A686" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C686" s="3" t="s">
         <v>1369</v>
-      </c>
-      <c r="B686" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C686" s="3" t="s">
-        <v>1370</v>
       </c>
       <c r="D686" s="2" t="s">
         <v>7</v>
@@ -21090,13 +21087,13 @@
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A687" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C687" s="3" t="s">
         <v>1372</v>
-      </c>
-      <c r="B687" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C687" s="3" t="s">
-        <v>1373</v>
       </c>
       <c r="D687" s="2" t="s">
         <v>7</v>
@@ -21104,13 +21101,13 @@
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A688" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C688" s="3" t="s">
         <v>1374</v>
-      </c>
-      <c r="B688" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C688" s="3" t="s">
-        <v>1375</v>
       </c>
       <c r="D688" s="2" t="s">
         <v>7</v>
@@ -21118,13 +21115,13 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A689" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B689" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C689" s="3" t="s">
         <v>1376</v>
-      </c>
-      <c r="B689" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C689" s="3" t="s">
-        <v>1377</v>
       </c>
       <c r="D689" s="2" t="s">
         <v>7</v>
@@ -21132,13 +21129,13 @@
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A690" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B690" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C690" s="3" t="s">
         <v>1378</v>
-      </c>
-      <c r="B690" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C690" s="3" t="s">
-        <v>1379</v>
       </c>
       <c r="D690" s="2" t="s">
         <v>7</v>
@@ -21146,13 +21143,13 @@
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A691" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C691" s="3" t="s">
         <v>1380</v>
-      </c>
-      <c r="B691" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C691" s="3" t="s">
-        <v>1381</v>
       </c>
       <c r="D691" s="2" t="s">
         <v>7</v>
@@ -21160,13 +21157,13 @@
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A692" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C692" s="3" t="s">
         <v>1382</v>
-      </c>
-      <c r="B692" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C692" s="3" t="s">
-        <v>1383</v>
       </c>
       <c r="D692" s="2" t="s">
         <v>7</v>
@@ -21174,13 +21171,13 @@
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A693" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C693" s="3" t="s">
         <v>1384</v>
-      </c>
-      <c r="B693" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C693" s="3" t="s">
-        <v>1385</v>
       </c>
       <c r="D693" s="2" t="s">
         <v>7</v>
@@ -21188,13 +21185,13 @@
     </row>
     <row r="694" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A694" s="2" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="B694" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C694" s="3" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="D694" s="2" t="s">
         <v>20</v>
@@ -21202,13 +21199,13 @@
     </row>
     <row r="695" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A695" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C695" s="3" t="s">
         <v>1390</v>
-      </c>
-      <c r="B695" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C695" s="3" t="s">
-        <v>1391</v>
       </c>
       <c r="D695" s="2" t="s">
         <v>20</v>
@@ -21216,13 +21213,13 @@
     </row>
     <row r="696" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A696" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C696" s="3" t="s">
         <v>1393</v>
-      </c>
-      <c r="B696" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C696" s="3" t="s">
-        <v>1394</v>
       </c>
       <c r="D696" s="2" t="s">
         <v>20</v>
@@ -21230,13 +21227,13 @@
     </row>
     <row r="697" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A697" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B697" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C697" s="3" t="s">
         <v>1396</v>
-      </c>
-      <c r="B697" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C697" s="3" t="s">
-        <v>1397</v>
       </c>
       <c r="D697" s="2" t="s">
         <v>20</v>
@@ -21244,13 +21241,13 @@
     </row>
     <row r="698" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A698" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C698" s="3" t="s">
         <v>1399</v>
-      </c>
-      <c r="B698" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C698" s="3" t="s">
-        <v>1400</v>
       </c>
       <c r="D698" s="2" t="s">
         <v>20</v>
@@ -21258,13 +21255,13 @@
     </row>
     <row r="699" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A699" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C699" s="3" t="s">
         <v>1402</v>
-      </c>
-      <c r="B699" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C699" s="3" t="s">
-        <v>1403</v>
       </c>
       <c r="D699" s="2" t="s">
         <v>20</v>
@@ -21272,13 +21269,13 @@
     </row>
     <row r="700" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A700" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B700" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C700" s="3" t="s">
         <v>1405</v>
-      </c>
-      <c r="B700" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C700" s="3" t="s">
-        <v>1406</v>
       </c>
       <c r="D700" s="2" t="s">
         <v>20</v>
@@ -21286,13 +21283,13 @@
     </row>
     <row r="701" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A701" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C701" s="3" t="s">
         <v>1408</v>
-      </c>
-      <c r="B701" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C701" s="3" t="s">
-        <v>1409</v>
       </c>
       <c r="D701" s="2" t="s">
         <v>7</v>
@@ -21300,13 +21297,13 @@
     </row>
     <row r="702" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A702" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C702" s="3" t="s">
         <v>1411</v>
-      </c>
-      <c r="B702" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C702" s="3" t="s">
-        <v>1412</v>
       </c>
       <c r="D702" s="2" t="s">
         <v>7</v>
@@ -21314,13 +21311,13 @@
     </row>
     <row r="703" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A703" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C703" s="3" t="s">
         <v>1414</v>
-      </c>
-      <c r="B703" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C703" s="3" t="s">
-        <v>1415</v>
       </c>
       <c r="D703" s="2" t="s">
         <v>7</v>
@@ -21328,13 +21325,13 @@
     </row>
     <row r="704" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A704" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C704" s="3" t="s">
         <v>1417</v>
-      </c>
-      <c r="B704" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C704" s="3" t="s">
-        <v>1418</v>
       </c>
       <c r="D704" s="2" t="s">
         <v>7</v>
@@ -21342,13 +21339,13 @@
     </row>
     <row r="705" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A705" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C705" s="3" t="s">
         <v>1420</v>
-      </c>
-      <c r="B705" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C705" s="3" t="s">
-        <v>1421</v>
       </c>
       <c r="D705" s="2" t="s">
         <v>7</v>
@@ -21356,13 +21353,13 @@
     </row>
     <row r="706" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A706" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C706" s="3" t="s">
         <v>1422</v>
-      </c>
-      <c r="B706" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C706" s="3" t="s">
-        <v>1423</v>
       </c>
       <c r="D706" s="2" t="s">
         <v>7</v>
@@ -21370,13 +21367,13 @@
     </row>
     <row r="707" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A707" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B707" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C707" s="3" t="s">
         <v>1426</v>
-      </c>
-      <c r="B707" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C707" s="3" t="s">
-        <v>1427</v>
       </c>
       <c r="D707" s="2" t="s">
         <v>7</v>
@@ -21384,13 +21381,13 @@
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A708" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C708" s="3" t="s">
         <v>1429</v>
-      </c>
-      <c r="B708" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C708" s="3" t="s">
-        <v>1430</v>
       </c>
       <c r="D708" s="2" t="s">
         <v>7</v>
@@ -21398,13 +21395,13 @@
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A709" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C709" s="3" t="s">
         <v>1432</v>
-      </c>
-      <c r="B709" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C709" s="3" t="s">
-        <v>1433</v>
       </c>
       <c r="D709" s="2" t="s">
         <v>7</v>
@@ -21412,13 +21409,13 @@
     </row>
     <row r="710" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A710" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B710" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C710" s="3" t="s">
         <v>1435</v>
-      </c>
-      <c r="B710" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C710" s="3" t="s">
-        <v>1436</v>
       </c>
       <c r="D710" s="2" t="s">
         <v>7</v>
@@ -21426,13 +21423,13 @@
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A711" s="2" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B711" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C711" s="3" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="D711" s="2" t="s">
         <v>7</v>
@@ -21440,13 +21437,13 @@
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A712" s="2" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B712" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C712" s="3" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D712" s="2" t="s">
         <v>7</v>
@@ -21454,13 +21451,13 @@
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A713" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C713" s="3" t="s">
         <v>1444</v>
-      </c>
-      <c r="B713" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C713" s="3" t="s">
-        <v>1445</v>
       </c>
       <c r="D713" s="2" t="s">
         <v>7</v>
@@ -21468,13 +21465,13 @@
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A714" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B714" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C714" s="3" t="s">
         <v>1448</v>
-      </c>
-      <c r="B714" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C714" s="3" t="s">
-        <v>1449</v>
       </c>
       <c r="D714" s="2" t="s">
         <v>7</v>
@@ -21482,13 +21479,13 @@
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A715" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B715" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C715" s="3" t="s">
         <v>1450</v>
-      </c>
-      <c r="B715" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C715" s="3" t="s">
-        <v>1451</v>
       </c>
       <c r="D715" s="2" t="s">
         <v>7</v>
@@ -21496,13 +21493,13 @@
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A716" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B716" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C716" s="3" t="s">
         <v>1453</v>
-      </c>
-      <c r="B716" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C716" s="3" t="s">
-        <v>1454</v>
       </c>
       <c r="D716" s="2" t="s">
         <v>7</v>
@@ -21510,13 +21507,13 @@
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A717" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C717" s="3" t="s">
         <v>1456</v>
-      </c>
-      <c r="B717" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C717" s="3" t="s">
-        <v>1457</v>
       </c>
       <c r="D717" s="2" t="s">
         <v>7</v>
@@ -21524,13 +21521,13 @@
     </row>
     <row r="718" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A718" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B718" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C718" s="3" t="s">
         <v>1459</v>
-      </c>
-      <c r="B718" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C718" s="3" t="s">
-        <v>1460</v>
       </c>
       <c r="D718" s="2" t="s">
         <v>7</v>
@@ -21544,7 +21541,7 @@
         <v>5</v>
       </c>
       <c r="C719" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="D719" s="2" t="s">
         <v>7</v>
@@ -21558,7 +21555,7 @@
         <v>5</v>
       </c>
       <c r="C720" s="3" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="D720" s="2" t="s">
         <v>7</v>
@@ -21572,7 +21569,7 @@
         <v>5</v>
       </c>
       <c r="C721" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="D721" s="2" t="s">
         <v>7</v>
@@ -21586,7 +21583,7 @@
         <v>5</v>
       </c>
       <c r="C722" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="D722" s="2" t="s">
         <v>7</v>
@@ -21600,7 +21597,7 @@
         <v>5</v>
       </c>
       <c r="C723" s="3" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="D723" s="2" t="s">
         <v>7</v>
@@ -21614,7 +21611,7 @@
         <v>5</v>
       </c>
       <c r="C724" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="D724" s="2" t="s">
         <v>7</v>
@@ -21628,7 +21625,7 @@
         <v>5</v>
       </c>
       <c r="C725" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="D725" s="2" t="s">
         <v>7</v>
@@ -21642,7 +21639,7 @@
         <v>5</v>
       </c>
       <c r="C726" s="3" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="D726" s="2" t="s">
         <v>7</v>
@@ -21656,7 +21653,7 @@
         <v>5</v>
       </c>
       <c r="C727" s="3" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="D727" s="2" t="s">
         <v>7</v>
@@ -21670,7 +21667,7 @@
         <v>5</v>
       </c>
       <c r="C728" s="3" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="D728" s="2" t="s">
         <v>7</v>
@@ -21684,7 +21681,7 @@
         <v>5</v>
       </c>
       <c r="C729" s="3" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="D729" s="2" t="s">
         <v>7</v>
@@ -21698,7 +21695,7 @@
         <v>5</v>
       </c>
       <c r="C730" s="3" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D730" s="2" t="s">
         <v>7</v>
@@ -21712,7 +21709,7 @@
         <v>5</v>
       </c>
       <c r="C731" s="3" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="D731" s="2" t="s">
         <v>7</v>
@@ -21726,7 +21723,7 @@
         <v>5</v>
       </c>
       <c r="C732" s="3" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D732" s="2" t="s">
         <v>7</v>
@@ -21740,7 +21737,7 @@
         <v>5</v>
       </c>
       <c r="C733" s="3" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D733" s="2" t="s">
         <v>7</v>
@@ -21754,7 +21751,7 @@
         <v>5</v>
       </c>
       <c r="C734" s="3" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D734" s="2" t="s">
         <v>7</v>
@@ -21768,7 +21765,7 @@
         <v>5</v>
       </c>
       <c r="C735" s="3" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D735" s="2" t="s">
         <v>7</v>
@@ -21782,7 +21779,7 @@
         <v>5</v>
       </c>
       <c r="C736" s="3" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D736" s="2" t="s">
         <v>7</v>
@@ -21796,7 +21793,7 @@
         <v>5</v>
       </c>
       <c r="C737" s="3" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D737" s="2" t="s">
         <v>7</v>
@@ -21810,7 +21807,7 @@
         <v>5</v>
       </c>
       <c r="C738" s="3" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D738" s="2" t="s">
         <v>7</v>
@@ -21824,7 +21821,7 @@
         <v>5</v>
       </c>
       <c r="C739" s="3" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D739" s="2" t="s">
         <v>7</v>
@@ -21838,7 +21835,7 @@
         <v>5</v>
       </c>
       <c r="C740" s="3" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D740" s="2" t="s">
         <v>7</v>
@@ -21852,7 +21849,7 @@
         <v>5</v>
       </c>
       <c r="C741" s="3" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D741" s="2" t="s">
         <v>7</v>
@@ -21866,7 +21863,7 @@
         <v>5</v>
       </c>
       <c r="C742" s="3" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D742" s="2" t="s">
         <v>7</v>
@@ -21874,13 +21871,13 @@
     </row>
     <row r="743" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A743" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C743" s="3" t="s">
         <v>1509</v>
-      </c>
-      <c r="B743" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C743" s="3" t="s">
-        <v>1510</v>
       </c>
       <c r="D743" s="2" t="s">
         <v>7</v>
@@ -21894,7 +21891,7 @@
         <v>5</v>
       </c>
       <c r="C744" s="3" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D744" s="2" t="s">
         <v>7</v>
@@ -21902,13 +21899,13 @@
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A745" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C745" s="3" t="s">
         <v>1225</v>
-      </c>
-      <c r="B745" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C745" s="3" t="s">
-        <v>1226</v>
       </c>
       <c r="D745" s="2" t="s">
         <v>7</v>
@@ -21922,7 +21919,7 @@
         <v>5</v>
       </c>
       <c r="C746" s="3" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="D746" s="2" t="s">
         <v>7</v>
@@ -21930,13 +21927,13 @@
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A747" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C747" s="3" t="s">
         <v>1514</v>
-      </c>
-      <c r="B747" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C747" s="3" t="s">
-        <v>1515</v>
       </c>
       <c r="D747" s="2" t="s">
         <v>7</v>
@@ -21950,7 +21947,7 @@
         <v>5</v>
       </c>
       <c r="C748" s="3" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D748" s="2" t="s">
         <v>7</v>
@@ -22006,7 +22003,7 @@
         <v>5</v>
       </c>
       <c r="C752" s="3" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="D752" s="2" t="s">
         <v>7</v>
@@ -22028,13 +22025,13 @@
     </row>
     <row r="754" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A754" s="5" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B754" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C754" s="3" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="D754" s="2" t="s">
         <v>7</v>
@@ -22048,7 +22045,7 @@
         <v>5</v>
       </c>
       <c r="C755" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D755" s="2" t="s">
         <v>7</v>
@@ -22056,13 +22053,13 @@
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A756" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B756" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C756" s="3" t="s">
         <v>1531</v>
-      </c>
-      <c r="B756" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C756" s="3" t="s">
-        <v>1532</v>
       </c>
       <c r="D756" s="2" t="s">
         <v>7</v>
@@ -22266,13 +22263,13 @@
     </row>
     <row r="771" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A771" s="2" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B771" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C771" s="3" t="s">
         <v>1547</v>
-      </c>
-      <c r="B771" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C771" s="3" t="s">
-        <v>1548</v>
       </c>
       <c r="D771" s="2" t="s">
         <v>7</v>
@@ -22280,13 +22277,13 @@
     </row>
     <row r="772" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A772" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B772" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C772" s="3" t="s">
         <v>1551</v>
-      </c>
-      <c r="B772" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C772" s="3" t="s">
-        <v>1552</v>
       </c>
       <c r="D772" s="2" t="s">
         <v>7</v>
@@ -22364,13 +22361,13 @@
     </row>
     <row r="778" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A778" s="5" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B778" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C778" s="3" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="D778" s="2" t="s">
         <v>7</v>
@@ -22398,7 +22395,7 @@
         <v>5</v>
       </c>
       <c r="C780" s="3" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D780" s="2" t="s">
         <v>7</v>
@@ -22406,13 +22403,13 @@
     </row>
     <row r="781" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A781" s="2" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B781" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C781" s="3" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D781" s="2" t="s">
         <v>7</v>
@@ -22426,7 +22423,7 @@
         <v>5</v>
       </c>
       <c r="C782" s="3" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="D782" s="2" t="s">
         <v>20</v>
@@ -22490,13 +22487,13 @@
     </row>
     <row r="787" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A787" s="5" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B787" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C787" s="3" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="D787" s="2" t="s">
         <v>7</v>
@@ -22504,13 +22501,13 @@
     </row>
     <row r="788" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A788" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B788" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C788" s="3" t="s">
         <v>1573</v>
-      </c>
-      <c r="B788" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C788" s="3" t="s">
-        <v>1574</v>
       </c>
       <c r="D788" s="2" t="s">
         <v>7</v>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F08338-0AE8-4FA3-9AA0-F41A3C35F67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96F7963-A136-4D2A-92EF-7C4A6598382A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -4692,9 +4692,6 @@
     <t>.Soprano - Quadro de Distribuição ABS - Embutir - 36 polos DIN - cód. 05129.0036.11</t>
   </si>
   <si>
-    <t>Comp 2052</t>
-  </si>
-  <si>
     <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE EMBUTIR, COM BARRAMENTO TRIFÁSICO, PARA 36 DISJUNTORES DIN 100A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025 (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 106022 - 04/2026)</t>
   </si>
   <si>
@@ -4762,6 +4759,9 @@
   </si>
   <si>
     <t>LUMINÁRIA ARANDELA SOBREPOR EXTERNA, COM 1 LÂMPADA LED DE 40 W, SEM REATOR - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97607 - 09/2024))</t>
+  </si>
+  <si>
+    <t>Comp 2056</t>
   </si>
 </sst>
 </file>
@@ -11339,7 +11339,7 @@
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A773" s="3" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="B773" s="2" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A774" s="3" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B774" s="1" t="s">
         <v>20</v>
@@ -11355,7 +11355,7 @@
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A775" s="3" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B775" s="1" t="s">
         <v>20</v>
@@ -11363,7 +11363,7 @@
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A776" s="3" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B776" s="1" t="s">
         <v>20</v>
@@ -11371,7 +11371,7 @@
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A777" s="3" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B777" s="2" t="s">
         <v>7</v>
@@ -11379,7 +11379,7 @@
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A778" s="3" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="B778" s="2" t="s">
         <v>7</v>
@@ -11387,7 +11387,7 @@
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A779" s="3" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B779" s="2" t="s">
         <v>7</v>
@@ -11395,7 +11395,7 @@
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A780" s="3" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B780" s="2" t="s">
         <v>7</v>
@@ -11403,7 +11403,7 @@
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A781" s="3" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B781" s="2" t="s">
         <v>7</v>
@@ -11411,7 +11411,7 @@
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A782" s="3" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="B782" s="1" t="s">
         <v>20</v>
@@ -11419,7 +11419,7 @@
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A783" s="3" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B783" s="1" t="s">
         <v>20</v>
@@ -11427,7 +11427,7 @@
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A784" s="3" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B784" s="2" t="s">
         <v>7</v>
@@ -11435,7 +11435,7 @@
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A785" s="3" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B785" s="2" t="s">
         <v>7</v>
@@ -11443,7 +11443,7 @@
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A786" s="3" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B786" s="2" t="s">
         <v>7</v>
@@ -11451,7 +11451,7 @@
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A787" s="3" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="B787" s="2" t="s">
         <v>7</v>
@@ -11459,7 +11459,7 @@
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A788" s="3" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B788" s="2" t="s">
         <v>7</v>
@@ -12225,7 +12225,7 @@
     </row>
     <row r="54" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>91836</v>
+        <v>97667</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
@@ -22277,13 +22277,13 @@
     </row>
     <row r="772" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A772" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B772" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C772" s="3" t="s">
         <v>1550</v>
-      </c>
-      <c r="B772" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C772" s="3" t="s">
-        <v>1551</v>
       </c>
       <c r="D772" s="2" t="s">
         <v>7</v>
@@ -22395,7 +22395,7 @@
         <v>5</v>
       </c>
       <c r="C780" s="3" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D780" s="2" t="s">
         <v>7</v>
@@ -22403,13 +22403,13 @@
     </row>
     <row r="781" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A781" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B781" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C781" s="3" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D781" s="2" t="s">
         <v>7</v>
@@ -22423,7 +22423,7 @@
         <v>5</v>
       </c>
       <c r="C782" s="3" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="D782" s="2" t="s">
         <v>20</v>
@@ -22501,13 +22501,13 @@
     </row>
     <row r="788" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A788" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B788" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C788" s="3" t="s">
         <v>1572</v>
-      </c>
-      <c r="B788" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C788" s="3" t="s">
-        <v>1573</v>
       </c>
       <c r="D788" s="2" t="s">
         <v>7</v>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96F7963-A136-4D2A-92EF-7C4A6598382A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5EBA76-C0AF-4069-ACA5-C7213F993686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="1574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4374" uniqueCount="1600">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4762,6 +4762,84 @@
   </si>
   <si>
     <t>Comp 2056</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 10 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 10 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 10 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 10 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 10 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 16 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 25 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 25 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 25 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 25 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 4 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 4 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 50 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 50 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 50 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 50 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 6 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 6 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 6 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 6 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 50 A - 3 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 50A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 100A - 10 kA</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -600x400x200mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23</t>
+  </si>
+  <si>
+    <t>Comp 1060</t>
+  </si>
+  <si>
+    <t>PAINEL MODULAR -600x400x200mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23)</t>
   </si>
 </sst>
 </file>
@@ -5154,7 +5232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B788"/>
+  <dimension ref="A1:B811"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -11465,6 +11543,190 @@
         <v>7</v>
       </c>
     </row>
+    <row r="789" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A789" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B789" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A790" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B790" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A791" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B791" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A792" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B792" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A793" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B793" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A794" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B794" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A795" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B795" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A796" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B796" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A797" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B797" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A798" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B798" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A799" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B799" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A800" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B800" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A801" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B801" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A802" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B802" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A803" s="3" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B803" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A804" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B804" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A805" s="3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B805" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A806" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B806" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A807" s="3" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B807" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A808" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B808" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A809" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B809" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A810" s="3" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B810" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A811" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B811" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -11472,7 +11734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D788"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -22513,6 +22775,328 @@
         <v>7</v>
       </c>
     </row>
+    <row r="789" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A789" s="2">
+        <v>91933</v>
+      </c>
+      <c r="B789" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C789" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D789" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A790" s="2">
+        <v>91933</v>
+      </c>
+      <c r="B790" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C790" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D790" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A791" s="2">
+        <v>91933</v>
+      </c>
+      <c r="B791" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C791" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D791" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A792" s="2">
+        <v>91933</v>
+      </c>
+      <c r="B792" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C792" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D792" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A793" s="2">
+        <v>91933</v>
+      </c>
+      <c r="B793" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C793" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D793" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A794" s="2">
+        <v>91935</v>
+      </c>
+      <c r="B794" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C794" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D794" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A795" s="2">
+        <v>92984</v>
+      </c>
+      <c r="B795" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C795" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D795" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A796" s="2">
+        <v>92984</v>
+      </c>
+      <c r="B796" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C796" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D796" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A797" s="2">
+        <v>92984</v>
+      </c>
+      <c r="B797" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C797" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D797" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A798" s="2">
+        <v>92984</v>
+      </c>
+      <c r="B798" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C798" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D798" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A799" s="2">
+        <v>91929</v>
+      </c>
+      <c r="B799" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C799" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D799" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A800" s="2">
+        <v>91929</v>
+      </c>
+      <c r="B800" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C800" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D800" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A801" s="2">
+        <v>92988</v>
+      </c>
+      <c r="B801" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C801" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D801" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A802" s="2">
+        <v>92988</v>
+      </c>
+      <c r="B802" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C802" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D802" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A803" s="2">
+        <v>92988</v>
+      </c>
+      <c r="B803" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C803" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D803" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A804" s="2">
+        <v>92988</v>
+      </c>
+      <c r="B804" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C804" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D804" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A805" s="2">
+        <v>91931</v>
+      </c>
+      <c r="B805" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C805" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D805" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A806" s="2">
+        <v>91931</v>
+      </c>
+      <c r="B806" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C806" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D806" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A807" s="2">
+        <v>91931</v>
+      </c>
+      <c r="B807" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C807" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D807" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A808" s="2">
+        <v>91931</v>
+      </c>
+      <c r="B808" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C808" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D808" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A809" s="2">
+        <v>93673</v>
+      </c>
+      <c r="B809" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C809" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D809" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A810" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B810" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C810" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D810" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A811" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B811" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C811" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D811" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB5D7EF-27F9-49D7-97FE-630BB4B75503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED9BCB1-B9BE-4F45-AAF6-FD57FEECB0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4379" uniqueCount="1601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4408" uniqueCount="1611">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4843,6 +4843,36 @@
   </si>
   <si>
     <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 25 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo PP - Cabo PP 3x1.5mm</t>
+  </si>
+  <si>
+    <t>Cabo - Plugue - Plugue macho</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Caixa PVC octogonal - 3x3"</t>
+  </si>
+  <si>
+    <t>CAIXA OCTOGONAL 3" X 3", PVC, INSTALADA EM LAJE - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Cruzeta - X - horizontal 90° - 38x38mm</t>
+  </si>
+  <si>
+    <t>Comp 1054</t>
+  </si>
+  <si>
+    <t>CRUZETA HORIZONTAL PARA PERFILADO 38X38MM (COMPOSIÇÃO DE REFERÊNCIA: 063746 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, compacto - DIN - Cap. 30 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>COMP 2061</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, COM BARRAMENTO TRIFÁSICO, PARA 30 DISJUNTORES DIN 100A - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101880 - 03/2025)</t>
   </si>
 </sst>
 </file>
@@ -5238,7 +5268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B812"/>
+  <dimension ref="A1:B817"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -11741,6 +11771,46 @@
         <v>20</v>
       </c>
     </row>
+    <row r="813" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A813" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B813" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A814" s="3" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B814" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A815" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B815" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A816" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B816" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A817" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B817" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -11748,10 +11818,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D812"/>
+  <dimension ref="A1:D817"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.77734375" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="121.21875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="2"/>
@@ -23125,6 +23195,76 @@
         <v>20</v>
       </c>
     </row>
+    <row r="813" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A813" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B813" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C813" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D813" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A814" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B814" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C814" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D814" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A815" s="5">
+        <v>91937</v>
+      </c>
+      <c r="B815" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C815" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D815" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A816" s="5" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B816" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C816" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D816" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A817" s="5" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B817" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C817" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D817" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED9BCB1-B9BE-4F45-AAF6-FD57FEECB0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE55DEE-6656-4F08-8285-D671CAB6A99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4408" uniqueCount="1611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4413" uniqueCount="1612">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4873,6 +4873,9 @@
   </si>
   <si>
     <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, COM BARRAMENTO TRIFÁSICO, PARA 30 DISJUNTORES DIN 100A - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101880 - 03/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 220 V/127 V - DIN - Curva C - 16 A - 5 kA</t>
   </si>
 </sst>
 </file>
@@ -5268,7 +5271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B817"/>
+  <dimension ref="A1:B818"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -11811,6 +11814,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="818" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A818" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B818" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -11818,7 +11829,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D817"/>
+  <dimension ref="A1:D818"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -23265,6 +23276,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="818" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A818" s="5">
+        <v>93661</v>
+      </c>
+      <c r="B818" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C818" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D818" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE55DEE-6656-4F08-8285-D671CAB6A99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E069C2C-4080-4A6E-B771-9F916471E8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4413" uniqueCount="1612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4418" uniqueCount="1613">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4876,6 +4876,9 @@
   </si>
   <si>
     <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 220 V/127 V - DIN - Curva C - 16 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 6 mm² - Vermelho</t>
   </si>
 </sst>
 </file>
@@ -5271,7 +5274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B818"/>
+  <dimension ref="A1:B819"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -11822,6 +11825,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="819" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A819" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B819" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -11829,7 +11840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D818"/>
+  <dimension ref="A1:D819"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -23290,6 +23301,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="819" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A819" s="5">
+        <v>91931</v>
+      </c>
+      <c r="B819" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C819" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D819" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E069C2C-4080-4A6E-B771-9F916471E8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D615C7-325C-4113-9799-B49850E733C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4418" uniqueCount="1613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4453" uniqueCount="1626">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4879,6 +4879,45 @@
   </si>
   <si>
     <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 6 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 50 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Interruptor tetrapolar DR - 3 fases/neutro - In 30mA - DIN - 63 A</t>
+  </si>
+  <si>
+    <t>Comp 1289</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TETRAPOLAR DR 63A TIPO AC 30MA - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: ORSE 9969 - 05/2023)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, compacto - DIN - Ref. Moratori - Cap. 30 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, - DIN - Ref. Moratori - Cap. 32 disj. unip.+Geral - In barr. 225 A</t>
+  </si>
+  <si>
+    <t>COMP 2065</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, COM BARRAMENTO TRIFÁSICO, PARA 32 DISJUNTORES DIN 225A - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REF.  101879 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, compacto - DIN - Ref. Moratori - Cap. 42 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>COMP 328</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva horizontal 90° - 400x100mm chapa 16</t>
+  </si>
+  <si>
+    <t>Comp 454</t>
+  </si>
+  <si>
+    <t>CURVA HORIZONTAL 90º PARA ELETROCALHA, LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA DE 400MM E ALTURA DE 100MM - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97278 - 02/2023)</t>
   </si>
 </sst>
 </file>
@@ -5274,7 +5313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B819"/>
+  <dimension ref="A1:B825"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -11833,6 +11872,54 @@
         <v>20</v>
       </c>
     </row>
+    <row r="820" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A820" s="3" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B820" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A821" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B821" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A822" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B822" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A823" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B823" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A824" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B824" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A825" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B825" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -11840,7 +11927,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D819"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -23315,6 +23402,90 @@
         <v>20</v>
       </c>
     </row>
+    <row r="820" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A820" s="5">
+        <v>93673</v>
+      </c>
+      <c r="B820" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C820" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D820" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A821" s="5" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B821" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C821" s="3" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D821" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A822" s="5" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B822" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C822" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D822" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A823" s="5" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B823" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C823" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D823" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A824" s="5" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B824" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C824" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D824" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A825" s="5" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B825" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C825" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D825" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D615C7-325C-4113-9799-B49850E733C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FF647E-59B0-4520-AA40-ADB96FDEBF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4453" uniqueCount="1626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4469" uniqueCount="1629">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4918,6 +4918,15 @@
   </si>
   <si>
     <t>CURVA HORIZONTAL 90º PARA ELETROCALHA, LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA DE 400MM E ALTURA DE 100MM - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97278 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, compacto - DIN - Cap. 42 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 50 A - 6 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 40 A - 4,5 kA</t>
   </si>
 </sst>
 </file>
@@ -5313,7 +5322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B825"/>
+  <dimension ref="A1:B828"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -11920,6 +11929,30 @@
         <v>7</v>
       </c>
     </row>
+    <row r="826" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A826" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B826" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A827" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B827" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A828" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B828" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -11927,7 +11960,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D828"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -23486,6 +23519,48 @@
         <v>7</v>
       </c>
     </row>
+    <row r="826" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A826" s="5" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B826" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C826" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D826" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A827" s="5">
+        <v>93673</v>
+      </c>
+      <c r="B827" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C827" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D827" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A828" s="5">
+        <v>93672</v>
+      </c>
+      <c r="B828" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C828" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="D828" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FF647E-59B0-4520-AA40-ADB96FDEBF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299638C3-2F1C-47BB-95B1-6DF4CA802026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4469" uniqueCount="1629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4498" uniqueCount="1636">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4927,6 +4927,27 @@
   </si>
   <si>
     <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 40 A - 4,5 kA</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, - DIN - Cap. 50 disj. unip. - In barr. 225 A</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 2 - 2P+T 20A Baixa</t>
+  </si>
+  <si>
+    <t>TOMADA BAIXA DE EMBUTIR (2 MÓDULOS), 2P+T 20 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO. AF_03/2023</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 2 - 2P+T 10A - Piso</t>
+  </si>
+  <si>
+    <t>.Soprano - Quadro de Distribuição ABS - Sobrepor - 36 polos DIN - cód. 05129.2036.11</t>
+  </si>
+  <si>
+    <t>COMP 2056</t>
+  </si>
+  <si>
+    <t>Quadro distrib. plástico - sobrepor - Sem barramento - DIN - Cap. 16 disj. unipol.</t>
   </si>
 </sst>
 </file>
@@ -5322,7 +5343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B828"/>
+  <dimension ref="A1:B833"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -11953,6 +11974,46 @@
         <v>7</v>
       </c>
     </row>
+    <row r="829" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A829" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B829" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A830" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B830" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A831" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B831" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A832" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B832" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A833" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B833" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -11960,7 +12021,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D828"/>
+  <dimension ref="A1:D833"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -23561,6 +23622,76 @@
         <v>7</v>
       </c>
     </row>
+    <row r="829" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A829" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B829" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C829" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D829" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A830" s="5">
+        <v>92009</v>
+      </c>
+      <c r="B830" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C830" s="3" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D830" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A831" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="B831" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C831" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D831" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A832" s="5" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B832" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C832" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D832" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A833" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B833" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C833" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D833" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299638C3-2F1C-47BB-95B1-6DF4CA802026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAFF9E9-6CDA-4CA6-ADAC-8129F4305B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4498" uniqueCount="1636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4585" uniqueCount="1655">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4948,6 +4948,63 @@
   </si>
   <si>
     <t>Quadro distrib. plástico - sobrepor - Sem barramento - DIN - Cap. 16 disj. unipol.</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 16 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 16 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 16 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 16 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 50 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 95 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 95 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 95 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 95 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo - Cabo isolado 0,6 a 1kV EPR - 120mm</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 120 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 120 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 120 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 120 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Caixa de passagem - embutir - Alvenaria - 400x400x400mm</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -600x400x200mm</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 40 A - 18 kA</t>
+  </si>
+  <si>
+    <t>Comp 807</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 40A, 5kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
   </si>
 </sst>
 </file>
@@ -5343,7 +5400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B833"/>
+  <dimension ref="A1:B850"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12014,6 +12071,142 @@
         <v>7</v>
       </c>
     </row>
+    <row r="834" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A834" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B834" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A835" s="3" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B835" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A836" s="3" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B836" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A837" s="3" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B837" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A838" s="3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B838" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A839" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B839" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A840" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B840" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A841" s="3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B841" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A842" s="3" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B842" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A843" s="3" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B843" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A844" s="3" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B844" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A845" s="3" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B845" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A846" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B846" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A847" s="3" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B847" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A848" s="3" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B848" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A849" s="3" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B849" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A850" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B850" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12021,7 +12214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D833"/>
+  <dimension ref="A1:D850"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -23692,6 +23885,244 @@
         <v>7</v>
       </c>
     </row>
+    <row r="834" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A834" s="5">
+        <v>91935</v>
+      </c>
+      <c r="B834" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C834" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D834" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A835" s="5">
+        <v>91935</v>
+      </c>
+      <c r="B835" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C835" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D835" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A836" s="5">
+        <v>91935</v>
+      </c>
+      <c r="B836" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C836" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D836" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A837" s="5">
+        <v>91935</v>
+      </c>
+      <c r="B837" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C837" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D837" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A838" s="5">
+        <v>92988</v>
+      </c>
+      <c r="B838" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C838" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D838" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A839" s="5">
+        <v>92992</v>
+      </c>
+      <c r="B839" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C839" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D839" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A840" s="5">
+        <v>92992</v>
+      </c>
+      <c r="B840" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C840" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D840" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A841" s="5">
+        <v>92992</v>
+      </c>
+      <c r="B841" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C841" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D841" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A842" s="5">
+        <v>92992</v>
+      </c>
+      <c r="B842" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C842" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D842" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A843" s="5">
+        <v>92994</v>
+      </c>
+      <c r="B843" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C843" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D843" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A844" s="5">
+        <v>92994</v>
+      </c>
+      <c r="B844" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C844" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D844" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A845" s="5">
+        <v>92994</v>
+      </c>
+      <c r="B845" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C845" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D845" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A846" s="5">
+        <v>92994</v>
+      </c>
+      <c r="B846" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C846" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D846" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A847" s="5">
+        <v>92994</v>
+      </c>
+      <c r="B847" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C847" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D847" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A848" s="5">
+        <v>97887</v>
+      </c>
+      <c r="B848" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C848" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D848" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A849" s="5" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B849" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C849" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D849" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A850" s="5" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B850" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C850" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D850" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAFF9E9-6CDA-4CA6-ADAC-8129F4305B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D15FC82-5102-423C-BE16-B8A3FE61B89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4585" uniqueCount="1655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4597" uniqueCount="1657">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5005,6 +5005,12 @@
   </si>
   <si>
     <t>DISJUNTOR CAIXA MOLDADA 40A, 5kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Acessórios para Perfilados - Saída final para eletroduto</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Acessórios para Perfilados - Saída lateral dupla</t>
   </si>
 </sst>
 </file>
@@ -5400,7 +5406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B850"/>
+  <dimension ref="A1:B852"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12207,6 +12213,22 @@
         <v>7</v>
       </c>
     </row>
+    <row r="851" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A851" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B851" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A852" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B852" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12214,7 +12236,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D850"/>
+  <dimension ref="A1:D852"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -24123,6 +24145,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="851" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A851" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B851" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C851" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D851" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A852" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B852" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C852" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D852" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D15FC82-5102-423C-BE16-B8A3FE61B89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B46B01-2956-4DF1-AAB7-E0281DB9693E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4597" uniqueCount="1657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4608" uniqueCount="1661">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5011,6 +5011,18 @@
   </si>
   <si>
     <t>Acessórios Perfilados perfurados - Acessórios para Perfilados - Saída lateral dupla</t>
+  </si>
+  <si>
+    <t>.S.O.S CAIXAS - 80x80 - piso - CAIXA DE PASSAGEM EM ALVENARIA, DIM.: 80x80cm</t>
+  </si>
+  <si>
+    <t>COMP 602</t>
+  </si>
+  <si>
+    <t>TRANSFORMADOR DE CORRENTE 600/5A (COMPOSIÇÃO DE REFERÊNCIA: C2519 - SEINFRA 028)</t>
+  </si>
+  <si>
+    <t>Transformador - Transformador - Transformador de corrente 600/5A</t>
   </si>
 </sst>
 </file>
@@ -5406,7 +5418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B852"/>
+  <dimension ref="A1:B854"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12229,6 +12241,22 @@
         <v>7</v>
       </c>
     </row>
+    <row r="853" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A853" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B853" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A854" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B854" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12236,7 +12264,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D852"/>
+  <dimension ref="A1:D854"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -24173,6 +24201,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="853" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A853" s="5">
+        <v>97889</v>
+      </c>
+      <c r="B853" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C853" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D853" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A854" s="5" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B854" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C854" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D854" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B46B01-2956-4DF1-AAB7-E0281DB9693E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D1A489-21BC-4077-BC54-6586119BD02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4608" uniqueCount="1661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4620" uniqueCount="1667">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5023,6 +5023,24 @@
   </si>
   <si>
     <t>Transformador - Transformador - Transformador de corrente 600/5A</t>
+  </si>
+  <si>
+    <t>Acessórios uso geral - Outros - Liquido prateador - 1L</t>
+  </si>
+  <si>
+    <t>COMP 1066</t>
+  </si>
+  <si>
+    <t>PINTURA COM LIQUIDOR PRATEADOR (REFERÊNCIA SBC 160048 04/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios uso geral - Outros - Trilho DIN</t>
+  </si>
+  <si>
+    <t>COMP 2073</t>
+  </si>
+  <si>
+    <t>TRILHO DIN, PARA PAINEL MODULAR - FORNECIMENTO E INSTALAÇÃO. AF_11/2025 (COMPOSIÇÃO REFERÊNCIA: SINAPI 106264  - 03/2026)</t>
   </si>
 </sst>
 </file>
@@ -5418,7 +5436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B854"/>
+  <dimension ref="A1:B856"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12257,6 +12275,22 @@
         <v>7</v>
       </c>
     </row>
+    <row r="855" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A855" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B855" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A856" s="3" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B856" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12264,7 +12298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D854"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -24229,6 +24263,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="855" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A855" s="5" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B855" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C855" s="3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D855" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A856" s="5" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B856" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C856" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D856" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D1A489-21BC-4077-BC54-6586119BD02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10669228-FA7F-45F9-BED3-3E5246A72450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4620" uniqueCount="1667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4643" uniqueCount="1675">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5041,6 +5041,30 @@
   </si>
   <si>
     <t>TRILHO DIN, PARA PAINEL MODULAR - FORNECIMENTO E INSTALAÇÃO. AF_11/2025 (COMPOSIÇÃO REFERÊNCIA: SINAPI 106264  - 03/2026)</t>
+  </si>
+  <si>
+    <t>Condutores de proteção - SPDA - Barra chata em alumínio - com furos - 7/8" x 1/8"</t>
+  </si>
+  <si>
+    <t>COMP 2074</t>
+  </si>
+  <si>
+    <t>FITA DE ALUMÍNIO 70 MM² PARA SPDA - FORNECIMENTO E INSTALAÇÃO. AF_08/2023 (COMPOSIÇÃO REFERÊNCIA: SINAPI 96980 - 03/2026)</t>
+  </si>
+  <si>
+    <t>Aterramento - Caixa de inspeção - Cimento - Ø300x300mm</t>
+  </si>
+  <si>
+    <t>Eletroduto metálico rígido leve - Eletroduto galvanizado - 1"</t>
+  </si>
+  <si>
+    <t>Aterramento - Barramento de equipotencialização - 11 terminais</t>
+  </si>
+  <si>
+    <t>COMP 1344</t>
+  </si>
+  <si>
+    <t>CAIXA DE EQUIPOTENCIALIZAÇÃO DE POTENCIAIS (BEP) - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA 077169 06/2025)</t>
   </si>
 </sst>
 </file>
@@ -5436,7 +5460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B856"/>
+  <dimension ref="A1:B860"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12291,6 +12315,38 @@
         <v>7</v>
       </c>
     </row>
+    <row r="857" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A857" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B857" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A858" s="3" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B858" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A859" s="3" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B859" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A860" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B860" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12298,7 +12354,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D856"/>
+  <dimension ref="A1:D860"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -24291,6 +24347,62 @@
         <v>7</v>
       </c>
     </row>
+    <row r="857" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A857" s="5" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B857" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C857" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D857" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A858" s="5">
+        <v>98111</v>
+      </c>
+      <c r="B858" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C858" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D858" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A859" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B859" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C859" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D859" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A860" s="5" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B860" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C860" s="3" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D860" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10669228-FA7F-45F9-BED3-3E5246A72450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC28218-4035-47E6-881F-EEA741968195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4643" uniqueCount="1675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4655" uniqueCount="1681">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5065,6 +5065,24 @@
   </si>
   <si>
     <t>CAIXA DE EQUIPOTENCIALIZAÇÃO DE POTENCIAIS (BEP) - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA 077169 06/2025)</t>
+  </si>
+  <si>
+    <t>COMP 2075</t>
+  </si>
+  <si>
+    <t>CONECTOR DE MEDICAO E EMENDA 16 A 70MM 560 - TERMOTECNICA (COMPOSIÇÃO REFERÊNCIA: SBC 078389 - 04/2026)</t>
+  </si>
+  <si>
+    <t>SPDA - Conector estrutural - Conector de medição em aço com 4 parafusos</t>
+  </si>
+  <si>
+    <t>COMP 2076</t>
+  </si>
+  <si>
+    <t>CONECTOR CABO/HASTE TEL 584 TERMOTECNICA (COMPOSIÇÃO REFERÊNCIA: SBC 078368 - 04/2026)</t>
+  </si>
+  <si>
+    <t>SPDA - Conectores duplo-clips - Conector Cabo-haste em latão estanhado</t>
   </si>
 </sst>
 </file>
@@ -5460,7 +5478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B860"/>
+  <dimension ref="A1:B862"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12347,6 +12365,22 @@
         <v>7</v>
       </c>
     </row>
+    <row r="861" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A861" s="3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B861" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A862" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B862" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12354,7 +12388,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D860"/>
+  <dimension ref="A1:D862"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -24403,6 +24437,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="861" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A861" s="5" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B861" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C861" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D861" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A862" s="5" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B862" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C862" s="3" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D862" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC28218-4035-47E6-881F-EEA741968195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26BF522-B82A-4F26-A80C-F553D7BC2B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4655" uniqueCount="1681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4700" uniqueCount="1690">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5083,6 +5083,33 @@
   </si>
   <si>
     <t>SPDA - Conectores duplo-clips - Conector Cabo-haste em latão estanhado</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 35 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 35 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 35 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 35 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 35 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 70 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 70 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 70 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 70 mm² - Vermelho</t>
   </si>
 </sst>
 </file>
@@ -5478,7 +5505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B862"/>
+  <dimension ref="A1:B871"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12381,6 +12408,78 @@
         <v>7</v>
       </c>
     </row>
+    <row r="863" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A863" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B863" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A864" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B864" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="865" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A865" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B865" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="866" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A866" s="3" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B866" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="867" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A867" s="3" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B867" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="868" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A868" s="3" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B868" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="869" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A869" s="3" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B869" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="870" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A870" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B870" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="871" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A871" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B871" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12388,7 +12487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D862"/>
+  <dimension ref="A1:D871"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -24465,6 +24564,132 @@
         <v>7</v>
       </c>
     </row>
+    <row r="863" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A863" s="5">
+        <v>92986</v>
+      </c>
+      <c r="B863" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C863" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D863" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A864" s="5">
+        <v>92986</v>
+      </c>
+      <c r="B864" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C864" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D864" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A865" s="5">
+        <v>92986</v>
+      </c>
+      <c r="B865" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C865" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D865" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A866" s="5">
+        <v>92986</v>
+      </c>
+      <c r="B866" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C866" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D866" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A867" s="5">
+        <v>92986</v>
+      </c>
+      <c r="B867" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C867" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D867" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A868" s="5">
+        <v>92990</v>
+      </c>
+      <c r="B868" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C868" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D868" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A869" s="5">
+        <v>92990</v>
+      </c>
+      <c r="B869" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C869" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D869" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A870" s="5">
+        <v>92990</v>
+      </c>
+      <c r="B870" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C870" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D870" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A871" s="5">
+        <v>92990</v>
+      </c>
+      <c r="B871" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C871" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D871" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26BF522-B82A-4F26-A80C-F553D7BC2B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45825357-4C4B-44B9-BFA1-CDA097342227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4700" uniqueCount="1690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4739" uniqueCount="1701">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5110,6 +5110,39 @@
   </si>
   <si>
     <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 70 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Interruptor tetrapolar DR - 3 fases/neutro - In 30mA - DIN - 40 A</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TETRAPOLAR TIPO DR, CORRENTE NOMINAL DE 40A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 380 V/220 V - DIN - Curva C - 25 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 25A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, - DIN - Cap. 32 disj. unip. - In barr. 150 A</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva C - 40 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - embutir - Sem barr. - DIN - Cap. 16 disj. unip.</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, - DIN - Cap. 40 disj. unip. - In barr. 150 A</t>
+  </si>
+  <si>
+    <t>Caixa de passagem - embutir - Aço pintada - ref Moratori - 150x150x75 mm</t>
+  </si>
+  <si>
+    <t>COMP 149</t>
+  </si>
+  <si>
+    <t>CAIXA DE PASSAGEM/ LUZ / TELEFONIA, DE EMBUTIR, EM PVC, DIMENSOES 150 X 150 X *75* MM (PADRAO CONCESSIONARIA LOCAL) - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 92871 - 05/2022)</t>
   </si>
 </sst>
 </file>
@@ -5505,7 +5538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B871"/>
+  <dimension ref="A1:B878"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12480,6 +12513,62 @@
         <v>20</v>
       </c>
     </row>
+    <row r="872" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A872" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B872" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="873" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A873" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B873" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="874" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A874" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B874" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="875" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A875" s="3" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B875" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="876" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A876" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B876" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="877" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A877" s="3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B877" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="878" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A878" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B878" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12487,7 +12576,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D871"/>
+  <dimension ref="A1:D878"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -24690,6 +24779,104 @@
         <v>20</v>
       </c>
     </row>
+    <row r="872" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A872" s="5">
+        <v>97711</v>
+      </c>
+      <c r="B872" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C872" s="3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D872" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A873" s="5">
+        <v>93670</v>
+      </c>
+      <c r="B873" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C873" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D873" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A874" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="B874" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C874" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D874" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A875" s="5">
+        <v>93675</v>
+      </c>
+      <c r="B875" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C875" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="D875" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A876" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B876" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C876" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D876" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A877" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B877" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C877" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D877" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A878" s="5" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B878" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C878" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D878" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45825357-4C4B-44B9-BFA1-CDA097342227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151D8004-21E1-41F3-98C5-5ADE3792CC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4739" uniqueCount="1701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4757" uniqueCount="1710">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5143,6 +5143,33 @@
   </si>
   <si>
     <t>CAIXA DE PASSAGEM/ LUZ / TELEFONIA, DE EMBUTIR, EM PVC, DIMENSOES 150 X 150 X *75* MM (PADRAO CONCESSIONARIA LOCAL) - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 92871 - 05/2022)</t>
+  </si>
+  <si>
+    <t>Acessórios uso geral - Outros - Barramento para 400A</t>
+  </si>
+  <si>
+    <t>COMP 805</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE PARA 400A - (COMPOSIÇÃO DE REFERÊNCIA SIURB:9006078)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 400 A - 35 kA</t>
+  </si>
+  <si>
+    <t>COMP 808</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 400A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Transformador - Transformador - Transformador de corrente 400/5A</t>
+  </si>
+  <si>
+    <t>COMP 604</t>
+  </si>
+  <si>
+    <t>TRANSFORMADOR DE CORRENTE 400/5A (COMPOSIÇÃO DE REFERÊNCIA: C2519 - SEINFRA 028)</t>
   </si>
 </sst>
 </file>
@@ -5538,7 +5565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B878"/>
+  <dimension ref="A1:B881"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12569,6 +12596,30 @@
         <v>7</v>
       </c>
     </row>
+    <row r="879" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A879" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B879" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="880" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A880" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B880" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="881" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A881" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B881" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12576,7 +12627,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D878"/>
+  <dimension ref="A1:D881"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -24877,6 +24928,48 @@
         <v>7</v>
       </c>
     </row>
+    <row r="879" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A879" s="5" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B879" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C879" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D879" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A880" s="5" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B880" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C880" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D880" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A881" s="5" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B881" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C881" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D881" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151D8004-21E1-41F3-98C5-5ADE3792CC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E883BF-91AD-4BA1-B30D-4A5B49AD841D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4757" uniqueCount="1710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4763" uniqueCount="1711">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5170,6 +5170,9 @@
   </si>
   <si>
     <t>TRANSFORMADOR DE CORRENTE 400/5A (COMPOSIÇÃO DE REFERÊNCIA: C2519 - SEINFRA 028)</t>
+  </si>
+  <si>
+    <t>Aterramento - Haste de aterramento - cobreada - 5/8" x 3,00m</t>
   </si>
 </sst>
 </file>
@@ -5565,7 +5568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B881"/>
+  <dimension ref="A1:B882"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12620,6 +12623,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="882" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A882" s="3" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B882" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12627,7 +12638,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D881"/>
+  <dimension ref="A1:D882"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -24970,6 +24981,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="882" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A882" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B882" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C882" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D882" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E883BF-91AD-4BA1-B30D-4A5B49AD841D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD35D07-A980-4649-BA8D-1A81DED1F2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4763" uniqueCount="1711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4770" uniqueCount="1714">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5173,6 +5173,15 @@
   </si>
   <si>
     <t>Aterramento - Haste de aterramento - cobreada - 5/8" x 3,00m</t>
+  </si>
+  <si>
+    <t>Intelbras - Equipamentos de Rede e Rack - Rack de Piso - 28U  19" x 570mm RPD 2857</t>
+  </si>
+  <si>
+    <t>RACK ABERTO PADRÃO 19" 28U  (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>COMP 1281</t>
   </si>
 </sst>
 </file>
@@ -5568,7 +5577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B882"/>
+  <dimension ref="A1:B883"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12631,6 +12640,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="883" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A883" s="3" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B883" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12638,7 +12655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D882"/>
+  <dimension ref="A1:D884"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -24995,6 +25012,25 @@
         <v>7</v>
       </c>
     </row>
+    <row r="883" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A883" s="5" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B883" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C883" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D883" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D884" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD35D07-A980-4649-BA8D-1A81DED1F2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDB16E4-ECCE-4BAB-87D1-507ABF123871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4770" uniqueCount="1714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4775" uniqueCount="1717">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5182,6 +5182,15 @@
   </si>
   <si>
     <t>COMP 1281</t>
+  </si>
+  <si>
+    <t>Intelbras - Equipamentos de Rede e Rack - Rack de Piso - 32U  19” x 670mm RPD 3267</t>
+  </si>
+  <si>
+    <t>COMP 2102</t>
+  </si>
+  <si>
+    <t>RACK ABERTO PADRÃO 19" 32U  (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
   </si>
 </sst>
 </file>
@@ -5577,7 +5586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B883"/>
+  <dimension ref="A1:B884"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12645,6 +12654,14 @@
         <v>1711</v>
       </c>
       <c r="B883" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="884" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A884" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B884" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -25027,6 +25044,15 @@
       </c>
     </row>
     <row r="884" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A884" s="5" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B884" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C884" s="3" t="s">
+        <v>1716</v>
+      </c>
       <c r="D884" s="2" t="s">
         <v>7</v>
       </c>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDB16E4-ECCE-4BAB-87D1-507ABF123871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E08DCF3-3ADE-4B9D-8B79-959DE1E9C11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4775" uniqueCount="1717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4781" uniqueCount="1718">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5191,6 +5191,9 @@
   </si>
   <si>
     <t>RACK ABERTO PADRÃO 19" 32U  (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>Intelbras - Equipamentos de Rede e Rack - Rack de Piso - 16U  19” x 570mm RPD 1657</t>
   </si>
 </sst>
 </file>
@@ -5586,7 +5589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B884"/>
+  <dimension ref="A1:B885"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12665,6 +12668,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="885" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A885" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B885" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12672,7 +12683,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D884"/>
+  <dimension ref="A1:D885"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -25057,6 +25068,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="885" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A885" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B885" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C885" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D885" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E08DCF3-3ADE-4B9D-8B79-959DE1E9C11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F960E78-9DDF-4143-8B02-006D585B63F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4781" uniqueCount="1718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5052" uniqueCount="1776">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5194,6 +5194,180 @@
   </si>
   <si>
     <t>Intelbras - Equipamentos de Rede e Rack - Rack de Piso - 16U  19” x 570mm RPD 1657</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 1.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 1.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 1.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 1.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 10 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 10 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 10 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 10 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 10 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 10 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 120 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 120 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 120 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 120 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 16 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 16 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 16 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 16 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 16 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 16 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 2.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 2.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 2.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 2.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 2.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 2.5 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 25 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 25 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 25 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 25 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 35 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 4 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 4 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 4 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 4 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 4 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 4 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 50 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 50 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 50 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 6 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 6 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 6 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 6 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 6 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 6 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 70 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 70 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 70 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 0,6/1kV - ref. Inbrac Polivinil Antichama - 70 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Caixa de passagem - embutir - Aço pintada - ref Lukbox - 300x300x120 mm</t>
+  </si>
+  <si>
+    <t>COMP 2103</t>
+  </si>
+  <si>
+    <t>CAIXA DE PASSAGEM METÁLICA DE EMBUTIR, 30X30X15 CM - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: AGETOP CIVIL 070645 - 11/2017)</t>
+  </si>
+  <si>
+    <t>Caixa de passagem - embutir - Alvenaria - 600x600x600mm</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 220 V/127 V - DIN - Curva B - 10 A - 5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR BIPOLAR TIPO DIN, CORRENTE NOMINAL DE 10A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva B - 10 A - 5 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TRIPOLAR TIPO DIN, CORRENTE NOMINAL DE 10A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
   </si>
 </sst>
 </file>
@@ -5589,7 +5763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B885"/>
+  <dimension ref="A1:B939"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -12676,6 +12850,438 @@
         <v>7</v>
       </c>
     </row>
+    <row r="886" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A886" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B886" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="887" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A887" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B887" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A888" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B888" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A889" s="3" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B889" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="890" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A890" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B890" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="891" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A891" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B891" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="892" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A892" s="3" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B892" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="893" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A893" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B893" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="894" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A894" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B894" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="895" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A895" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B895" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="896" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A896" s="3" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B896" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="897" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A897" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B897" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="898" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A898" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B898" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="899" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A899" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B899" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="900" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A900" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B900" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="901" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A901" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B901" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="902" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A902" s="3" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B902" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="903" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A903" s="3" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B903" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="904" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A904" s="3" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B904" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="905" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A905" s="3" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B905" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="906" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A906" s="3" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B906" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="907" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A907" s="3" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B907" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="908" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A908" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B908" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="909" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A